--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{284FD83C-E3E1-4998-906A-FC265667ADB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4120B8B1-A549-4A43-8102-12EED60A125C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{F425FBA8-E65A-4F03-9270-551F3EA7C4F5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="309">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -770,10 +770,6 @@
     <t>P1</t>
   </si>
   <si>
-    <t>？</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>进入活动页面</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1242,6 +1238,14 @@
   </si>
   <si>
     <t>活动入口不显示</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>结束时间不明确，活动时间是2天，活动范围是3天</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>并列排序？</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1405,9 +1409,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1422,6 +1423,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1745,7 +1749,7 @@
     <col min="4" max="4" width="94" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="53.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="40.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1781,17 +1785,17 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="18" t="s">
         <v>9</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F2" t="s">
         <v>176</v>
@@ -1804,13 +1808,13 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="15"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="14"/>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F3" t="s">
         <v>177</v>
@@ -1823,13 +1827,13 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="15"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="14"/>
       <c r="D4" t="s">
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F4" t="s">
         <v>177</v>
@@ -1842,15 +1846,15 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="15" t="s">
+      <c r="B5" s="17"/>
+      <c r="C5" s="14" t="s">
         <v>14</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F5" t="s">
         <v>178</v>
@@ -1863,13 +1867,13 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="15"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="14"/>
       <c r="D6" t="s">
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F6" t="s">
         <v>179</v>
@@ -1882,13 +1886,13 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="15"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="14"/>
       <c r="D7" t="s">
         <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F7" t="s">
         <v>179</v>
@@ -1901,7 +1905,7 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="18"/>
+      <c r="B8" s="17"/>
       <c r="C8" s="7" t="s">
         <v>33</v>
       </c>
@@ -1922,34 +1926,37 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="15" t="s">
+      <c r="B9" s="17"/>
+      <c r="C9" s="14" t="s">
         <v>18</v>
       </c>
       <c r="D9" t="s">
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F9" t="s">
         <v>184</v>
       </c>
       <c r="H9" t="s">
         <v>181</v>
+      </c>
+      <c r="I9" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="15"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="14"/>
       <c r="D10" t="s">
         <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F10" t="s">
         <v>185</v>
@@ -1962,13 +1969,13 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="15"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="14"/>
       <c r="D11" t="s">
         <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F11" t="s">
         <v>185</v>
@@ -1981,7 +1988,7 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="18"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="7" t="s">
         <v>45</v>
       </c>
@@ -1989,7 +1996,7 @@
         <v>46</v>
       </c>
       <c r="E12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F12" t="s">
         <v>186</v>
@@ -2012,7 +2019,7 @@
         <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F13" t="s">
         <v>176</v>
@@ -2033,7 +2040,7 @@
         <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F14" t="s">
         <v>177</v>
@@ -2054,7 +2061,7 @@
         <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F15" t="s">
         <v>177</v>
@@ -2072,10 +2079,10 @@
         <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>177</v>
@@ -2091,17 +2098,17 @@
       <c r="B17" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="14" t="s">
         <v>31</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H17" t="s">
         <v>187</v>
@@ -2112,15 +2119,15 @@
         <v>17</v>
       </c>
       <c r="B18" s="13"/>
-      <c r="C18" s="15"/>
+      <c r="C18" s="14"/>
       <c r="D18" t="s">
         <v>12</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H18" t="s">
         <v>182</v>
@@ -2131,15 +2138,15 @@
         <v>18</v>
       </c>
       <c r="B19" s="13"/>
-      <c r="C19" s="15"/>
+      <c r="C19" s="14"/>
       <c r="D19" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H19" t="s">
         <v>187</v>
@@ -2157,10 +2164,10 @@
         <v>39</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H20" t="s">
         <v>183</v>
@@ -2178,10 +2185,10 @@
         <v>37</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H21" t="s">
         <v>183</v>
@@ -2199,10 +2206,10 @@
         <v>36</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H22" t="s">
         <v>182</v>
@@ -2213,17 +2220,17 @@
         <v>22</v>
       </c>
       <c r="B23" s="13"/>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="14" t="s">
         <v>32</v>
       </c>
       <c r="D23" t="s">
         <v>19</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H23" t="s">
         <v>187</v>
@@ -2234,15 +2241,15 @@
         <v>23</v>
       </c>
       <c r="B24" s="13"/>
-      <c r="C24" s="15"/>
+      <c r="C24" s="14"/>
       <c r="D24" t="s">
         <v>20</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H24" t="s">
         <v>182</v>
@@ -2253,15 +2260,15 @@
         <v>24</v>
       </c>
       <c r="B25" s="13"/>
-      <c r="C25" s="15"/>
+      <c r="C25" s="14"/>
       <c r="D25" t="s">
         <v>21</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H25" t="s">
         <v>181</v>
@@ -2276,13 +2283,13 @@
         <v>45</v>
       </c>
       <c r="D26" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E26" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="F26" s="10" t="s">
         <v>306</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>307</v>
       </c>
       <c r="H26" t="s">
         <v>187</v>
@@ -2295,13 +2302,13 @@
       <c r="B27" s="13"/>
       <c r="C27" s="12"/>
       <c r="D27" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H27" t="s">
         <v>187</v>
@@ -2321,10 +2328,10 @@
         <v>42</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H28" t="s">
         <v>183</v>
@@ -2342,10 +2349,10 @@
         <v>42</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H29" t="s">
         <v>183</v>
@@ -2363,10 +2370,10 @@
         <v>42</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H30" t="s">
         <v>183</v>
@@ -2377,17 +2384,17 @@
         <v>30</v>
       </c>
       <c r="B31" s="13"/>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="14" t="s">
         <v>53</v>
       </c>
       <c r="D31" t="s">
         <v>48</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H31" t="s">
         <v>181</v>
@@ -2398,15 +2405,15 @@
         <v>31</v>
       </c>
       <c r="B32" s="13"/>
-      <c r="C32" s="15"/>
+      <c r="C32" s="14"/>
       <c r="D32" t="s">
         <v>49</v>
       </c>
       <c r="E32" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="F32" s="10" t="s">
         <v>197</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>198</v>
       </c>
       <c r="H32" t="s">
         <v>181</v>
@@ -2417,15 +2424,15 @@
         <v>32</v>
       </c>
       <c r="B33" s="13"/>
-      <c r="C33" s="15"/>
+      <c r="C33" s="14"/>
       <c r="D33" t="s">
         <v>50</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H33" t="s">
         <v>181</v>
@@ -2436,17 +2443,17 @@
         <v>33</v>
       </c>
       <c r="B34" s="13"/>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="14" t="s">
         <v>47</v>
       </c>
       <c r="D34" t="s">
         <v>51</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H34" t="s">
         <v>187</v>
@@ -2457,15 +2464,15 @@
         <v>34</v>
       </c>
       <c r="B35" s="13"/>
-      <c r="C35" s="15"/>
+      <c r="C35" s="14"/>
       <c r="D35" t="s">
         <v>52</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H35" t="s">
         <v>187</v>
@@ -2478,17 +2485,17 @@
       <c r="B36" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C36" s="14" t="s">
         <v>55</v>
       </c>
       <c r="D36" t="s">
         <v>57</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F36" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H36" t="s">
         <v>187</v>
@@ -2499,15 +2506,15 @@
         <v>36</v>
       </c>
       <c r="B37" s="13"/>
-      <c r="C37" s="15"/>
+      <c r="C37" s="14"/>
       <c r="D37" t="s">
         <v>58</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F37" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H37" t="s">
         <v>187</v>
@@ -2518,15 +2525,15 @@
         <v>37</v>
       </c>
       <c r="B38" s="13"/>
-      <c r="C38" s="15"/>
+      <c r="C38" s="14"/>
       <c r="D38" t="s">
         <v>58</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F38" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H38" t="s">
         <v>182</v>
@@ -2537,23 +2544,23 @@
         <v>38</v>
       </c>
       <c r="B39" s="13"/>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="14" t="s">
         <v>59</v>
       </c>
       <c r="D39" t="s">
         <v>60</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F39" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H39" t="s">
         <v>181</v>
       </c>
       <c r="I39" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -2561,15 +2568,15 @@
         <v>39</v>
       </c>
       <c r="B40" s="13"/>
-      <c r="C40" s="15"/>
+      <c r="C40" s="14"/>
       <c r="D40" t="s">
         <v>61</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F40" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H40" t="s">
         <v>187</v>
@@ -2587,10 +2594,10 @@
         <v>65</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F41" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H41" t="s">
         <v>182</v>
@@ -2606,10 +2613,10 @@
         <v>62</v>
       </c>
       <c r="E42" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="F42" t="s">
         <v>208</v>
-      </c>
-      <c r="F42" t="s">
-        <v>209</v>
       </c>
       <c r="H42" t="s">
         <v>182</v>
@@ -2625,10 +2632,10 @@
         <v>63</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="F43" t="s">
         <v>208</v>
-      </c>
-      <c r="F43" t="s">
-        <v>209</v>
       </c>
       <c r="H43" t="s">
         <v>182</v>
@@ -2644,10 +2651,10 @@
         <v>64</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F44" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H44" t="s">
         <v>182</v>
@@ -2663,10 +2670,10 @@
         <v>66</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F45" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H45" t="s">
         <v>182</v>
@@ -2679,13 +2686,13 @@
       <c r="B46" s="13"/>
       <c r="C46" s="12"/>
       <c r="D46" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F46" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H46" t="s">
         <v>187</v>
@@ -2703,10 +2710,10 @@
         <v>77</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H47" t="s">
         <v>182</v>
@@ -2722,10 +2729,10 @@
         <v>78</v>
       </c>
       <c r="E48" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="F48" t="s">
         <v>208</v>
-      </c>
-      <c r="F48" t="s">
-        <v>209</v>
       </c>
       <c r="H48" t="s">
         <v>182</v>
@@ -2741,10 +2748,10 @@
         <v>79</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F49" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H49" t="s">
         <v>187</v>
@@ -2760,10 +2767,10 @@
         <v>173</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F50" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H50" t="s">
         <v>187</v>
@@ -2776,17 +2783,17 @@
       <c r="B51" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="C51" s="14" t="s">
         <v>75</v>
       </c>
       <c r="D51" t="s">
         <v>69</v>
       </c>
       <c r="E51" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="F51" t="s">
         <v>214</v>
-      </c>
-      <c r="F51" t="s">
-        <v>215</v>
       </c>
       <c r="H51" t="s">
         <v>182</v>
@@ -2797,15 +2804,15 @@
         <v>51</v>
       </c>
       <c r="B52" s="13"/>
-      <c r="C52" s="15"/>
+      <c r="C52" s="14"/>
       <c r="D52" t="s">
         <v>72</v>
       </c>
       <c r="E52" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="F52" t="s">
         <v>216</v>
-      </c>
-      <c r="F52" t="s">
-        <v>217</v>
       </c>
       <c r="H52" t="s">
         <v>187</v>
@@ -2816,15 +2823,15 @@
         <v>52</v>
       </c>
       <c r="B53" s="13"/>
-      <c r="C53" s="15"/>
+      <c r="C53" s="14"/>
       <c r="D53" t="s">
         <v>73</v>
       </c>
       <c r="E53" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="F53" t="s">
         <v>216</v>
-      </c>
-      <c r="F53" t="s">
-        <v>217</v>
       </c>
       <c r="H53" t="s">
         <v>187</v>
@@ -2835,17 +2842,17 @@
         <v>53</v>
       </c>
       <c r="B54" s="13"/>
-      <c r="C54" s="15" t="s">
+      <c r="C54" s="14" t="s">
         <v>74</v>
       </c>
       <c r="D54" t="s">
         <v>80</v>
       </c>
       <c r="E54" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="F54" t="s">
         <v>214</v>
-      </c>
-      <c r="F54" t="s">
-        <v>215</v>
       </c>
       <c r="H54" t="s">
         <v>182</v>
@@ -2856,15 +2863,15 @@
         <v>54</v>
       </c>
       <c r="B55" s="13"/>
-      <c r="C55" s="15"/>
+      <c r="C55" s="14"/>
       <c r="D55" t="s">
         <v>76</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F55" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H55" t="s">
         <v>187</v>
@@ -2875,15 +2882,15 @@
         <v>55</v>
       </c>
       <c r="B56" s="13"/>
-      <c r="C56" s="15"/>
+      <c r="C56" s="14"/>
       <c r="D56" t="s">
         <v>81</v>
       </c>
       <c r="E56" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="F56" t="s">
         <v>214</v>
-      </c>
-      <c r="F56" t="s">
-        <v>215</v>
       </c>
       <c r="H56" t="s">
         <v>182</v>
@@ -2894,15 +2901,15 @@
         <v>56</v>
       </c>
       <c r="B57" s="13"/>
-      <c r="C57" s="15"/>
+      <c r="C57" s="14"/>
       <c r="D57" t="s">
         <v>82</v>
       </c>
       <c r="E57" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="F57" t="s">
         <v>214</v>
-      </c>
-      <c r="F57" t="s">
-        <v>215</v>
       </c>
       <c r="H57" t="s">
         <v>182</v>
@@ -2913,15 +2920,15 @@
         <v>57</v>
       </c>
       <c r="B58" s="13"/>
-      <c r="C58" s="15"/>
+      <c r="C58" s="14"/>
       <c r="D58" t="s">
         <v>83</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F58" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H58" t="s">
         <v>182</v>
@@ -2932,15 +2939,15 @@
         <v>58</v>
       </c>
       <c r="B59" s="13"/>
-      <c r="C59" s="15"/>
+      <c r="C59" s="14"/>
       <c r="D59" t="s">
         <v>71</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F59" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H59" t="s">
         <v>182</v>
@@ -2951,15 +2958,15 @@
         <v>59</v>
       </c>
       <c r="B60" s="13"/>
-      <c r="C60" s="15"/>
+      <c r="C60" s="14"/>
       <c r="D60" t="s">
         <v>86</v>
       </c>
       <c r="E60" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="F60" t="s">
         <v>214</v>
-      </c>
-      <c r="F60" t="s">
-        <v>215</v>
       </c>
       <c r="H60" t="s">
         <v>187</v>
@@ -2970,17 +2977,17 @@
         <v>60</v>
       </c>
       <c r="B61" s="13"/>
-      <c r="C61" s="15" t="s">
+      <c r="C61" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D61" t="s">
         <v>85</v>
       </c>
       <c r="E61" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="F61" t="s">
         <v>214</v>
-      </c>
-      <c r="F61" t="s">
-        <v>215</v>
       </c>
       <c r="H61" t="s">
         <v>182</v>
@@ -2991,15 +2998,15 @@
         <v>61</v>
       </c>
       <c r="B62" s="13"/>
-      <c r="C62" s="15"/>
+      <c r="C62" s="14"/>
       <c r="D62" t="s">
         <v>84</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F62" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H62" t="s">
         <v>182</v>
@@ -3012,17 +3019,17 @@
       <c r="B63" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C63" s="15" t="s">
+      <c r="C63" s="14" t="s">
         <v>94</v>
       </c>
       <c r="D63" t="s">
         <v>95</v>
       </c>
       <c r="E63" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="F63" t="s">
         <v>221</v>
-      </c>
-      <c r="F63" t="s">
-        <v>222</v>
       </c>
       <c r="H63" t="s">
         <v>182</v>
@@ -3033,15 +3040,15 @@
         <v>63</v>
       </c>
       <c r="B64" s="13"/>
-      <c r="C64" s="15"/>
+      <c r="C64" s="14"/>
       <c r="D64" t="s">
         <v>96</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F64" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H64" t="s">
         <v>187</v>
@@ -3054,17 +3061,17 @@
       <c r="B65" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C65" s="15" t="s">
+      <c r="C65" s="14" t="s">
         <v>172</v>
       </c>
       <c r="D65" t="s">
         <v>88</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F65" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H65" t="s">
         <v>187</v>
@@ -3075,15 +3082,15 @@
         <v>65</v>
       </c>
       <c r="B66" s="13"/>
-      <c r="C66" s="15"/>
+      <c r="C66" s="14"/>
       <c r="D66" t="s">
         <v>89</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F66" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H66" t="s">
         <v>182</v>
@@ -3094,15 +3101,15 @@
         <v>66</v>
       </c>
       <c r="B67" s="13"/>
-      <c r="C67" s="15"/>
+      <c r="C67" s="14"/>
       <c r="D67" t="s">
         <v>90</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F67" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H67" t="s">
         <v>187</v>
@@ -3120,10 +3127,10 @@
         <v>92</v>
       </c>
       <c r="E68" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="F68" s="10" t="s">
         <v>226</v>
-      </c>
-      <c r="F68" s="10" t="s">
-        <v>227</v>
       </c>
       <c r="H68" t="s">
         <v>187</v>
@@ -3134,19 +3141,19 @@
         <v>68</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="C69" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="C69" s="14" t="s">
         <v>97</v>
       </c>
       <c r="D69" t="s">
         <v>98</v>
       </c>
       <c r="E69" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="F69" s="10" t="s">
         <v>228</v>
-      </c>
-      <c r="F69" s="10" t="s">
-        <v>229</v>
       </c>
       <c r="H69" t="s">
         <v>187</v>
@@ -3157,15 +3164,15 @@
         <v>69</v>
       </c>
       <c r="B70" s="13"/>
-      <c r="C70" s="15"/>
+      <c r="C70" s="14"/>
       <c r="D70" t="s">
         <v>99</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H70" t="s">
         <v>182</v>
@@ -3176,15 +3183,15 @@
         <v>70</v>
       </c>
       <c r="B71" s="13"/>
-      <c r="C71" s="15"/>
+      <c r="C71" s="14"/>
       <c r="D71" t="s">
         <v>100</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H71" t="s">
         <v>187</v>
@@ -3195,7 +3202,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="13"/>
-      <c r="C72" s="15" t="s">
+      <c r="C72" s="14" t="s">
         <v>101</v>
       </c>
       <c r="D72" t="s">
@@ -3216,7 +3223,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="13"/>
-      <c r="C73" s="15"/>
+      <c r="C73" s="14"/>
       <c r="D73" t="s">
         <v>105</v>
       </c>
@@ -3235,7 +3242,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="13"/>
-      <c r="C74" s="15"/>
+      <c r="C74" s="14"/>
       <c r="D74" t="s">
         <v>108</v>
       </c>
@@ -3256,17 +3263,17 @@
       <c r="B75" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="C75" s="16" t="s">
-        <v>274</v>
+      <c r="C75" s="15" t="s">
+        <v>273</v>
       </c>
       <c r="D75" t="s">
         <v>112</v>
       </c>
       <c r="E75" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F75" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H75" t="s">
         <v>182</v>
@@ -3277,15 +3284,15 @@
         <v>75</v>
       </c>
       <c r="B76" s="13"/>
-      <c r="C76" s="16"/>
+      <c r="C76" s="15"/>
       <c r="D76" t="s">
         <v>113</v>
       </c>
       <c r="E76" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F76" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H76" t="s">
         <v>182</v>
@@ -3296,15 +3303,15 @@
         <v>76</v>
       </c>
       <c r="B77" s="13"/>
-      <c r="C77" s="16"/>
+      <c r="C77" s="15"/>
       <c r="D77" t="s">
         <v>114</v>
       </c>
       <c r="E77" t="s">
+        <v>232</v>
+      </c>
+      <c r="F77" t="s">
         <v>233</v>
-      </c>
-      <c r="F77" t="s">
-        <v>234</v>
       </c>
       <c r="H77" t="s">
         <v>182</v>
@@ -3315,14 +3322,14 @@
         <v>77</v>
       </c>
       <c r="B78" s="13"/>
-      <c r="C78" s="14" t="s">
+      <c r="C78" s="19" t="s">
         <v>117</v>
       </c>
       <c r="D78" t="s">
         <v>124</v>
       </c>
       <c r="E78" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F78" t="s">
         <v>118</v>
@@ -3336,12 +3343,12 @@
         <v>78</v>
       </c>
       <c r="B79" s="13"/>
-      <c r="C79" s="14"/>
+      <c r="C79" s="19"/>
       <c r="D79" t="s">
         <v>124</v>
       </c>
       <c r="E79" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F79" t="s">
         <v>119</v>
@@ -3355,17 +3362,17 @@
         <v>79</v>
       </c>
       <c r="B80" s="13"/>
-      <c r="C80" s="14" t="s">
+      <c r="C80" s="19" t="s">
         <v>132</v>
       </c>
       <c r="D80" t="s">
         <v>133</v>
       </c>
       <c r="E80" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F80" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H80" t="s">
         <v>181</v>
@@ -3376,15 +3383,15 @@
         <v>80</v>
       </c>
       <c r="B81" s="13"/>
-      <c r="C81" s="14"/>
+      <c r="C81" s="19"/>
       <c r="D81" t="s">
         <v>134</v>
       </c>
       <c r="E81" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F81" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H81" t="s">
         <v>181</v>
@@ -3395,15 +3402,15 @@
         <v>81</v>
       </c>
       <c r="B82" s="13"/>
-      <c r="C82" s="14"/>
+      <c r="C82" s="19"/>
       <c r="D82" t="s">
         <v>135</v>
       </c>
       <c r="E82" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F82" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H82" t="s">
         <v>181</v>
@@ -3414,14 +3421,14 @@
         <v>82</v>
       </c>
       <c r="B83" s="13"/>
-      <c r="C83" s="14" t="s">
+      <c r="C83" s="19" t="s">
         <v>120</v>
       </c>
       <c r="D83" t="s">
         <v>124</v>
       </c>
       <c r="E83" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F83" t="s">
         <v>121</v>
@@ -3435,12 +3442,12 @@
         <v>83</v>
       </c>
       <c r="B84" s="13"/>
-      <c r="C84" s="14"/>
+      <c r="C84" s="19"/>
       <c r="D84" t="s">
         <v>124</v>
       </c>
       <c r="E84" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F84" t="s">
         <v>122</v>
@@ -3461,10 +3468,10 @@
         <v>129</v>
       </c>
       <c r="E85" t="s">
+        <v>234</v>
+      </c>
+      <c r="F85" t="s">
         <v>235</v>
-      </c>
-      <c r="F85" t="s">
-        <v>236</v>
       </c>
       <c r="H85" t="s">
         <v>187</v>
@@ -3480,10 +3487,10 @@
         <v>128</v>
       </c>
       <c r="E86" t="s">
+        <v>234</v>
+      </c>
+      <c r="F86" t="s">
         <v>235</v>
-      </c>
-      <c r="F86" t="s">
-        <v>236</v>
       </c>
       <c r="H86" t="s">
         <v>182</v>
@@ -3499,10 +3506,10 @@
         <v>130</v>
       </c>
       <c r="E87" t="s">
+        <v>234</v>
+      </c>
+      <c r="F87" t="s">
         <v>235</v>
-      </c>
-      <c r="F87" t="s">
-        <v>236</v>
       </c>
       <c r="H87" t="s">
         <v>187</v>
@@ -3520,10 +3527,10 @@
         <v>116</v>
       </c>
       <c r="E88" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F88" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H88" t="s">
         <v>187</v>
@@ -3538,13 +3545,13 @@
         <v>125</v>
       </c>
       <c r="D89" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E89" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F89" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H89" t="s">
         <v>187</v>
@@ -3557,13 +3564,13 @@
       <c r="B90" s="13"/>
       <c r="C90" s="12"/>
       <c r="D90" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E90" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F90" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H90" t="s">
         <v>187</v>
@@ -3579,10 +3586,10 @@
         <v>126</v>
       </c>
       <c r="E91" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F91" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H91" t="s">
         <v>187</v>
@@ -3598,10 +3605,10 @@
         <v>141</v>
       </c>
       <c r="E92" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F92" t="s">
-        <v>188</v>
+        <v>308</v>
       </c>
       <c r="H92" t="s">
         <v>182</v>
@@ -3621,10 +3628,10 @@
         <v>129</v>
       </c>
       <c r="E93" t="s">
+        <v>240</v>
+      </c>
+      <c r="F93" t="s">
         <v>241</v>
-      </c>
-      <c r="F93" t="s">
-        <v>242</v>
       </c>
       <c r="H93" t="s">
         <v>187</v>
@@ -3640,7 +3647,7 @@
         <v>128</v>
       </c>
       <c r="E94" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F94" t="s">
         <v>127</v>
@@ -3659,7 +3666,7 @@
         <v>130</v>
       </c>
       <c r="E95" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F95" t="s">
         <v>127</v>
@@ -3682,10 +3689,10 @@
         <v>140</v>
       </c>
       <c r="E96" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F96" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H96" t="s">
         <v>182</v>
@@ -3703,10 +3710,10 @@
         <v>147</v>
       </c>
       <c r="E97" t="s">
+        <v>243</v>
+      </c>
+      <c r="F97" t="s">
         <v>244</v>
-      </c>
-      <c r="F97" t="s">
-        <v>245</v>
       </c>
       <c r="H97" t="s">
         <v>182</v>
@@ -3724,10 +3731,10 @@
         <v>138</v>
       </c>
       <c r="E98" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F98" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H98" t="s">
         <v>182</v>
@@ -3745,10 +3752,10 @@
         <v>143</v>
       </c>
       <c r="E99" t="s">
+        <v>246</v>
+      </c>
+      <c r="F99" t="s">
         <v>247</v>
-      </c>
-      <c r="F99" t="s">
-        <v>248</v>
       </c>
       <c r="H99" t="s">
         <v>182</v>
@@ -3766,10 +3773,10 @@
         <v>145</v>
       </c>
       <c r="E100" t="s">
+        <v>248</v>
+      </c>
+      <c r="F100" t="s">
         <v>249</v>
-      </c>
-      <c r="F100" t="s">
-        <v>250</v>
       </c>
       <c r="H100" t="s">
         <v>182</v>
@@ -3787,10 +3794,10 @@
         <v>19</v>
       </c>
       <c r="E101" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F101" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H101" t="s">
         <v>187</v>
@@ -3806,10 +3813,10 @@
         <v>149</v>
       </c>
       <c r="E102" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F102" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H102" t="s">
         <v>182</v>
@@ -3825,10 +3832,10 @@
         <v>150</v>
       </c>
       <c r="E103" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F103" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H103" t="s">
         <v>187</v>
@@ -3846,10 +3853,10 @@
         <v>19</v>
       </c>
       <c r="E104" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F104" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H104" t="s">
         <v>187</v>
@@ -3865,10 +3872,10 @@
         <v>149</v>
       </c>
       <c r="E105" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F105" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H105" t="s">
         <v>182</v>
@@ -3884,10 +3891,10 @@
         <v>150</v>
       </c>
       <c r="E106" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F106" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H106" t="s">
         <v>187</v>
@@ -3905,10 +3912,10 @@
         <v>19</v>
       </c>
       <c r="E107" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F107" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H107" t="s">
         <v>187</v>
@@ -3924,10 +3931,10 @@
         <v>149</v>
       </c>
       <c r="E108" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F108" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H108" t="s">
         <v>182</v>
@@ -3943,10 +3950,10 @@
         <v>150</v>
       </c>
       <c r="E109" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F109" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H109" t="s">
         <v>181</v>
@@ -3964,10 +3971,10 @@
         <v>152</v>
       </c>
       <c r="E110" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F110" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H110" t="s">
         <v>181</v>
@@ -3983,10 +3990,10 @@
         <v>153</v>
       </c>
       <c r="E111" t="s">
+        <v>256</v>
+      </c>
+      <c r="F111" t="s">
         <v>257</v>
-      </c>
-      <c r="F111" t="s">
-        <v>258</v>
       </c>
       <c r="H111" t="s">
         <v>182</v>
@@ -3999,13 +4006,13 @@
       <c r="B112" s="13"/>
       <c r="C112" s="12"/>
       <c r="D112" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E112" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F112" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H112" t="s">
         <v>187</v>
@@ -4018,13 +4025,13 @@
       <c r="B113" s="13"/>
       <c r="C113" s="12"/>
       <c r="D113" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E113" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F113" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H113" t="s">
         <v>182</v>
@@ -4037,13 +4044,13 @@
       <c r="B114" s="13"/>
       <c r="C114" s="12"/>
       <c r="D114" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E114" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F114" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H114" t="s">
         <v>181</v>
@@ -4063,10 +4070,10 @@
         <v>156</v>
       </c>
       <c r="E115" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F115" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H115" t="s">
         <v>182</v>
@@ -4084,10 +4091,10 @@
         <v>160</v>
       </c>
       <c r="E116" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F116" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H116" t="s">
         <v>182</v>
@@ -4107,10 +4114,10 @@
         <v>163</v>
       </c>
       <c r="E117" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F117" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H117" t="s">
         <v>182</v>
@@ -4130,10 +4137,10 @@
         <v>166</v>
       </c>
       <c r="E118" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F118" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H118" t="s">
         <v>187</v>
@@ -4149,10 +4156,10 @@
         <v>167</v>
       </c>
       <c r="E119" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F119" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H119" t="s">
         <v>182</v>
@@ -4168,10 +4175,10 @@
         <v>168</v>
       </c>
       <c r="E120" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F120" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H120" t="s">
         <v>181</v>
@@ -4189,10 +4196,10 @@
         <v>170</v>
       </c>
       <c r="E121" t="s">
+        <v>262</v>
+      </c>
+      <c r="F121" t="s">
         <v>263</v>
-      </c>
-      <c r="F121" t="s">
-        <v>264</v>
       </c>
       <c r="H121" t="s">
         <v>182</v>
@@ -4208,10 +4215,10 @@
         <v>171</v>
       </c>
       <c r="E122" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F122" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H122" t="s">
         <v>187</v>
@@ -4227,10 +4234,10 @@
         <v>174</v>
       </c>
       <c r="E123" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F123" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H123" t="s">
         <v>187</v>
@@ -4241,19 +4248,19 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
+        <v>269</v>
+      </c>
+      <c r="C124" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="C124" s="11" t="s">
+      <c r="D124" t="s">
         <v>271</v>
       </c>
-      <c r="D124" t="s">
+      <c r="E124" t="s">
+        <v>300</v>
+      </c>
+      <c r="F124" t="s">
         <v>272</v>
-      </c>
-      <c r="E124" t="s">
-        <v>301</v>
-      </c>
-      <c r="F124" t="s">
-        <v>273</v>
       </c>
       <c r="H124" t="s">
         <v>187</v>
@@ -4261,14 +4268,28 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="B28:B35"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="B51:B62"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="C54:C60"/>
+    <mergeCell ref="C121:C123"/>
+    <mergeCell ref="B118:B123"/>
+    <mergeCell ref="C47:C50"/>
+    <mergeCell ref="B36:B50"/>
+    <mergeCell ref="C41:C46"/>
+    <mergeCell ref="B115:B116"/>
+    <mergeCell ref="C118:C120"/>
+    <mergeCell ref="B75:B92"/>
+    <mergeCell ref="B96:B114"/>
+    <mergeCell ref="C110:C114"/>
+    <mergeCell ref="C104:C106"/>
+    <mergeCell ref="C107:C109"/>
+    <mergeCell ref="C93:C95"/>
+    <mergeCell ref="B93:B95"/>
+    <mergeCell ref="C80:C82"/>
+    <mergeCell ref="C101:C103"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="C85:C87"/>
+    <mergeCell ref="C69:C71"/>
+    <mergeCell ref="C72:C74"/>
+    <mergeCell ref="C89:C92"/>
     <mergeCell ref="B69:B74"/>
     <mergeCell ref="C75:C77"/>
     <mergeCell ref="C65:C67"/>
@@ -4285,28 +4306,14 @@
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="C34:C35"/>
     <mergeCell ref="C31:C33"/>
-    <mergeCell ref="C101:C103"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="C85:C87"/>
-    <mergeCell ref="C69:C71"/>
-    <mergeCell ref="C72:C74"/>
-    <mergeCell ref="C89:C92"/>
-    <mergeCell ref="C121:C123"/>
-    <mergeCell ref="B118:B123"/>
-    <mergeCell ref="C47:C50"/>
-    <mergeCell ref="B36:B50"/>
-    <mergeCell ref="C41:C46"/>
-    <mergeCell ref="B115:B116"/>
-    <mergeCell ref="C118:C120"/>
-    <mergeCell ref="B75:B92"/>
-    <mergeCell ref="B96:B114"/>
-    <mergeCell ref="C110:C114"/>
-    <mergeCell ref="C104:C106"/>
-    <mergeCell ref="C107:C109"/>
-    <mergeCell ref="C93:C95"/>
-    <mergeCell ref="B93:B95"/>
-    <mergeCell ref="C80:C82"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="B28:B35"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="B51:B62"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="C54:C60"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4120B8B1-A549-4A43-8102-12EED60A125C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEDAFC41-46AD-4A76-BD2D-FAA646C76A0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{F425FBA8-E65A-4F03-9270-551F3EA7C4F5}"/>
   </bookViews>
@@ -774,10 +774,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>活动开启后将账号等级升至10级</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>正确</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1246,6 +1242,10 @@
   </si>
   <si>
     <t>并列排序？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家参与活动可参与活动</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1795,7 +1795,7 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F2" t="s">
         <v>176</v>
@@ -1814,7 +1814,7 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F3" t="s">
         <v>177</v>
@@ -1833,7 +1833,7 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F4" t="s">
         <v>177</v>
@@ -1854,7 +1854,7 @@
         <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F5" t="s">
         <v>178</v>
@@ -1873,7 +1873,7 @@
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F6" t="s">
         <v>179</v>
@@ -1892,7 +1892,7 @@
         <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F7" t="s">
         <v>179</v>
@@ -1934,7 +1934,7 @@
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F9" t="s">
         <v>184</v>
@@ -1943,7 +1943,7 @@
         <v>181</v>
       </c>
       <c r="I9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1956,7 +1956,7 @@
         <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F10" t="s">
         <v>185</v>
@@ -1975,7 +1975,7 @@
         <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F11" t="s">
         <v>185</v>
@@ -1996,7 +1996,7 @@
         <v>46</v>
       </c>
       <c r="E12" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F12" t="s">
         <v>186</v>
@@ -2079,10 +2079,10 @@
         <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>189</v>
+        <v>308</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>177</v>
@@ -2105,10 +2105,10 @@
         <v>11</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H17" t="s">
         <v>187</v>
@@ -2124,10 +2124,10 @@
         <v>12</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H18" t="s">
         <v>182</v>
@@ -2143,10 +2143,10 @@
         <v>13</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H19" t="s">
         <v>187</v>
@@ -2164,10 +2164,10 @@
         <v>39</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H20" t="s">
         <v>183</v>
@@ -2185,10 +2185,10 @@
         <v>37</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H21" t="s">
         <v>183</v>
@@ -2206,10 +2206,10 @@
         <v>36</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H22" t="s">
         <v>182</v>
@@ -2227,10 +2227,10 @@
         <v>19</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H23" t="s">
         <v>187</v>
@@ -2246,10 +2246,10 @@
         <v>20</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H24" t="s">
         <v>182</v>
@@ -2265,10 +2265,10 @@
         <v>21</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H25" t="s">
         <v>181</v>
@@ -2283,13 +2283,13 @@
         <v>45</v>
       </c>
       <c r="D26" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E26" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="F26" s="10" t="s">
         <v>305</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>306</v>
       </c>
       <c r="H26" t="s">
         <v>187</v>
@@ -2302,13 +2302,13 @@
       <c r="B27" s="13"/>
       <c r="C27" s="12"/>
       <c r="D27" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H27" t="s">
         <v>187</v>
@@ -2328,10 +2328,10 @@
         <v>42</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H28" t="s">
         <v>183</v>
@@ -2349,10 +2349,10 @@
         <v>42</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H29" t="s">
         <v>183</v>
@@ -2370,10 +2370,10 @@
         <v>42</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H30" t="s">
         <v>183</v>
@@ -2391,10 +2391,10 @@
         <v>48</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H31" t="s">
         <v>181</v>
@@ -2410,10 +2410,10 @@
         <v>49</v>
       </c>
       <c r="E32" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="F32" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="H32" t="s">
         <v>181</v>
@@ -2429,10 +2429,10 @@
         <v>50</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H33" t="s">
         <v>181</v>
@@ -2450,10 +2450,10 @@
         <v>51</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H34" t="s">
         <v>187</v>
@@ -2469,10 +2469,10 @@
         <v>52</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H35" t="s">
         <v>187</v>
@@ -2492,10 +2492,10 @@
         <v>57</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H36" t="s">
         <v>187</v>
@@ -2511,10 +2511,10 @@
         <v>58</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F37" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H37" t="s">
         <v>187</v>
@@ -2530,10 +2530,10 @@
         <v>58</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F38" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H38" t="s">
         <v>182</v>
@@ -2551,16 +2551,16 @@
         <v>60</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F39" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H39" t="s">
         <v>181</v>
       </c>
       <c r="I39" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -2573,10 +2573,10 @@
         <v>61</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F40" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H40" t="s">
         <v>187</v>
@@ -2594,10 +2594,10 @@
         <v>65</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H41" t="s">
         <v>182</v>
@@ -2613,10 +2613,10 @@
         <v>62</v>
       </c>
       <c r="E42" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F42" t="s">
         <v>207</v>
-      </c>
-      <c r="F42" t="s">
-        <v>208</v>
       </c>
       <c r="H42" t="s">
         <v>182</v>
@@ -2632,10 +2632,10 @@
         <v>63</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F43" t="s">
         <v>207</v>
-      </c>
-      <c r="F43" t="s">
-        <v>208</v>
       </c>
       <c r="H43" t="s">
         <v>182</v>
@@ -2651,10 +2651,10 @@
         <v>64</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F44" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H44" t="s">
         <v>182</v>
@@ -2670,10 +2670,10 @@
         <v>66</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F45" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H45" t="s">
         <v>182</v>
@@ -2686,13 +2686,13 @@
       <c r="B46" s="13"/>
       <c r="C46" s="12"/>
       <c r="D46" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F46" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H46" t="s">
         <v>187</v>
@@ -2710,10 +2710,10 @@
         <v>77</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F47" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H47" t="s">
         <v>182</v>
@@ -2729,10 +2729,10 @@
         <v>78</v>
       </c>
       <c r="E48" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F48" t="s">
         <v>207</v>
-      </c>
-      <c r="F48" t="s">
-        <v>208</v>
       </c>
       <c r="H48" t="s">
         <v>182</v>
@@ -2748,10 +2748,10 @@
         <v>79</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F49" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H49" t="s">
         <v>187</v>
@@ -2767,10 +2767,10 @@
         <v>173</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F50" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H50" t="s">
         <v>187</v>
@@ -2790,10 +2790,10 @@
         <v>69</v>
       </c>
       <c r="E51" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="F51" t="s">
         <v>213</v>
-      </c>
-      <c r="F51" t="s">
-        <v>214</v>
       </c>
       <c r="H51" t="s">
         <v>182</v>
@@ -2809,10 +2809,10 @@
         <v>72</v>
       </c>
       <c r="E52" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="F52" t="s">
         <v>215</v>
-      </c>
-      <c r="F52" t="s">
-        <v>216</v>
       </c>
       <c r="H52" t="s">
         <v>187</v>
@@ -2828,10 +2828,10 @@
         <v>73</v>
       </c>
       <c r="E53" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="F53" t="s">
         <v>215</v>
-      </c>
-      <c r="F53" t="s">
-        <v>216</v>
       </c>
       <c r="H53" t="s">
         <v>187</v>
@@ -2849,10 +2849,10 @@
         <v>80</v>
       </c>
       <c r="E54" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="F54" t="s">
         <v>213</v>
-      </c>
-      <c r="F54" t="s">
-        <v>214</v>
       </c>
       <c r="H54" t="s">
         <v>182</v>
@@ -2868,10 +2868,10 @@
         <v>76</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F55" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H55" t="s">
         <v>187</v>
@@ -2887,10 +2887,10 @@
         <v>81</v>
       </c>
       <c r="E56" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="F56" t="s">
         <v>213</v>
-      </c>
-      <c r="F56" t="s">
-        <v>214</v>
       </c>
       <c r="H56" t="s">
         <v>182</v>
@@ -2906,10 +2906,10 @@
         <v>82</v>
       </c>
       <c r="E57" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="F57" t="s">
         <v>213</v>
-      </c>
-      <c r="F57" t="s">
-        <v>214</v>
       </c>
       <c r="H57" t="s">
         <v>182</v>
@@ -2925,10 +2925,10 @@
         <v>83</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F58" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H58" t="s">
         <v>182</v>
@@ -2944,10 +2944,10 @@
         <v>71</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F59" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H59" t="s">
         <v>182</v>
@@ -2963,10 +2963,10 @@
         <v>86</v>
       </c>
       <c r="E60" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="F60" t="s">
         <v>213</v>
-      </c>
-      <c r="F60" t="s">
-        <v>214</v>
       </c>
       <c r="H60" t="s">
         <v>187</v>
@@ -2984,10 +2984,10 @@
         <v>85</v>
       </c>
       <c r="E61" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="F61" t="s">
         <v>213</v>
-      </c>
-      <c r="F61" t="s">
-        <v>214</v>
       </c>
       <c r="H61" t="s">
         <v>182</v>
@@ -3003,10 +3003,10 @@
         <v>84</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F62" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H62" t="s">
         <v>182</v>
@@ -3026,10 +3026,10 @@
         <v>95</v>
       </c>
       <c r="E63" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="F63" t="s">
         <v>220</v>
-      </c>
-      <c r="F63" t="s">
-        <v>221</v>
       </c>
       <c r="H63" t="s">
         <v>182</v>
@@ -3045,10 +3045,10 @@
         <v>96</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F64" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H64" t="s">
         <v>187</v>
@@ -3068,10 +3068,10 @@
         <v>88</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F65" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H65" t="s">
         <v>187</v>
@@ -3087,10 +3087,10 @@
         <v>89</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F66" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H66" t="s">
         <v>182</v>
@@ -3106,10 +3106,10 @@
         <v>90</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F67" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H67" t="s">
         <v>187</v>
@@ -3127,10 +3127,10 @@
         <v>92</v>
       </c>
       <c r="E68" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="F68" s="10" t="s">
         <v>225</v>
-      </c>
-      <c r="F68" s="10" t="s">
-        <v>226</v>
       </c>
       <c r="H68" t="s">
         <v>187</v>
@@ -3141,7 +3141,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C69" s="14" t="s">
         <v>97</v>
@@ -3150,10 +3150,10 @@
         <v>98</v>
       </c>
       <c r="E69" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="F69" s="10" t="s">
         <v>227</v>
-      </c>
-      <c r="F69" s="10" t="s">
-        <v>228</v>
       </c>
       <c r="H69" t="s">
         <v>187</v>
@@ -3169,10 +3169,10 @@
         <v>99</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H70" t="s">
         <v>182</v>
@@ -3188,10 +3188,10 @@
         <v>100</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H71" t="s">
         <v>187</v>
@@ -3264,16 +3264,16 @@
         <v>111</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D75" t="s">
         <v>112</v>
       </c>
       <c r="E75" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F75" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H75" t="s">
         <v>182</v>
@@ -3289,10 +3289,10 @@
         <v>113</v>
       </c>
       <c r="E76" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F76" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H76" t="s">
         <v>182</v>
@@ -3308,10 +3308,10 @@
         <v>114</v>
       </c>
       <c r="E77" t="s">
+        <v>231</v>
+      </c>
+      <c r="F77" t="s">
         <v>232</v>
-      </c>
-      <c r="F77" t="s">
-        <v>233</v>
       </c>
       <c r="H77" t="s">
         <v>182</v>
@@ -3329,7 +3329,7 @@
         <v>124</v>
       </c>
       <c r="E78" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F78" t="s">
         <v>118</v>
@@ -3348,7 +3348,7 @@
         <v>124</v>
       </c>
       <c r="E79" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F79" t="s">
         <v>119</v>
@@ -3369,10 +3369,10 @@
         <v>133</v>
       </c>
       <c r="E80" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H80" t="s">
         <v>181</v>
@@ -3388,10 +3388,10 @@
         <v>134</v>
       </c>
       <c r="E81" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F81" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H81" t="s">
         <v>181</v>
@@ -3407,10 +3407,10 @@
         <v>135</v>
       </c>
       <c r="E82" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F82" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H82" t="s">
         <v>181</v>
@@ -3428,7 +3428,7 @@
         <v>124</v>
       </c>
       <c r="E83" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F83" t="s">
         <v>121</v>
@@ -3447,7 +3447,7 @@
         <v>124</v>
       </c>
       <c r="E84" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F84" t="s">
         <v>122</v>
@@ -3468,10 +3468,10 @@
         <v>129</v>
       </c>
       <c r="E85" t="s">
+        <v>233</v>
+      </c>
+      <c r="F85" t="s">
         <v>234</v>
-      </c>
-      <c r="F85" t="s">
-        <v>235</v>
       </c>
       <c r="H85" t="s">
         <v>187</v>
@@ -3487,10 +3487,10 @@
         <v>128</v>
       </c>
       <c r="E86" t="s">
+        <v>233</v>
+      </c>
+      <c r="F86" t="s">
         <v>234</v>
-      </c>
-      <c r="F86" t="s">
-        <v>235</v>
       </c>
       <c r="H86" t="s">
         <v>182</v>
@@ -3506,10 +3506,10 @@
         <v>130</v>
       </c>
       <c r="E87" t="s">
+        <v>233</v>
+      </c>
+      <c r="F87" t="s">
         <v>234</v>
-      </c>
-      <c r="F87" t="s">
-        <v>235</v>
       </c>
       <c r="H87" t="s">
         <v>187</v>
@@ -3527,10 +3527,10 @@
         <v>116</v>
       </c>
       <c r="E88" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F88" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H88" t="s">
         <v>187</v>
@@ -3545,13 +3545,13 @@
         <v>125</v>
       </c>
       <c r="D89" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E89" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F89" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H89" t="s">
         <v>187</v>
@@ -3564,13 +3564,13 @@
       <c r="B90" s="13"/>
       <c r="C90" s="12"/>
       <c r="D90" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E90" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F90" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H90" t="s">
         <v>187</v>
@@ -3586,10 +3586,10 @@
         <v>126</v>
       </c>
       <c r="E91" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F91" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H91" t="s">
         <v>187</v>
@@ -3605,10 +3605,10 @@
         <v>141</v>
       </c>
       <c r="E92" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F92" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H92" t="s">
         <v>182</v>
@@ -3628,10 +3628,10 @@
         <v>129</v>
       </c>
       <c r="E93" t="s">
+        <v>239</v>
+      </c>
+      <c r="F93" t="s">
         <v>240</v>
-      </c>
-      <c r="F93" t="s">
-        <v>241</v>
       </c>
       <c r="H93" t="s">
         <v>187</v>
@@ -3647,7 +3647,7 @@
         <v>128</v>
       </c>
       <c r="E94" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F94" t="s">
         <v>127</v>
@@ -3666,7 +3666,7 @@
         <v>130</v>
       </c>
       <c r="E95" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F95" t="s">
         <v>127</v>
@@ -3689,10 +3689,10 @@
         <v>140</v>
       </c>
       <c r="E96" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F96" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H96" t="s">
         <v>182</v>
@@ -3710,10 +3710,10 @@
         <v>147</v>
       </c>
       <c r="E97" t="s">
+        <v>242</v>
+      </c>
+      <c r="F97" t="s">
         <v>243</v>
-      </c>
-      <c r="F97" t="s">
-        <v>244</v>
       </c>
       <c r="H97" t="s">
         <v>182</v>
@@ -3731,10 +3731,10 @@
         <v>138</v>
       </c>
       <c r="E98" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F98" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H98" t="s">
         <v>182</v>
@@ -3752,10 +3752,10 @@
         <v>143</v>
       </c>
       <c r="E99" t="s">
+        <v>245</v>
+      </c>
+      <c r="F99" t="s">
         <v>246</v>
-      </c>
-      <c r="F99" t="s">
-        <v>247</v>
       </c>
       <c r="H99" t="s">
         <v>182</v>
@@ -3773,10 +3773,10 @@
         <v>145</v>
       </c>
       <c r="E100" t="s">
+        <v>247</v>
+      </c>
+      <c r="F100" t="s">
         <v>248</v>
-      </c>
-      <c r="F100" t="s">
-        <v>249</v>
       </c>
       <c r="H100" t="s">
         <v>182</v>
@@ -3794,10 +3794,10 @@
         <v>19</v>
       </c>
       <c r="E101" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F101" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H101" t="s">
         <v>187</v>
@@ -3813,10 +3813,10 @@
         <v>149</v>
       </c>
       <c r="E102" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F102" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H102" t="s">
         <v>182</v>
@@ -3832,10 +3832,10 @@
         <v>150</v>
       </c>
       <c r="E103" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F103" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H103" t="s">
         <v>187</v>
@@ -3853,10 +3853,10 @@
         <v>19</v>
       </c>
       <c r="E104" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F104" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H104" t="s">
         <v>187</v>
@@ -3872,10 +3872,10 @@
         <v>149</v>
       </c>
       <c r="E105" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F105" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H105" t="s">
         <v>182</v>
@@ -3891,10 +3891,10 @@
         <v>150</v>
       </c>
       <c r="E106" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F106" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H106" t="s">
         <v>187</v>
@@ -3912,10 +3912,10 @@
         <v>19</v>
       </c>
       <c r="E107" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F107" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H107" t="s">
         <v>187</v>
@@ -3931,10 +3931,10 @@
         <v>149</v>
       </c>
       <c r="E108" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F108" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H108" t="s">
         <v>182</v>
@@ -3950,10 +3950,10 @@
         <v>150</v>
       </c>
       <c r="E109" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F109" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H109" t="s">
         <v>181</v>
@@ -3971,10 +3971,10 @@
         <v>152</v>
       </c>
       <c r="E110" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F110" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H110" t="s">
         <v>181</v>
@@ -3990,10 +3990,10 @@
         <v>153</v>
       </c>
       <c r="E111" t="s">
+        <v>255</v>
+      </c>
+      <c r="F111" t="s">
         <v>256</v>
-      </c>
-      <c r="F111" t="s">
-        <v>257</v>
       </c>
       <c r="H111" t="s">
         <v>182</v>
@@ -4006,13 +4006,13 @@
       <c r="B112" s="13"/>
       <c r="C112" s="12"/>
       <c r="D112" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E112" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F112" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H112" t="s">
         <v>187</v>
@@ -4025,13 +4025,13 @@
       <c r="B113" s="13"/>
       <c r="C113" s="12"/>
       <c r="D113" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E113" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F113" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H113" t="s">
         <v>182</v>
@@ -4044,13 +4044,13 @@
       <c r="B114" s="13"/>
       <c r="C114" s="12"/>
       <c r="D114" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E114" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F114" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H114" t="s">
         <v>181</v>
@@ -4070,10 +4070,10 @@
         <v>156</v>
       </c>
       <c r="E115" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F115" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H115" t="s">
         <v>182</v>
@@ -4091,10 +4091,10 @@
         <v>160</v>
       </c>
       <c r="E116" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F116" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H116" t="s">
         <v>182</v>
@@ -4114,10 +4114,10 @@
         <v>163</v>
       </c>
       <c r="E117" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F117" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H117" t="s">
         <v>182</v>
@@ -4137,10 +4137,10 @@
         <v>166</v>
       </c>
       <c r="E118" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F118" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H118" t="s">
         <v>187</v>
@@ -4156,10 +4156,10 @@
         <v>167</v>
       </c>
       <c r="E119" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F119" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H119" t="s">
         <v>182</v>
@@ -4175,10 +4175,10 @@
         <v>168</v>
       </c>
       <c r="E120" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F120" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H120" t="s">
         <v>181</v>
@@ -4196,10 +4196,10 @@
         <v>170</v>
       </c>
       <c r="E121" t="s">
+        <v>261</v>
+      </c>
+      <c r="F121" t="s">
         <v>262</v>
-      </c>
-      <c r="F121" t="s">
-        <v>263</v>
       </c>
       <c r="H121" t="s">
         <v>182</v>
@@ -4215,10 +4215,10 @@
         <v>171</v>
       </c>
       <c r="E122" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F122" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H122" t="s">
         <v>187</v>
@@ -4234,10 +4234,10 @@
         <v>174</v>
       </c>
       <c r="E123" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F123" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H123" t="s">
         <v>187</v>
@@ -4248,19 +4248,19 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
+        <v>268</v>
+      </c>
+      <c r="C124" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="C124" s="11" t="s">
+      <c r="D124" t="s">
         <v>270</v>
       </c>
-      <c r="D124" t="s">
+      <c r="E124" t="s">
+        <v>299</v>
+      </c>
+      <c r="F124" t="s">
         <v>271</v>
-      </c>
-      <c r="E124" t="s">
-        <v>300</v>
-      </c>
-      <c r="F124" t="s">
-        <v>272</v>
       </c>
       <c r="H124" t="s">
         <v>187</v>

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C28C97-DEC6-49D2-B52D-26ED603ABA57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06C39CA-AA81-4AF8-B88A-720A634C2277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{F425FBA8-E65A-4F03-9270-551F3EA7C4F5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="314">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -782,10 +782,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>合适</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>使用手机登录账号查看活动界面</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1154,18 +1150,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>查看活动背景</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>查看活动UI</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>查看活动文本</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>重复登录查看登录任务</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1266,6 +1250,22 @@
   </si>
   <si>
     <t>正常跳转至活动页面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入活动中心，点击周末冲分活动进入界面查看</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>背景图显示正确</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动UI显示正确</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动文本显示正确</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1773,7 +1773,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>176</v>
@@ -1794,7 +1794,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>177</v>
@@ -1815,7 +1815,7 @@
         <v>13</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>177</v>
@@ -1838,7 +1838,7 @@
         <v>15</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>178</v>
@@ -1859,7 +1859,7 @@
         <v>16</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>179</v>
@@ -1880,7 +1880,7 @@
         <v>17</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>179</v>
@@ -1926,7 +1926,7 @@
         <v>19</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>184</v>
@@ -1936,7 +1936,7 @@
         <v>181</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1949,7 +1949,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>185</v>
@@ -1970,7 +1970,7 @@
         <v>21</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>185</v>
@@ -1993,7 +1993,7 @@
         <v>46</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>186</v>
@@ -2084,10 +2084,10 @@
         <v>27</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>177</v>
@@ -2112,10 +2112,10 @@
         <v>11</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4" t="s">
@@ -2133,10 +2133,10 @@
         <v>12</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
@@ -2154,10 +2154,10 @@
         <v>13</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
@@ -2166,27 +2166,31 @@
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
+      <c r="A20" s="4">
+        <v>19</v>
+      </c>
       <c r="B20" s="5"/>
       <c r="C20" s="7" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
+      <c r="H20" s="4" t="s">
+        <v>187</v>
+      </c>
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="7" t="s">
@@ -2196,10 +2200,10 @@
         <v>39</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
@@ -2209,7 +2213,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="7" t="s">
@@ -2219,10 +2223,10 @@
         <v>37</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4" t="s">
@@ -2232,7 +2236,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="7" t="s">
@@ -2242,10 +2246,10 @@
         <v>36</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4" t="s">
@@ -2255,7 +2259,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="6" t="s">
@@ -2265,10 +2269,10 @@
         <v>19</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4" t="s">
@@ -2278,7 +2282,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="6"/>
@@ -2286,10 +2290,10 @@
         <v>20</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
@@ -2299,7 +2303,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="6"/>
@@ -2307,10 +2311,10 @@
         <v>21</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4" t="s">
@@ -2320,20 +2324,20 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="9" t="s">
         <v>45</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4" t="s">
@@ -2343,15 +2347,15 @@
     </row>
     <row r="28" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="9"/>
       <c r="D28" s="10" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>190</v>
@@ -2364,7 +2368,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>40</v>
@@ -2376,10 +2380,10 @@
         <v>42</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>191</v>
+        <v>311</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="4" t="s">
@@ -2389,7 +2393,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="7" t="s">
@@ -2399,10 +2403,10 @@
         <v>42</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>191</v>
+        <v>312</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4" t="s">
@@ -2412,7 +2416,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="7" t="s">
@@ -2422,10 +2426,10 @@
         <v>42</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>191</v>
+        <v>313</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="4" t="s">
@@ -2435,7 +2439,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="6" t="s">
@@ -2445,10 +2449,10 @@
         <v>48</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4" t="s">
@@ -2458,7 +2462,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="6"/>
@@ -2466,10 +2470,10 @@
         <v>49</v>
       </c>
       <c r="E33" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="F33" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>195</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="4" t="s">
@@ -2479,7 +2483,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="6"/>
@@ -2487,10 +2491,10 @@
         <v>50</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4" t="s">
@@ -2500,7 +2504,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="6" t="s">
@@ -2510,10 +2514,10 @@
         <v>51</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4" t="s">
@@ -2523,7 +2527,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="6"/>
@@ -2531,10 +2535,10 @@
         <v>52</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="4" t="s">
@@ -2544,7 +2548,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>54</v>
@@ -2556,10 +2560,10 @@
         <v>57</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4" t="s">
@@ -2569,7 +2573,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="6"/>
@@ -2577,10 +2581,10 @@
         <v>58</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4" t="s">
@@ -2590,7 +2594,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="6"/>
@@ -2598,10 +2602,10 @@
         <v>58</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4" t="s">
@@ -2611,7 +2615,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="6" t="s">
@@ -2621,22 +2625,22 @@
         <v>60</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4" t="s">
         <v>181</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="6"/>
@@ -2644,10 +2648,10 @@
         <v>61</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4" t="s">
@@ -2657,7 +2661,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="9" t="s">
@@ -2667,10 +2671,10 @@
         <v>65</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4" t="s">
@@ -2680,7 +2684,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="9"/>
@@ -2688,10 +2692,10 @@
         <v>62</v>
       </c>
       <c r="E43" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="F43" s="4" t="s">
         <v>205</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>206</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4" t="s">
@@ -2701,7 +2705,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="9"/>
@@ -2709,10 +2713,10 @@
         <v>63</v>
       </c>
       <c r="E44" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="F44" s="4" t="s">
         <v>205</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>206</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4" t="s">
@@ -2722,7 +2726,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="9"/>
@@ -2730,10 +2734,10 @@
         <v>64</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4" t="s">
@@ -2743,7 +2747,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="9"/>
@@ -2751,10 +2755,10 @@
         <v>66</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4" t="s">
@@ -2764,18 +2768,18 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="9"/>
       <c r="D47" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4" t="s">
@@ -2785,7 +2789,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="9" t="s">
@@ -2795,10 +2799,10 @@
         <v>77</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4" t="s">
@@ -2808,7 +2812,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="9"/>
@@ -2816,10 +2820,10 @@
         <v>78</v>
       </c>
       <c r="E49" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="F49" s="4" t="s">
         <v>205</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>206</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4" t="s">
@@ -2829,7 +2833,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="9"/>
@@ -2837,10 +2841,10 @@
         <v>79</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="4" t="s">
@@ -2850,7 +2854,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="9"/>
@@ -2858,10 +2862,10 @@
         <v>173</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4" t="s">
@@ -2871,7 +2875,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>68</v>
@@ -2883,10 +2887,10 @@
         <v>69</v>
       </c>
       <c r="E52" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F52" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4" t="s">
@@ -2896,7 +2900,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="6"/>
@@ -2904,10 +2908,10 @@
         <v>72</v>
       </c>
       <c r="E53" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="F53" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>214</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4" t="s">
@@ -2917,7 +2921,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="6"/>
@@ -2925,10 +2929,10 @@
         <v>73</v>
       </c>
       <c r="E54" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="F54" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>214</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="4" t="s">
@@ -2938,7 +2942,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="6" t="s">
@@ -2948,10 +2952,10 @@
         <v>80</v>
       </c>
       <c r="E55" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F55" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="4" t="s">
@@ -2961,7 +2965,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="6"/>
@@ -2969,10 +2973,10 @@
         <v>76</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G56" s="4"/>
       <c r="H56" s="4" t="s">
@@ -2982,7 +2986,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="6"/>
@@ -2990,10 +2994,10 @@
         <v>81</v>
       </c>
       <c r="E57" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F57" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="G57" s="4"/>
       <c r="H57" s="4" t="s">
@@ -3003,7 +3007,7 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="6"/>
@@ -3011,10 +3015,10 @@
         <v>82</v>
       </c>
       <c r="E58" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F58" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="4" t="s">
@@ -3024,7 +3028,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -3032,10 +3036,10 @@
         <v>83</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="4" t="s">
@@ -3045,7 +3049,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -3053,10 +3057,10 @@
         <v>71</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="4" t="s">
@@ -3066,7 +3070,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -3074,10 +3078,10 @@
         <v>86</v>
       </c>
       <c r="E61" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="G61" s="4"/>
       <c r="H61" s="4" t="s">
@@ -3087,7 +3091,7 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="6" t="s">
@@ -3097,10 +3101,10 @@
         <v>85</v>
       </c>
       <c r="E62" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4" t="s">
@@ -3110,7 +3114,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="6"/>
@@ -3118,10 +3122,10 @@
         <v>84</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4" t="s">
@@ -3131,7 +3135,7 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>93</v>
@@ -3143,10 +3147,10 @@
         <v>95</v>
       </c>
       <c r="E64" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="F64" s="4" t="s">
         <v>218</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>219</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="4" t="s">
@@ -3156,7 +3160,7 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="6"/>
@@ -3164,10 +3168,10 @@
         <v>96</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G65" s="4"/>
       <c r="H65" s="4" t="s">
@@ -3177,7 +3181,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>87</v>
@@ -3189,10 +3193,10 @@
         <v>88</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="4" t="s">
@@ -3202,7 +3206,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B67" s="5"/>
       <c r="C67" s="6"/>
@@ -3210,10 +3214,10 @@
         <v>89</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="4" t="s">
@@ -3223,7 +3227,7 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B68" s="5"/>
       <c r="C68" s="6"/>
@@ -3231,10 +3235,10 @@
         <v>90</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G68" s="4"/>
       <c r="H68" s="4" t="s">
@@ -3244,7 +3248,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="7" t="s">
@@ -3254,10 +3258,10 @@
         <v>92</v>
       </c>
       <c r="E69" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="F69" s="8" t="s">
         <v>223</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>224</v>
       </c>
       <c r="G69" s="4"/>
       <c r="H69" s="4" t="s">
@@ -3267,10 +3271,10 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>97</v>
@@ -3279,10 +3283,10 @@
         <v>98</v>
       </c>
       <c r="E70" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="F70" s="8" t="s">
         <v>225</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>226</v>
       </c>
       <c r="G70" s="4"/>
       <c r="H70" s="4" t="s">
@@ -3292,7 +3296,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B71" s="5"/>
       <c r="C71" s="6"/>
@@ -3300,10 +3304,10 @@
         <v>99</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G71" s="4"/>
       <c r="H71" s="4" t="s">
@@ -3313,7 +3317,7 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B72" s="5"/>
       <c r="C72" s="6"/>
@@ -3321,10 +3325,10 @@
         <v>100</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G72" s="4"/>
       <c r="H72" s="4" t="s">
@@ -3334,7 +3338,7 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="6" t="s">
@@ -3357,7 +3361,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="6"/>
@@ -3378,7 +3382,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B75" s="5"/>
       <c r="C75" s="6"/>
@@ -3399,22 +3403,22 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>111</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>112</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="4" t="s">
@@ -3424,7 +3428,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B77" s="5"/>
       <c r="C77" s="6"/>
@@ -3432,10 +3436,10 @@
         <v>113</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G77" s="4"/>
       <c r="H77" s="4" t="s">
@@ -3445,7 +3449,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B78" s="5"/>
       <c r="C78" s="6"/>
@@ -3453,10 +3457,10 @@
         <v>114</v>
       </c>
       <c r="E78" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="F78" s="4" t="s">
         <v>230</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>231</v>
       </c>
       <c r="G78" s="4"/>
       <c r="H78" s="4" t="s">
@@ -3466,7 +3470,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B79" s="5"/>
       <c r="C79" s="9" t="s">
@@ -3476,7 +3480,7 @@
         <v>124</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>118</v>
@@ -3489,7 +3493,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B80" s="5"/>
       <c r="C80" s="9"/>
@@ -3497,7 +3501,7 @@
         <v>124</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>119</v>
@@ -3510,7 +3514,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B81" s="5"/>
       <c r="C81" s="9" t="s">
@@ -3520,7 +3524,7 @@
         <v>133</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>189</v>
@@ -3533,7 +3537,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B82" s="5"/>
       <c r="C82" s="9"/>
@@ -3541,7 +3545,7 @@
         <v>134</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>189</v>
@@ -3554,7 +3558,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B83" s="5"/>
       <c r="C83" s="9"/>
@@ -3562,7 +3566,7 @@
         <v>135</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>189</v>
@@ -3575,7 +3579,7 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B84" s="5"/>
       <c r="C84" s="9" t="s">
@@ -3585,7 +3589,7 @@
         <v>124</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>121</v>
@@ -3598,7 +3602,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B85" s="5"/>
       <c r="C85" s="9"/>
@@ -3606,7 +3610,7 @@
         <v>124</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>122</v>
@@ -3619,7 +3623,7 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B86" s="5"/>
       <c r="C86" s="9" t="s">
@@ -3629,10 +3633,10 @@
         <v>129</v>
       </c>
       <c r="E86" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="F86" s="4" t="s">
         <v>232</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>233</v>
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="4" t="s">
@@ -3642,7 +3646,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B87" s="5"/>
       <c r="C87" s="9"/>
@@ -3650,10 +3654,10 @@
         <v>128</v>
       </c>
       <c r="E87" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="F87" s="4" t="s">
         <v>232</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>233</v>
       </c>
       <c r="G87" s="4"/>
       <c r="H87" s="4" t="s">
@@ -3663,7 +3667,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B88" s="5"/>
       <c r="C88" s="9"/>
@@ -3671,10 +3675,10 @@
         <v>130</v>
       </c>
       <c r="E88" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="F88" s="4" t="s">
         <v>232</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>233</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4" t="s">
@@ -3684,7 +3688,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B89" s="5"/>
       <c r="C89" s="4" t="s">
@@ -3694,10 +3698,10 @@
         <v>116</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="4" t="s">
@@ -3707,20 +3711,20 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B90" s="5"/>
       <c r="C90" s="9" t="s">
         <v>125</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="4" t="s">
@@ -3730,18 +3734,18 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B91" s="5"/>
       <c r="C91" s="9"/>
       <c r="D91" s="4" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="4" t="s">
@@ -3751,7 +3755,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B92" s="5"/>
       <c r="C92" s="9"/>
@@ -3759,10 +3763,10 @@
         <v>126</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="4" t="s">
@@ -3772,7 +3776,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B93" s="5"/>
       <c r="C93" s="9"/>
@@ -3780,10 +3784,10 @@
         <v>141</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="4" t="s">
@@ -3793,7 +3797,7 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>127</v>
@@ -3805,10 +3809,10 @@
         <v>129</v>
       </c>
       <c r="E94" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F94" s="4" t="s">
         <v>238</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>239</v>
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="4" t="s">
@@ -3818,7 +3822,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B95" s="5"/>
       <c r="C95" s="9"/>
@@ -3826,7 +3830,7 @@
         <v>128</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>127</v>
@@ -3839,7 +3843,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B96" s="5"/>
       <c r="C96" s="9"/>
@@ -3847,7 +3851,7 @@
         <v>130</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>127</v>
@@ -3860,7 +3864,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>136</v>
@@ -3872,10 +3876,10 @@
         <v>140</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4" t="s">
@@ -3885,7 +3889,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B98" s="5"/>
       <c r="C98" s="11" t="s">
@@ -3895,10 +3899,10 @@
         <v>147</v>
       </c>
       <c r="E98" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F98" s="4" t="s">
         <v>241</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>242</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4" t="s">
@@ -3908,7 +3912,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B99" s="5"/>
       <c r="C99" s="4" t="s">
@@ -3918,10 +3922,10 @@
         <v>138</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G99" s="4"/>
       <c r="H99" s="4" t="s">
@@ -3931,7 +3935,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B100" s="5"/>
       <c r="C100" s="4" t="s">
@@ -3941,10 +3945,10 @@
         <v>143</v>
       </c>
       <c r="E100" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F100" s="4" t="s">
         <v>244</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>245</v>
       </c>
       <c r="G100" s="4"/>
       <c r="H100" s="4" t="s">
@@ -3954,7 +3958,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B101" s="5"/>
       <c r="C101" s="4" t="s">
@@ -3964,10 +3968,10 @@
         <v>145</v>
       </c>
       <c r="E101" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="F101" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="F101" s="4" t="s">
-        <v>247</v>
       </c>
       <c r="G101" s="4"/>
       <c r="H101" s="4" t="s">
@@ -3977,7 +3981,7 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B102" s="5"/>
       <c r="C102" s="9" t="s">
@@ -3987,10 +3991,10 @@
         <v>19</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="4" t="s">
@@ -4000,7 +4004,7 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B103" s="5"/>
       <c r="C103" s="9"/>
@@ -4008,10 +4012,10 @@
         <v>149</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="4" t="s">
@@ -4021,7 +4025,7 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B104" s="5"/>
       <c r="C104" s="9"/>
@@ -4029,10 +4033,10 @@
         <v>150</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4" t="s">
@@ -4042,7 +4046,7 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B105" s="5"/>
       <c r="C105" s="9" t="s">
@@ -4052,10 +4056,10 @@
         <v>19</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G105" s="4"/>
       <c r="H105" s="4" t="s">
@@ -4065,7 +4069,7 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B106" s="5"/>
       <c r="C106" s="9"/>
@@ -4073,10 +4077,10 @@
         <v>149</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G106" s="4"/>
       <c r="H106" s="4" t="s">
@@ -4086,7 +4090,7 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B107" s="5"/>
       <c r="C107" s="9"/>
@@ -4094,10 +4098,10 @@
         <v>150</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G107" s="4"/>
       <c r="H107" s="4" t="s">
@@ -4107,7 +4111,7 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B108" s="5"/>
       <c r="C108" s="9" t="s">
@@ -4117,10 +4121,10 @@
         <v>19</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G108" s="4"/>
       <c r="H108" s="4" t="s">
@@ -4130,7 +4134,7 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B109" s="5"/>
       <c r="C109" s="9"/>
@@ -4138,10 +4142,10 @@
         <v>149</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G109" s="4"/>
       <c r="H109" s="4" t="s">
@@ -4151,7 +4155,7 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B110" s="5"/>
       <c r="C110" s="9"/>
@@ -4159,10 +4163,10 @@
         <v>150</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G110" s="4"/>
       <c r="H110" s="4" t="s">
@@ -4172,7 +4176,7 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B111" s="5"/>
       <c r="C111" s="9" t="s">
@@ -4182,10 +4186,10 @@
         <v>152</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="4" t="s">
@@ -4195,7 +4199,7 @@
     </row>
     <row r="112" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B112" s="5"/>
       <c r="C112" s="9"/>
@@ -4203,10 +4207,10 @@
         <v>153</v>
       </c>
       <c r="E112" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="F112" s="4" t="s">
         <v>254</v>
-      </c>
-      <c r="F112" s="4" t="s">
-        <v>255</v>
       </c>
       <c r="G112" s="4"/>
       <c r="H112" s="4" t="s">
@@ -4216,18 +4220,18 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B113" s="5"/>
       <c r="C113" s="9"/>
       <c r="D113" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G113" s="4"/>
       <c r="H113" s="4" t="s">
@@ -4237,18 +4241,18 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="4">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B114" s="5"/>
       <c r="C114" s="9"/>
       <c r="D114" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G114" s="4"/>
       <c r="H114" s="4" t="s">
@@ -4258,18 +4262,18 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B115" s="5"/>
       <c r="C115" s="9"/>
       <c r="D115" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G115" s="4"/>
       <c r="H115" s="4" t="s">
@@ -4279,7 +4283,7 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>154</v>
@@ -4291,10 +4295,10 @@
         <v>156</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G116" s="4"/>
       <c r="H116" s="4" t="s">
@@ -4304,7 +4308,7 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B117" s="5"/>
       <c r="C117" s="4" t="s">
@@ -4314,10 +4318,10 @@
         <v>160</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G117" s="4"/>
       <c r="H117" s="4" t="s">
@@ -4327,7 +4331,7 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="4">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B118" s="12" t="s">
         <v>162</v>
@@ -4339,10 +4343,10 @@
         <v>163</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G118" s="4"/>
       <c r="H118" s="4" t="s">
@@ -4352,7 +4356,7 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>164</v>
@@ -4364,10 +4368,10 @@
         <v>166</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G119" s="4"/>
       <c r="H119" s="4" t="s">
@@ -4377,7 +4381,7 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B120" s="5"/>
       <c r="C120" s="9"/>
@@ -4385,10 +4389,10 @@
         <v>167</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="4" t="s">
@@ -4398,7 +4402,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B121" s="5"/>
       <c r="C121" s="9"/>
@@ -4406,10 +4410,10 @@
         <v>168</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G121" s="4"/>
       <c r="H121" s="4" t="s">
@@ -4419,7 +4423,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B122" s="5"/>
       <c r="C122" s="9" t="s">
@@ -4429,10 +4433,10 @@
         <v>170</v>
       </c>
       <c r="E122" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="F122" s="4" t="s">
         <v>260</v>
-      </c>
-      <c r="F122" s="4" t="s">
-        <v>261</v>
       </c>
       <c r="G122" s="4"/>
       <c r="H122" s="4" t="s">
@@ -4442,7 +4446,7 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B123" s="5"/>
       <c r="C123" s="9"/>
@@ -4450,10 +4454,10 @@
         <v>171</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G123" s="4"/>
       <c r="H123" s="4" t="s">
@@ -4463,7 +4467,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="4">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B124" s="5"/>
       <c r="C124" s="9"/>
@@ -4471,10 +4475,10 @@
         <v>174</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G124" s="4"/>
       <c r="H124" s="4" t="s">
@@ -4484,22 +4488,22 @@
     </row>
     <row r="125" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
-        <v>123</v>
-      </c>
-      <c r="B125" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B125" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="C125" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="C125" s="13" t="s">
+      <c r="D125" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="D125" s="4" t="s">
+      <c r="E125" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="F125" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="E125" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="F125" s="4" t="s">
-        <v>270</v>
       </c>
       <c r="G125" s="4"/>
       <c r="H125" s="4" t="s">

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06C39CA-AA81-4AF8-B88A-720A634C2277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6EEC539-3635-43DD-9FAE-F315C926FEF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{F425FBA8-E65A-4F03-9270-551F3EA7C4F5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="340">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1266,6 +1267,110 @@
   </si>
   <si>
     <t>活动文本显示正确</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动任务测试</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计完成6场普通/排位对局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计登录未完成任务状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间未登录游戏</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>后台查看任务状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务状态为未完成</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动任务</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计任务-未完成任务状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>后天查看任务状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计任务-已完成任务状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间已登录游戏</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入活动后查看任务状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务状态为“领取”</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入活动领取奖励</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务状态为“已领取”</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计任务进度展示</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入活动查看任务进度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务进度变为1/1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试任务刷新时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改服务器时间到xxxxxx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入活动查看任务状态刷新</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否刷新？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动登录任务刷新</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计完成6场普通/排位对局-未完成任务状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计完成6场普通/排位对局-已完成任务状态</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1273,7 +1378,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1318,6 +1423,22 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1333,7 +1454,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1356,13 +1477,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1373,6 +1505,24 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
@@ -1404,6 +1554,21 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1719,7 +1884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DF7E13A-4D63-4E82-9598-D598C8858D86}">
-  <dimension ref="A1:I125"/>
+  <dimension ref="A1:I133"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
@@ -1760,2788 +1925,2926 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
+      <c r="G2" s="10"/>
+      <c r="H2" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I2" s="4"/>
+      <c r="I2" s="10"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="11"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I3" s="4"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I3" s="10"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="A4" s="10">
         <v>3</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="4" t="s">
+      <c r="B4" s="11"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
+      <c r="G4" s="10"/>
+      <c r="H4" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I4" s="4"/>
+      <c r="I4" s="10"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="A5" s="10">
         <v>4</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="6" t="s">
+      <c r="B5" s="11"/>
+      <c r="C5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4" t="s">
+      <c r="G5" s="10"/>
+      <c r="H5" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I5" s="4"/>
+      <c r="I5" s="10"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+      <c r="A6" s="10">
         <v>5</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="4" t="s">
+      <c r="B6" s="11"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I6" s="4"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I6" s="10"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+      <c r="A7" s="10">
         <v>6</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="4" t="s">
+      <c r="B7" s="11"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4" t="s">
+      <c r="G7" s="10"/>
+      <c r="H7" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I7" s="4"/>
+      <c r="I7" s="10"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+      <c r="A8" s="10">
         <v>7</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="7" t="s">
+      <c r="B8" s="11"/>
+      <c r="C8" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4" t="s">
+      <c r="G8" s="10"/>
+      <c r="H8" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="I8" s="4"/>
+      <c r="I8" s="10"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
+      <c r="A9" s="10">
         <v>8</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="6" t="s">
+      <c r="B9" s="11"/>
+      <c r="C9" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4" t="s">
+      <c r="G9" s="10"/>
+      <c r="H9" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="10" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
+      <c r="A10" s="10">
         <v>9</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="4" t="s">
+      <c r="B10" s="11"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I10" s="4"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I10" s="10"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
+      <c r="A11" s="10">
         <v>10</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="4" t="s">
+      <c r="B11" s="11"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4" t="s">
+      <c r="G11" s="10"/>
+      <c r="H11" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I11" s="4"/>
+      <c r="I11" s="10"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
+      <c r="A12" s="10">
         <v>11</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="7" t="s">
+      <c r="B12" s="11"/>
+      <c r="C12" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4" t="s">
+      <c r="G12" s="10"/>
+      <c r="H12" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I12" s="4"/>
+      <c r="I12" s="10"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
+      <c r="A13" s="10">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I13" s="4"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I13" s="10"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
+      <c r="A14" s="10">
         <v>13</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="7" t="s">
+      <c r="B14" s="11"/>
+      <c r="C14" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I14" s="4"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I14" s="10"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
+      <c r="A15" s="10">
         <v>14</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="7" t="s">
+      <c r="B15" s="11"/>
+      <c r="C15" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4" t="s">
+      <c r="G15" s="10"/>
+      <c r="H15" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I15" s="4"/>
+      <c r="I15" s="10"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
+      <c r="A16" s="10">
         <v>15</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="7" t="s">
+      <c r="B16" s="11"/>
+      <c r="C16" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4" t="s">
+      <c r="G16" s="10"/>
+      <c r="H16" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I16" s="4"/>
+      <c r="I16" s="10"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
+      <c r="A17" s="10">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="14" t="s">
         <v>274</v>
       </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4" t="s">
+      <c r="G17" s="10"/>
+      <c r="H17" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I17" s="4"/>
+      <c r="I17" s="10"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
+      <c r="A18" s="10">
         <v>17</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="4" t="s">
+      <c r="B18" s="11"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I18" s="4"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I18" s="10"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
+      <c r="A19" s="10">
         <v>18</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="4" t="s">
+      <c r="B19" s="11"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4" t="s">
+      <c r="G19" s="10"/>
+      <c r="H19" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I19" s="4"/>
+      <c r="I19" s="10"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
+      <c r="A20" s="10">
         <v>19</v>
       </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="7" t="s">
+      <c r="B20" s="11"/>
+      <c r="C20" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4" t="s">
+      <c r="G20" s="10"/>
+      <c r="H20" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I20" s="4"/>
+      <c r="I20" s="10"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
+      <c r="A21" s="10">
         <v>20</v>
       </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="7" t="s">
+      <c r="B21" s="11"/>
+      <c r="C21" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="14" t="s">
         <v>307</v>
       </c>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4" t="s">
+      <c r="G21" s="10"/>
+      <c r="H21" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="I21" s="4"/>
+      <c r="I21" s="10"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
+      <c r="A22" s="10">
         <v>21</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="7" t="s">
+      <c r="B22" s="11"/>
+      <c r="C22" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="14" t="s">
         <v>308</v>
       </c>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4" t="s">
+      <c r="G22" s="10"/>
+      <c r="H22" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="I22" s="4"/>
+      <c r="I22" s="10"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
+      <c r="A23" s="10">
         <v>22</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="7" t="s">
+      <c r="B23" s="11"/>
+      <c r="C23" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I23" s="4"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I23" s="10"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
+      <c r="A24" s="10">
         <v>23</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="6" t="s">
+      <c r="B24" s="11"/>
+      <c r="C24" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4" t="s">
+      <c r="G24" s="10"/>
+      <c r="H24" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I24" s="4"/>
+      <c r="I24" s="10"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
+      <c r="A25" s="10">
         <v>24</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="4" t="s">
+      <c r="B25" s="11"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="14" t="s">
         <v>274</v>
       </c>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I25" s="4"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I25" s="10"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
+      <c r="A26" s="10">
         <v>25</v>
       </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="4" t="s">
+      <c r="B26" s="11"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="14" t="s">
         <v>274</v>
       </c>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4" t="s">
+      <c r="G26" s="10"/>
+      <c r="H26" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I26" s="4"/>
+      <c r="I26" s="10"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
+      <c r="A27" s="10">
         <v>26</v>
       </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="9" t="s">
+      <c r="B27" s="11"/>
+      <c r="C27" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4" t="s">
+      <c r="G27" s="10"/>
+      <c r="H27" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I27" s="4"/>
+      <c r="I27" s="10"/>
     </row>
     <row r="28" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A28" s="4">
+      <c r="A28" s="10">
         <v>27</v>
       </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="10" t="s">
+      <c r="B28" s="11"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="16" t="s">
         <v>298</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4" t="s">
+      <c r="G28" s="10"/>
+      <c r="H28" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I28" s="4"/>
+      <c r="I28" s="10"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="4">
+      <c r="A29" s="10">
         <v>28</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="F29" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4" t="s">
+      <c r="G29" s="10"/>
+      <c r="H29" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="I29" s="4"/>
+      <c r="I29" s="10"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="4">
+      <c r="A30" s="10">
         <v>29</v>
       </c>
-      <c r="B30" s="5"/>
-      <c r="C30" s="7" t="s">
+      <c r="B30" s="11"/>
+      <c r="C30" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="F30" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4" t="s">
+      <c r="G30" s="10"/>
+      <c r="H30" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="I30" s="4"/>
+      <c r="I30" s="10"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="4">
+      <c r="A31" s="10">
         <v>30</v>
       </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="7" t="s">
+      <c r="B31" s="11"/>
+      <c r="C31" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="F31" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4" t="s">
+      <c r="G31" s="10"/>
+      <c r="H31" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="I31" s="4"/>
+      <c r="I31" s="10"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="4">
+      <c r="A32" s="10">
         <v>31</v>
       </c>
-      <c r="B32" s="5"/>
-      <c r="C32" s="6" t="s">
+      <c r="B32" s="11"/>
+      <c r="C32" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E32" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="F32" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4" t="s">
+      <c r="G32" s="10"/>
+      <c r="H32" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I32" s="4"/>
+      <c r="I32" s="10"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
+      <c r="A33" s="10">
         <v>32</v>
       </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="4" t="s">
+      <c r="B33" s="11"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="F33" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4" t="s">
+      <c r="G33" s="10"/>
+      <c r="H33" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I33" s="4"/>
+      <c r="I33" s="10"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="4">
+      <c r="A34" s="10">
         <v>33</v>
       </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="4" t="s">
+      <c r="B34" s="11"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4" t="s">
+      <c r="G34" s="10"/>
+      <c r="H34" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I34" s="4"/>
+      <c r="I34" s="10"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="4">
+      <c r="A35" s="10">
         <v>34</v>
       </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="6" t="s">
+      <c r="B35" s="11"/>
+      <c r="C35" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="F35" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4" t="s">
+      <c r="G35" s="10"/>
+      <c r="H35" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I35" s="4"/>
+      <c r="I35" s="10"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="4">
+      <c r="A36" s="10">
         <v>35</v>
       </c>
-      <c r="B36" s="5"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="4" t="s">
+      <c r="B36" s="11"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="E36" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="F36" s="8" t="s">
+      <c r="F36" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4" t="s">
+      <c r="G36" s="10"/>
+      <c r="H36" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I36" s="4"/>
+      <c r="I36" s="10"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="4">
+      <c r="A37" s="10"/>
+      <c r="B37" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="D37" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="E37" s="24" t="s">
+        <v>322</v>
+      </c>
+      <c r="F37" s="24" t="s">
+        <v>319</v>
+      </c>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="10"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="D38" s="24" t="s">
+        <v>324</v>
+      </c>
+      <c r="E38" s="24" t="s">
+        <v>325</v>
+      </c>
+      <c r="F38" s="24" t="s">
+        <v>326</v>
+      </c>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="10"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="D39" s="24" t="s">
+        <v>324</v>
+      </c>
+      <c r="E39" s="24" t="s">
+        <v>327</v>
+      </c>
+      <c r="F39" s="24" t="s">
+        <v>328</v>
+      </c>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="10"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="D40" s="24" t="s">
+        <v>324</v>
+      </c>
+      <c r="E40" s="24" t="s">
+        <v>330</v>
+      </c>
+      <c r="F40" s="24" t="s">
+        <v>331</v>
+      </c>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="10"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D41" s="24" t="s">
+        <v>336</v>
+      </c>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="10"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="10"/>
+      <c r="B43" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="10"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="10"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="10">
         <v>36</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B45" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C45" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D45" t="s">
         <v>57</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E45" t="s">
         <v>197</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F45" t="s">
         <v>201</v>
       </c>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4" t="s">
+      <c r="G45" s="10"/>
+      <c r="H45" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I37" s="4"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="4">
+      <c r="I45" s="10"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="10">
         <v>37</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="4" t="s">
+      <c r="B46" s="9"/>
+      <c r="C46" s="23"/>
+      <c r="D46" t="s">
         <v>58</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E46" t="s">
         <v>199</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F46" t="s">
         <v>201</v>
       </c>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4" t="s">
+      <c r="G46" s="10"/>
+      <c r="H46" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I38" s="4"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="4">
+      <c r="I46" s="10"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="10">
         <v>38</v>
       </c>
-      <c r="B39" s="5"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="4" t="s">
+      <c r="B47" s="9"/>
+      <c r="C47" s="23"/>
+      <c r="D47" t="s">
         <v>58</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E47" t="s">
         <v>200</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F47" t="s">
         <v>198</v>
       </c>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I39" s="4"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="4">
+      <c r="G47" s="10"/>
+      <c r="H47" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I47" s="10"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="10">
         <v>39</v>
       </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="6" t="s">
+      <c r="B48" s="9"/>
+      <c r="C48" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D48" t="s">
         <v>60</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E48" t="s">
         <v>284</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F48" t="s">
         <v>201</v>
       </c>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4" t="s">
+      <c r="G48" s="10"/>
+      <c r="H48" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I40" s="4" t="s">
+      <c r="I48" s="10" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="4">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="10">
         <v>40</v>
       </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="4" t="s">
+      <c r="B49" s="9"/>
+      <c r="C49" s="23"/>
+      <c r="D49" t="s">
         <v>61</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="E49" t="s">
         <v>202</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F49" t="s">
         <v>198</v>
       </c>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4" t="s">
+      <c r="G49" s="10"/>
+      <c r="H49" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I41" s="4"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="4">
+      <c r="I49" s="10"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="10">
         <v>41</v>
       </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="9" t="s">
+      <c r="B50" s="9"/>
+      <c r="C50" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D50" t="s">
         <v>65</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E50" t="s">
         <v>209</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F50" t="s">
         <v>208</v>
       </c>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I42" s="4"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="4">
+      <c r="G50" s="10"/>
+      <c r="H50" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I50" s="10"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="10">
         <v>42</v>
       </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="4" t="s">
+      <c r="B51" s="9"/>
+      <c r="C51" s="8"/>
+      <c r="D51" t="s">
         <v>62</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="E51" t="s">
         <v>204</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F51" t="s">
         <v>205</v>
       </c>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I43" s="4"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="4">
+      <c r="G51" s="10"/>
+      <c r="H51" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I51" s="10"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="10">
         <v>43</v>
       </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="4" t="s">
+      <c r="B52" s="9"/>
+      <c r="C52" s="8"/>
+      <c r="D52" t="s">
         <v>63</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E52" t="s">
         <v>204</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F52" t="s">
         <v>205</v>
       </c>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I44" s="4"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="4">
+      <c r="G52" s="10"/>
+      <c r="H52" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I52" s="10"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="10">
         <v>44</v>
       </c>
-      <c r="B45" s="5"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="4" t="s">
+      <c r="B53" s="9"/>
+      <c r="C53" s="8"/>
+      <c r="D53" t="s">
         <v>64</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E53" t="s">
         <v>203</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F53" t="s">
         <v>201</v>
       </c>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I45" s="4"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="4">
+      <c r="G53" s="10"/>
+      <c r="H53" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I53" s="10"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="10">
         <v>45</v>
       </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="4" t="s">
+      <c r="B54" s="9"/>
+      <c r="C54" s="8"/>
+      <c r="D54" t="s">
         <v>66</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E54" t="s">
         <v>206</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F54" t="s">
         <v>198</v>
       </c>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I46" s="4"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="4">
+      <c r="G54" s="10"/>
+      <c r="H54" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I54" s="10"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="10">
         <v>46</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="4" t="s">
+      <c r="B55" s="9"/>
+      <c r="C55" s="8"/>
+      <c r="D55" t="s">
         <v>265</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E55" t="s">
         <v>203</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F55" t="s">
         <v>208</v>
       </c>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4" t="s">
+      <c r="G55" s="10"/>
+      <c r="H55" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I47" s="4"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="4">
+      <c r="I55" s="10"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="10">
         <v>47</v>
       </c>
-      <c r="B48" s="5"/>
-      <c r="C48" s="9" t="s">
+      <c r="B56" s="9"/>
+      <c r="C56" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D56" t="s">
         <v>77</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E56" t="s">
         <v>207</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F56" t="s">
         <v>205</v>
       </c>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I48" s="4"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="4">
+      <c r="G56" s="10"/>
+      <c r="H56" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I56" s="10"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="10">
         <v>48</v>
       </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="4" t="s">
+      <c r="B57" s="9"/>
+      <c r="C57" s="8"/>
+      <c r="D57" t="s">
         <v>78</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="E57" t="s">
         <v>204</v>
       </c>
-      <c r="F49" s="4" t="s">
+      <c r="F57" t="s">
         <v>205</v>
       </c>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I49" s="4"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="4">
+      <c r="G57" s="10"/>
+      <c r="H57" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I57" s="10"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="10">
         <v>49</v>
       </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="4" t="s">
+      <c r="B58" s="9"/>
+      <c r="C58" s="8"/>
+      <c r="D58" t="s">
         <v>79</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E58" t="s">
         <v>203</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="F58" t="s">
         <v>208</v>
       </c>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4" t="s">
+      <c r="G58" s="10"/>
+      <c r="H58" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I50" s="4"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="4">
+      <c r="I58" s="10"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="10">
         <v>50</v>
       </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="4" t="s">
+      <c r="B59" s="9"/>
+      <c r="C59" s="8"/>
+      <c r="D59" t="s">
         <v>173</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="E59" t="s">
         <v>262</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="F59" t="s">
         <v>239</v>
       </c>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4" t="s">
+      <c r="G59" s="10"/>
+      <c r="H59" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I51" s="4"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="4">
+      <c r="I59" s="10"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="10">
         <v>51</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B60" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C60" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D60" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="E60" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="F60" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I52" s="4"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="4">
+      <c r="G60" s="10"/>
+      <c r="H60" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I60" s="10"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="10">
         <v>52</v>
       </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="4" t="s">
+      <c r="B61" s="11"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="E61" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="F61" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4" t="s">
+      <c r="G61" s="10"/>
+      <c r="H61" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I53" s="4"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="4">
+      <c r="I61" s="10"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="10">
         <v>53</v>
       </c>
-      <c r="B54" s="5"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="4" t="s">
+      <c r="B62" s="11"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="E62" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="F62" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4" t="s">
+      <c r="G62" s="10"/>
+      <c r="H62" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I54" s="4"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="4">
+      <c r="I62" s="10"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="10">
         <v>54</v>
       </c>
-      <c r="B55" s="5"/>
-      <c r="C55" s="6" t="s">
+      <c r="B63" s="11"/>
+      <c r="C63" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="D63" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E55" s="8" t="s">
+      <c r="E63" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="F63" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I55" s="4"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="4">
+      <c r="G63" s="10"/>
+      <c r="H63" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I63" s="10"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="10">
         <v>55</v>
       </c>
-      <c r="B56" s="5"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="4" t="s">
+      <c r="B64" s="11"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="E56" s="8" t="s">
+      <c r="E64" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="F56" s="4" t="s">
+      <c r="F64" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4" t="s">
+      <c r="G64" s="10"/>
+      <c r="H64" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I56" s="4"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="4">
+      <c r="I64" s="10"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="10">
         <v>56</v>
       </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="4" t="s">
+      <c r="B65" s="11"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="E57" s="8" t="s">
+      <c r="E65" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="F57" s="4" t="s">
+      <c r="F65" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I57" s="4"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="4">
+      <c r="G65" s="10"/>
+      <c r="H65" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I65" s="10"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="10">
         <v>57</v>
       </c>
-      <c r="B58" s="5"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="4" t="s">
+      <c r="B66" s="11"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="E58" s="8" t="s">
+      <c r="E66" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="F66" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I58" s="4"/>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="4">
+      <c r="G66" s="10"/>
+      <c r="H66" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I66" s="10"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="10">
         <v>58</v>
       </c>
-      <c r="B59" s="5"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="4" t="s">
+      <c r="B67" s="11"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="E59" s="8" t="s">
+      <c r="E67" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="F59" s="4" t="s">
+      <c r="F67" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I59" s="4"/>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="4">
+      <c r="G67" s="10"/>
+      <c r="H67" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I67" s="10"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="10">
         <v>59</v>
       </c>
-      <c r="B60" s="5"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="4" t="s">
+      <c r="B68" s="11"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E60" s="8" t="s">
+      <c r="E68" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="F60" s="4" t="s">
+      <c r="F68" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I60" s="4"/>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="4">
+      <c r="G68" s="10"/>
+      <c r="H68" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I68" s="10"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="10">
         <v>60</v>
       </c>
-      <c r="B61" s="5"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="4" t="s">
+      <c r="B69" s="11"/>
+      <c r="C69" s="12"/>
+      <c r="D69" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="E61" s="8" t="s">
+      <c r="E69" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="F61" s="4" t="s">
+      <c r="F69" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4" t="s">
+      <c r="G69" s="10"/>
+      <c r="H69" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I61" s="4"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="4">
+      <c r="I69" s="10"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="10">
         <v>61</v>
       </c>
-      <c r="B62" s="5"/>
-      <c r="C62" s="6" t="s">
+      <c r="B70" s="11"/>
+      <c r="C70" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D70" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="E70" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="F62" s="4" t="s">
+      <c r="F70" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I62" s="4"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="4">
+      <c r="G70" s="10"/>
+      <c r="H70" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I70" s="10"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="10">
         <v>62</v>
       </c>
-      <c r="B63" s="5"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="4" t="s">
+      <c r="B71" s="11"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E63" s="8" t="s">
+      <c r="E71" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="F63" s="4" t="s">
+      <c r="F71" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I63" s="4"/>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="4">
+      <c r="G71" s="10"/>
+      <c r="H71" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I71" s="10"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="10">
         <v>63</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B72" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C72" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D72" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="E64" s="8" t="s">
+      <c r="E72" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="F64" s="4" t="s">
+      <c r="F72" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I64" s="4"/>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="4">
+      <c r="G72" s="10"/>
+      <c r="H72" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I72" s="10"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="10">
         <v>64</v>
       </c>
-      <c r="B65" s="5"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="4" t="s">
+      <c r="B73" s="11"/>
+      <c r="C73" s="12"/>
+      <c r="D73" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="E65" s="8" t="s">
+      <c r="E73" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="F65" s="4" t="s">
+      <c r="F73" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="G65" s="4"/>
-      <c r="H65" s="4" t="s">
+      <c r="G73" s="10"/>
+      <c r="H73" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I65" s="4"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="4">
+      <c r="I73" s="10"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="10">
         <v>65</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B74" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C74" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D74" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E66" s="8" t="s">
+      <c r="E74" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="F66" s="4" t="s">
+      <c r="F74" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4" t="s">
+      <c r="G74" s="10"/>
+      <c r="H74" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I66" s="4"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="4">
+      <c r="I74" s="10"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="10">
         <v>66</v>
       </c>
-      <c r="B67" s="5"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="4" t="s">
+      <c r="B75" s="11"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="E67" s="8" t="s">
+      <c r="E75" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="F67" s="4" t="s">
+      <c r="F75" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I67" s="4"/>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="4">
+      <c r="G75" s="10"/>
+      <c r="H75" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I75" s="10"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="10">
         <v>67</v>
       </c>
-      <c r="B68" s="5"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="4" t="s">
+      <c r="B76" s="11"/>
+      <c r="C76" s="12"/>
+      <c r="D76" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="E68" s="8" t="s">
+      <c r="E76" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="F68" s="4" t="s">
+      <c r="F76" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4" t="s">
+      <c r="G76" s="10"/>
+      <c r="H76" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I68" s="4"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="4">
+      <c r="I76" s="10"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="10">
         <v>68</v>
       </c>
-      <c r="B69" s="5"/>
-      <c r="C69" s="7" t="s">
+      <c r="B77" s="11"/>
+      <c r="C77" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D77" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="E69" s="8" t="s">
+      <c r="E77" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="F69" s="8" t="s">
+      <c r="F77" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4" t="s">
+      <c r="G77" s="10"/>
+      <c r="H77" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I69" s="4"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="4">
+      <c r="I77" s="10"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="10">
         <v>69</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="B78" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="C70" s="6" t="s">
+      <c r="C78" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D78" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="E70" s="8" t="s">
+      <c r="E78" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="F70" s="8" t="s">
+      <c r="F78" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="G70" s="4"/>
-      <c r="H70" s="4" t="s">
+      <c r="G78" s="10"/>
+      <c r="H78" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I70" s="4"/>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="4">
+      <c r="I78" s="10"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="10">
         <v>70</v>
       </c>
-      <c r="B71" s="5"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="4" t="s">
+      <c r="B79" s="11"/>
+      <c r="C79" s="12"/>
+      <c r="D79" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="E71" s="8" t="s">
+      <c r="E79" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="F71" s="8" t="s">
+      <c r="F79" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I71" s="4"/>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="4">
+      <c r="G79" s="10"/>
+      <c r="H79" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I79" s="10"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="10">
         <v>71</v>
       </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="6"/>
-      <c r="D72" s="4" t="s">
+      <c r="B80" s="11"/>
+      <c r="C80" s="12"/>
+      <c r="D80" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="E72" s="8" t="s">
+      <c r="E80" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="F72" s="8" t="s">
+      <c r="F80" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4" t="s">
+      <c r="G80" s="10"/>
+      <c r="H80" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I72" s="4"/>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="4">
+      <c r="I80" s="10"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="10">
         <v>72</v>
       </c>
-      <c r="B73" s="5"/>
-      <c r="C73" s="6" t="s">
+      <c r="B81" s="11"/>
+      <c r="C81" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="D81" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="E73" s="4" t="s">
+      <c r="E81" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="F73" s="4" t="s">
+      <c r="F81" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I73" s="4"/>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="4">
+      <c r="G81" s="10"/>
+      <c r="H81" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I81" s="10"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="10">
         <v>73</v>
       </c>
-      <c r="B74" s="5"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="4" t="s">
+      <c r="B82" s="11"/>
+      <c r="C82" s="12"/>
+      <c r="D82" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="E74" s="4" t="s">
+      <c r="E82" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F74" s="4" t="s">
+      <c r="F82" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I74" s="4"/>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="4">
+      <c r="G82" s="10"/>
+      <c r="H82" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I82" s="10"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="10">
         <v>74</v>
       </c>
-      <c r="B75" s="5"/>
-      <c r="C75" s="6"/>
-      <c r="D75" s="4" t="s">
+      <c r="B83" s="11"/>
+      <c r="C83" s="12"/>
+      <c r="D83" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E75" s="4" t="s">
+      <c r="E83" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="F75" s="4" t="s">
+      <c r="F83" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I75" s="4"/>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="4">
+      <c r="G83" s="10"/>
+      <c r="H83" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I83" s="10"/>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="10">
         <v>75</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B84" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C76" s="6" t="s">
+      <c r="C84" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="D84" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="E76" s="4" t="s">
+      <c r="E84" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="F84" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I76" s="4"/>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="4">
+      <c r="G84" s="10"/>
+      <c r="H84" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I84" s="10"/>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="10">
         <v>76</v>
       </c>
-      <c r="B77" s="5"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="4" t="s">
+      <c r="B85" s="11"/>
+      <c r="C85" s="12"/>
+      <c r="D85" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="E77" s="4" t="s">
+      <c r="E85" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="F77" s="4" t="s">
+      <c r="F85" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I77" s="4"/>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="4">
+      <c r="G85" s="10"/>
+      <c r="H85" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I85" s="10"/>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="10">
         <v>77</v>
       </c>
-      <c r="B78" s="5"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="4" t="s">
+      <c r="B86" s="11"/>
+      <c r="C86" s="12"/>
+      <c r="D86" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="E78" s="4" t="s">
+      <c r="E86" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="F86" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I78" s="4"/>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="4">
+      <c r="G86" s="10"/>
+      <c r="H86" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I86" s="10"/>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="10">
         <v>78</v>
       </c>
-      <c r="B79" s="5"/>
-      <c r="C79" s="9" t="s">
+      <c r="B87" s="11"/>
+      <c r="C87" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="D79" s="4" t="s">
+      <c r="D87" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="E79" s="4" t="s">
+      <c r="E87" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="F79" s="4" t="s">
+      <c r="F87" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4" t="s">
+      <c r="G87" s="10"/>
+      <c r="H87" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I79" s="4"/>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="4">
+      <c r="I87" s="10"/>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="10">
         <v>79</v>
       </c>
-      <c r="B80" s="5"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="4" t="s">
+      <c r="B88" s="11"/>
+      <c r="C88" s="15"/>
+      <c r="D88" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="E80" s="4" t="s">
+      <c r="E88" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="F80" s="4" t="s">
+      <c r="F88" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4" t="s">
+      <c r="G88" s="10"/>
+      <c r="H88" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I80" s="4"/>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="4">
+      <c r="I88" s="10"/>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="10">
         <v>80</v>
       </c>
-      <c r="B81" s="5"/>
-      <c r="C81" s="9" t="s">
+      <c r="B89" s="11"/>
+      <c r="C89" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="D89" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="E81" s="4" t="s">
+      <c r="E89" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="F89" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4" t="s">
+      <c r="G89" s="10"/>
+      <c r="H89" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I81" s="4"/>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="4">
+      <c r="I89" s="10"/>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="10">
         <v>81</v>
       </c>
-      <c r="B82" s="5"/>
-      <c r="C82" s="9"/>
-      <c r="D82" s="4" t="s">
+      <c r="B90" s="11"/>
+      <c r="C90" s="15"/>
+      <c r="D90" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="E82" s="4" t="s">
+      <c r="E90" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="F82" s="4" t="s">
+      <c r="F90" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="G82" s="4"/>
-      <c r="H82" s="4" t="s">
+      <c r="G90" s="10"/>
+      <c r="H90" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I82" s="4"/>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" s="4">
+      <c r="I90" s="10"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="10">
         <v>82</v>
       </c>
-      <c r="B83" s="5"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="4" t="s">
+      <c r="B91" s="11"/>
+      <c r="C91" s="15"/>
+      <c r="D91" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="E83" s="4" t="s">
+      <c r="E91" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="F83" s="4" t="s">
+      <c r="F91" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="G83" s="4"/>
-      <c r="H83" s="4" t="s">
+      <c r="G91" s="10"/>
+      <c r="H91" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I83" s="4"/>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="4">
+      <c r="I91" s="10"/>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="10">
         <v>83</v>
       </c>
-      <c r="B84" s="5"/>
-      <c r="C84" s="9" t="s">
+      <c r="B92" s="11"/>
+      <c r="C92" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="D84" s="4" t="s">
+      <c r="D92" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="E84" s="4" t="s">
+      <c r="E92" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="F92" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="G84" s="4"/>
-      <c r="H84" s="4" t="s">
+      <c r="G92" s="10"/>
+      <c r="H92" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I84" s="4"/>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" s="4">
+      <c r="I92" s="10"/>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="10">
         <v>84</v>
       </c>
-      <c r="B85" s="5"/>
-      <c r="C85" s="9"/>
-      <c r="D85" s="4" t="s">
+      <c r="B93" s="11"/>
+      <c r="C93" s="15"/>
+      <c r="D93" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="E85" s="4" t="s">
+      <c r="E93" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="F85" s="4" t="s">
+      <c r="F93" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="G85" s="4"/>
-      <c r="H85" s="4" t="s">
+      <c r="G93" s="10"/>
+      <c r="H93" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I85" s="4"/>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="4">
+      <c r="I93" s="10"/>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="10">
         <v>85</v>
       </c>
-      <c r="B86" s="5"/>
-      <c r="C86" s="9" t="s">
+      <c r="B94" s="11"/>
+      <c r="C94" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="D94" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="E86" s="4" t="s">
+      <c r="E94" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="F86" s="4" t="s">
+      <c r="F94" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="G86" s="4"/>
-      <c r="H86" s="4" t="s">
+      <c r="G94" s="10"/>
+      <c r="H94" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I86" s="4"/>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="4">
+      <c r="I94" s="10"/>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="10">
         <v>86</v>
       </c>
-      <c r="B87" s="5"/>
-      <c r="C87" s="9"/>
-      <c r="D87" s="4" t="s">
+      <c r="B95" s="11"/>
+      <c r="C95" s="15"/>
+      <c r="D95" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="E87" s="4" t="s">
+      <c r="E95" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="F87" s="4" t="s">
+      <c r="F95" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="G87" s="4"/>
-      <c r="H87" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I87" s="4"/>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="4">
+      <c r="G95" s="10"/>
+      <c r="H95" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I95" s="10"/>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="10">
         <v>87</v>
       </c>
-      <c r="B88" s="5"/>
-      <c r="C88" s="9"/>
-      <c r="D88" s="4" t="s">
+      <c r="B96" s="11"/>
+      <c r="C96" s="15"/>
+      <c r="D96" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="E88" s="4" t="s">
+      <c r="E96" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="F88" s="4" t="s">
+      <c r="F96" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="G88" s="4"/>
-      <c r="H88" s="4" t="s">
+      <c r="G96" s="10"/>
+      <c r="H96" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I88" s="4"/>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="4">
+      <c r="I96" s="10"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="10">
         <v>88</v>
       </c>
-      <c r="B89" s="5"/>
-      <c r="C89" s="4" t="s">
+      <c r="B97" s="11"/>
+      <c r="C97" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="D89" s="4" t="s">
+      <c r="D97" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="E89" s="4" t="s">
+      <c r="E97" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="F89" s="4" t="s">
+      <c r="F97" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="G89" s="4"/>
-      <c r="H89" s="4" t="s">
+      <c r="G97" s="10"/>
+      <c r="H97" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I89" s="4"/>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="4">
+      <c r="I97" s="10"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="10">
         <v>89</v>
       </c>
-      <c r="B90" s="5"/>
-      <c r="C90" s="9" t="s">
+      <c r="B98" s="11"/>
+      <c r="C98" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="D90" s="4" t="s">
+      <c r="D98" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="E90" s="4" t="s">
+      <c r="E98" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="F90" s="4" t="s">
+      <c r="F98" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="G90" s="4"/>
-      <c r="H90" s="4" t="s">
+      <c r="G98" s="10"/>
+      <c r="H98" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I90" s="4"/>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" s="4">
+      <c r="I98" s="10"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="10">
         <v>90</v>
       </c>
-      <c r="B91" s="5"/>
-      <c r="C91" s="9"/>
-      <c r="D91" s="4" t="s">
+      <c r="B99" s="11"/>
+      <c r="C99" s="15"/>
+      <c r="D99" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="E91" s="4" t="s">
+      <c r="E99" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="F91" s="4" t="s">
+      <c r="F99" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="G91" s="4"/>
-      <c r="H91" s="4" t="s">
+      <c r="G99" s="10"/>
+      <c r="H99" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I91" s="4"/>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="4">
+      <c r="I99" s="10"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="10">
         <v>91</v>
       </c>
-      <c r="B92" s="5"/>
-      <c r="C92" s="9"/>
-      <c r="D92" s="4" t="s">
+      <c r="B100" s="11"/>
+      <c r="C100" s="15"/>
+      <c r="D100" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="E92" s="4" t="s">
+      <c r="E100" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="F92" s="4" t="s">
+      <c r="F100" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="G92" s="4"/>
-      <c r="H92" s="4" t="s">
+      <c r="G100" s="10"/>
+      <c r="H100" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I92" s="4"/>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="4">
+      <c r="I100" s="10"/>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="10">
         <v>92</v>
       </c>
-      <c r="B93" s="5"/>
-      <c r="C93" s="9"/>
-      <c r="D93" s="4" t="s">
+      <c r="B101" s="11"/>
+      <c r="C101" s="15"/>
+      <c r="D101" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="E93" s="4" t="s">
+      <c r="E101" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="F93" s="4" t="s">
+      <c r="F101" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="G93" s="4"/>
-      <c r="H93" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I93" s="4"/>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" s="4">
+      <c r="G101" s="10"/>
+      <c r="H101" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I101" s="10"/>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="10">
         <v>93</v>
       </c>
-      <c r="B94" s="5" t="s">
+      <c r="B102" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="C94" s="9" t="s">
+      <c r="C102" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="D94" s="4" t="s">
+      <c r="D102" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="E94" s="4" t="s">
+      <c r="E102" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="F94" s="4" t="s">
+      <c r="F102" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="G94" s="4"/>
-      <c r="H94" s="4" t="s">
+      <c r="G102" s="10"/>
+      <c r="H102" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I94" s="4"/>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="4">
+      <c r="I102" s="10"/>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="10">
         <v>94</v>
       </c>
-      <c r="B95" s="5"/>
-      <c r="C95" s="9"/>
-      <c r="D95" s="4" t="s">
+      <c r="B103" s="11"/>
+      <c r="C103" s="15"/>
+      <c r="D103" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="E95" s="4" t="s">
+      <c r="E103" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="F95" s="4" t="s">
+      <c r="F103" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="G95" s="4"/>
-      <c r="H95" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I95" s="4"/>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="4">
+      <c r="G103" s="10"/>
+      <c r="H103" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I103" s="10"/>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="10">
         <v>95</v>
       </c>
-      <c r="B96" s="5"/>
-      <c r="C96" s="9"/>
-      <c r="D96" s="4" t="s">
+      <c r="B104" s="11"/>
+      <c r="C104" s="15"/>
+      <c r="D104" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="E96" s="4" t="s">
+      <c r="E104" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="F96" s="4" t="s">
+      <c r="F104" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="G96" s="4"/>
-      <c r="H96" s="4" t="s">
+      <c r="G104" s="10"/>
+      <c r="H104" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I96" s="4"/>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="4">
+      <c r="I104" s="10"/>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="10">
         <v>96</v>
       </c>
-      <c r="B97" s="5" t="s">
+      <c r="B105" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="C97" s="11" t="s">
+      <c r="C105" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="D97" s="4" t="s">
+      <c r="D105" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="E97" s="4" t="s">
+      <c r="E105" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F97" s="4" t="s">
+      <c r="F105" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="G97" s="4"/>
-      <c r="H97" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I97" s="4"/>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="4">
+      <c r="G105" s="10"/>
+      <c r="H105" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I105" s="10"/>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="10">
         <v>97</v>
       </c>
-      <c r="B98" s="5"/>
-      <c r="C98" s="11" t="s">
+      <c r="B106" s="11"/>
+      <c r="C106" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="D106" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="E98" s="4" t="s">
+      <c r="E106" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="F98" s="4" t="s">
+      <c r="F106" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="G98" s="4"/>
-      <c r="H98" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I98" s="4"/>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" s="4">
+      <c r="G106" s="10"/>
+      <c r="H106" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I106" s="10"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="10">
         <v>98</v>
       </c>
-      <c r="B99" s="5"/>
-      <c r="C99" s="4" t="s">
+      <c r="B107" s="11"/>
+      <c r="C107" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="D99" s="4" t="s">
+      <c r="D107" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="E99" s="4" t="s">
+      <c r="E107" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="F99" s="4" t="s">
+      <c r="F107" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="G99" s="4"/>
-      <c r="H99" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I99" s="4"/>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="4">
+      <c r="G107" s="10"/>
+      <c r="H107" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I107" s="10"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="10">
         <v>99</v>
       </c>
-      <c r="B100" s="5"/>
-      <c r="C100" s="4" t="s">
+      <c r="B108" s="11"/>
+      <c r="C108" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="D100" s="4" t="s">
+      <c r="D108" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="E100" s="4" t="s">
+      <c r="E108" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="F100" s="4" t="s">
+      <c r="F108" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="G100" s="4"/>
-      <c r="H100" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I100" s="4"/>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="4">
+      <c r="G108" s="10"/>
+      <c r="H108" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I108" s="10"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="10">
         <v>100</v>
       </c>
-      <c r="B101" s="5"/>
-      <c r="C101" s="4" t="s">
+      <c r="B109" s="11"/>
+      <c r="C109" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="D101" s="4" t="s">
+      <c r="D109" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="E101" s="4" t="s">
+      <c r="E109" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="F101" s="4" t="s">
+      <c r="F109" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="G101" s="4"/>
-      <c r="H101" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I101" s="4"/>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" s="4">
+      <c r="G109" s="10"/>
+      <c r="H109" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I109" s="10"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="10">
         <v>101</v>
       </c>
-      <c r="B102" s="5"/>
-      <c r="C102" s="9" t="s">
+      <c r="B110" s="11"/>
+      <c r="C110" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="D102" s="4" t="s">
+      <c r="D110" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E102" s="4" t="s">
+      <c r="E110" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="F102" s="4" t="s">
+      <c r="F110" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="G102" s="4"/>
-      <c r="H102" s="4" t="s">
+      <c r="G110" s="10"/>
+      <c r="H110" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I102" s="4"/>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="4">
+      <c r="I110" s="10"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="10">
         <v>102</v>
       </c>
-      <c r="B103" s="5"/>
-      <c r="C103" s="9"/>
-      <c r="D103" s="4" t="s">
+      <c r="B111" s="11"/>
+      <c r="C111" s="15"/>
+      <c r="D111" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="E103" s="4" t="s">
+      <c r="E111" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="F103" s="4" t="s">
+      <c r="F111" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="G103" s="4"/>
-      <c r="H103" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I103" s="4"/>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="4">
+      <c r="G111" s="10"/>
+      <c r="H111" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I111" s="10"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="10">
         <v>103</v>
       </c>
-      <c r="B104" s="5"/>
-      <c r="C104" s="9"/>
-      <c r="D104" s="4" t="s">
+      <c r="B112" s="11"/>
+      <c r="C112" s="15"/>
+      <c r="D112" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="E104" s="4" t="s">
+      <c r="E112" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="F104" s="4" t="s">
+      <c r="F112" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="G104" s="4"/>
-      <c r="H104" s="4" t="s">
+      <c r="G112" s="10"/>
+      <c r="H112" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I104" s="4"/>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="4">
+      <c r="I112" s="10"/>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" s="10">
         <v>104</v>
       </c>
-      <c r="B105" s="5"/>
-      <c r="C105" s="9" t="s">
+      <c r="B113" s="11"/>
+      <c r="C113" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="D105" s="4" t="s">
+      <c r="D113" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E105" s="4" t="s">
+      <c r="E113" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="F105" s="4" t="s">
+      <c r="F113" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="G105" s="4"/>
-      <c r="H105" s="4" t="s">
+      <c r="G113" s="10"/>
+      <c r="H113" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I105" s="4"/>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" s="4">
+      <c r="I113" s="10"/>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="10">
         <v>105</v>
       </c>
-      <c r="B106" s="5"/>
-      <c r="C106" s="9"/>
-      <c r="D106" s="4" t="s">
+      <c r="B114" s="11"/>
+      <c r="C114" s="15"/>
+      <c r="D114" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="E106" s="4" t="s">
+      <c r="E114" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="F106" s="4" t="s">
+      <c r="F114" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="G106" s="4"/>
-      <c r="H106" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I106" s="4"/>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="4">
+      <c r="G114" s="10"/>
+      <c r="H114" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I114" s="10"/>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" s="10">
         <v>106</v>
       </c>
-      <c r="B107" s="5"/>
-      <c r="C107" s="9"/>
-      <c r="D107" s="4" t="s">
+      <c r="B115" s="11"/>
+      <c r="C115" s="15"/>
+      <c r="D115" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="E107" s="4" t="s">
+      <c r="E115" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="F107" s="4" t="s">
+      <c r="F115" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="G107" s="4"/>
-      <c r="H107" s="4" t="s">
+      <c r="G115" s="10"/>
+      <c r="H115" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I107" s="4"/>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" s="4">
+      <c r="I115" s="10"/>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" s="10">
         <v>107</v>
       </c>
-      <c r="B108" s="5"/>
-      <c r="C108" s="9" t="s">
+      <c r="B116" s="11"/>
+      <c r="C116" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="D108" s="4" t="s">
+      <c r="D116" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E108" s="4" t="s">
+      <c r="E116" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="F108" s="4" t="s">
+      <c r="F116" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="G108" s="4"/>
-      <c r="H108" s="4" t="s">
+      <c r="G116" s="10"/>
+      <c r="H116" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I108" s="4"/>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="4">
+      <c r="I116" s="10"/>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" s="10">
         <v>108</v>
       </c>
-      <c r="B109" s="5"/>
-      <c r="C109" s="9"/>
-      <c r="D109" s="4" t="s">
+      <c r="B117" s="11"/>
+      <c r="C117" s="15"/>
+      <c r="D117" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="E109" s="4" t="s">
+      <c r="E117" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="F109" s="4" t="s">
+      <c r="F117" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="G109" s="4"/>
-      <c r="H109" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I109" s="4"/>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="4">
+      <c r="G117" s="10"/>
+      <c r="H117" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I117" s="10"/>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" s="10">
         <v>109</v>
       </c>
-      <c r="B110" s="5"/>
-      <c r="C110" s="9"/>
-      <c r="D110" s="4" t="s">
+      <c r="B118" s="11"/>
+      <c r="C118" s="15"/>
+      <c r="D118" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="E110" s="4" t="s">
+      <c r="E118" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="F110" s="4" t="s">
+      <c r="F118" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="G110" s="4"/>
-      <c r="H110" s="4" t="s">
+      <c r="G118" s="10"/>
+      <c r="H118" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I110" s="4"/>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="4">
+      <c r="I118" s="10"/>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" s="10">
         <v>110</v>
       </c>
-      <c r="B111" s="5"/>
-      <c r="C111" s="9" t="s">
+      <c r="B119" s="11"/>
+      <c r="C119" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="D111" s="4" t="s">
+      <c r="D119" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="E111" s="4" t="s">
+      <c r="E119" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="F111" s="4" t="s">
+      <c r="F119" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="G111" s="4"/>
-      <c r="H111" s="4" t="s">
+      <c r="G119" s="10"/>
+      <c r="H119" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I111" s="4"/>
-    </row>
-    <row r="112" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A112" s="4">
+      <c r="I119" s="10"/>
+    </row>
+    <row r="120" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A120" s="10">
         <v>111</v>
       </c>
-      <c r="B112" s="5"/>
-      <c r="C112" s="9"/>
-      <c r="D112" s="10" t="s">
+      <c r="B120" s="11"/>
+      <c r="C120" s="15"/>
+      <c r="D120" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="E112" s="4" t="s">
+      <c r="E120" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="F112" s="4" t="s">
+      <c r="F120" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="G112" s="4"/>
-      <c r="H112" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I112" s="4"/>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" s="4">
+      <c r="G120" s="10"/>
+      <c r="H120" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I120" s="10"/>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121" s="10">
         <v>112</v>
       </c>
-      <c r="B113" s="5"/>
-      <c r="C113" s="9"/>
-      <c r="D113" s="7" t="s">
+      <c r="B121" s="11"/>
+      <c r="C121" s="15"/>
+      <c r="D121" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="E113" s="4" t="s">
+      <c r="E121" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="F113" s="4" t="s">
+      <c r="F121" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="G113" s="4"/>
-      <c r="H113" s="4" t="s">
+      <c r="G121" s="10"/>
+      <c r="H121" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I113" s="4"/>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="4">
+      <c r="I121" s="10"/>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" s="10">
         <v>113</v>
       </c>
-      <c r="B114" s="5"/>
-      <c r="C114" s="9"/>
-      <c r="D114" s="7" t="s">
+      <c r="B122" s="11"/>
+      <c r="C122" s="15"/>
+      <c r="D122" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="E114" s="4" t="s">
+      <c r="E122" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="F114" s="4" t="s">
+      <c r="F122" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="G114" s="4"/>
-      <c r="H114" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I114" s="4"/>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="4">
+      <c r="G122" s="10"/>
+      <c r="H122" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I122" s="10"/>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" s="10">
         <v>114</v>
       </c>
-      <c r="B115" s="5"/>
-      <c r="C115" s="9"/>
-      <c r="D115" s="7" t="s">
+      <c r="B123" s="11"/>
+      <c r="C123" s="15"/>
+      <c r="D123" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="E115" s="4" t="s">
+      <c r="E123" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="F115" s="4" t="s">
+      <c r="F123" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="G115" s="4"/>
-      <c r="H115" s="4" t="s">
+      <c r="G123" s="10"/>
+      <c r="H123" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I115" s="4"/>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" s="4">
+      <c r="I123" s="10"/>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" s="10">
         <v>115</v>
       </c>
-      <c r="B116" s="5" t="s">
+      <c r="B124" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C124" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="D116" s="4" t="s">
+      <c r="D124" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="E116" s="4" t="s">
+      <c r="E124" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="F116" s="4" t="s">
+      <c r="F124" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="G116" s="4"/>
-      <c r="H116" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I116" s="4"/>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="4">
+      <c r="G124" s="10"/>
+      <c r="H124" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I124" s="10"/>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" s="10">
         <v>116</v>
       </c>
-      <c r="B117" s="5"/>
-      <c r="C117" s="4" t="s">
+      <c r="B125" s="11"/>
+      <c r="C125" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="D117" s="4" t="s">
+      <c r="D125" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="E117" s="4" t="s">
+      <c r="E125" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="F117" s="4" t="s">
+      <c r="F125" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="G117" s="4"/>
-      <c r="H117" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I117" s="4"/>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" s="4">
+      <c r="G125" s="10"/>
+      <c r="H125" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I125" s="10"/>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" s="10">
         <v>117</v>
       </c>
-      <c r="B118" s="12" t="s">
+      <c r="B126" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C118" s="4" t="s">
+      <c r="C126" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="D118" s="4" t="s">
+      <c r="D126" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="E118" s="4" t="s">
+      <c r="E126" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="F118" s="4" t="s">
+      <c r="F126" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="G118" s="4"/>
-      <c r="H118" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I118" s="4"/>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" s="4">
+      <c r="G126" s="10"/>
+      <c r="H126" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I126" s="10"/>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" s="10">
         <v>118</v>
       </c>
-      <c r="B119" s="5" t="s">
+      <c r="B127" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="C119" s="9" t="s">
+      <c r="C127" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="D119" s="4" t="s">
+      <c r="D127" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="E119" s="4" t="s">
+      <c r="E127" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="F119" s="4" t="s">
+      <c r="F127" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="G119" s="4"/>
-      <c r="H119" s="4" t="s">
+      <c r="G127" s="10"/>
+      <c r="H127" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I119" s="4"/>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120" s="4">
+      <c r="I127" s="10"/>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" s="10">
         <v>119</v>
       </c>
-      <c r="B120" s="5"/>
-      <c r="C120" s="9"/>
-      <c r="D120" s="4" t="s">
+      <c r="B128" s="11"/>
+      <c r="C128" s="15"/>
+      <c r="D128" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="E120" s="4" t="s">
+      <c r="E128" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="F120" s="4" t="s">
+      <c r="F128" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="G120" s="4"/>
-      <c r="H120" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I120" s="4"/>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" s="4">
+      <c r="G128" s="10"/>
+      <c r="H128" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I128" s="10"/>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" s="10">
         <v>120</v>
       </c>
-      <c r="B121" s="5"/>
-      <c r="C121" s="9"/>
-      <c r="D121" s="4" t="s">
+      <c r="B129" s="11"/>
+      <c r="C129" s="15"/>
+      <c r="D129" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="E121" s="4" t="s">
+      <c r="E129" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="F121" s="4" t="s">
+      <c r="F129" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="G121" s="4"/>
-      <c r="H121" s="4" t="s">
+      <c r="G129" s="10"/>
+      <c r="H129" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I121" s="4"/>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="4">
+      <c r="I129" s="10"/>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" s="10">
         <v>121</v>
       </c>
-      <c r="B122" s="5"/>
-      <c r="C122" s="9" t="s">
+      <c r="B130" s="11"/>
+      <c r="C130" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="D122" s="4" t="s">
+      <c r="D130" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="E122" s="4" t="s">
+      <c r="E130" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="F122" s="4" t="s">
+      <c r="F130" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="G122" s="4"/>
-      <c r="H122" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I122" s="4"/>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="4">
+      <c r="G130" s="10"/>
+      <c r="H130" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I130" s="10"/>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" s="10">
         <v>122</v>
       </c>
-      <c r="B123" s="5"/>
-      <c r="C123" s="9"/>
-      <c r="D123" s="4" t="s">
+      <c r="B131" s="11"/>
+      <c r="C131" s="15"/>
+      <c r="D131" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="E123" s="4" t="s">
+      <c r="E131" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="F123" s="4" t="s">
+      <c r="F131" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="G123" s="4"/>
-      <c r="H123" s="4" t="s">
+      <c r="G131" s="10"/>
+      <c r="H131" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I123" s="4"/>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" s="4">
+      <c r="I131" s="10"/>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" s="10">
         <v>123</v>
       </c>
-      <c r="B124" s="5"/>
-      <c r="C124" s="9"/>
-      <c r="D124" s="4" t="s">
+      <c r="B132" s="11"/>
+      <c r="C132" s="15"/>
+      <c r="D132" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="E124" s="4" t="s">
+      <c r="E132" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="F124" s="4" t="s">
+      <c r="F132" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="G124" s="4"/>
-      <c r="H124" s="4" t="s">
+      <c r="G132" s="10"/>
+      <c r="H132" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I124" s="4"/>
-    </row>
-    <row r="125" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A125" s="4">
+      <c r="I132" s="10"/>
+    </row>
+    <row r="133" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A133" s="10">
         <v>124</v>
       </c>
-      <c r="B125" s="12" t="s">
+      <c r="B133" s="18" t="s">
         <v>266</v>
       </c>
-      <c r="C125" s="13" t="s">
+      <c r="C133" s="19" t="s">
         <v>267</v>
       </c>
-      <c r="D125" s="4" t="s">
+      <c r="D133" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="E125" s="4" t="s">
+      <c r="E133" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="F125" s="4" t="s">
+      <c r="F133" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="G125" s="4"/>
-      <c r="H125" s="4" t="s">
+      <c r="G133" s="10"/>
+      <c r="H133" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I125" s="4"/>
+      <c r="I133" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="C122:C124"/>
-    <mergeCell ref="B119:B124"/>
-    <mergeCell ref="C48:C51"/>
-    <mergeCell ref="B37:B51"/>
-    <mergeCell ref="C42:C47"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="C119:C121"/>
-    <mergeCell ref="B76:B93"/>
-    <mergeCell ref="B97:B115"/>
-    <mergeCell ref="C111:C115"/>
-    <mergeCell ref="C105:C107"/>
-    <mergeCell ref="C108:C110"/>
+    <mergeCell ref="C130:C132"/>
+    <mergeCell ref="B127:B132"/>
+    <mergeCell ref="C56:C59"/>
+    <mergeCell ref="B45:B59"/>
+    <mergeCell ref="C50:C55"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="C127:C129"/>
+    <mergeCell ref="B84:B101"/>
+    <mergeCell ref="B105:B123"/>
+    <mergeCell ref="C119:C123"/>
+    <mergeCell ref="C113:C115"/>
+    <mergeCell ref="C116:C118"/>
+    <mergeCell ref="C102:C104"/>
+    <mergeCell ref="B102:B104"/>
+    <mergeCell ref="C89:C91"/>
+    <mergeCell ref="C110:C112"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="C92:C93"/>
     <mergeCell ref="C94:C96"/>
-    <mergeCell ref="B94:B96"/>
+    <mergeCell ref="C78:C80"/>
     <mergeCell ref="C81:C83"/>
-    <mergeCell ref="C102:C104"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="C86:C88"/>
-    <mergeCell ref="C70:C72"/>
-    <mergeCell ref="C73:C75"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="B70:B75"/>
-    <mergeCell ref="C76:C78"/>
-    <mergeCell ref="C66:C68"/>
+    <mergeCell ref="C98:C101"/>
+    <mergeCell ref="B78:B83"/>
+    <mergeCell ref="C84:C86"/>
+    <mergeCell ref="C74:C76"/>
     <mergeCell ref="B2:B12"/>
-    <mergeCell ref="B66:B69"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="B74:B77"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="B72:B73"/>
     <mergeCell ref="C17:C19"/>
     <mergeCell ref="C24:C26"/>
     <mergeCell ref="B17:B28"/>
@@ -4553,12 +4856,12 @@
     <mergeCell ref="C32:C34"/>
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="B29:B36"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="B52:B63"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="C55:C61"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="B60:B71"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="C63:C69"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
@@ -4569,4 +4872,77 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CF7B26D-E2A8-4887-8F63-92439D43C540}">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="22" customFormat="1" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>314</v>
+      </c>
+      <c r="C6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E6" t="s">
+        <v>318</v>
+      </c>
+      <c r="F6" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>315</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+</worksheet>
 </file>
--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6EEC539-3635-43DD-9FAE-F315C926FEF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0265EEB-F9E7-4CE8-8808-6E99F01D2E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{F425FBA8-E65A-4F03-9270-551F3EA7C4F5}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="373">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1298,18 +1298,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>累计任务-未完成任务状态</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>后天查看任务状态</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>累计任务-已完成任务状态</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>活动期间已登录游戏</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1330,10 +1322,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>累计任务进度展示</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>进入活动查看任务进度</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1358,19 +1346,163 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>活动期间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>活动登录任务刷新</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>累计完成6场普通/排位对局-未完成任务状态</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>累计完成6场普通/排位对局-已完成任务状态</t>
+    <t>累计对局任务-任务状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计对局任务-任务参与模式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计对局任务-胜负条件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计对局任务-任务进度展示</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计对局任务-任务参与人数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计登录任务-未完成任务状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计登录任务-已完成任务状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计登录任务进度展示</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间内完成任务条件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务状态为“前往”</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入活动查看任务状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间内未完成任务</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间内未完成任务条件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计对局任务-前往按钮跳转功能测试</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入活动点击按钮</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>跳转至对战大厅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间进入对战大厅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择排位模式，胜利一局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可完成任务</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择普通模式，胜利一局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择娱乐模式，胜利一句</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法完成任务</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择自定义，胜利一局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择排位/普通模式，胜利一局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择排位/普通模式，失败一局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择排位/普通模式，平局一局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间未完成任务</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务进度1/6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.16选择排位/普通模式，胜利一局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.16选择排位/普通模式，胜利2局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.17选择排位/普通模式，胜利3局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.18选择排位/普通模式，胜利5局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务进度2/6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务进度3/6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务进度4/6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务进度5/6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务进度6/6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.17选择排位/普通模式，胜利4局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.18选择排位/普通模式，胜利6局</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1454,7 +1586,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1478,14 +1610,25 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1507,23 +1650,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
@@ -1564,11 +1695,23 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1884,7 +2027,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DF7E13A-4D63-4E82-9598-D598C8858D86}">
-  <dimension ref="A1:I133"/>
+  <dimension ref="A1:I151"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
@@ -1925,2926 +2068,3232 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="10">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10" t="s">
+      <c r="G2" s="6"/>
+      <c r="H2" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="I2" s="10"/>
+      <c r="I2" s="6"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="10" t="s">
+      <c r="B3" s="7"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10" t="s">
+      <c r="G3" s="6"/>
+      <c r="H3" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I3" s="10"/>
+      <c r="I3" s="6"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="10">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="10" t="s">
+      <c r="B4" s="7"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10" t="s">
+      <c r="G4" s="6"/>
+      <c r="H4" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="I4" s="10"/>
+      <c r="I4" s="6"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
+      <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10" t="s">
+      <c r="G5" s="6"/>
+      <c r="H5" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="I5" s="10"/>
+      <c r="I5" s="6"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="10">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="10" t="s">
+      <c r="B6" s="7"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10" t="s">
+      <c r="G6" s="6"/>
+      <c r="H6" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I6" s="10"/>
+      <c r="I6" s="6"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="10" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10" t="s">
+      <c r="G7" s="6"/>
+      <c r="H7" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="I7" s="10"/>
+      <c r="I7" s="6"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="10">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="13" t="s">
+      <c r="B8" s="7"/>
+      <c r="C8" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10" t="s">
+      <c r="G8" s="6"/>
+      <c r="H8" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="I8" s="10"/>
+      <c r="I8" s="6"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+      <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="12" t="s">
+      <c r="B9" s="7"/>
+      <c r="C9" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10" t="s">
+      <c r="G9" s="6"/>
+      <c r="H9" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="6" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="10">
+      <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="10" t="s">
+      <c r="B10" s="7"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10" t="s">
+      <c r="G10" s="6"/>
+      <c r="H10" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I10" s="10"/>
+      <c r="I10" s="6"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
+      <c r="A11" s="6">
         <v>10</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="10" t="s">
+      <c r="B11" s="7"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10" t="s">
+      <c r="G11" s="6"/>
+      <c r="H11" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="I11" s="10"/>
+      <c r="I11" s="6"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
+      <c r="A12" s="6">
         <v>11</v>
       </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="13" t="s">
+      <c r="B12" s="7"/>
+      <c r="C12" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10" t="s">
+      <c r="G12" s="6"/>
+      <c r="H12" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I12" s="10"/>
+      <c r="I12" s="6"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10" t="s">
+      <c r="G13" s="6"/>
+      <c r="H13" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I13" s="10"/>
+      <c r="I13" s="6"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="10">
+      <c r="A14" s="6">
         <v>13</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="13" t="s">
+      <c r="B14" s="7"/>
+      <c r="C14" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10" t="s">
+      <c r="G14" s="6"/>
+      <c r="H14" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I14" s="10"/>
+      <c r="I14" s="6"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
+      <c r="A15" s="6">
         <v>14</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="13" t="s">
+      <c r="B15" s="7"/>
+      <c r="C15" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10" t="s">
+      <c r="G15" s="6"/>
+      <c r="H15" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I15" s="10"/>
+      <c r="I15" s="6"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="10">
+      <c r="A16" s="6">
         <v>15</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="13" t="s">
+      <c r="B16" s="7"/>
+      <c r="C16" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10" t="s">
+      <c r="G16" s="6"/>
+      <c r="H16" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="I16" s="10"/>
+      <c r="I16" s="6"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="10">
+      <c r="A17" s="6">
         <v>16</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10" t="s">
+      <c r="G17" s="6"/>
+      <c r="H17" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I17" s="10"/>
+      <c r="I17" s="6"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="10">
+      <c r="A18" s="6">
         <v>17</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="10" t="s">
+      <c r="B18" s="7"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10" t="s">
+      <c r="G18" s="6"/>
+      <c r="H18" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I18" s="10"/>
+      <c r="I18" s="6"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="10">
+      <c r="A19" s="6">
         <v>18</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="10" t="s">
+      <c r="B19" s="7"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10" t="s">
+      <c r="G19" s="6"/>
+      <c r="H19" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I19" s="10"/>
+      <c r="I19" s="6"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="10">
+      <c r="A20" s="6">
         <v>19</v>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="13" t="s">
+      <c r="B20" s="7"/>
+      <c r="C20" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E20" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10" t="s">
+      <c r="G20" s="6"/>
+      <c r="H20" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I20" s="10"/>
+      <c r="I20" s="6"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="10">
+      <c r="A21" s="6">
         <v>20</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="13" t="s">
+      <c r="B21" s="7"/>
+      <c r="C21" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10" t="s">
+      <c r="G21" s="6"/>
+      <c r="H21" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="I21" s="10"/>
+      <c r="I21" s="6"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="10">
+      <c r="A22" s="6">
         <v>21</v>
       </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="13" t="s">
+      <c r="B22" s="7"/>
+      <c r="C22" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10" t="s">
+      <c r="G22" s="6"/>
+      <c r="H22" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="I22" s="10"/>
+      <c r="I22" s="6"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="10">
+      <c r="A23" s="6">
         <v>22</v>
       </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="13" t="s">
+      <c r="B23" s="7"/>
+      <c r="C23" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10" t="s">
+      <c r="G23" s="6"/>
+      <c r="H23" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I23" s="10"/>
+      <c r="I23" s="6"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="10">
+      <c r="A24" s="6">
         <v>23</v>
       </c>
-      <c r="B24" s="11"/>
-      <c r="C24" s="12" t="s">
+      <c r="B24" s="7"/>
+      <c r="C24" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10" t="s">
+      <c r="G24" s="6"/>
+      <c r="H24" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I24" s="10"/>
+      <c r="I24" s="6"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="10">
+      <c r="A25" s="6">
         <v>24</v>
       </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="10" t="s">
+      <c r="B25" s="7"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10" t="s">
+      <c r="G25" s="6"/>
+      <c r="H25" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I25" s="10"/>
+      <c r="I25" s="6"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="10">
+      <c r="A26" s="6">
         <v>25</v>
       </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="10" t="s">
+      <c r="B26" s="7"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10" t="s">
+      <c r="G26" s="6"/>
+      <c r="H26" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="I26" s="10"/>
+      <c r="I26" s="6"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="10">
+      <c r="A27" s="6">
         <v>26</v>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="15" t="s">
+      <c r="B27" s="7"/>
+      <c r="C27" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10" t="s">
+      <c r="G27" s="6"/>
+      <c r="H27" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I27" s="10"/>
+      <c r="I27" s="6"/>
     </row>
     <row r="28" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A28" s="10">
+      <c r="A28" s="6">
         <v>27</v>
       </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="16" t="s">
+      <c r="B28" s="7"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F28" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10" t="s">
+      <c r="G28" s="6"/>
+      <c r="H28" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I28" s="10"/>
+      <c r="I28" s="6"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="10">
+      <c r="A29" s="6">
         <v>28</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10" t="s">
+      <c r="G29" s="6"/>
+      <c r="H29" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="I29" s="10"/>
+      <c r="I29" s="6"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="10">
+      <c r="A30" s="6">
         <v>29</v>
       </c>
-      <c r="B30" s="11"/>
-      <c r="C30" s="13" t="s">
+      <c r="B30" s="7"/>
+      <c r="C30" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="F30" s="14" t="s">
+      <c r="F30" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10" t="s">
+      <c r="G30" s="6"/>
+      <c r="H30" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="I30" s="10"/>
+      <c r="I30" s="6"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="10">
+      <c r="A31" s="6">
         <v>30</v>
       </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="13" t="s">
+      <c r="B31" s="7"/>
+      <c r="C31" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10" t="s">
+      <c r="G31" s="6"/>
+      <c r="H31" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="I31" s="10"/>
+      <c r="I31" s="6"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="10">
+      <c r="A32" s="6">
         <v>31</v>
       </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="12" t="s">
+      <c r="B32" s="7"/>
+      <c r="C32" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10" t="s">
+      <c r="G32" s="6"/>
+      <c r="H32" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="I32" s="10"/>
+      <c r="I32" s="6"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="10">
+      <c r="A33" s="6">
         <v>32</v>
       </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="10" t="s">
+      <c r="B33" s="7"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F33" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10" t="s">
+      <c r="G33" s="6"/>
+      <c r="H33" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="I33" s="10"/>
+      <c r="I33" s="6"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="10">
+      <c r="A34" s="6">
         <v>33</v>
       </c>
-      <c r="B34" s="11"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="10" t="s">
+      <c r="B34" s="7"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E34" s="14" t="s">
+      <c r="E34" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F34" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10" t="s">
+      <c r="G34" s="6"/>
+      <c r="H34" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="I34" s="10"/>
+      <c r="I34" s="6"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="10">
+      <c r="A35" s="6">
         <v>34</v>
       </c>
-      <c r="B35" s="11"/>
-      <c r="C35" s="12" t="s">
+      <c r="B35" s="7"/>
+      <c r="C35" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10" t="s">
+      <c r="G35" s="6"/>
+      <c r="H35" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I35" s="10"/>
+      <c r="I35" s="6"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="10">
+      <c r="A36" s="6">
         <v>35</v>
       </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="10" t="s">
+      <c r="B36" s="7"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E36" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="F36" s="14" t="s">
+      <c r="F36" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10" t="s">
+      <c r="G36" s="6"/>
+      <c r="H36" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I36" s="10"/>
+      <c r="I36" s="6"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="10"/>
-      <c r="B37" s="7" t="s">
+      <c r="A37" s="6"/>
+      <c r="B37" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="E37" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="D37" s="24" t="s">
-        <v>317</v>
-      </c>
-      <c r="E37" s="24" t="s">
+      <c r="F37" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="6"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="D38" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="F37" s="24" t="s">
-        <v>319</v>
-      </c>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="10"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="6" t="s">
+      <c r="E38" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="D38" s="24" t="s">
+      <c r="F38" s="19" t="s">
         <v>324</v>
       </c>
-      <c r="E38" s="24" t="s">
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="6"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="E39" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="F38" s="24" t="s">
+      <c r="F39" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="10"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="D39" s="24" t="s">
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="6"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="6"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="6"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="6"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="F43" s="19" t="s">
         <v>324</v>
       </c>
-      <c r="E39" s="24" t="s">
-        <v>327</v>
-      </c>
-      <c r="F39" s="24" t="s">
-        <v>328</v>
-      </c>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="10"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="6" t="s">
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="6"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="F44" s="19" t="s">
+        <v>326</v>
+      </c>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="6"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="22" t="s">
+        <v>347</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="6"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>352</v>
+      </c>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="6"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>352</v>
+      </c>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="6"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="6"/>
+      <c r="B49" s="14"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="F49" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="6"/>
+      <c r="B50" s="14"/>
+      <c r="C50" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="F50" s="19" t="s">
+        <v>352</v>
+      </c>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="6"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="F51" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="6"/>
+      <c r="B52" s="14"/>
+      <c r="C52" s="21"/>
+      <c r="D52" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="6"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="20" t="s">
+        <v>337</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="6"/>
+      <c r="B54" s="14"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="6"/>
+      <c r="B55" s="14"/>
+      <c r="C55" s="20"/>
+      <c r="D55" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="6"/>
+      <c r="B56" s="14"/>
+      <c r="C56" s="20"/>
+      <c r="D56" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="6"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="20"/>
+      <c r="D57" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="6"/>
+      <c r="B58" s="14"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="6"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="D59" s="10"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="6"/>
+      <c r="B60" s="14"/>
+      <c r="C60" s="20"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="10"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="6"/>
+      <c r="B61" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="C61" s="20" t="s">
         <v>329</v>
       </c>
-      <c r="D40" s="24" t="s">
-        <v>324</v>
-      </c>
-      <c r="E40" s="24" t="s">
+      <c r="D61" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="F40" s="24" t="s">
+      <c r="E61" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="10"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="D41" s="24" t="s">
-        <v>336</v>
-      </c>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="10"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="10"/>
-      <c r="B43" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="C43" s="6" t="s">
+      <c r="F61" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="D43" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="10"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="10">
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="6"/>
+      <c r="B62" s="14"/>
+      <c r="C62" s="20"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="10"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="6">
         <v>36</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B63" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C63" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D63" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E63" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F63" t="s">
         <v>201</v>
       </c>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10" t="s">
+      <c r="G63" s="6"/>
+      <c r="H63" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I45" s="10"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="10">
+      <c r="I63" s="6"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
         <v>37</v>
       </c>
-      <c r="B46" s="9"/>
-      <c r="C46" s="23"/>
-      <c r="D46" t="s">
+      <c r="B64" s="7"/>
+      <c r="C64" s="23"/>
+      <c r="D64" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E64" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F64" t="s">
         <v>201</v>
       </c>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10" t="s">
+      <c r="G64" s="6"/>
+      <c r="H64" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I46" s="10"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="10">
+      <c r="I64" s="6"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
         <v>38</v>
       </c>
-      <c r="B47" s="9"/>
-      <c r="C47" s="23"/>
-      <c r="D47" t="s">
+      <c r="B65" s="7"/>
+      <c r="C65" s="23"/>
+      <c r="D65" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E65" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F65" t="s">
         <v>198</v>
       </c>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10" t="s">
+      <c r="G65" s="6"/>
+      <c r="H65" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I47" s="10"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="10">
+      <c r="I65" s="6"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
         <v>39</v>
       </c>
-      <c r="B48" s="9"/>
-      <c r="C48" s="23" t="s">
+      <c r="B66" s="7"/>
+      <c r="C66" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D66" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E66" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F66" t="s">
         <v>201</v>
       </c>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10" t="s">
+      <c r="G66" s="6"/>
+      <c r="H66" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="I48" s="10" t="s">
+      <c r="I66" s="6" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="10">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
         <v>40</v>
       </c>
-      <c r="B49" s="9"/>
-      <c r="C49" s="23"/>
-      <c r="D49" t="s">
+      <c r="B67" s="7"/>
+      <c r="C67" s="23"/>
+      <c r="D67" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E67" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F67" t="s">
         <v>198</v>
       </c>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10" t="s">
+      <c r="G67" s="6"/>
+      <c r="H67" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I49" s="10"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="10">
+      <c r="I67" s="6"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
         <v>41</v>
       </c>
-      <c r="B50" s="9"/>
-      <c r="C50" s="8" t="s">
+      <c r="B68" s="7"/>
+      <c r="C68" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D68" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E68" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F68" t="s">
         <v>208</v>
       </c>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10" t="s">
+      <c r="G68" s="6"/>
+      <c r="H68" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I50" s="10"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="10">
+      <c r="I68" s="6"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="6">
         <v>42</v>
       </c>
-      <c r="B51" s="9"/>
-      <c r="C51" s="8"/>
-      <c r="D51" t="s">
+      <c r="B69" s="7"/>
+      <c r="C69" s="24"/>
+      <c r="D69" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E69" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F69" t="s">
         <v>205</v>
       </c>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10" t="s">
+      <c r="G69" s="6"/>
+      <c r="H69" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I51" s="10"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="10">
+      <c r="I69" s="6"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
         <v>43</v>
       </c>
-      <c r="B52" s="9"/>
-      <c r="C52" s="8"/>
-      <c r="D52" t="s">
+      <c r="B70" s="7"/>
+      <c r="C70" s="24"/>
+      <c r="D70" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E70" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F70" t="s">
         <v>205</v>
       </c>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10" t="s">
+      <c r="G70" s="6"/>
+      <c r="H70" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I52" s="10"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="10">
+      <c r="I70" s="6"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="6">
         <v>44</v>
       </c>
-      <c r="B53" s="9"/>
-      <c r="C53" s="8"/>
-      <c r="D53" t="s">
+      <c r="B71" s="7"/>
+      <c r="C71" s="24"/>
+      <c r="D71" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E71" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F71" t="s">
         <v>201</v>
       </c>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10" t="s">
+      <c r="G71" s="6"/>
+      <c r="H71" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I53" s="10"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="10">
+      <c r="I71" s="6"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
         <v>45</v>
       </c>
-      <c r="B54" s="9"/>
-      <c r="C54" s="8"/>
-      <c r="D54" t="s">
+      <c r="B72" s="7"/>
+      <c r="C72" s="24"/>
+      <c r="D72" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E72" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F72" t="s">
         <v>198</v>
       </c>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10" t="s">
+      <c r="G72" s="6"/>
+      <c r="H72" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I54" s="10"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="10">
+      <c r="I72" s="6"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
         <v>46</v>
       </c>
-      <c r="B55" s="9"/>
-      <c r="C55" s="8"/>
-      <c r="D55" t="s">
+      <c r="B73" s="7"/>
+      <c r="C73" s="24"/>
+      <c r="D73" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E73" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F73" t="s">
         <v>208</v>
       </c>
-      <c r="G55" s="10"/>
-      <c r="H55" s="10" t="s">
+      <c r="G73" s="6"/>
+      <c r="H73" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I55" s="10"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="10">
+      <c r="I73" s="6"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="6">
         <v>47</v>
       </c>
-      <c r="B56" s="9"/>
-      <c r="C56" s="8" t="s">
+      <c r="B74" s="7"/>
+      <c r="C74" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D74" t="s">
         <v>77</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E74" t="s">
         <v>207</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F74" t="s">
         <v>205</v>
       </c>
-      <c r="G56" s="10"/>
-      <c r="H56" s="10" t="s">
+      <c r="G74" s="6"/>
+      <c r="H74" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I56" s="10"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="10">
+      <c r="I74" s="6"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
         <v>48</v>
       </c>
-      <c r="B57" s="9"/>
-      <c r="C57" s="8"/>
-      <c r="D57" t="s">
+      <c r="B75" s="7"/>
+      <c r="C75" s="5"/>
+      <c r="D75" t="s">
         <v>78</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E75" t="s">
         <v>204</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F75" t="s">
         <v>205</v>
       </c>
-      <c r="G57" s="10"/>
-      <c r="H57" s="10" t="s">
+      <c r="G75" s="6"/>
+      <c r="H75" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I57" s="10"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="10">
+      <c r="I75" s="6"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
         <v>49</v>
       </c>
-      <c r="B58" s="9"/>
-      <c r="C58" s="8"/>
-      <c r="D58" t="s">
+      <c r="B76" s="7"/>
+      <c r="C76" s="5"/>
+      <c r="D76" t="s">
         <v>79</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E76" t="s">
         <v>203</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F76" t="s">
         <v>208</v>
       </c>
-      <c r="G58" s="10"/>
-      <c r="H58" s="10" t="s">
+      <c r="G76" s="6"/>
+      <c r="H76" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I58" s="10"/>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="10">
+      <c r="I76" s="6"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="6">
         <v>50</v>
       </c>
-      <c r="B59" s="9"/>
-      <c r="C59" s="8"/>
-      <c r="D59" t="s">
+      <c r="B77" s="7"/>
+      <c r="C77" s="5"/>
+      <c r="D77" t="s">
         <v>173</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E77" t="s">
         <v>262</v>
       </c>
-      <c r="F59" t="s">
+      <c r="F77" t="s">
         <v>239</v>
       </c>
-      <c r="G59" s="10"/>
-      <c r="H59" s="10" t="s">
+      <c r="G77" s="6"/>
+      <c r="H77" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I59" s="10"/>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="10">
+      <c r="I77" s="6"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="6">
         <v>51</v>
       </c>
-      <c r="B60" s="11" t="s">
+      <c r="B78" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="C78" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D60" s="10" t="s">
+      <c r="D78" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E60" s="14" t="s">
+      <c r="E78" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="F60" s="10" t="s">
+      <c r="F78" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="G60" s="10"/>
-      <c r="H60" s="10" t="s">
+      <c r="G78" s="6"/>
+      <c r="H78" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I60" s="10"/>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="10">
+      <c r="I78" s="6"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="6">
         <v>52</v>
       </c>
-      <c r="B61" s="11"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="10" t="s">
+      <c r="B79" s="7"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E61" s="14" t="s">
+      <c r="E79" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="F61" s="10" t="s">
+      <c r="F79" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="G61" s="10"/>
-      <c r="H61" s="10" t="s">
+      <c r="G79" s="6"/>
+      <c r="H79" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I61" s="10"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="10">
+      <c r="I79" s="6"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="6">
         <v>53</v>
       </c>
-      <c r="B62" s="11"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="10" t="s">
+      <c r="B80" s="7"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E62" s="14" t="s">
+      <c r="E80" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="F62" s="10" t="s">
+      <c r="F80" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="G62" s="10"/>
-      <c r="H62" s="10" t="s">
+      <c r="G80" s="6"/>
+      <c r="H80" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I62" s="10"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="10">
+      <c r="I80" s="6"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
         <v>54</v>
       </c>
-      <c r="B63" s="11"/>
-      <c r="C63" s="12" t="s">
+      <c r="B81" s="7"/>
+      <c r="C81" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D63" s="10" t="s">
+      <c r="D81" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E63" s="14" t="s">
+      <c r="E81" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="F63" s="10" t="s">
+      <c r="F81" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="G63" s="10"/>
-      <c r="H63" s="10" t="s">
+      <c r="G81" s="6"/>
+      <c r="H81" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I63" s="10"/>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="10">
+      <c r="I81" s="6"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="6">
         <v>55</v>
       </c>
-      <c r="B64" s="11"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="10" t="s">
+      <c r="B82" s="7"/>
+      <c r="C82" s="8"/>
+      <c r="D82" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E64" s="14" t="s">
+      <c r="E82" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="F64" s="10" t="s">
+      <c r="F82" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="G64" s="10"/>
-      <c r="H64" s="10" t="s">
+      <c r="G82" s="6"/>
+      <c r="H82" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I64" s="10"/>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="10">
+      <c r="I82" s="6"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="6">
         <v>56</v>
       </c>
-      <c r="B65" s="11"/>
-      <c r="C65" s="12"/>
-      <c r="D65" s="10" t="s">
+      <c r="B83" s="7"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E65" s="14" t="s">
+      <c r="E83" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="F65" s="10" t="s">
+      <c r="F83" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="G65" s="10"/>
-      <c r="H65" s="10" t="s">
+      <c r="G83" s="6"/>
+      <c r="H83" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I65" s="10"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="10">
+      <c r="I83" s="6"/>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
         <v>57</v>
       </c>
-      <c r="B66" s="11"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="10" t="s">
+      <c r="B84" s="7"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="E66" s="14" t="s">
+      <c r="E84" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="F66" s="10" t="s">
+      <c r="F84" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="G66" s="10"/>
-      <c r="H66" s="10" t="s">
+      <c r="G84" s="6"/>
+      <c r="H84" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I66" s="10"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="10">
+      <c r="I84" s="6"/>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
         <v>58</v>
       </c>
-      <c r="B67" s="11"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="10" t="s">
+      <c r="B85" s="7"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="E67" s="14" t="s">
+      <c r="E85" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="F67" s="10" t="s">
+      <c r="F85" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="G67" s="10"/>
-      <c r="H67" s="10" t="s">
+      <c r="G85" s="6"/>
+      <c r="H85" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I67" s="10"/>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="10">
+      <c r="I85" s="6"/>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="6">
         <v>59</v>
       </c>
-      <c r="B68" s="11"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="10" t="s">
+      <c r="B86" s="7"/>
+      <c r="C86" s="8"/>
+      <c r="D86" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E68" s="14" t="s">
+      <c r="E86" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="F68" s="10" t="s">
+      <c r="F86" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="G68" s="10"/>
-      <c r="H68" s="10" t="s">
+      <c r="G86" s="6"/>
+      <c r="H86" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I68" s="10"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="10">
+      <c r="I86" s="6"/>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
         <v>60</v>
       </c>
-      <c r="B69" s="11"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="10" t="s">
+      <c r="B87" s="7"/>
+      <c r="C87" s="8"/>
+      <c r="D87" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E69" s="14" t="s">
+      <c r="E87" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="F69" s="10" t="s">
+      <c r="F87" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="G69" s="10"/>
-      <c r="H69" s="10" t="s">
+      <c r="G87" s="6"/>
+      <c r="H87" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I69" s="10"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="10">
+      <c r="I87" s="6"/>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
         <v>61</v>
       </c>
-      <c r="B70" s="11"/>
-      <c r="C70" s="12" t="s">
+      <c r="B88" s="7"/>
+      <c r="C88" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D70" s="10" t="s">
+      <c r="D88" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E70" s="14" t="s">
+      <c r="E88" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="F70" s="10" t="s">
+      <c r="F88" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="G70" s="10"/>
-      <c r="H70" s="10" t="s">
+      <c r="G88" s="6"/>
+      <c r="H88" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I70" s="10"/>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="10">
+      <c r="I88" s="6"/>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
         <v>62</v>
       </c>
-      <c r="B71" s="11"/>
-      <c r="C71" s="12"/>
-      <c r="D71" s="10" t="s">
+      <c r="B89" s="7"/>
+      <c r="C89" s="8"/>
+      <c r="D89" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E71" s="14" t="s">
+      <c r="E89" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="F71" s="10" t="s">
+      <c r="F89" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="G71" s="10"/>
-      <c r="H71" s="10" t="s">
+      <c r="G89" s="6"/>
+      <c r="H89" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I71" s="10"/>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="10">
+      <c r="I89" s="6"/>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
         <v>63</v>
       </c>
-      <c r="B72" s="11" t="s">
+      <c r="B90" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C72" s="12" t="s">
+      <c r="C90" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D72" s="10" t="s">
+      <c r="D90" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E72" s="14" t="s">
+      <c r="E90" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="F72" s="10" t="s">
+      <c r="F90" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="G72" s="10"/>
-      <c r="H72" s="10" t="s">
+      <c r="G90" s="6"/>
+      <c r="H90" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I72" s="10"/>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="10">
+      <c r="I90" s="6"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="6">
         <v>64</v>
       </c>
-      <c r="B73" s="11"/>
-      <c r="C73" s="12"/>
-      <c r="D73" s="10" t="s">
+      <c r="B91" s="7"/>
+      <c r="C91" s="8"/>
+      <c r="D91" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="E73" s="14" t="s">
+      <c r="E91" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="F73" s="10" t="s">
+      <c r="F91" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="G73" s="10"/>
-      <c r="H73" s="10" t="s">
+      <c r="G91" s="6"/>
+      <c r="H91" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I73" s="10"/>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="10">
+      <c r="I91" s="6"/>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="6">
         <v>65</v>
       </c>
-      <c r="B74" s="11" t="s">
+      <c r="B92" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C74" s="12" t="s">
+      <c r="C92" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D74" s="10" t="s">
+      <c r="D92" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E74" s="14" t="s">
+      <c r="E92" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="F74" s="10" t="s">
+      <c r="F92" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="G74" s="10"/>
-      <c r="H74" s="10" t="s">
+      <c r="G92" s="6"/>
+      <c r="H92" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I74" s="10"/>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="10">
+      <c r="I92" s="6"/>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="6">
         <v>66</v>
       </c>
-      <c r="B75" s="11"/>
-      <c r="C75" s="12"/>
-      <c r="D75" s="10" t="s">
+      <c r="B93" s="7"/>
+      <c r="C93" s="8"/>
+      <c r="D93" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="E75" s="14" t="s">
+      <c r="E93" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="F75" s="10" t="s">
+      <c r="F93" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="G75" s="10"/>
-      <c r="H75" s="10" t="s">
+      <c r="G93" s="6"/>
+      <c r="H93" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I75" s="10"/>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="10">
+      <c r="I93" s="6"/>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="6">
         <v>67</v>
       </c>
-      <c r="B76" s="11"/>
-      <c r="C76" s="12"/>
-      <c r="D76" s="10" t="s">
+      <c r="B94" s="7"/>
+      <c r="C94" s="8"/>
+      <c r="D94" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E76" s="14" t="s">
+      <c r="E94" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="F76" s="10" t="s">
+      <c r="F94" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="G76" s="10"/>
-      <c r="H76" s="10" t="s">
+      <c r="G94" s="6"/>
+      <c r="H94" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I76" s="10"/>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="10">
+      <c r="I94" s="6"/>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="6">
         <v>68</v>
       </c>
-      <c r="B77" s="11"/>
-      <c r="C77" s="13" t="s">
+      <c r="B95" s="7"/>
+      <c r="C95" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D77" s="10" t="s">
+      <c r="D95" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E77" s="14" t="s">
+      <c r="E95" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="F77" s="14" t="s">
+      <c r="F95" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="G77" s="10"/>
-      <c r="H77" s="10" t="s">
+      <c r="G95" s="6"/>
+      <c r="H95" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I77" s="10"/>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="10">
+      <c r="I95" s="6"/>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="6">
         <v>69</v>
       </c>
-      <c r="B78" s="11" t="s">
+      <c r="B96" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="C78" s="12" t="s">
+      <c r="C96" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D78" s="10" t="s">
+      <c r="D96" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E78" s="14" t="s">
+      <c r="E96" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="F78" s="14" t="s">
+      <c r="F96" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="G78" s="10"/>
-      <c r="H78" s="10" t="s">
+      <c r="G96" s="6"/>
+      <c r="H96" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I78" s="10"/>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="10">
+      <c r="I96" s="6"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="6">
         <v>70</v>
       </c>
-      <c r="B79" s="11"/>
-      <c r="C79" s="12"/>
-      <c r="D79" s="10" t="s">
+      <c r="B97" s="7"/>
+      <c r="C97" s="8"/>
+      <c r="D97" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E79" s="14" t="s">
+      <c r="E97" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="F79" s="14" t="s">
+      <c r="F97" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="G79" s="10"/>
-      <c r="H79" s="10" t="s">
+      <c r="G97" s="6"/>
+      <c r="H97" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I79" s="10"/>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="10">
+      <c r="I97" s="6"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="6">
         <v>71</v>
       </c>
-      <c r="B80" s="11"/>
-      <c r="C80" s="12"/>
-      <c r="D80" s="10" t="s">
+      <c r="B98" s="7"/>
+      <c r="C98" s="8"/>
+      <c r="D98" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E80" s="14" t="s">
+      <c r="E98" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="F80" s="14" t="s">
+      <c r="F98" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="G80" s="10"/>
-      <c r="H80" s="10" t="s">
+      <c r="G98" s="6"/>
+      <c r="H98" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I80" s="10"/>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="10">
+      <c r="I98" s="6"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="6">
         <v>72</v>
       </c>
-      <c r="B81" s="11"/>
-      <c r="C81" s="12" t="s">
+      <c r="B99" s="7"/>
+      <c r="C99" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D81" s="10" t="s">
+      <c r="D99" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E81" s="10" t="s">
+      <c r="E99" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="F81" s="10" t="s">
+      <c r="F99" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="G81" s="10"/>
-      <c r="H81" s="10" t="s">
+      <c r="G99" s="6"/>
+      <c r="H99" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I81" s="10"/>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="10">
+      <c r="I99" s="6"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="6">
         <v>73</v>
       </c>
-      <c r="B82" s="11"/>
-      <c r="C82" s="12"/>
-      <c r="D82" s="10" t="s">
+      <c r="B100" s="7"/>
+      <c r="C100" s="8"/>
+      <c r="D100" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="E82" s="10" t="s">
+      <c r="E100" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="F82" s="10" t="s">
+      <c r="F100" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="G82" s="10"/>
-      <c r="H82" s="10" t="s">
+      <c r="G100" s="6"/>
+      <c r="H100" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I82" s="10"/>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" s="10">
+      <c r="I100" s="6"/>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="6">
         <v>74</v>
       </c>
-      <c r="B83" s="11"/>
-      <c r="C83" s="12"/>
-      <c r="D83" s="10" t="s">
+      <c r="B101" s="7"/>
+      <c r="C101" s="8"/>
+      <c r="D101" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="E83" s="10" t="s">
+      <c r="E101" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="F83" s="10" t="s">
+      <c r="F101" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="G83" s="10"/>
-      <c r="H83" s="10" t="s">
+      <c r="G101" s="6"/>
+      <c r="H101" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I83" s="10"/>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="10">
+      <c r="I101" s="6"/>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="6">
         <v>75</v>
       </c>
-      <c r="B84" s="11" t="s">
+      <c r="B102" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="C84" s="12" t="s">
+      <c r="C102" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="D84" s="10" t="s">
+      <c r="D102" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E84" s="10" t="s">
+      <c r="E102" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="F84" s="10" t="s">
+      <c r="F102" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="G84" s="10"/>
-      <c r="H84" s="10" t="s">
+      <c r="G102" s="6"/>
+      <c r="H102" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I84" s="10"/>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" s="10">
+      <c r="I102" s="6"/>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="6">
         <v>76</v>
       </c>
-      <c r="B85" s="11"/>
-      <c r="C85" s="12"/>
-      <c r="D85" s="10" t="s">
+      <c r="B103" s="7"/>
+      <c r="C103" s="8"/>
+      <c r="D103" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="E85" s="10" t="s">
+      <c r="E103" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="F85" s="10" t="s">
+      <c r="F103" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="G85" s="10"/>
-      <c r="H85" s="10" t="s">
+      <c r="G103" s="6"/>
+      <c r="H103" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I85" s="10"/>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="10">
+      <c r="I103" s="6"/>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="6">
         <v>77</v>
       </c>
-      <c r="B86" s="11"/>
-      <c r="C86" s="12"/>
-      <c r="D86" s="10" t="s">
+      <c r="B104" s="7"/>
+      <c r="C104" s="8"/>
+      <c r="D104" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="E86" s="10" t="s">
+      <c r="E104" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="F86" s="10" t="s">
+      <c r="F104" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="G86" s="10"/>
-      <c r="H86" s="10" t="s">
+      <c r="G104" s="6"/>
+      <c r="H104" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I86" s="10"/>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="10">
+      <c r="I104" s="6"/>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="6">
         <v>78</v>
       </c>
-      <c r="B87" s="11"/>
-      <c r="C87" s="15" t="s">
+      <c r="B105" s="7"/>
+      <c r="C105" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="D87" s="10" t="s">
+      <c r="D105" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E87" s="10" t="s">
+      <c r="E105" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F87" s="10" t="s">
+      <c r="F105" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="G87" s="10"/>
-      <c r="H87" s="10" t="s">
+      <c r="G105" s="6"/>
+      <c r="H105" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I87" s="10"/>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="10">
+      <c r="I105" s="6"/>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="6">
         <v>79</v>
       </c>
-      <c r="B88" s="11"/>
-      <c r="C88" s="15"/>
-      <c r="D88" s="10" t="s">
+      <c r="B106" s="7"/>
+      <c r="C106" s="11"/>
+      <c r="D106" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E88" s="10" t="s">
+      <c r="E106" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F88" s="10" t="s">
+      <c r="F106" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="G88" s="10"/>
-      <c r="H88" s="10" t="s">
+      <c r="G106" s="6"/>
+      <c r="H106" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I88" s="10"/>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="10">
+      <c r="I106" s="6"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="6">
         <v>80</v>
       </c>
-      <c r="B89" s="11"/>
-      <c r="C89" s="15" t="s">
+      <c r="B107" s="7"/>
+      <c r="C107" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="D89" s="10" t="s">
+      <c r="D107" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="E89" s="10" t="s">
+      <c r="E107" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F89" s="10" t="s">
+      <c r="F107" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="G89" s="10"/>
-      <c r="H89" s="10" t="s">
+      <c r="G107" s="6"/>
+      <c r="H107" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="I89" s="10"/>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="10">
+      <c r="I107" s="6"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="6">
         <v>81</v>
       </c>
-      <c r="B90" s="11"/>
-      <c r="C90" s="15"/>
-      <c r="D90" s="10" t="s">
+      <c r="B108" s="7"/>
+      <c r="C108" s="11"/>
+      <c r="D108" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="E90" s="10" t="s">
+      <c r="E108" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F90" s="10" t="s">
+      <c r="F108" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="G90" s="10"/>
-      <c r="H90" s="10" t="s">
+      <c r="G108" s="6"/>
+      <c r="H108" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="I90" s="10"/>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" s="10">
+      <c r="I108" s="6"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="6">
         <v>82</v>
       </c>
-      <c r="B91" s="11"/>
-      <c r="C91" s="15"/>
-      <c r="D91" s="10" t="s">
+      <c r="B109" s="7"/>
+      <c r="C109" s="11"/>
+      <c r="D109" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="E91" s="10" t="s">
+      <c r="E109" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F91" s="10" t="s">
+      <c r="F109" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="G91" s="10"/>
-      <c r="H91" s="10" t="s">
+      <c r="G109" s="6"/>
+      <c r="H109" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="I91" s="10"/>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="10">
+      <c r="I109" s="6"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="6">
         <v>83</v>
       </c>
-      <c r="B92" s="11"/>
-      <c r="C92" s="15" t="s">
+      <c r="B110" s="7"/>
+      <c r="C110" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="D92" s="10" t="s">
+      <c r="D110" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E92" s="10" t="s">
+      <c r="E110" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F92" s="10" t="s">
+      <c r="F110" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="G92" s="10"/>
-      <c r="H92" s="10" t="s">
+      <c r="G110" s="6"/>
+      <c r="H110" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I92" s="10"/>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="10">
+      <c r="I110" s="6"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="6">
         <v>84</v>
       </c>
-      <c r="B93" s="11"/>
-      <c r="C93" s="15"/>
-      <c r="D93" s="10" t="s">
+      <c r="B111" s="7"/>
+      <c r="C111" s="11"/>
+      <c r="D111" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E93" s="10" t="s">
+      <c r="E111" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F93" s="10" t="s">
+      <c r="F111" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="G93" s="10"/>
-      <c r="H93" s="10" t="s">
+      <c r="G111" s="6"/>
+      <c r="H111" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I93" s="10"/>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" s="10">
+      <c r="I111" s="6"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="6">
         <v>85</v>
       </c>
-      <c r="B94" s="11"/>
-      <c r="C94" s="15" t="s">
+      <c r="B112" s="7"/>
+      <c r="C112" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D94" s="10" t="s">
+      <c r="D112" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="E94" s="10" t="s">
+      <c r="E112" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F94" s="10" t="s">
+      <c r="F112" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="G94" s="10"/>
-      <c r="H94" s="10" t="s">
+      <c r="G112" s="6"/>
+      <c r="H112" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I94" s="10"/>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="10">
+      <c r="I112" s="6"/>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" s="6">
         <v>86</v>
       </c>
-      <c r="B95" s="11"/>
-      <c r="C95" s="15"/>
-      <c r="D95" s="10" t="s">
+      <c r="B113" s="7"/>
+      <c r="C113" s="11"/>
+      <c r="D113" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E95" s="10" t="s">
+      <c r="E113" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F95" s="10" t="s">
+      <c r="F113" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="G95" s="10"/>
-      <c r="H95" s="10" t="s">
+      <c r="G113" s="6"/>
+      <c r="H113" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I95" s="10"/>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="10">
+      <c r="I113" s="6"/>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="6">
         <v>87</v>
       </c>
-      <c r="B96" s="11"/>
-      <c r="C96" s="15"/>
-      <c r="D96" s="10" t="s">
+      <c r="B114" s="7"/>
+      <c r="C114" s="11"/>
+      <c r="D114" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="E96" s="10" t="s">
+      <c r="E114" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F96" s="10" t="s">
+      <c r="F114" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="G96" s="10"/>
-      <c r="H96" s="10" t="s">
+      <c r="G114" s="6"/>
+      <c r="H114" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I96" s="10"/>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="10">
+      <c r="I114" s="6"/>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" s="6">
         <v>88</v>
       </c>
-      <c r="B97" s="11"/>
-      <c r="C97" s="10" t="s">
+      <c r="B115" s="7"/>
+      <c r="C115" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="D97" s="10" t="s">
+      <c r="D115" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E97" s="10" t="s">
+      <c r="E115" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F97" s="10" t="s">
+      <c r="F115" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="G97" s="10"/>
-      <c r="H97" s="10" t="s">
+      <c r="G115" s="6"/>
+      <c r="H115" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I97" s="10"/>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="10">
+      <c r="I115" s="6"/>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" s="6">
         <v>89</v>
       </c>
-      <c r="B98" s="11"/>
-      <c r="C98" s="15" t="s">
+      <c r="B116" s="7"/>
+      <c r="C116" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="D98" s="10" t="s">
+      <c r="D116" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="E98" s="10" t="s">
+      <c r="E116" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="F98" s="10" t="s">
+      <c r="F116" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="G98" s="10"/>
-      <c r="H98" s="10" t="s">
+      <c r="G116" s="6"/>
+      <c r="H116" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I98" s="10"/>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" s="10">
+      <c r="I116" s="6"/>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" s="6">
         <v>90</v>
       </c>
-      <c r="B99" s="11"/>
-      <c r="C99" s="15"/>
-      <c r="D99" s="10" t="s">
+      <c r="B117" s="7"/>
+      <c r="C117" s="11"/>
+      <c r="D117" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="E99" s="10" t="s">
+      <c r="E117" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="F99" s="10" t="s">
+      <c r="F117" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="G99" s="10"/>
-      <c r="H99" s="10" t="s">
+      <c r="G117" s="6"/>
+      <c r="H117" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I99" s="10"/>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="10">
+      <c r="I117" s="6"/>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" s="6">
         <v>91</v>
       </c>
-      <c r="B100" s="11"/>
-      <c r="C100" s="15"/>
-      <c r="D100" s="10" t="s">
+      <c r="B118" s="7"/>
+      <c r="C118" s="11"/>
+      <c r="D118" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="E100" s="10" t="s">
+      <c r="E118" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="F100" s="10" t="s">
+      <c r="F118" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="G100" s="10"/>
-      <c r="H100" s="10" t="s">
+      <c r="G118" s="6"/>
+      <c r="H118" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I100" s="10"/>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="10">
+      <c r="I118" s="6"/>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" s="6">
         <v>92</v>
       </c>
-      <c r="B101" s="11"/>
-      <c r="C101" s="15"/>
-      <c r="D101" s="10" t="s">
+      <c r="B119" s="7"/>
+      <c r="C119" s="11"/>
+      <c r="D119" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="E101" s="10" t="s">
+      <c r="E119" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="F101" s="10" t="s">
+      <c r="F119" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="G101" s="10"/>
-      <c r="H101" s="10" t="s">
+      <c r="G119" s="6"/>
+      <c r="H119" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I101" s="10"/>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" s="10">
+      <c r="I119" s="6"/>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A120" s="6">
         <v>93</v>
       </c>
-      <c r="B102" s="11" t="s">
+      <c r="B120" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C102" s="15" t="s">
+      <c r="C120" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="D102" s="10" t="s">
+      <c r="D120" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="E102" s="10" t="s">
+      <c r="E120" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="F102" s="10" t="s">
+      <c r="F120" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="G102" s="10"/>
-      <c r="H102" s="10" t="s">
+      <c r="G120" s="6"/>
+      <c r="H120" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I102" s="10"/>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="10">
+      <c r="I120" s="6"/>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121" s="6">
         <v>94</v>
       </c>
-      <c r="B103" s="11"/>
-      <c r="C103" s="15"/>
-      <c r="D103" s="10" t="s">
+      <c r="B121" s="7"/>
+      <c r="C121" s="11"/>
+      <c r="D121" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E103" s="10" t="s">
+      <c r="E121" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="F103" s="10" t="s">
+      <c r="F121" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="G103" s="10"/>
-      <c r="H103" s="10" t="s">
+      <c r="G121" s="6"/>
+      <c r="H121" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I103" s="10"/>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="10">
+      <c r="I121" s="6"/>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" s="6">
         <v>95</v>
       </c>
-      <c r="B104" s="11"/>
-      <c r="C104" s="15"/>
-      <c r="D104" s="10" t="s">
+      <c r="B122" s="7"/>
+      <c r="C122" s="11"/>
+      <c r="D122" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="E104" s="10" t="s">
+      <c r="E122" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="F104" s="10" t="s">
+      <c r="F122" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="G104" s="10"/>
-      <c r="H104" s="10" t="s">
+      <c r="G122" s="6"/>
+      <c r="H122" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I104" s="10"/>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="10">
+      <c r="I122" s="6"/>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" s="6">
         <v>96</v>
       </c>
-      <c r="B105" s="11" t="s">
+      <c r="B123" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="C105" s="17" t="s">
+      <c r="C123" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="D105" s="10" t="s">
+      <c r="D123" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="E105" s="10" t="s">
+      <c r="E123" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F105" s="10" t="s">
+      <c r="F123" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="G105" s="10"/>
-      <c r="H105" s="10" t="s">
+      <c r="G123" s="6"/>
+      <c r="H123" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I105" s="10"/>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" s="10">
+      <c r="I123" s="6"/>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" s="6">
         <v>97</v>
       </c>
-      <c r="B106" s="11"/>
-      <c r="C106" s="17" t="s">
+      <c r="B124" s="7"/>
+      <c r="C124" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="D106" s="10" t="s">
+      <c r="D124" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E106" s="10" t="s">
+      <c r="E124" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="F106" s="10" t="s">
+      <c r="F124" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="G106" s="10"/>
-      <c r="H106" s="10" t="s">
+      <c r="G124" s="6"/>
+      <c r="H124" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I106" s="10"/>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="10">
+      <c r="I124" s="6"/>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" s="6">
         <v>98</v>
       </c>
-      <c r="B107" s="11"/>
-      <c r="C107" s="10" t="s">
+      <c r="B125" s="7"/>
+      <c r="C125" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D107" s="10" t="s">
+      <c r="D125" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E107" s="10" t="s">
+      <c r="E125" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="F107" s="10" t="s">
+      <c r="F125" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="G107" s="10"/>
-      <c r="H107" s="10" t="s">
+      <c r="G125" s="6"/>
+      <c r="H125" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I107" s="10"/>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" s="10">
+      <c r="I125" s="6"/>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" s="6">
         <v>99</v>
       </c>
-      <c r="B108" s="11"/>
-      <c r="C108" s="10" t="s">
+      <c r="B126" s="7"/>
+      <c r="C126" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D108" s="10" t="s">
+      <c r="D126" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E108" s="10" t="s">
+      <c r="E126" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="F108" s="10" t="s">
+      <c r="F126" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="G108" s="10"/>
-      <c r="H108" s="10" t="s">
+      <c r="G126" s="6"/>
+      <c r="H126" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I108" s="10"/>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="10">
+      <c r="I126" s="6"/>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" s="6">
         <v>100</v>
       </c>
-      <c r="B109" s="11"/>
-      <c r="C109" s="10" t="s">
+      <c r="B127" s="7"/>
+      <c r="C127" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="D109" s="10" t="s">
+      <c r="D127" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="E109" s="10" t="s">
+      <c r="E127" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="F109" s="10" t="s">
+      <c r="F127" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="G109" s="10"/>
-      <c r="H109" s="10" t="s">
+      <c r="G127" s="6"/>
+      <c r="H127" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I109" s="10"/>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="10">
+      <c r="I127" s="6"/>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" s="6">
         <v>101</v>
       </c>
-      <c r="B110" s="11"/>
-      <c r="C110" s="15" t="s">
+      <c r="B128" s="7"/>
+      <c r="C128" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="D110" s="10" t="s">
+      <c r="D128" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E110" s="10" t="s">
+      <c r="E128" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="F110" s="10" t="s">
+      <c r="F128" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="G110" s="10"/>
-      <c r="H110" s="10" t="s">
+      <c r="G128" s="6"/>
+      <c r="H128" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I110" s="10"/>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="10">
+      <c r="I128" s="6"/>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" s="6">
         <v>102</v>
       </c>
-      <c r="B111" s="11"/>
-      <c r="C111" s="15"/>
-      <c r="D111" s="10" t="s">
+      <c r="B129" s="7"/>
+      <c r="C129" s="11"/>
+      <c r="D129" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="E111" s="10" t="s">
+      <c r="E129" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="F111" s="10" t="s">
+      <c r="F129" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="G111" s="10"/>
-      <c r="H111" s="10" t="s">
+      <c r="G129" s="6"/>
+      <c r="H129" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I111" s="10"/>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="10">
+      <c r="I129" s="6"/>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" s="6">
         <v>103</v>
       </c>
-      <c r="B112" s="11"/>
-      <c r="C112" s="15"/>
-      <c r="D112" s="10" t="s">
+      <c r="B130" s="7"/>
+      <c r="C130" s="11"/>
+      <c r="D130" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="E112" s="10" t="s">
+      <c r="E130" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="F112" s="10" t="s">
+      <c r="F130" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="G112" s="10"/>
-      <c r="H112" s="10" t="s">
+      <c r="G130" s="6"/>
+      <c r="H130" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I112" s="10"/>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" s="10">
+      <c r="I130" s="6"/>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" s="6">
         <v>104</v>
       </c>
-      <c r="B113" s="11"/>
-      <c r="C113" s="15" t="s">
+      <c r="B131" s="7"/>
+      <c r="C131" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="D113" s="10" t="s">
+      <c r="D131" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E113" s="10" t="s">
+      <c r="E131" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="F113" s="10" t="s">
+      <c r="F131" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="G113" s="10"/>
-      <c r="H113" s="10" t="s">
+      <c r="G131" s="6"/>
+      <c r="H131" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I113" s="10"/>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="10">
+      <c r="I131" s="6"/>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" s="6">
         <v>105</v>
       </c>
-      <c r="B114" s="11"/>
-      <c r="C114" s="15"/>
-      <c r="D114" s="10" t="s">
+      <c r="B132" s="7"/>
+      <c r="C132" s="11"/>
+      <c r="D132" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="E114" s="10" t="s">
+      <c r="E132" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="F114" s="10" t="s">
+      <c r="F132" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="G114" s="10"/>
-      <c r="H114" s="10" t="s">
+      <c r="G132" s="6"/>
+      <c r="H132" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I114" s="10"/>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="10">
+      <c r="I132" s="6"/>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" s="6">
         <v>106</v>
       </c>
-      <c r="B115" s="11"/>
-      <c r="C115" s="15"/>
-      <c r="D115" s="10" t="s">
+      <c r="B133" s="7"/>
+      <c r="C133" s="11"/>
+      <c r="D133" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="E115" s="10" t="s">
+      <c r="E133" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="F115" s="10" t="s">
+      <c r="F133" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="G115" s="10"/>
-      <c r="H115" s="10" t="s">
+      <c r="G133" s="6"/>
+      <c r="H133" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I115" s="10"/>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" s="10">
+      <c r="I133" s="6"/>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A134" s="6">
         <v>107</v>
       </c>
-      <c r="B116" s="11"/>
-      <c r="C116" s="15" t="s">
+      <c r="B134" s="7"/>
+      <c r="C134" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="D116" s="10" t="s">
+      <c r="D134" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E116" s="10" t="s">
+      <c r="E134" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="F116" s="10" t="s">
+      <c r="F134" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="G116" s="10"/>
-      <c r="H116" s="10" t="s">
+      <c r="G134" s="6"/>
+      <c r="H134" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I116" s="10"/>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="10">
+      <c r="I134" s="6"/>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A135" s="6">
         <v>108</v>
       </c>
-      <c r="B117" s="11"/>
-      <c r="C117" s="15"/>
-      <c r="D117" s="10" t="s">
+      <c r="B135" s="7"/>
+      <c r="C135" s="11"/>
+      <c r="D135" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="E117" s="10" t="s">
+      <c r="E135" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="F117" s="10" t="s">
+      <c r="F135" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="G117" s="10"/>
-      <c r="H117" s="10" t="s">
+      <c r="G135" s="6"/>
+      <c r="H135" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I117" s="10"/>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" s="10">
+      <c r="I135" s="6"/>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A136" s="6">
         <v>109</v>
       </c>
-      <c r="B118" s="11"/>
-      <c r="C118" s="15"/>
-      <c r="D118" s="10" t="s">
+      <c r="B136" s="7"/>
+      <c r="C136" s="11"/>
+      <c r="D136" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="E118" s="10" t="s">
+      <c r="E136" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="F118" s="10" t="s">
+      <c r="F136" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="G118" s="10"/>
-      <c r="H118" s="10" t="s">
+      <c r="G136" s="6"/>
+      <c r="H136" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="I118" s="10"/>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" s="10">
+      <c r="I136" s="6"/>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A137" s="6">
         <v>110</v>
       </c>
-      <c r="B119" s="11"/>
-      <c r="C119" s="15" t="s">
+      <c r="B137" s="7"/>
+      <c r="C137" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="D119" s="10" t="s">
+      <c r="D137" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E119" s="10" t="s">
+      <c r="E137" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="F119" s="10" t="s">
+      <c r="F137" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="G119" s="10"/>
-      <c r="H119" s="10" t="s">
+      <c r="G137" s="6"/>
+      <c r="H137" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="I119" s="10"/>
-    </row>
-    <row r="120" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A120" s="10">
+      <c r="I137" s="6"/>
+    </row>
+    <row r="138" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A138" s="6">
         <v>111</v>
       </c>
-      <c r="B120" s="11"/>
-      <c r="C120" s="15"/>
-      <c r="D120" s="16" t="s">
+      <c r="B138" s="7"/>
+      <c r="C138" s="11"/>
+      <c r="D138" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="E120" s="10" t="s">
+      <c r="E138" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="F120" s="10" t="s">
+      <c r="F138" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="G120" s="10"/>
-      <c r="H120" s="10" t="s">
+      <c r="G138" s="6"/>
+      <c r="H138" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I120" s="10"/>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" s="10">
+      <c r="I138" s="6"/>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A139" s="6">
         <v>112</v>
       </c>
-      <c r="B121" s="11"/>
-      <c r="C121" s="15"/>
-      <c r="D121" s="13" t="s">
+      <c r="B139" s="7"/>
+      <c r="C139" s="11"/>
+      <c r="D139" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="E121" s="10" t="s">
+      <c r="E139" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="F121" s="10" t="s">
+      <c r="F139" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="G121" s="10"/>
-      <c r="H121" s="10" t="s">
+      <c r="G139" s="6"/>
+      <c r="H139" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I121" s="10"/>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="10">
+      <c r="I139" s="6"/>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A140" s="6">
         <v>113</v>
       </c>
-      <c r="B122" s="11"/>
-      <c r="C122" s="15"/>
-      <c r="D122" s="13" t="s">
+      <c r="B140" s="7"/>
+      <c r="C140" s="11"/>
+      <c r="D140" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="E122" s="10" t="s">
+      <c r="E140" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="F122" s="10" t="s">
+      <c r="F140" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="G122" s="10"/>
-      <c r="H122" s="10" t="s">
+      <c r="G140" s="6"/>
+      <c r="H140" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I122" s="10"/>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="10">
+      <c r="I140" s="6"/>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A141" s="6">
         <v>114</v>
       </c>
-      <c r="B123" s="11"/>
-      <c r="C123" s="15"/>
-      <c r="D123" s="13" t="s">
+      <c r="B141" s="7"/>
+      <c r="C141" s="11"/>
+      <c r="D141" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="E123" s="10" t="s">
+      <c r="E141" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="F123" s="10" t="s">
+      <c r="F141" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="G123" s="10"/>
-      <c r="H123" s="10" t="s">
+      <c r="G141" s="6"/>
+      <c r="H141" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="I123" s="10"/>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" s="10">
+      <c r="I141" s="6"/>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A142" s="6">
         <v>115</v>
       </c>
-      <c r="B124" s="11" t="s">
+      <c r="B142" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C124" s="10" t="s">
+      <c r="C142" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="D124" s="10" t="s">
+      <c r="D142" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="E124" s="10" t="s">
+      <c r="E142" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="F124" s="10" t="s">
+      <c r="F142" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="G124" s="10"/>
-      <c r="H124" s="10" t="s">
+      <c r="G142" s="6"/>
+      <c r="H142" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I124" s="10"/>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A125" s="10">
+      <c r="I142" s="6"/>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A143" s="6">
         <v>116</v>
       </c>
-      <c r="B125" s="11"/>
-      <c r="C125" s="10" t="s">
+      <c r="B143" s="7"/>
+      <c r="C143" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="D125" s="10" t="s">
+      <c r="D143" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="E125" s="10" t="s">
+      <c r="E143" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="F125" s="10" t="s">
+      <c r="F143" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="G125" s="10"/>
-      <c r="H125" s="10" t="s">
+      <c r="G143" s="6"/>
+      <c r="H143" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I125" s="10"/>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A126" s="10">
+      <c r="I143" s="6"/>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" s="6">
         <v>117</v>
       </c>
-      <c r="B126" s="18" t="s">
+      <c r="B144" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="C126" s="10" t="s">
+      <c r="C144" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="D126" s="10" t="s">
+      <c r="D144" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="E126" s="10" t="s">
+      <c r="E144" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="F126" s="10" t="s">
+      <c r="F144" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="G126" s="10"/>
-      <c r="H126" s="10" t="s">
+      <c r="G144" s="6"/>
+      <c r="H144" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I126" s="10"/>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A127" s="10">
+      <c r="I144" s="6"/>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" s="6">
         <v>118</v>
       </c>
-      <c r="B127" s="11" t="s">
+      <c r="B145" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C127" s="15" t="s">
+      <c r="C145" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="D127" s="10" t="s">
+      <c r="D145" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="E127" s="10" t="s">
+      <c r="E145" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="F127" s="10" t="s">
+      <c r="F145" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="G127" s="10"/>
-      <c r="H127" s="10" t="s">
+      <c r="G145" s="6"/>
+      <c r="H145" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I127" s="10"/>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A128" s="10">
+      <c r="I145" s="6"/>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" s="6">
         <v>119</v>
       </c>
-      <c r="B128" s="11"/>
-      <c r="C128" s="15"/>
-      <c r="D128" s="10" t="s">
+      <c r="B146" s="7"/>
+      <c r="C146" s="11"/>
+      <c r="D146" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="E128" s="10" t="s">
+      <c r="E146" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="F128" s="10" t="s">
+      <c r="F146" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="G128" s="10"/>
-      <c r="H128" s="10" t="s">
+      <c r="G146" s="6"/>
+      <c r="H146" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I128" s="10"/>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A129" s="10">
+      <c r="I146" s="6"/>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" s="6">
         <v>120</v>
       </c>
-      <c r="B129" s="11"/>
-      <c r="C129" s="15"/>
-      <c r="D129" s="10" t="s">
+      <c r="B147" s="7"/>
+      <c r="C147" s="11"/>
+      <c r="D147" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="E129" s="10" t="s">
+      <c r="E147" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="F129" s="10" t="s">
+      <c r="F147" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="G129" s="10"/>
-      <c r="H129" s="10" t="s">
+      <c r="G147" s="6"/>
+      <c r="H147" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="I129" s="10"/>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A130" s="10">
+      <c r="I147" s="6"/>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" s="6">
         <v>121</v>
       </c>
-      <c r="B130" s="11"/>
-      <c r="C130" s="15" t="s">
+      <c r="B148" s="7"/>
+      <c r="C148" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="D130" s="10" t="s">
+      <c r="D148" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="E130" s="10" t="s">
+      <c r="E148" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="F130" s="10" t="s">
+      <c r="F148" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="G130" s="10"/>
-      <c r="H130" s="10" t="s">
+      <c r="G148" s="6"/>
+      <c r="H148" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I130" s="10"/>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A131" s="10">
+      <c r="I148" s="6"/>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" s="6">
         <v>122</v>
       </c>
-      <c r="B131" s="11"/>
-      <c r="C131" s="15"/>
-      <c r="D131" s="10" t="s">
+      <c r="B149" s="7"/>
+      <c r="C149" s="11"/>
+      <c r="D149" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="E131" s="10" t="s">
+      <c r="E149" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="F131" s="10" t="s">
+      <c r="F149" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="G131" s="10"/>
-      <c r="H131" s="10" t="s">
+      <c r="G149" s="6"/>
+      <c r="H149" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I131" s="10"/>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="10">
+      <c r="I149" s="6"/>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" s="6">
         <v>123</v>
       </c>
-      <c r="B132" s="11"/>
-      <c r="C132" s="15"/>
-      <c r="D132" s="10" t="s">
+      <c r="B150" s="7"/>
+      <c r="C150" s="11"/>
+      <c r="D150" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="E132" s="10" t="s">
+      <c r="E150" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="F132" s="10" t="s">
+      <c r="F150" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="G132" s="10"/>
-      <c r="H132" s="10" t="s">
+      <c r="G150" s="6"/>
+      <c r="H150" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I132" s="10"/>
-    </row>
-    <row r="133" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A133" s="10">
+      <c r="I150" s="6"/>
+    </row>
+    <row r="151" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A151" s="6">
         <v>124</v>
       </c>
-      <c r="B133" s="18" t="s">
+      <c r="B151" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="C133" s="19" t="s">
+      <c r="C151" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="D133" s="10" t="s">
+      <c r="D151" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="E133" s="10" t="s">
+      <c r="E151" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="F133" s="10" t="s">
+      <c r="F151" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="G133" s="10"/>
-      <c r="H133" s="10" t="s">
+      <c r="G151" s="6"/>
+      <c r="H151" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I133" s="10"/>
+      <c r="I151" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="46">
-    <mergeCell ref="C130:C132"/>
-    <mergeCell ref="B127:B132"/>
-    <mergeCell ref="C56:C59"/>
-    <mergeCell ref="B45:B59"/>
-    <mergeCell ref="C50:C55"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="C127:C129"/>
-    <mergeCell ref="B84:B101"/>
-    <mergeCell ref="B105:B123"/>
-    <mergeCell ref="C119:C123"/>
-    <mergeCell ref="C113:C115"/>
-    <mergeCell ref="C116:C118"/>
+  <mergeCells count="49">
+    <mergeCell ref="C148:C150"/>
+    <mergeCell ref="B145:B150"/>
+    <mergeCell ref="C74:C77"/>
+    <mergeCell ref="B63:B77"/>
+    <mergeCell ref="C68:C73"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="C145:C147"/>
+    <mergeCell ref="B102:B119"/>
+    <mergeCell ref="B123:B141"/>
+    <mergeCell ref="C137:C141"/>
+    <mergeCell ref="C131:C133"/>
+    <mergeCell ref="C134:C136"/>
+    <mergeCell ref="C120:C122"/>
+    <mergeCell ref="B120:B122"/>
+    <mergeCell ref="C107:C109"/>
+    <mergeCell ref="C128:C130"/>
+    <mergeCell ref="C105:C106"/>
+    <mergeCell ref="C110:C111"/>
+    <mergeCell ref="C112:C114"/>
+    <mergeCell ref="C96:C98"/>
+    <mergeCell ref="C99:C101"/>
+    <mergeCell ref="C116:C119"/>
+    <mergeCell ref="B96:B101"/>
     <mergeCell ref="C102:C104"/>
-    <mergeCell ref="B102:B104"/>
-    <mergeCell ref="C89:C91"/>
-    <mergeCell ref="C110:C112"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="C94:C96"/>
-    <mergeCell ref="C78:C80"/>
-    <mergeCell ref="C81:C83"/>
-    <mergeCell ref="C98:C101"/>
-    <mergeCell ref="B78:B83"/>
-    <mergeCell ref="C84:C86"/>
-    <mergeCell ref="C74:C76"/>
+    <mergeCell ref="C92:C94"/>
     <mergeCell ref="B2:B12"/>
-    <mergeCell ref="B74:B77"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="B92:B95"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="B90:B91"/>
     <mergeCell ref="C17:C19"/>
     <mergeCell ref="C24:C26"/>
     <mergeCell ref="B17:B28"/>
@@ -4856,12 +5305,15 @@
     <mergeCell ref="C32:C34"/>
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="B29:B36"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="B60:B71"/>
-    <mergeCell ref="C60:C62"/>
-    <mergeCell ref="C63:C69"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="B78:B89"/>
+    <mergeCell ref="C78:C80"/>
+    <mergeCell ref="C81:C87"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="C50:C52"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
@@ -4889,32 +5341,32 @@
     <col min="9" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="22" customFormat="1" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:9" s="18" customFormat="1" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="16" t="s">
         <v>8</v>
       </c>
     </row>

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0265EEB-F9E7-4CE8-8808-6E99F01D2E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{952B1094-17C4-4354-A5E7-BCC8ED551555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{F425FBA8-E65A-4F03-9270-551F3EA7C4F5}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="380">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1503,6 +1503,34 @@
   </si>
   <si>
     <t>2.18选择排位/普通模式，胜利6局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计对局任务-任务进度持久化测试</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.16选择排位模式，胜利一句后退出客户端</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务进度未1/6，数据不变</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间内进入活动大厅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择排位模式，单人胜利一局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以完成任务</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择排位模式，多人胜利一局</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1586,7 +1614,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1607,6 +1635,17 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1631,13 +1670,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1698,20 +1763,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2027,7 +2104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DF7E13A-4D63-4E82-9598-D598C8858D86}">
-  <dimension ref="A1:I151"/>
+  <dimension ref="A1:I152"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
@@ -2855,11 +2932,13 @@
       <c r="I36" s="6"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="6"/>
-      <c r="B37" s="14" t="s">
+      <c r="A37" s="6">
+        <v>36</v>
+      </c>
+      <c r="B37" s="26" t="s">
         <v>320</v>
       </c>
-      <c r="C37" s="20" t="s">
+      <c r="C37" s="21" t="s">
         <v>339</v>
       </c>
       <c r="D37" s="10" t="s">
@@ -2868,7 +2947,7 @@
       <c r="E37" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="F37" s="19" t="s">
+      <c r="F37" s="20" t="s">
         <v>319</v>
       </c>
       <c r="G37" s="6"/>
@@ -2876,9 +2955,11 @@
       <c r="I37" s="6"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="6"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="20" t="s">
+      <c r="A38" s="6">
+        <v>37</v>
+      </c>
+      <c r="B38" s="28"/>
+      <c r="C38" s="21" t="s">
         <v>340</v>
       </c>
       <c r="D38" s="10" t="s">
@@ -2887,7 +2968,7 @@
       <c r="E38" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="F38" s="19" t="s">
+      <c r="F38" s="20" t="s">
         <v>324</v>
       </c>
       <c r="G38" s="6"/>
@@ -2895,9 +2976,11 @@
       <c r="I38" s="6"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="6"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="20" t="s">
+      <c r="A39" s="6">
+        <v>38</v>
+      </c>
+      <c r="B39" s="28"/>
+      <c r="C39" s="21" t="s">
         <v>340</v>
       </c>
       <c r="D39" s="10" t="s">
@@ -2906,7 +2989,7 @@
       <c r="E39" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="F39" s="19" t="s">
+      <c r="F39" s="20" t="s">
         <v>326</v>
       </c>
       <c r="G39" s="6"/>
@@ -2914,9 +2997,11 @@
       <c r="I39" s="6"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="6"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="20" t="s">
+      <c r="A40" s="6">
+        <v>39</v>
+      </c>
+      <c r="B40" s="28"/>
+      <c r="C40" s="21" t="s">
         <v>341</v>
       </c>
       <c r="D40" s="10" t="s">
@@ -2925,7 +3010,7 @@
       <c r="E40" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="F40" s="19" t="s">
+      <c r="F40" s="20" t="s">
         <v>328</v>
       </c>
       <c r="G40" s="6"/>
@@ -2933,9 +3018,11 @@
       <c r="I40" s="6"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="6"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="20"/>
+      <c r="A41" s="6">
+        <v>40</v>
+      </c>
+      <c r="B41" s="28"/>
+      <c r="C41" s="21"/>
       <c r="D41" s="10"/>
       <c r="E41" s="10"/>
       <c r="F41" s="4"/>
@@ -2944,9 +3031,11 @@
       <c r="I41" s="6"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="6"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="21" t="s">
+      <c r="A42" s="6">
+        <v>41</v>
+      </c>
+      <c r="B42" s="28"/>
+      <c r="C42" s="22" t="s">
         <v>334</v>
       </c>
       <c r="D42" s="10" t="s">
@@ -2963,16 +3052,18 @@
       <c r="I42" s="6"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="6"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="21"/>
+      <c r="A43" s="6">
+        <v>42</v>
+      </c>
+      <c r="B43" s="28"/>
+      <c r="C43" s="22"/>
       <c r="D43" s="10" t="s">
         <v>342</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="F43" s="19" t="s">
+      <c r="F43" s="20" t="s">
         <v>324</v>
       </c>
       <c r="G43" s="6"/>
@@ -2980,16 +3071,18 @@
       <c r="I43" s="6"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="6"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="21"/>
+      <c r="A44" s="6">
+        <v>43</v>
+      </c>
+      <c r="B44" s="28"/>
+      <c r="C44" s="22"/>
       <c r="D44" s="10" t="s">
         <v>342</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="F44" s="19" t="s">
+      <c r="F44" s="20" t="s">
         <v>326</v>
       </c>
       <c r="G44" s="6"/>
@@ -2997,9 +3090,11 @@
       <c r="I44" s="6"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="6"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="22" t="s">
+      <c r="A45" s="6">
+        <v>44</v>
+      </c>
+      <c r="B45" s="28"/>
+      <c r="C45" s="23" t="s">
         <v>347</v>
       </c>
       <c r="D45" s="10" t="s">
@@ -3008,7 +3103,7 @@
       <c r="E45" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="F45" s="19" t="s">
+      <c r="F45" s="20" t="s">
         <v>349</v>
       </c>
       <c r="G45" s="6"/>
@@ -3016,9 +3111,11 @@
       <c r="I45" s="6"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="6"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="21" t="s">
+      <c r="A46" s="6">
+        <v>45</v>
+      </c>
+      <c r="B46" s="28"/>
+      <c r="C46" s="22" t="s">
         <v>335</v>
       </c>
       <c r="D46" s="10" t="s">
@@ -3027,7 +3124,7 @@
       <c r="E46" s="10" t="s">
         <v>351</v>
       </c>
-      <c r="F46" s="19" t="s">
+      <c r="F46" s="20" t="s">
         <v>352</v>
       </c>
       <c r="G46" s="6"/>
@@ -3035,16 +3132,18 @@
       <c r="I46" s="6"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="6"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="21"/>
+      <c r="A47" s="6">
+        <v>46</v>
+      </c>
+      <c r="B47" s="28"/>
+      <c r="C47" s="22"/>
       <c r="D47" s="10" t="s">
         <v>350</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="F47" s="19" t="s">
+      <c r="F47" s="20" t="s">
         <v>352</v>
       </c>
       <c r="G47" s="6"/>
@@ -3052,16 +3151,18 @@
       <c r="I47" s="6"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="6"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="21"/>
+      <c r="A48" s="6">
+        <v>47</v>
+      </c>
+      <c r="B48" s="28"/>
+      <c r="C48" s="22"/>
       <c r="D48" s="10" t="s">
         <v>350</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="F48" s="19" t="s">
+      <c r="F48" s="20" t="s">
         <v>355</v>
       </c>
       <c r="G48" s="6"/>
@@ -3069,16 +3170,18 @@
       <c r="I48" s="6"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="6"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="21"/>
+      <c r="A49" s="6">
+        <v>48</v>
+      </c>
+      <c r="B49" s="28"/>
+      <c r="C49" s="22"/>
       <c r="D49" s="10" t="s">
         <v>350</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>356</v>
       </c>
-      <c r="F49" s="19" t="s">
+      <c r="F49" s="20" t="s">
         <v>355</v>
       </c>
       <c r="G49" s="6"/>
@@ -3086,9 +3189,11 @@
       <c r="I49" s="6"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="6"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="21" t="s">
+      <c r="A50" s="6">
+        <v>49</v>
+      </c>
+      <c r="B50" s="28"/>
+      <c r="C50" s="22" t="s">
         <v>336</v>
       </c>
       <c r="D50" s="10" t="s">
@@ -3097,7 +3202,7 @@
       <c r="E50" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="F50" s="19" t="s">
+      <c r="F50" s="20" t="s">
         <v>352</v>
       </c>
       <c r="G50" s="6"/>
@@ -3105,16 +3210,18 @@
       <c r="I50" s="6"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="6"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="21"/>
+      <c r="A51" s="6">
+        <v>50</v>
+      </c>
+      <c r="B51" s="28"/>
+      <c r="C51" s="22"/>
       <c r="D51" s="10" t="s">
         <v>350</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="F51" s="19" t="s">
+      <c r="F51" s="20" t="s">
         <v>355</v>
       </c>
       <c r="G51" s="6"/>
@@ -3122,9 +3229,11 @@
       <c r="I51" s="6"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="6"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="21"/>
+      <c r="A52" s="6">
+        <v>51</v>
+      </c>
+      <c r="B52" s="28"/>
+      <c r="C52" s="22"/>
       <c r="D52" s="10" t="s">
         <v>350</v>
       </c>
@@ -3139,9 +3248,11 @@
       <c r="I52" s="6"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="6"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="20" t="s">
+      <c r="A53" s="6">
+        <v>52</v>
+      </c>
+      <c r="B53" s="28"/>
+      <c r="C53" s="26" t="s">
         <v>337</v>
       </c>
       <c r="D53" s="10" t="s">
@@ -3158,9 +3269,11 @@
       <c r="I53" s="6"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="6"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="20"/>
+      <c r="A54" s="6">
+        <v>53</v>
+      </c>
+      <c r="B54" s="28"/>
+      <c r="C54" s="28"/>
       <c r="D54" s="10" t="s">
         <v>360</v>
       </c>
@@ -3175,9 +3288,11 @@
       <c r="I54" s="6"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="6"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="20"/>
+      <c r="A55" s="6">
+        <v>54</v>
+      </c>
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
       <c r="D55" s="10" t="s">
         <v>360</v>
       </c>
@@ -3192,9 +3307,11 @@
       <c r="I55" s="6"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="6"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="20"/>
+      <c r="A56" s="6">
+        <v>55</v>
+      </c>
+      <c r="B56" s="28"/>
+      <c r="C56" s="28"/>
       <c r="D56" s="10" t="s">
         <v>360</v>
       </c>
@@ -3209,9 +3326,11 @@
       <c r="I56" s="6"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="6"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="20"/>
+      <c r="A57" s="6">
+        <v>56</v>
+      </c>
+      <c r="B57" s="28"/>
+      <c r="C57" s="28"/>
       <c r="D57" s="10" t="s">
         <v>360</v>
       </c>
@@ -3226,9 +3345,11 @@
       <c r="I57" s="6"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="6"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="20"/>
+      <c r="A58" s="6">
+        <v>57</v>
+      </c>
+      <c r="B58" s="28"/>
+      <c r="C58" s="27"/>
       <c r="D58" s="10" t="s">
         <v>360</v>
       </c>
@@ -3243,97 +3364,117 @@
       <c r="I58" s="6"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="6"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="20" t="s">
-        <v>338</v>
-      </c>
-      <c r="D59" s="10"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="4"/>
+      <c r="A59" s="6">
+        <v>58</v>
+      </c>
+      <c r="B59" s="28"/>
+      <c r="C59" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="F59" s="19" t="s">
+        <v>375</v>
+      </c>
       <c r="G59" s="6"/>
       <c r="H59" s="6"/>
       <c r="I59" s="6"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="6"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="20"/>
-      <c r="D60" s="10"/>
-      <c r="E60" s="10"/>
-      <c r="F60" s="4"/>
+      <c r="A60" s="6">
+        <v>59</v>
+      </c>
+      <c r="B60" s="28"/>
+      <c r="C60" s="26" t="s">
+        <v>338</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="F60" s="19" t="s">
+        <v>378</v>
+      </c>
       <c r="G60" s="6"/>
       <c r="H60" s="6"/>
       <c r="I60" s="6"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="6"/>
-      <c r="B61" s="14" t="s">
-        <v>333</v>
-      </c>
-      <c r="C61" s="20" t="s">
-        <v>329</v>
-      </c>
+      <c r="A61" s="6">
+        <v>60</v>
+      </c>
+      <c r="B61" s="27"/>
+      <c r="C61" s="27"/>
       <c r="D61" s="10" t="s">
-        <v>330</v>
+        <v>376</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>332</v>
+        <v>379</v>
+      </c>
+      <c r="F61" s="19" t="s">
+        <v>378</v>
       </c>
       <c r="G61" s="6"/>
       <c r="H61" s="6"/>
       <c r="I61" s="6"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="6"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="20"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="10"/>
-      <c r="F62" s="4"/>
+      <c r="A62" s="6">
+        <v>61</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="C62" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>332</v>
+      </c>
       <c r="G62" s="6"/>
       <c r="H62" s="6"/>
       <c r="I62" s="6"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>36</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C63" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="F63" t="s">
-        <v>201</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B63" s="14"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="10"/>
+      <c r="F63" s="4"/>
       <c r="G63" s="6"/>
-      <c r="H63" s="6" t="s">
-        <v>187</v>
-      </c>
+      <c r="H63" s="6"/>
       <c r="I63" s="6"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>37</v>
-      </c>
-      <c r="B64" s="7"/>
-      <c r="C64" s="23"/>
+        <v>63</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C64" s="24" t="s">
+        <v>55</v>
+      </c>
       <c r="D64" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F64" t="s">
         <v>201</v>
@@ -3346,108 +3487,108 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="B65" s="7"/>
-      <c r="C65" s="23"/>
+      <c r="C65" s="24"/>
       <c r="D65" s="6" t="s">
         <v>58</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F65" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G65" s="6"/>
       <c r="H65" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I65" s="6"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="B66" s="7"/>
-      <c r="C66" s="23" t="s">
-        <v>59</v>
-      </c>
+      <c r="C66" s="24"/>
       <c r="D66" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>284</v>
+        <v>200</v>
       </c>
       <c r="F66" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G66" s="6"/>
       <c r="H66" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="I66" s="6" t="s">
-        <v>285</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="I66" s="6"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="B67" s="7"/>
-      <c r="C67" s="23"/>
+      <c r="C67" s="24" t="s">
+        <v>59</v>
+      </c>
       <c r="D67" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>202</v>
+        <v>284</v>
       </c>
       <c r="F67" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G67" s="6"/>
       <c r="H67" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="I67" s="6"/>
+        <v>181</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="B68" s="7"/>
-      <c r="C68" s="24" t="s">
-        <v>56</v>
-      </c>
+      <c r="C68" s="24"/>
       <c r="D68" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F68" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="G68" s="6"/>
       <c r="H68" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I68" s="6"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="B69" s="7"/>
-      <c r="C69" s="24"/>
+      <c r="C69" s="25" t="s">
+        <v>56</v>
+      </c>
       <c r="D69" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F69" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G69" s="6"/>
       <c r="H69" s="6" t="s">
@@ -3457,12 +3598,12 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="B70" s="7"/>
-      <c r="C70" s="24"/>
+      <c r="C70" s="25"/>
       <c r="D70" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>204</v>
@@ -3478,18 +3619,18 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B71" s="7"/>
-      <c r="C71" s="24"/>
+      <c r="C71" s="25"/>
       <c r="D71" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F71" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="G71" s="6"/>
       <c r="H71" s="6" t="s">
@@ -3499,18 +3640,18 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="B72" s="7"/>
-      <c r="C72" s="24"/>
+      <c r="C72" s="25"/>
       <c r="D72" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F72" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G72" s="6"/>
       <c r="H72" s="6" t="s">
@@ -3520,59 +3661,59 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="B73" s="7"/>
-      <c r="C73" s="24"/>
+      <c r="C73" s="25"/>
       <c r="D73" s="6" t="s">
-        <v>265</v>
+        <v>66</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F73" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="G73" s="6"/>
       <c r="H73" s="6" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I73" s="6"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="B74" s="7"/>
-      <c r="C74" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D74" t="s">
-        <v>77</v>
-      </c>
-      <c r="E74" t="s">
-        <v>207</v>
+      <c r="C74" s="25"/>
+      <c r="D74" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>203</v>
       </c>
       <c r="F74" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G74" s="6"/>
       <c r="H74" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I74" s="6"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="B75" s="7"/>
-      <c r="C75" s="5"/>
+      <c r="C75" s="5" t="s">
+        <v>67</v>
+      </c>
       <c r="D75" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E75" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F75" t="s">
         <v>205</v>
@@ -3585,39 +3726,39 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="B76" s="7"/>
       <c r="C76" s="5"/>
       <c r="D76" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E76" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F76" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G76" s="6"/>
       <c r="H76" s="6" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I76" s="6"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="B77" s="7"/>
       <c r="C77" s="5"/>
       <c r="D77" t="s">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="E77" t="s">
-        <v>262</v>
+        <v>203</v>
       </c>
       <c r="F77" t="s">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="G77" s="6"/>
       <c r="H77" s="6" t="s">
@@ -3627,58 +3768,58 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
-        <v>51</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E78" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="F78" s="6" t="s">
-        <v>211</v>
+        <v>77</v>
+      </c>
+      <c r="B78" s="7"/>
+      <c r="C78" s="5"/>
+      <c r="D78" t="s">
+        <v>173</v>
+      </c>
+      <c r="E78" t="s">
+        <v>262</v>
+      </c>
+      <c r="F78" t="s">
+        <v>239</v>
       </c>
       <c r="G78" s="6"/>
       <c r="H78" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I78" s="6"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
-        <v>52</v>
-      </c>
-      <c r="B79" s="7"/>
-      <c r="C79" s="8"/>
+        <v>78</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="D79" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G79" s="6"/>
       <c r="H79" s="6" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I79" s="6"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="B80" s="7"/>
       <c r="C80" s="8"/>
       <c r="D80" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>212</v>
@@ -3694,77 +3835,77 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="B81" s="7"/>
-      <c r="C81" s="8" t="s">
-        <v>74</v>
-      </c>
+      <c r="C81" s="8"/>
       <c r="D81" s="6" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G81" s="6"/>
       <c r="H81" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I81" s="6"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="B82" s="7"/>
-      <c r="C82" s="8"/>
+      <c r="C82" s="8" t="s">
+        <v>74</v>
+      </c>
       <c r="D82" s="6" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G82" s="6"/>
       <c r="H82" s="6" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I82" s="6"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="B83" s="7"/>
       <c r="C83" s="8"/>
       <c r="D83" s="6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G83" s="6"/>
       <c r="H83" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I83" s="6"/>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="B84" s="7"/>
       <c r="C84" s="8"/>
       <c r="D84" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E84" s="10" t="s">
         <v>210</v>
@@ -3780,18 +3921,18 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="B85" s="7"/>
       <c r="C85" s="8"/>
       <c r="D85" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G85" s="6"/>
       <c r="H85" s="6" t="s">
@@ -3801,12 +3942,12 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="B86" s="7"/>
       <c r="C86" s="8"/>
       <c r="D86" s="6" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="E86" s="10" t="s">
         <v>215</v>
@@ -3822,35 +3963,33 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="B87" s="7"/>
       <c r="C87" s="8"/>
       <c r="D87" s="6" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G87" s="6"/>
       <c r="H87" s="6" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I87" s="6"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="B88" s="7"/>
-      <c r="C88" s="8" t="s">
-        <v>70</v>
-      </c>
+      <c r="C88" s="8"/>
       <c r="D88" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>210</v>
@@ -3860,21 +3999,23 @@
       </c>
       <c r="G88" s="6"/>
       <c r="H88" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I88" s="6"/>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="B89" s="7"/>
-      <c r="C89" s="8"/>
+      <c r="C89" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="D89" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F89" s="6" t="s">
         <v>211</v>
@@ -3887,22 +4028,18 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
-        <v>63</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>94</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="B90" s="7"/>
+      <c r="C90" s="8"/>
       <c r="D90" s="6" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E90" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="G90" s="6"/>
       <c r="H90" s="6" t="s">
@@ -3912,43 +4049,43 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
-        <v>64</v>
-      </c>
-      <c r="B91" s="7"/>
-      <c r="C91" s="8"/>
+        <v>90</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>94</v>
+      </c>
       <c r="D91" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>217</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G91" s="6"/>
       <c r="H91" s="6" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I91" s="6"/>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
-        <v>65</v>
-      </c>
-      <c r="B92" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>172</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="B92" s="7"/>
+      <c r="C92" s="8"/>
       <c r="D92" s="6" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>286</v>
+        <v>217</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G92" s="6"/>
       <c r="H92" s="6" t="s">
@@ -3958,33 +4095,37 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
-        <v>66</v>
-      </c>
-      <c r="B93" s="7"/>
-      <c r="C93" s="8"/>
+        <v>92</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>172</v>
+      </c>
       <c r="D93" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>286</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G93" s="6"/>
       <c r="H93" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I93" s="6"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="B94" s="7"/>
       <c r="C94" s="8"/>
       <c r="D94" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E94" s="10" t="s">
         <v>286</v>
@@ -3994,26 +4135,24 @@
       </c>
       <c r="G94" s="6"/>
       <c r="H94" s="6" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I94" s="6"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="B95" s="7"/>
-      <c r="C95" s="9" t="s">
-        <v>91</v>
-      </c>
+      <c r="C95" s="8"/>
       <c r="D95" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="F95" s="10" t="s">
-        <v>223</v>
+        <v>286</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>221</v>
       </c>
       <c r="G95" s="6"/>
       <c r="H95" s="6" t="s">
@@ -4023,22 +4162,20 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
-        <v>69</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="C96" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
+      </c>
+      <c r="B96" s="7"/>
+      <c r="C96" s="9" t="s">
+        <v>91</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F96" s="10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G96" s="6"/>
       <c r="H96" s="6" t="s">
@@ -4048,33 +4185,37 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
-        <v>70</v>
-      </c>
-      <c r="B97" s="7"/>
-      <c r="C97" s="8"/>
+        <v>96</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>97</v>
+      </c>
       <c r="D97" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>224</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G97" s="6"/>
       <c r="H97" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I97" s="6"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="B98" s="7"/>
       <c r="C98" s="8"/>
       <c r="D98" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E98" s="10" t="s">
         <v>224</v>
@@ -4084,47 +4225,47 @@
       </c>
       <c r="G98" s="6"/>
       <c r="H98" s="6" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I98" s="6"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="B99" s="7"/>
-      <c r="C99" s="8" t="s">
-        <v>101</v>
-      </c>
+      <c r="C99" s="8"/>
       <c r="D99" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E99" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>226</v>
       </c>
       <c r="G99" s="6"/>
       <c r="H99" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I99" s="6"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="B100" s="7"/>
-      <c r="C100" s="8"/>
+      <c r="C100" s="8" t="s">
+        <v>101</v>
+      </c>
       <c r="D100" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G100" s="6"/>
       <c r="H100" s="6" t="s">
@@ -4134,18 +4275,18 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="B101" s="7"/>
       <c r="C101" s="8"/>
       <c r="D101" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G101" s="6"/>
       <c r="H101" s="6" t="s">
@@ -4155,22 +4296,18 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
-        <v>75</v>
-      </c>
-      <c r="B102" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C102" s="8" t="s">
-        <v>270</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="B102" s="7"/>
+      <c r="C102" s="8"/>
       <c r="D102" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>227</v>
+        <v>109</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="G102" s="6"/>
       <c r="H102" s="6" t="s">
@@ -4180,15 +4317,19 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
-        <v>76</v>
-      </c>
-      <c r="B103" s="7"/>
-      <c r="C103" s="8"/>
+        <v>102</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>270</v>
+      </c>
       <c r="D103" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F103" s="6" t="s">
         <v>230</v>
@@ -4201,15 +4342,15 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="B104" s="7"/>
       <c r="C104" s="8"/>
       <c r="D104" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>230</v>
@@ -4222,33 +4363,33 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="B105" s="7"/>
-      <c r="C105" s="11" t="s">
-        <v>117</v>
-      </c>
+      <c r="C105" s="8"/>
       <c r="D105" s="6" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>118</v>
+        <v>230</v>
       </c>
       <c r="G105" s="6"/>
       <c r="H105" s="6" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I105" s="6"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="B106" s="7"/>
-      <c r="C106" s="11"/>
+      <c r="C106" s="11" t="s">
+        <v>117</v>
+      </c>
       <c r="D106" s="6" t="s">
         <v>124</v>
       </c>
@@ -4256,7 +4397,7 @@
         <v>231</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G106" s="6"/>
       <c r="H106" s="6" t="s">
@@ -4266,35 +4407,35 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="B107" s="7"/>
-      <c r="C107" s="11" t="s">
-        <v>132</v>
-      </c>
+      <c r="C107" s="11"/>
       <c r="D107" s="6" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E107" s="6" t="s">
         <v>231</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>189</v>
+        <v>119</v>
       </c>
       <c r="G107" s="6"/>
       <c r="H107" s="6" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I107" s="6"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="B108" s="7"/>
-      <c r="C108" s="11"/>
+      <c r="C108" s="11" t="s">
+        <v>132</v>
+      </c>
       <c r="D108" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>231</v>
@@ -4310,12 +4451,12 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="B109" s="7"/>
       <c r="C109" s="11"/>
       <c r="D109" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E109" s="6" t="s">
         <v>231</v>
@@ -4331,33 +4472,33 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="B110" s="7"/>
-      <c r="C110" s="11" t="s">
-        <v>120</v>
-      </c>
+      <c r="C110" s="11"/>
       <c r="D110" s="6" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>231</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>121</v>
+        <v>189</v>
       </c>
       <c r="G110" s="6"/>
       <c r="H110" s="6" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="I110" s="6"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="B111" s="7"/>
-      <c r="C111" s="11"/>
+      <c r="C111" s="11" t="s">
+        <v>120</v>
+      </c>
       <c r="D111" s="6" t="s">
         <v>124</v>
       </c>
@@ -4365,7 +4506,7 @@
         <v>231</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G111" s="6"/>
       <c r="H111" s="6" t="s">
@@ -4375,20 +4516,18 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="B112" s="7"/>
-      <c r="C112" s="11" t="s">
-        <v>123</v>
-      </c>
+      <c r="C112" s="11"/>
       <c r="D112" s="6" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>231</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>232</v>
+        <v>122</v>
       </c>
       <c r="G112" s="6"/>
       <c r="H112" s="6" t="s">
@@ -4398,12 +4537,14 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="B113" s="7"/>
-      <c r="C113" s="11"/>
+      <c r="C113" s="11" t="s">
+        <v>123</v>
+      </c>
       <c r="D113" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E113" s="6" t="s">
         <v>231</v>
@@ -4413,18 +4554,18 @@
       </c>
       <c r="G113" s="6"/>
       <c r="H113" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I113" s="6"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="B114" s="7"/>
       <c r="C114" s="11"/>
       <c r="D114" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>231</v>
@@ -4434,26 +4575,24 @@
       </c>
       <c r="G114" s="6"/>
       <c r="H114" s="6" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I114" s="6"/>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="B115" s="7"/>
-      <c r="C115" s="6" t="s">
-        <v>115</v>
-      </c>
+      <c r="C115" s="11"/>
       <c r="D115" s="6" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="E115" s="6" t="s">
         <v>231</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G115" s="6"/>
       <c r="H115" s="6" t="s">
@@ -4463,20 +4602,20 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="B116" s="7"/>
-      <c r="C116" s="11" t="s">
-        <v>125</v>
+      <c r="C116" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>288</v>
+        <v>116</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G116" s="6"/>
       <c r="H116" s="6" t="s">
@@ -4486,12 +4625,14 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="B117" s="7"/>
-      <c r="C117" s="11"/>
+      <c r="C117" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="D117" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E117" s="6" t="s">
         <v>234</v>
@@ -4507,12 +4648,12 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="B118" s="7"/>
       <c r="C118" s="11"/>
       <c r="D118" s="6" t="s">
-        <v>126</v>
+        <v>287</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>234</v>
@@ -4528,79 +4669,79 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="B119" s="7"/>
       <c r="C119" s="11"/>
       <c r="D119" s="6" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>302</v>
+        <v>236</v>
       </c>
       <c r="G119" s="6"/>
       <c r="H119" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I119" s="6"/>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
-        <v>93</v>
-      </c>
-      <c r="B120" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="C120" s="11" t="s">
-        <v>131</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="B120" s="7"/>
+      <c r="C120" s="11"/>
       <c r="D120" s="6" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="G120" s="6"/>
       <c r="H120" s="6" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I120" s="6"/>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
-        <v>94</v>
-      </c>
-      <c r="B121" s="7"/>
-      <c r="C121" s="11"/>
+        <v>120</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C121" s="11" t="s">
+        <v>131</v>
+      </c>
       <c r="D121" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E121" s="6" t="s">
         <v>237</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>127</v>
+        <v>238</v>
       </c>
       <c r="G121" s="6"/>
       <c r="H121" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I121" s="6"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="B122" s="7"/>
       <c r="C122" s="11"/>
       <c r="D122" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>237</v>
@@ -4610,51 +4751,49 @@
       </c>
       <c r="G122" s="6"/>
       <c r="H122" s="6" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I122" s="6"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
-        <v>96</v>
-      </c>
-      <c r="B123" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C123" s="13" t="s">
-        <v>139</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="B123" s="7"/>
+      <c r="C123" s="11"/>
       <c r="D123" s="6" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>200</v>
+        <v>237</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>239</v>
+        <v>127</v>
       </c>
       <c r="G123" s="6"/>
       <c r="H123" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I123" s="6"/>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
-        <v>97</v>
-      </c>
-      <c r="B124" s="7"/>
+        <v>123</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>136</v>
+      </c>
       <c r="C124" s="13" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G124" s="6"/>
       <c r="H124" s="6" t="s">
@@ -4664,20 +4803,20 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="B125" s="7"/>
-      <c r="C125" s="6" t="s">
-        <v>137</v>
+      <c r="C125" s="13" t="s">
+        <v>146</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G125" s="6"/>
       <c r="H125" s="6" t="s">
@@ -4687,20 +4826,20 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="B126" s="7"/>
       <c r="C126" s="6" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="G126" s="6"/>
       <c r="H126" s="6" t="s">
@@ -4710,20 +4849,20 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="B127" s="7"/>
       <c r="C127" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G127" s="6"/>
       <c r="H127" s="6" t="s">
@@ -4733,35 +4872,37 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="B128" s="7"/>
-      <c r="C128" s="11" t="s">
-        <v>148</v>
+      <c r="C128" s="6" t="s">
+        <v>144</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>289</v>
+        <v>245</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G128" s="6"/>
       <c r="H128" s="6" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I128" s="6"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="B129" s="7"/>
-      <c r="C129" s="11"/>
+      <c r="C129" s="11" t="s">
+        <v>148</v>
+      </c>
       <c r="D129" s="6" t="s">
-        <v>149</v>
+        <v>19</v>
       </c>
       <c r="E129" s="6" t="s">
         <v>289</v>
@@ -4771,18 +4912,18 @@
       </c>
       <c r="G129" s="6"/>
       <c r="H129" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I129" s="6"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="B130" s="7"/>
       <c r="C130" s="11"/>
       <c r="D130" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>289</v>
@@ -4792,26 +4933,24 @@
       </c>
       <c r="G130" s="6"/>
       <c r="H130" s="6" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I130" s="6"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="B131" s="7"/>
-      <c r="C131" s="11" t="s">
-        <v>158</v>
-      </c>
+      <c r="C131" s="11"/>
       <c r="D131" s="6" t="s">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>242</v>
+        <v>289</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="G131" s="6"/>
       <c r="H131" s="6" t="s">
@@ -4821,12 +4960,14 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="B132" s="7"/>
-      <c r="C132" s="11"/>
+      <c r="C132" s="11" t="s">
+        <v>158</v>
+      </c>
       <c r="D132" s="6" t="s">
-        <v>149</v>
+        <v>19</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>242</v>
@@ -4836,18 +4977,18 @@
       </c>
       <c r="G132" s="6"/>
       <c r="H132" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I132" s="6"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="B133" s="7"/>
       <c r="C133" s="11"/>
       <c r="D133" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E133" s="6" t="s">
         <v>242</v>
@@ -4857,26 +4998,24 @@
       </c>
       <c r="G133" s="6"/>
       <c r="H133" s="6" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I133" s="6"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="B134" s="7"/>
-      <c r="C134" s="11" t="s">
-        <v>159</v>
-      </c>
+      <c r="C134" s="11"/>
       <c r="D134" s="6" t="s">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="G134" s="6"/>
       <c r="H134" s="6" t="s">
@@ -4886,33 +5025,35 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="B135" s="7"/>
-      <c r="C135" s="11"/>
+      <c r="C135" s="11" t="s">
+        <v>159</v>
+      </c>
       <c r="D135" s="6" t="s">
-        <v>149</v>
+        <v>19</v>
       </c>
       <c r="E135" s="6" t="s">
         <v>247</v>
       </c>
       <c r="F135" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G135" s="6"/>
       <c r="H135" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I135" s="6"/>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="B136" s="7"/>
       <c r="C136" s="11"/>
       <c r="D136" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>247</v>
@@ -4922,26 +5063,24 @@
       </c>
       <c r="G136" s="6"/>
       <c r="H136" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I136" s="6"/>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="B137" s="7"/>
-      <c r="C137" s="11" t="s">
-        <v>151</v>
-      </c>
+      <c r="C137" s="11"/>
       <c r="D137" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G137" s="6"/>
       <c r="H137" s="6" t="s">
@@ -4949,56 +5088,58 @@
       </c>
       <c r="I137" s="6"/>
     </row>
-    <row r="138" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="B138" s="7"/>
-      <c r="C138" s="11"/>
-      <c r="D138" s="12" t="s">
-        <v>153</v>
+      <c r="C138" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>152</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G138" s="6"/>
       <c r="H138" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I138" s="6"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="B139" s="7"/>
       <c r="C139" s="11"/>
-      <c r="D139" s="9" t="s">
-        <v>271</v>
+      <c r="D139" s="12" t="s">
+        <v>153</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>290</v>
+        <v>253</v>
       </c>
       <c r="F139" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G139" s="6"/>
       <c r="H139" s="6" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I139" s="6"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="B140" s="7"/>
       <c r="C140" s="11"/>
       <c r="D140" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>290</v>
@@ -5008,18 +5149,18 @@
       </c>
       <c r="G140" s="6"/>
       <c r="H140" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I140" s="6"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="B141" s="7"/>
       <c r="C141" s="11"/>
       <c r="D141" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E141" s="6" t="s">
         <v>290</v>
@@ -5029,45 +5170,43 @@
       </c>
       <c r="G141" s="6"/>
       <c r="H141" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I141" s="6"/>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
-        <v>115</v>
-      </c>
-      <c r="B142" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="C142" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="D142" s="6" t="s">
-        <v>156</v>
+        <v>141</v>
+      </c>
+      <c r="B142" s="7"/>
+      <c r="C142" s="11"/>
+      <c r="D142" s="9" t="s">
+        <v>273</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F142" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G142" s="6"/>
       <c r="H142" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I142" s="6"/>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
-        <v>116</v>
-      </c>
-      <c r="B143" s="7"/>
+        <v>142</v>
+      </c>
+      <c r="B143" s="7" t="s">
+        <v>154</v>
+      </c>
       <c r="C143" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E143" s="6" t="s">
         <v>291</v>
@@ -5083,22 +5222,20 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
-        <v>117</v>
-      </c>
-      <c r="B144" s="14" t="s">
-        <v>162</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="B144" s="7"/>
       <c r="C144" s="6" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>291</v>
       </c>
       <c r="F144" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G144" s="6"/>
       <c r="H144" s="6" t="s">
@@ -5108,58 +5245,62 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
-        <v>118</v>
-      </c>
-      <c r="B145" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C145" s="11" t="s">
-        <v>165</v>
+        <v>144</v>
+      </c>
+      <c r="B145" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>161</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E145" s="6" t="s">
         <v>291</v>
       </c>
       <c r="F145" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G145" s="6"/>
       <c r="H145" s="6" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I145" s="6"/>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
-        <v>119</v>
-      </c>
-      <c r="B146" s="7"/>
-      <c r="C146" s="11"/>
+        <v>145</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C146" s="11" t="s">
+        <v>165</v>
+      </c>
       <c r="D146" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>291</v>
       </c>
       <c r="F146" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G146" s="6"/>
       <c r="H146" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I146" s="6"/>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="B147" s="7"/>
       <c r="C147" s="11"/>
       <c r="D147" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E147" s="6" t="s">
         <v>291</v>
@@ -5169,68 +5310,68 @@
       </c>
       <c r="G147" s="6"/>
       <c r="H147" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I147" s="6"/>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="B148" s="7"/>
-      <c r="C148" s="11" t="s">
-        <v>169</v>
-      </c>
+      <c r="C148" s="11"/>
       <c r="D148" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>259</v>
+        <v>291</v>
       </c>
       <c r="F148" s="6" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="G148" s="6"/>
       <c r="H148" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I148" s="6"/>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="B149" s="7"/>
-      <c r="C149" s="11"/>
+      <c r="C149" s="11" t="s">
+        <v>169</v>
+      </c>
       <c r="D149" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>292</v>
+        <v>259</v>
       </c>
       <c r="F149" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G149" s="6"/>
       <c r="H149" s="6" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I149" s="6"/>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="B150" s="7"/>
       <c r="C150" s="11"/>
       <c r="D150" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F150" s="6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G150" s="6"/>
       <c r="H150" s="6" t="s">
@@ -5238,24 +5379,20 @@
       </c>
       <c r="I150" s="6"/>
     </row>
-    <row r="151" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
-        <v>124</v>
-      </c>
-      <c r="B151" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="C151" s="15" t="s">
-        <v>267</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="B151" s="7"/>
+      <c r="C151" s="11"/>
       <c r="D151" s="6" t="s">
-        <v>268</v>
+        <v>174</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F151" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="G151" s="6"/>
       <c r="H151" s="6" t="s">
@@ -5263,37 +5400,62 @@
       </c>
       <c r="I151" s="6"/>
     </row>
+    <row r="152" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A152" s="6">
+        <v>151</v>
+      </c>
+      <c r="B152" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="C152" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="E152" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="F152" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="G152" s="6"/>
+      <c r="H152" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="I152" s="6"/>
+    </row>
   </sheetData>
-  <mergeCells count="49">
-    <mergeCell ref="C148:C150"/>
-    <mergeCell ref="B145:B150"/>
-    <mergeCell ref="C74:C77"/>
-    <mergeCell ref="B63:B77"/>
-    <mergeCell ref="C68:C73"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="C145:C147"/>
-    <mergeCell ref="B102:B119"/>
-    <mergeCell ref="B123:B141"/>
-    <mergeCell ref="C137:C141"/>
-    <mergeCell ref="C131:C133"/>
-    <mergeCell ref="C134:C136"/>
-    <mergeCell ref="C120:C122"/>
-    <mergeCell ref="B120:B122"/>
-    <mergeCell ref="C107:C109"/>
-    <mergeCell ref="C128:C130"/>
-    <mergeCell ref="C105:C106"/>
-    <mergeCell ref="C110:C111"/>
-    <mergeCell ref="C112:C114"/>
-    <mergeCell ref="C96:C98"/>
-    <mergeCell ref="C99:C101"/>
-    <mergeCell ref="C116:C119"/>
-    <mergeCell ref="B96:B101"/>
-    <mergeCell ref="C102:C104"/>
-    <mergeCell ref="C92:C94"/>
+  <mergeCells count="52">
+    <mergeCell ref="C149:C151"/>
+    <mergeCell ref="B146:B151"/>
+    <mergeCell ref="C75:C78"/>
+    <mergeCell ref="B64:B78"/>
+    <mergeCell ref="C69:C74"/>
+    <mergeCell ref="B143:B144"/>
+    <mergeCell ref="C146:C148"/>
+    <mergeCell ref="B103:B120"/>
+    <mergeCell ref="B124:B142"/>
+    <mergeCell ref="C138:C142"/>
+    <mergeCell ref="C132:C134"/>
+    <mergeCell ref="C135:C137"/>
+    <mergeCell ref="C121:C123"/>
+    <mergeCell ref="B121:B123"/>
+    <mergeCell ref="C108:C110"/>
+    <mergeCell ref="C129:C131"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="C113:C115"/>
+    <mergeCell ref="C97:C99"/>
+    <mergeCell ref="C100:C102"/>
+    <mergeCell ref="C117:C120"/>
+    <mergeCell ref="B97:B102"/>
+    <mergeCell ref="C103:C105"/>
+    <mergeCell ref="C93:C95"/>
     <mergeCell ref="B2:B12"/>
-    <mergeCell ref="B92:B95"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="B93:B96"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="B91:B92"/>
     <mergeCell ref="C17:C19"/>
     <mergeCell ref="C24:C26"/>
     <mergeCell ref="B17:B28"/>
@@ -5305,15 +5467,18 @@
     <mergeCell ref="C32:C34"/>
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="B29:B36"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="B78:B89"/>
-    <mergeCell ref="C78:C80"/>
-    <mergeCell ref="C81:C87"/>
+    <mergeCell ref="C64:C66"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="B79:B90"/>
+    <mergeCell ref="C79:C81"/>
+    <mergeCell ref="C82:C88"/>
     <mergeCell ref="C42:C44"/>
     <mergeCell ref="C46:C49"/>
     <mergeCell ref="C50:C52"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="C53:C58"/>
+    <mergeCell ref="B37:B61"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{952B1094-17C4-4354-A5E7-BCC8ED551555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FCB68BB-E7D6-40EA-A739-8DDB60353E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{F425FBA8-E65A-4F03-9270-551F3EA7C4F5}"/>
   </bookViews>
@@ -259,10 +259,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>期间累计完成6场普通/排位对局</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>活动已开启，未登录游戏</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -300,10 +296,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>期间累计完成6场普通/排位对局异常测试</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>双倍积分次数使用规则</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1531,6 +1523,14 @@
   </si>
   <si>
     <t>选择排位模式，多人胜利一局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>期间累计对局任务异常测试</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>期间累计对局任务</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2158,14 +2158,14 @@
         <v>11</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I2" s="6"/>
     </row>
@@ -2179,14 +2179,14 @@
         <v>12</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I3" s="6"/>
     </row>
@@ -2200,14 +2200,14 @@
         <v>13</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I4" s="6"/>
     </row>
@@ -2223,14 +2223,14 @@
         <v>15</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I5" s="6"/>
     </row>
@@ -2244,14 +2244,14 @@
         <v>16</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I6" s="6"/>
     </row>
@@ -2265,14 +2265,14 @@
         <v>17</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I7" s="6"/>
     </row>
@@ -2288,14 +2288,14 @@
         <v>34</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I8" s="6"/>
     </row>
@@ -2311,17 +2311,17 @@
         <v>19</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -2334,14 +2334,14 @@
         <v>20</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I10" s="6"/>
     </row>
@@ -2355,14 +2355,14 @@
         <v>21</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I11" s="6"/>
     </row>
@@ -2378,14 +2378,14 @@
         <v>46</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I12" s="6"/>
     </row>
@@ -2403,14 +2403,14 @@
         <v>24</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I13" s="6"/>
     </row>
@@ -2426,14 +2426,14 @@
         <v>26</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I14" s="6"/>
     </row>
@@ -2449,14 +2449,14 @@
         <v>29</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I15" s="6"/>
     </row>
@@ -2469,17 +2469,17 @@
         <v>27</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I16" s="6"/>
     </row>
@@ -2497,14 +2497,14 @@
         <v>11</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I17" s="6"/>
     </row>
@@ -2518,14 +2518,14 @@
         <v>12</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I18" s="6"/>
     </row>
@@ -2539,14 +2539,14 @@
         <v>13</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I19" s="6"/>
     </row>
@@ -2556,20 +2556,20 @@
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="9" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>42</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I20" s="6"/>
     </row>
@@ -2585,14 +2585,14 @@
         <v>39</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I21" s="6"/>
     </row>
@@ -2608,14 +2608,14 @@
         <v>37</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I22" s="6"/>
     </row>
@@ -2631,14 +2631,14 @@
         <v>36</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I23" s="6"/>
     </row>
@@ -2654,14 +2654,14 @@
         <v>19</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I24" s="6"/>
     </row>
@@ -2675,14 +2675,14 @@
         <v>20</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I25" s="6"/>
     </row>
@@ -2696,14 +2696,14 @@
         <v>21</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I26" s="6"/>
     </row>
@@ -2716,17 +2716,17 @@
         <v>45</v>
       </c>
       <c r="D27" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="E27" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="E27" s="10" t="s">
-        <v>299</v>
-      </c>
       <c r="F27" s="10" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I27" s="6"/>
     </row>
@@ -2737,17 +2737,17 @@
       <c r="B28" s="7"/>
       <c r="C28" s="11"/>
       <c r="D28" s="12" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G28" s="6"/>
       <c r="H28" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I28" s="6"/>
     </row>
@@ -2765,14 +2765,14 @@
         <v>42</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I29" s="6"/>
     </row>
@@ -2788,14 +2788,14 @@
         <v>42</v>
       </c>
       <c r="E30" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="F30" s="10" t="s">
         <v>310</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>312</v>
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I30" s="6"/>
     </row>
@@ -2811,14 +2811,14 @@
         <v>42</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G31" s="6"/>
       <c r="H31" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I31" s="6"/>
     </row>
@@ -2834,14 +2834,14 @@
         <v>48</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I32" s="6"/>
     </row>
@@ -2855,14 +2855,14 @@
         <v>49</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G33" s="6"/>
       <c r="H33" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I33" s="6"/>
     </row>
@@ -2876,14 +2876,14 @@
         <v>50</v>
       </c>
       <c r="E34" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="F34" s="10" t="s">
         <v>192</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>194</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I34" s="6"/>
     </row>
@@ -2899,14 +2899,14 @@
         <v>51</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I35" s="6"/>
     </row>
@@ -2920,14 +2920,14 @@
         <v>52</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G36" s="6"/>
       <c r="H36" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I36" s="6"/>
     </row>
@@ -2936,19 +2936,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D37" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="F37" s="20" t="s">
         <v>317</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>321</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>319</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
@@ -2960,16 +2960,16 @@
       </c>
       <c r="B38" s="28"/>
       <c r="C38" s="21" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D38" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="F38" s="20" t="s">
         <v>322</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="F38" s="20" t="s">
-        <v>324</v>
       </c>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
@@ -2981,16 +2981,16 @@
       </c>
       <c r="B39" s="28"/>
       <c r="C39" s="21" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
@@ -3002,16 +3002,16 @@
       </c>
       <c r="B40" s="28"/>
       <c r="C40" s="21" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
@@ -3036,16 +3036,16 @@
       </c>
       <c r="B42" s="28"/>
       <c r="C42" s="22" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
@@ -3058,13 +3058,13 @@
       <c r="B43" s="28"/>
       <c r="C43" s="22"/>
       <c r="D43" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="E43" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="E43" s="10" t="s">
-        <v>344</v>
-      </c>
       <c r="F43" s="20" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
@@ -3077,13 +3077,13 @@
       <c r="B44" s="28"/>
       <c r="C44" s="22"/>
       <c r="D44" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="E44" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="E44" s="10" t="s">
-        <v>344</v>
-      </c>
       <c r="F44" s="20" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
@@ -3095,16 +3095,16 @@
       </c>
       <c r="B45" s="28"/>
       <c r="C45" s="23" t="s">
+        <v>345</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="F45" s="20" t="s">
         <v>347</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="F45" s="20" t="s">
-        <v>349</v>
       </c>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
@@ -3116,16 +3116,16 @@
       </c>
       <c r="B46" s="28"/>
       <c r="C46" s="22" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D46" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="F46" s="20" t="s">
         <v>350</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>351</v>
-      </c>
-      <c r="F46" s="20" t="s">
-        <v>352</v>
       </c>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
@@ -3138,13 +3138,13 @@
       <c r="B47" s="28"/>
       <c r="C47" s="22"/>
       <c r="D47" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="F47" s="20" t="s">
         <v>350</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="F47" s="20" t="s">
-        <v>352</v>
       </c>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
@@ -3157,13 +3157,13 @@
       <c r="B48" s="28"/>
       <c r="C48" s="22"/>
       <c r="D48" s="10" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F48" s="20" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
@@ -3176,13 +3176,13 @@
       <c r="B49" s="28"/>
       <c r="C49" s="22"/>
       <c r="D49" s="10" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
@@ -3194,16 +3194,16 @@
       </c>
       <c r="B50" s="28"/>
       <c r="C50" s="22" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D50" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="F50" s="20" t="s">
         <v>350</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="F50" s="20" t="s">
-        <v>352</v>
       </c>
       <c r="G50" s="6"/>
       <c r="H50" s="6"/>
@@ -3216,13 +3216,13 @@
       <c r="B51" s="28"/>
       <c r="C51" s="22"/>
       <c r="D51" s="10" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G51" s="6"/>
       <c r="H51" s="6"/>
@@ -3235,13 +3235,13 @@
       <c r="B52" s="28"/>
       <c r="C52" s="22"/>
       <c r="D52" s="10" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G52" s="6"/>
       <c r="H52" s="6"/>
@@ -3253,16 +3253,16 @@
       </c>
       <c r="B53" s="28"/>
       <c r="C53" s="26" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D53" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="E53" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="E53" s="10" t="s">
-        <v>362</v>
-      </c>
       <c r="F53" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G53" s="6"/>
       <c r="H53" s="6"/>
@@ -3275,13 +3275,13 @@
       <c r="B54" s="28"/>
       <c r="C54" s="28"/>
       <c r="D54" s="10" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="6"/>
@@ -3294,13 +3294,13 @@
       <c r="B55" s="28"/>
       <c r="C55" s="28"/>
       <c r="D55" s="10" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="G55" s="6"/>
       <c r="H55" s="6"/>
@@ -3313,13 +3313,13 @@
       <c r="B56" s="28"/>
       <c r="C56" s="28"/>
       <c r="D56" s="10" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G56" s="6"/>
       <c r="H56" s="6"/>
@@ -3332,13 +3332,13 @@
       <c r="B57" s="28"/>
       <c r="C57" s="28"/>
       <c r="D57" s="10" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
@@ -3351,13 +3351,13 @@
       <c r="B58" s="28"/>
       <c r="C58" s="27"/>
       <c r="D58" s="10" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
@@ -3369,16 +3369,16 @@
       </c>
       <c r="B59" s="28"/>
       <c r="C59" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="F59" s="19" t="s">
         <v>373</v>
-      </c>
-      <c r="D59" s="10" t="s">
-        <v>360</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="F59" s="19" t="s">
-        <v>375</v>
       </c>
       <c r="G59" s="6"/>
       <c r="H59" s="6"/>
@@ -3390,16 +3390,16 @@
       </c>
       <c r="B60" s="28"/>
       <c r="C60" s="26" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D60" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="F60" s="19" t="s">
         <v>376</v>
-      </c>
-      <c r="E60" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="F60" s="19" t="s">
-        <v>378</v>
       </c>
       <c r="G60" s="6"/>
       <c r="H60" s="6"/>
@@ -3412,13 +3412,13 @@
       <c r="B61" s="27"/>
       <c r="C61" s="27"/>
       <c r="D61" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="F61" s="19" t="s">
         <v>376</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="F61" s="19" t="s">
-        <v>378</v>
       </c>
       <c r="G61" s="6"/>
       <c r="H61" s="6"/>
@@ -3429,19 +3429,19 @@
         <v>61</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C62" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="E62" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="D62" s="10" t="s">
+      <c r="F62" s="4" t="s">
         <v>330</v>
-      </c>
-      <c r="E62" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>332</v>
       </c>
       <c r="G62" s="6"/>
       <c r="H62" s="6"/>
@@ -3449,27 +3449,35 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>62</v>
-      </c>
-      <c r="B63" s="14"/>
-      <c r="C63" s="21"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="10"/>
-      <c r="F63" s="4"/>
+        <v>63</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C63" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F63" t="s">
+        <v>199</v>
+      </c>
       <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
+      <c r="H63" s="6" t="s">
+        <v>185</v>
+      </c>
       <c r="I63" s="6"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>63</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C64" s="24" t="s">
-        <v>55</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="B64" s="7"/>
+      <c r="C64" s="24"/>
       <c r="D64" s="6" t="s">
         <v>57</v>
       </c>
@@ -3477,128 +3485,128 @@
         <v>197</v>
       </c>
       <c r="F64" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G64" s="6"/>
       <c r="H64" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I64" s="6"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B65" s="7"/>
       <c r="C65" s="24"/>
       <c r="D65" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F65" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="G65" s="6"/>
       <c r="H65" s="6" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="I65" s="6"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B66" s="7"/>
-      <c r="C66" s="24"/>
+      <c r="C66" s="24" t="s">
+        <v>58</v>
+      </c>
       <c r="D66" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>200</v>
+        <v>282</v>
       </c>
       <c r="F66" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G66" s="6"/>
       <c r="H66" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="I66" s="6"/>
+        <v>179</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B67" s="7"/>
-      <c r="C67" s="24" t="s">
-        <v>59</v>
-      </c>
+      <c r="C67" s="24"/>
       <c r="D67" s="6" t="s">
         <v>60</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>284</v>
+        <v>200</v>
       </c>
       <c r="F67" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="G67" s="6"/>
       <c r="H67" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="I67" s="6" t="s">
-        <v>285</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="I67" s="6"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B68" s="7"/>
-      <c r="C68" s="24"/>
+      <c r="C68" s="25" t="s">
+        <v>379</v>
+      </c>
       <c r="D68" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F68" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="G68" s="6"/>
       <c r="H68" s="6" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="I68" s="6"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B69" s="7"/>
-      <c r="C69" s="25" t="s">
-        <v>56</v>
-      </c>
+      <c r="C69" s="25"/>
       <c r="D69" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F69" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G69" s="6"/>
       <c r="H69" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I69" s="6"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B70" s="7"/>
       <c r="C70" s="25"/>
@@ -3606,20 +3614,20 @@
         <v>62</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F70" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G70" s="6"/>
       <c r="H70" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I70" s="6"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B71" s="7"/>
       <c r="C71" s="25"/>
@@ -3627,101 +3635,88 @@
         <v>63</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F71" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="G71" s="6"/>
       <c r="H71" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I71" s="6"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B72" s="7"/>
       <c r="C72" s="25"/>
       <c r="D72" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F72" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="G72" s="6"/>
       <c r="H72" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I72" s="6"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B73" s="7"/>
       <c r="C73" s="25"/>
       <c r="D73" s="6" t="s">
-        <v>66</v>
+        <v>263</v>
       </c>
       <c r="E73" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="F73" t="s">
         <v>206</v>
-      </c>
-      <c r="F73" t="s">
-        <v>198</v>
       </c>
       <c r="G73" s="6"/>
       <c r="H73" s="6" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I73" s="6"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B74" s="7"/>
-      <c r="C74" s="25"/>
-      <c r="D74" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="E74" s="6" t="s">
+      <c r="C74" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="D74" t="s">
+        <v>75</v>
+      </c>
+      <c r="E74" t="s">
+        <v>205</v>
+      </c>
+      <c r="F74" t="s">
         <v>203</v>
-      </c>
-      <c r="F74" t="s">
-        <v>208</v>
       </c>
       <c r="G74" s="6"/>
       <c r="H74" s="6" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="I74" s="6"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="6">
-        <v>74</v>
-      </c>
+      <c r="A75" s="6"/>
       <c r="B75" s="7"/>
-      <c r="C75" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D75" t="s">
-        <v>77</v>
-      </c>
-      <c r="E75" t="s">
-        <v>207</v>
-      </c>
-      <c r="F75" t="s">
-        <v>205</v>
-      </c>
+      <c r="C75" s="5"/>
       <c r="G75" s="6"/>
-      <c r="H75" s="6" t="s">
-        <v>182</v>
-      </c>
+      <c r="H75" s="6"/>
       <c r="I75" s="6"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
@@ -3731,17 +3726,17 @@
       <c r="B76" s="7"/>
       <c r="C76" s="5"/>
       <c r="D76" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E76" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F76" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G76" s="6"/>
       <c r="H76" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I76" s="6"/>
     </row>
@@ -3752,17 +3747,17 @@
       <c r="B77" s="7"/>
       <c r="C77" s="5"/>
       <c r="D77" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E77" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F77" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G77" s="6"/>
       <c r="H77" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I77" s="6"/>
     </row>
@@ -3773,17 +3768,17 @@
       <c r="B78" s="7"/>
       <c r="C78" s="5"/>
       <c r="D78" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E78" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F78" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G78" s="6"/>
       <c r="H78" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I78" s="6"/>
     </row>
@@ -3792,23 +3787,23 @@
         <v>78</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G79" s="6"/>
       <c r="H79" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I79" s="6"/>
     </row>
@@ -3819,17 +3814,17 @@
       <c r="B80" s="7"/>
       <c r="C80" s="8"/>
       <c r="D80" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G80" s="6"/>
       <c r="H80" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I80" s="6"/>
     </row>
@@ -3840,17 +3835,17 @@
       <c r="B81" s="7"/>
       <c r="C81" s="8"/>
       <c r="D81" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G81" s="6"/>
       <c r="H81" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I81" s="6"/>
     </row>
@@ -3860,20 +3855,20 @@
       </c>
       <c r="B82" s="7"/>
       <c r="C82" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G82" s="6"/>
       <c r="H82" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I82" s="6"/>
     </row>
@@ -3884,17 +3879,17 @@
       <c r="B83" s="7"/>
       <c r="C83" s="8"/>
       <c r="D83" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G83" s="6"/>
       <c r="H83" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I83" s="6"/>
     </row>
@@ -3905,17 +3900,17 @@
       <c r="B84" s="7"/>
       <c r="C84" s="8"/>
       <c r="D84" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G84" s="6"/>
       <c r="H84" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I84" s="6"/>
     </row>
@@ -3926,17 +3921,17 @@
       <c r="B85" s="7"/>
       <c r="C85" s="8"/>
       <c r="D85" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G85" s="6"/>
       <c r="H85" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I85" s="6"/>
     </row>
@@ -3947,17 +3942,17 @@
       <c r="B86" s="7"/>
       <c r="C86" s="8"/>
       <c r="D86" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G86" s="6"/>
       <c r="H86" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I86" s="6"/>
     </row>
@@ -3968,17 +3963,17 @@
       <c r="B87" s="7"/>
       <c r="C87" s="8"/>
       <c r="D87" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G87" s="6"/>
       <c r="H87" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I87" s="6"/>
     </row>
@@ -3989,17 +3984,17 @@
       <c r="B88" s="7"/>
       <c r="C88" s="8"/>
       <c r="D88" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G88" s="6"/>
       <c r="H88" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I88" s="6"/>
     </row>
@@ -4009,20 +4004,20 @@
       </c>
       <c r="B89" s="7"/>
       <c r="C89" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G89" s="6"/>
       <c r="H89" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I89" s="6"/>
     </row>
@@ -4033,17 +4028,17 @@
       <c r="B90" s="7"/>
       <c r="C90" s="8"/>
       <c r="D90" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E90" s="10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G90" s="6"/>
       <c r="H90" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I90" s="6"/>
     </row>
@@ -4052,23 +4047,23 @@
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D91" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C91" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>95</v>
-      </c>
       <c r="E91" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G91" s="6"/>
       <c r="H91" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I91" s="6"/>
     </row>
@@ -4079,17 +4074,17 @@
       <c r="B92" s="7"/>
       <c r="C92" s="8"/>
       <c r="D92" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E92" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="F92" s="6" t="s">
         <v>217</v>
-      </c>
-      <c r="F92" s="6" t="s">
-        <v>219</v>
       </c>
       <c r="G92" s="6"/>
       <c r="H92" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I92" s="6"/>
     </row>
@@ -4098,23 +4093,23 @@
         <v>92</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G93" s="6"/>
       <c r="H93" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I93" s="6"/>
     </row>
@@ -4125,17 +4120,17 @@
       <c r="B94" s="7"/>
       <c r="C94" s="8"/>
       <c r="D94" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E94" s="10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G94" s="6"/>
       <c r="H94" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I94" s="6"/>
     </row>
@@ -4146,17 +4141,17 @@
       <c r="B95" s="7"/>
       <c r="C95" s="8"/>
       <c r="D95" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G95" s="6"/>
       <c r="H95" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I95" s="6"/>
     </row>
@@ -4166,20 +4161,20 @@
       </c>
       <c r="B96" s="7"/>
       <c r="C96" s="9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F96" s="10" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G96" s="6"/>
       <c r="H96" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I96" s="6"/>
     </row>
@@ -4188,23 +4183,23 @@
         <v>96</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G97" s="6"/>
       <c r="H97" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I97" s="6"/>
     </row>
@@ -4215,17 +4210,17 @@
       <c r="B98" s="7"/>
       <c r="C98" s="8"/>
       <c r="D98" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E98" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="F98" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="F98" s="10" t="s">
-        <v>226</v>
       </c>
       <c r="G98" s="6"/>
       <c r="H98" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I98" s="6"/>
     </row>
@@ -4236,17 +4231,17 @@
       <c r="B99" s="7"/>
       <c r="C99" s="8"/>
       <c r="D99" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E99" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="F99" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="F99" s="10" t="s">
-        <v>226</v>
       </c>
       <c r="G99" s="6"/>
       <c r="H99" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I99" s="6"/>
     </row>
@@ -4256,20 +4251,20 @@
       </c>
       <c r="B100" s="7"/>
       <c r="C100" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E100" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D100" s="6" t="s">
+      <c r="F100" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="E100" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F100" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="G100" s="6"/>
       <c r="H100" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I100" s="6"/>
     </row>
@@ -4280,17 +4275,17 @@
       <c r="B101" s="7"/>
       <c r="C101" s="8"/>
       <c r="D101" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F101" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="E101" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="F101" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="G101" s="6"/>
       <c r="H101" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I101" s="6"/>
     </row>
@@ -4301,17 +4296,17 @@
       <c r="B102" s="7"/>
       <c r="C102" s="8"/>
       <c r="D102" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F102" s="6" t="s">
         <v>108</v>
-      </c>
-      <c r="E102" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F102" s="6" t="s">
-        <v>110</v>
       </c>
       <c r="G102" s="6"/>
       <c r="H102" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I102" s="6"/>
     </row>
@@ -4320,23 +4315,23 @@
         <v>102</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G103" s="6"/>
       <c r="H103" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I103" s="6"/>
     </row>
@@ -4347,17 +4342,17 @@
       <c r="B104" s="7"/>
       <c r="C104" s="8"/>
       <c r="D104" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E104" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="F104" s="6" t="s">
         <v>228</v>
-      </c>
-      <c r="F104" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="G104" s="6"/>
       <c r="H104" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I104" s="6"/>
     </row>
@@ -4368,17 +4363,17 @@
       <c r="B105" s="7"/>
       <c r="C105" s="8"/>
       <c r="D105" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G105" s="6"/>
       <c r="H105" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I105" s="6"/>
     </row>
@@ -4388,20 +4383,20 @@
       </c>
       <c r="B106" s="7"/>
       <c r="C106" s="11" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G106" s="6"/>
       <c r="H106" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I106" s="6"/>
     </row>
@@ -4412,17 +4407,17 @@
       <c r="B107" s="7"/>
       <c r="C107" s="11"/>
       <c r="D107" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G107" s="6"/>
       <c r="H107" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I107" s="6"/>
     </row>
@@ -4432,20 +4427,20 @@
       </c>
       <c r="B108" s="7"/>
       <c r="C108" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G108" s="6"/>
       <c r="H108" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I108" s="6"/>
     </row>
@@ -4456,17 +4451,17 @@
       <c r="B109" s="7"/>
       <c r="C109" s="11"/>
       <c r="D109" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G109" s="6"/>
       <c r="H109" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I109" s="6"/>
     </row>
@@ -4477,17 +4472,17 @@
       <c r="B110" s="7"/>
       <c r="C110" s="11"/>
       <c r="D110" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G110" s="6"/>
       <c r="H110" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I110" s="6"/>
     </row>
@@ -4497,20 +4492,20 @@
       </c>
       <c r="B111" s="7"/>
       <c r="C111" s="11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G111" s="6"/>
       <c r="H111" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I111" s="6"/>
     </row>
@@ -4521,17 +4516,17 @@
       <c r="B112" s="7"/>
       <c r="C112" s="11"/>
       <c r="D112" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G112" s="6"/>
       <c r="H112" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I112" s="6"/>
     </row>
@@ -4541,20 +4536,20 @@
       </c>
       <c r="B113" s="7"/>
       <c r="C113" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G113" s="6"/>
       <c r="H113" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I113" s="6"/>
     </row>
@@ -4565,17 +4560,17 @@
       <c r="B114" s="7"/>
       <c r="C114" s="11"/>
       <c r="D114" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G114" s="6"/>
       <c r="H114" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I114" s="6"/>
     </row>
@@ -4586,17 +4581,17 @@
       <c r="B115" s="7"/>
       <c r="C115" s="11"/>
       <c r="D115" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G115" s="6"/>
       <c r="H115" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I115" s="6"/>
     </row>
@@ -4606,20 +4601,20 @@
       </c>
       <c r="B116" s="7"/>
       <c r="C116" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E116" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F116" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="G116" s="6"/>
       <c r="H116" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I116" s="6"/>
     </row>
@@ -4629,20 +4624,20 @@
       </c>
       <c r="B117" s="7"/>
       <c r="C117" s="11" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E117" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="F117" s="6" t="s">
         <v>234</v>
-      </c>
-      <c r="F117" s="6" t="s">
-        <v>236</v>
       </c>
       <c r="G117" s="6"/>
       <c r="H117" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I117" s="6"/>
     </row>
@@ -4653,17 +4648,17 @@
       <c r="B118" s="7"/>
       <c r="C118" s="11"/>
       <c r="D118" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E118" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="F118" s="6" t="s">
         <v>234</v>
-      </c>
-      <c r="F118" s="6" t="s">
-        <v>236</v>
       </c>
       <c r="G118" s="6"/>
       <c r="H118" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I118" s="6"/>
     </row>
@@ -4674,17 +4669,17 @@
       <c r="B119" s="7"/>
       <c r="C119" s="11"/>
       <c r="D119" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E119" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="F119" s="6" t="s">
         <v>234</v>
-      </c>
-      <c r="F119" s="6" t="s">
-        <v>236</v>
       </c>
       <c r="G119" s="6"/>
       <c r="H119" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I119" s="6"/>
     </row>
@@ -4695,17 +4690,17 @@
       <c r="B120" s="7"/>
       <c r="C120" s="11"/>
       <c r="D120" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G120" s="6"/>
       <c r="H120" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I120" s="6"/>
     </row>
@@ -4714,23 +4709,23 @@
         <v>120</v>
       </c>
       <c r="B121" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C121" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D121" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="C121" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>129</v>
-      </c>
       <c r="E121" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G121" s="6"/>
       <c r="H121" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I121" s="6"/>
     </row>
@@ -4741,17 +4736,17 @@
       <c r="B122" s="7"/>
       <c r="C122" s="11"/>
       <c r="D122" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G122" s="6"/>
       <c r="H122" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I122" s="6"/>
     </row>
@@ -4762,17 +4757,17 @@
       <c r="B123" s="7"/>
       <c r="C123" s="11"/>
       <c r="D123" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G123" s="6"/>
       <c r="H123" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I123" s="6"/>
     </row>
@@ -4781,23 +4776,23 @@
         <v>123</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C124" s="13" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G124" s="6"/>
       <c r="H124" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I124" s="6"/>
     </row>
@@ -4807,20 +4802,20 @@
       </c>
       <c r="B125" s="7"/>
       <c r="C125" s="13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G125" s="6"/>
       <c r="H125" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I125" s="6"/>
     </row>
@@ -4830,20 +4825,20 @@
       </c>
       <c r="B126" s="7"/>
       <c r="C126" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G126" s="6"/>
       <c r="H126" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I126" s="6"/>
     </row>
@@ -4853,20 +4848,20 @@
       </c>
       <c r="B127" s="7"/>
       <c r="C127" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G127" s="6"/>
       <c r="H127" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I127" s="6"/>
     </row>
@@ -4876,20 +4871,20 @@
       </c>
       <c r="B128" s="7"/>
       <c r="C128" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G128" s="6"/>
       <c r="H128" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I128" s="6"/>
     </row>
@@ -4899,20 +4894,20 @@
       </c>
       <c r="B129" s="7"/>
       <c r="C129" s="11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>19</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G129" s="6"/>
       <c r="H129" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I129" s="6"/>
     </row>
@@ -4923,17 +4918,17 @@
       <c r="B130" s="7"/>
       <c r="C130" s="11"/>
       <c r="D130" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G130" s="6"/>
       <c r="H130" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I130" s="6"/>
     </row>
@@ -4944,17 +4939,17 @@
       <c r="B131" s="7"/>
       <c r="C131" s="11"/>
       <c r="D131" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G131" s="6"/>
       <c r="H131" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I131" s="6"/>
     </row>
@@ -4964,20 +4959,20 @@
       </c>
       <c r="B132" s="7"/>
       <c r="C132" s="11" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>19</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G132" s="6"/>
       <c r="H132" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I132" s="6"/>
     </row>
@@ -4988,17 +4983,17 @@
       <c r="B133" s="7"/>
       <c r="C133" s="11"/>
       <c r="D133" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G133" s="6"/>
       <c r="H133" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I133" s="6"/>
     </row>
@@ -5009,17 +5004,17 @@
       <c r="B134" s="7"/>
       <c r="C134" s="11"/>
       <c r="D134" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G134" s="6"/>
       <c r="H134" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I134" s="6"/>
     </row>
@@ -5029,20 +5024,20 @@
       </c>
       <c r="B135" s="7"/>
       <c r="C135" s="11" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>19</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F135" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G135" s="6"/>
       <c r="H135" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I135" s="6"/>
     </row>
@@ -5053,17 +5048,17 @@
       <c r="B136" s="7"/>
       <c r="C136" s="11"/>
       <c r="D136" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G136" s="6"/>
       <c r="H136" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I136" s="6"/>
     </row>
@@ -5074,17 +5069,17 @@
       <c r="B137" s="7"/>
       <c r="C137" s="11"/>
       <c r="D137" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G137" s="6"/>
       <c r="H137" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I137" s="6"/>
     </row>
@@ -5094,20 +5089,20 @@
       </c>
       <c r="B138" s="7"/>
       <c r="C138" s="11" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G138" s="6"/>
       <c r="H138" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I138" s="6"/>
     </row>
@@ -5118,17 +5113,17 @@
       <c r="B139" s="7"/>
       <c r="C139" s="11"/>
       <c r="D139" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F139" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G139" s="6"/>
       <c r="H139" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I139" s="6"/>
     </row>
@@ -5139,17 +5134,17 @@
       <c r="B140" s="7"/>
       <c r="C140" s="11"/>
       <c r="D140" s="9" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F140" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G140" s="6"/>
       <c r="H140" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I140" s="6"/>
     </row>
@@ -5160,17 +5155,17 @@
       <c r="B141" s="7"/>
       <c r="C141" s="11"/>
       <c r="D141" s="9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F141" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G141" s="6"/>
       <c r="H141" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I141" s="6"/>
     </row>
@@ -5181,17 +5176,17 @@
       <c r="B142" s="7"/>
       <c r="C142" s="11"/>
       <c r="D142" s="9" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F142" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G142" s="6"/>
       <c r="H142" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I142" s="6"/>
     </row>
@@ -5200,23 +5195,23 @@
         <v>142</v>
       </c>
       <c r="B143" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D143" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="C143" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="D143" s="6" t="s">
-        <v>156</v>
-      </c>
       <c r="E143" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F143" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G143" s="6"/>
       <c r="H143" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I143" s="6"/>
     </row>
@@ -5226,20 +5221,20 @@
       </c>
       <c r="B144" s="7"/>
       <c r="C144" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F144" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G144" s="6"/>
       <c r="H144" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I144" s="6"/>
     </row>
@@ -5248,23 +5243,23 @@
         <v>144</v>
       </c>
       <c r="B145" s="14" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C145" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D145" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="D145" s="6" t="s">
-        <v>163</v>
-      </c>
       <c r="E145" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F145" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G145" s="6"/>
       <c r="H145" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I145" s="6"/>
     </row>
@@ -5273,23 +5268,23 @@
         <v>145</v>
       </c>
       <c r="B146" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C146" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="D146" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C146" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="D146" s="6" t="s">
-        <v>166</v>
-      </c>
       <c r="E146" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F146" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G146" s="6"/>
       <c r="H146" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I146" s="6"/>
     </row>
@@ -5300,17 +5295,17 @@
       <c r="B147" s="7"/>
       <c r="C147" s="11"/>
       <c r="D147" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F147" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G147" s="6"/>
       <c r="H147" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I147" s="6"/>
     </row>
@@ -5321,17 +5316,17 @@
       <c r="B148" s="7"/>
       <c r="C148" s="11"/>
       <c r="D148" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F148" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G148" s="6"/>
       <c r="H148" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I148" s="6"/>
     </row>
@@ -5341,20 +5336,20 @@
       </c>
       <c r="B149" s="7"/>
       <c r="C149" s="11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F149" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G149" s="6"/>
       <c r="H149" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I149" s="6"/>
     </row>
@@ -5365,17 +5360,17 @@
       <c r="B150" s="7"/>
       <c r="C150" s="11"/>
       <c r="D150" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F150" s="6" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G150" s="6"/>
       <c r="H150" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I150" s="6"/>
     </row>
@@ -5386,17 +5381,17 @@
       <c r="B151" s="7"/>
       <c r="C151" s="11"/>
       <c r="D151" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F151" s="6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G151" s="6"/>
       <c r="H151" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I151" s="6"/>
     </row>
@@ -5405,23 +5400,23 @@
         <v>151</v>
       </c>
       <c r="B152" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="C152" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="D152" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="C152" s="15" t="s">
+      <c r="E152" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="F152" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="D152" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="E152" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="F152" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="G152" s="6"/>
       <c r="H152" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I152" s="6"/>
     </row>
@@ -5429,9 +5424,9 @@
   <mergeCells count="52">
     <mergeCell ref="C149:C151"/>
     <mergeCell ref="B146:B151"/>
-    <mergeCell ref="C75:C78"/>
-    <mergeCell ref="B64:B78"/>
-    <mergeCell ref="C69:C74"/>
+    <mergeCell ref="C74:C78"/>
+    <mergeCell ref="B63:B78"/>
+    <mergeCell ref="C68:C73"/>
     <mergeCell ref="B143:B144"/>
     <mergeCell ref="C146:C148"/>
     <mergeCell ref="B103:B120"/>
@@ -5467,8 +5462,8 @@
     <mergeCell ref="C32:C34"/>
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="B29:B36"/>
-    <mergeCell ref="C64:C66"/>
-    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="C66:C67"/>
     <mergeCell ref="C89:C90"/>
     <mergeCell ref="B79:B90"/>
     <mergeCell ref="C79:C81"/>
@@ -5537,24 +5532,24 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C6" t="s">
         <v>314</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>315</v>
+      </c>
+      <c r="E6" t="s">
         <v>316</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>317</v>
-      </c>
-      <c r="E6" t="s">
-        <v>318</v>
-      </c>
-      <c r="F6" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{684790B6-F978-4685-A3A1-3B6F08169BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B04976-E8EC-4252-BA5C-7FA754D0E652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{F425FBA8-E65A-4F03-9270-551F3EA7C4F5}"/>
   </bookViews>

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D1BA4D-5566-4330-BC1D-1EEF6906D4B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F851F0-A23D-488D-B0AD-824C1E18519E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{F425FBA8-E65A-4F03-9270-551F3EA7C4F5}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="397">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1583,6 +1583,22 @@
   </si>
   <si>
     <t>进入活动点击领取</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>奖励到账</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成任务并已领取</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入每日首胜页面，查看数据</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>页面显示数据正常</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1695,7 +1711,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1706,6 +1722,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2108,3293 +2127,3293 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
+      <c r="G2" s="6"/>
+      <c r="H2" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I2" s="5"/>
+      <c r="I2" s="6"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="5" t="s">
+      <c r="B3" s="7"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="6"/>
+      <c r="H3" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I3" s="5"/>
+      <c r="I3" s="6"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="5" t="s">
+      <c r="B4" s="7"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="6"/>
+      <c r="H4" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I4" s="5"/>
+      <c r="I4" s="6"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+      <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="7" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5" t="s">
+      <c r="G5" s="6"/>
+      <c r="H5" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I5" s="5"/>
+      <c r="I5" s="6"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="5" t="s">
+      <c r="B6" s="7"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5" t="s">
+      <c r="G6" s="6"/>
+      <c r="H6" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I6" s="5"/>
+      <c r="I6" s="6"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="5" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5" t="s">
+      <c r="G7" s="6"/>
+      <c r="H7" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I7" s="5"/>
+      <c r="I7" s="6"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="7"/>
+      <c r="C8" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5" t="s">
+      <c r="G8" s="6"/>
+      <c r="H8" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="I8" s="5"/>
+      <c r="I8" s="6"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
+      <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="7" t="s">
+      <c r="B9" s="7"/>
+      <c r="C9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5" t="s">
+      <c r="G9" s="6"/>
+      <c r="H9" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="6" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
+      <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="5" t="s">
+      <c r="B10" s="7"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5" t="s">
+      <c r="G10" s="6"/>
+      <c r="H10" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I10" s="5"/>
+      <c r="I10" s="6"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
+      <c r="A11" s="6">
         <v>10</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="5" t="s">
+      <c r="B11" s="7"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5" t="s">
+      <c r="G11" s="6"/>
+      <c r="H11" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I11" s="5"/>
+      <c r="I11" s="6"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
+      <c r="A12" s="6">
         <v>11</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="8" t="s">
+      <c r="B12" s="7"/>
+      <c r="C12" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5" t="s">
+      <c r="G12" s="6"/>
+      <c r="H12" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I12" s="5"/>
+      <c r="I12" s="6"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="5">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5" t="s">
+      <c r="G13" s="6"/>
+      <c r="H13" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I13" s="5"/>
+      <c r="I13" s="6"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="5">
+      <c r="A14" s="6">
         <v>13</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="8" t="s">
+      <c r="B14" s="7"/>
+      <c r="C14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5" t="s">
+      <c r="G14" s="6"/>
+      <c r="H14" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I14" s="5"/>
+      <c r="I14" s="6"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="5">
+      <c r="A15" s="6">
         <v>14</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="8" t="s">
+      <c r="B15" s="7"/>
+      <c r="C15" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5" t="s">
+      <c r="G15" s="6"/>
+      <c r="H15" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I15" s="5"/>
+      <c r="I15" s="6"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
+      <c r="A16" s="6">
         <v>15</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="8" t="s">
+      <c r="B16" s="7"/>
+      <c r="C16" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5" t="s">
+      <c r="G16" s="6"/>
+      <c r="H16" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I16" s="5"/>
+      <c r="I16" s="6"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
+      <c r="A17" s="6">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5" t="s">
+      <c r="G17" s="6"/>
+      <c r="H17" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I17" s="5"/>
+      <c r="I17" s="6"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="5">
+      <c r="A18" s="6">
         <v>17</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="5" t="s">
+      <c r="B18" s="7"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5" t="s">
+      <c r="G18" s="6"/>
+      <c r="H18" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I18" s="5"/>
+      <c r="I18" s="6"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="5">
+      <c r="A19" s="6">
         <v>18</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="5" t="s">
+      <c r="B19" s="7"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5" t="s">
+      <c r="G19" s="6"/>
+      <c r="H19" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I19" s="5"/>
+      <c r="I19" s="6"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="5">
+      <c r="A20" s="6">
         <v>19</v>
       </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="8" t="s">
+      <c r="B20" s="7"/>
+      <c r="C20" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5" t="s">
+      <c r="G20" s="6"/>
+      <c r="H20" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I20" s="5"/>
+      <c r="I20" s="6"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="5">
+      <c r="A21" s="6">
         <v>20</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="8" t="s">
+      <c r="B21" s="7"/>
+      <c r="C21" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5" t="s">
+      <c r="G21" s="6"/>
+      <c r="H21" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="I21" s="5"/>
+      <c r="I21" s="6"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="5">
+      <c r="A22" s="6">
         <v>21</v>
       </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="8" t="s">
+      <c r="B22" s="7"/>
+      <c r="C22" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5" t="s">
+      <c r="G22" s="6"/>
+      <c r="H22" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="I22" s="5"/>
+      <c r="I22" s="6"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="5">
+      <c r="A23" s="6">
         <v>22</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="8" t="s">
+      <c r="B23" s="7"/>
+      <c r="C23" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5" t="s">
+      <c r="G23" s="6"/>
+      <c r="H23" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I23" s="5"/>
+      <c r="I23" s="6"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="5">
+      <c r="A24" s="6">
         <v>23</v>
       </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="7" t="s">
+      <c r="B24" s="7"/>
+      <c r="C24" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5" t="s">
+      <c r="G24" s="6"/>
+      <c r="H24" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I24" s="5"/>
+      <c r="I24" s="6"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="5">
+      <c r="A25" s="6">
         <v>24</v>
       </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="5" t="s">
+      <c r="B25" s="7"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5" t="s">
+      <c r="G25" s="6"/>
+      <c r="H25" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I25" s="5"/>
+      <c r="I25" s="6"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="5">
+      <c r="A26" s="6">
         <v>25</v>
       </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="5" t="s">
+      <c r="B26" s="7"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5" t="s">
+      <c r="G26" s="6"/>
+      <c r="H26" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I26" s="5"/>
+      <c r="I26" s="6"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="5">
+      <c r="A27" s="6">
         <v>26</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="10" t="s">
+      <c r="B27" s="7"/>
+      <c r="C27" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5" t="s">
+      <c r="G27" s="6"/>
+      <c r="H27" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I27" s="5"/>
+      <c r="I27" s="6"/>
     </row>
     <row r="28" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A28" s="5">
+      <c r="A28" s="6">
         <v>27</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11" t="s">
+      <c r="B28" s="7"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5" t="s">
+      <c r="G28" s="6"/>
+      <c r="H28" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I28" s="5"/>
+      <c r="I28" s="6"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="5">
+      <c r="A29" s="6">
         <v>28</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5" t="s">
+      <c r="G29" s="6"/>
+      <c r="H29" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="I29" s="5"/>
+      <c r="I29" s="6"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="5">
+      <c r="A30" s="6">
         <v>29</v>
       </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="8" t="s">
+      <c r="B30" s="7"/>
+      <c r="C30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5" t="s">
+      <c r="G30" s="6"/>
+      <c r="H30" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="I30" s="5"/>
+      <c r="I30" s="6"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="5">
+      <c r="A31" s="6">
         <v>30</v>
       </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="8" t="s">
+      <c r="B31" s="7"/>
+      <c r="C31" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E31" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="F31" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5" t="s">
+      <c r="G31" s="6"/>
+      <c r="H31" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="I31" s="5"/>
+      <c r="I31" s="6"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="5">
+      <c r="A32" s="6">
         <v>31</v>
       </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="7" t="s">
+      <c r="B32" s="7"/>
+      <c r="C32" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="E32" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5" t="s">
+      <c r="G32" s="6"/>
+      <c r="H32" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I32" s="5"/>
+      <c r="I32" s="6"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="5">
+      <c r="A33" s="6">
         <v>32</v>
       </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="5" t="s">
+      <c r="B33" s="7"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="F33" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5" t="s">
+      <c r="G33" s="6"/>
+      <c r="H33" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I33" s="5"/>
+      <c r="I33" s="6"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="5">
+      <c r="A34" s="6">
         <v>33</v>
       </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="5" t="s">
+      <c r="B34" s="7"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="E34" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5" t="s">
+      <c r="G34" s="6"/>
+      <c r="H34" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I34" s="5"/>
+      <c r="I34" s="6"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="5">
+      <c r="A35" s="6">
         <v>34</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="7" t="s">
+      <c r="B35" s="7"/>
+      <c r="C35" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F35" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5" t="s">
+      <c r="G35" s="6"/>
+      <c r="H35" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I35" s="5"/>
+      <c r="I35" s="6"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="5">
+      <c r="A36" s="6">
         <v>35</v>
       </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="5" t="s">
+      <c r="B36" s="7"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="E36" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="F36" s="9" t="s">
+      <c r="F36" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5" t="s">
+      <c r="G36" s="6"/>
+      <c r="H36" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I36" s="5"/>
+      <c r="I36" s="6"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="5">
+      <c r="A37" s="6">
         <v>36</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="E37" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="F37" s="9" t="s">
+      <c r="F37" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="5">
+      <c r="A38" s="6">
         <v>37</v>
       </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="8" t="s">
+      <c r="B38" s="7"/>
+      <c r="C38" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="D38" s="9" t="s">
+      <c r="D38" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="E38" s="9" t="s">
+      <c r="E38" s="10" t="s">
         <v>317</v>
       </c>
-      <c r="F38" s="9" t="s">
+      <c r="F38" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="5">
+      <c r="A39" s="6">
         <v>38</v>
       </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="8" t="s">
+      <c r="B39" s="7"/>
+      <c r="C39" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="D39" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="E39" s="9" t="s">
+      <c r="E39" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="F39" s="9" t="s">
+      <c r="F39" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="5">
+      <c r="A40" s="6">
         <v>39</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="8" t="s">
+      <c r="B40" s="7"/>
+      <c r="C40" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="D40" s="9" t="s">
+      <c r="D40" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="E40" s="9" t="s">
+      <c r="E40" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="F40" s="9" t="s">
+      <c r="F40" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="5">
+      <c r="A41" s="6">
         <v>40</v>
       </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="5">
+      <c r="A42" s="6">
         <v>41</v>
       </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6" t="s">
+      <c r="B42" s="7"/>
+      <c r="C42" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="D42" s="9" t="s">
+      <c r="D42" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="E42" s="9" t="s">
+      <c r="E42" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="F42" s="9" t="s">
+      <c r="F42" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="5">
+      <c r="A43" s="6">
         <v>42</v>
       </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="9" t="s">
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="E43" s="9" t="s">
+      <c r="E43" s="10" t="s">
         <v>338</v>
       </c>
-      <c r="F43" s="9" t="s">
+      <c r="F43" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="5">
+      <c r="A44" s="6">
         <v>43</v>
       </c>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="9" t="s">
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="E44" s="9" t="s">
+      <c r="E44" s="10" t="s">
         <v>338</v>
       </c>
-      <c r="F44" s="9" t="s">
+      <c r="F44" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="5">
+      <c r="A45" s="6">
         <v>44</v>
       </c>
-      <c r="B45" s="6"/>
-      <c r="C45" s="13" t="s">
+      <c r="B45" s="7"/>
+      <c r="C45" s="14" t="s">
         <v>341</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D45" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="E45" s="9" t="s">
+      <c r="E45" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="F45" s="9" t="s">
+      <c r="F45" s="10" t="s">
         <v>343</v>
       </c>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="5">
+      <c r="A46" s="6">
         <v>45</v>
       </c>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6" t="s">
+      <c r="B46" s="7"/>
+      <c r="C46" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="D46" s="9" t="s">
+      <c r="D46" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="E46" s="9" t="s">
+      <c r="E46" s="10" t="s">
         <v>345</v>
       </c>
-      <c r="F46" s="9" t="s">
+      <c r="F46" s="10" t="s">
         <v>346</v>
       </c>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="5">
+      <c r="A47" s="6">
         <v>46</v>
       </c>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="9" t="s">
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="E47" s="9" t="s">
+      <c r="E47" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="F47" s="9" t="s">
+      <c r="F47" s="10" t="s">
         <v>346</v>
       </c>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="5">
+      <c r="A48" s="6">
         <v>47</v>
       </c>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="9" t="s">
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="E48" s="9" t="s">
+      <c r="E48" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="F48" s="9" t="s">
+      <c r="F48" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="5">
+      <c r="A49" s="6">
         <v>48</v>
       </c>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="9" t="s">
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="E49" s="9" t="s">
+      <c r="E49" s="10" t="s">
         <v>350</v>
       </c>
-      <c r="F49" s="9" t="s">
+      <c r="F49" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
-      <c r="I49" s="5"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="5">
+      <c r="A50" s="6">
         <v>49</v>
       </c>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6" t="s">
+      <c r="B50" s="7"/>
+      <c r="C50" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="D50" s="9" t="s">
+      <c r="D50" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="E50" s="9" t="s">
+      <c r="E50" s="10" t="s">
         <v>351</v>
       </c>
-      <c r="F50" s="9" t="s">
+      <c r="F50" s="10" t="s">
         <v>346</v>
       </c>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
-      <c r="I50" s="5"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="5">
+      <c r="A51" s="6">
         <v>50</v>
       </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="9" t="s">
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="E51" s="9" t="s">
+      <c r="E51" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="F51" s="9" t="s">
+      <c r="F51" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="5">
+      <c r="A52" s="6">
         <v>51</v>
       </c>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="9" t="s">
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="E52" s="9" t="s">
+      <c r="E52" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="F52" s="9" t="s">
+      <c r="F52" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
-      <c r="I52" s="5"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="5">
+      <c r="A53" s="6">
         <v>52</v>
       </c>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6" t="s">
+      <c r="B53" s="7"/>
+      <c r="C53" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="D53" s="9" t="s">
+      <c r="D53" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="E53" s="9" t="s">
+      <c r="E53" s="10" t="s">
         <v>356</v>
       </c>
-      <c r="F53" s="9" t="s">
+      <c r="F53" s="10" t="s">
         <v>355</v>
       </c>
-      <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
-      <c r="I53" s="5"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="5">
+      <c r="A54" s="6">
         <v>53</v>
       </c>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="9" t="s">
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="E54" s="9" t="s">
+      <c r="E54" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="F54" s="9" t="s">
+      <c r="F54" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
-      <c r="I54" s="5"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="5">
+      <c r="A55" s="6">
         <v>54</v>
       </c>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="9" t="s">
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="E55" s="9" t="s">
+      <c r="E55" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="F55" s="9" t="s">
+      <c r="F55" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
-      <c r="I55" s="5"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="5">
+      <c r="A56" s="6">
         <v>55</v>
       </c>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="9" t="s">
+      <c r="B56" s="7"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="E56" s="9" t="s">
+      <c r="E56" s="10" t="s">
         <v>365</v>
       </c>
-      <c r="F56" s="9" t="s">
+      <c r="F56" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="G56" s="5"/>
-      <c r="H56" s="5"/>
-      <c r="I56" s="5"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="5">
+      <c r="A57" s="6">
         <v>56</v>
       </c>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="9" t="s">
+      <c r="B57" s="7"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="E57" s="9" t="s">
+      <c r="E57" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="F57" s="9" t="s">
+      <c r="F57" s="10" t="s">
         <v>363</v>
       </c>
-      <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
-      <c r="I57" s="5"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="5">
+      <c r="A58" s="6">
         <v>57</v>
       </c>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="9" t="s">
+      <c r="B58" s="7"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="E58" s="9" t="s">
+      <c r="E58" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="F58" s="9" t="s">
+      <c r="F58" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="G58" s="5"/>
-      <c r="H58" s="5"/>
-      <c r="I58" s="5"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="5">
+      <c r="A59" s="6">
         <v>58</v>
       </c>
-      <c r="B59" s="6"/>
-      <c r="C59" s="13" t="s">
+      <c r="B59" s="7"/>
+      <c r="C59" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="D59" s="9" t="s">
+      <c r="D59" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="E59" s="9" t="s">
+      <c r="E59" s="10" t="s">
         <v>368</v>
       </c>
-      <c r="F59" s="9" t="s">
+      <c r="F59" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="G59" s="5"/>
-      <c r="H59" s="5"/>
-      <c r="I59" s="5"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="5">
+      <c r="A60" s="6">
         <v>59</v>
       </c>
-      <c r="B60" s="6"/>
-      <c r="C60" s="6" t="s">
+      <c r="B60" s="7"/>
+      <c r="C60" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="D60" s="9" t="s">
+      <c r="D60" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="E60" s="9" t="s">
+      <c r="E60" s="10" t="s">
         <v>371</v>
       </c>
-      <c r="F60" s="9" t="s">
+      <c r="F60" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
-      <c r="I60" s="5"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="5">
+      <c r="A61" s="6">
         <v>60</v>
       </c>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="9" t="s">
+      <c r="B61" s="7"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="E61" s="9" t="s">
+      <c r="E61" s="10" t="s">
         <v>373</v>
       </c>
-      <c r="F61" s="9" t="s">
+      <c r="F61" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
-      <c r="I61" s="5"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="5">
+      <c r="A62" s="6">
         <v>61</v>
       </c>
-      <c r="B62" s="13" t="s">
+      <c r="B62" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="C62" s="13" t="s">
+      <c r="C62" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="D62" s="9" t="s">
+      <c r="D62" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="E62" s="9" t="s">
+      <c r="E62" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="F62" s="9" t="s">
+      <c r="F62" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
-      <c r="I62" s="5"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="5">
+      <c r="A63" s="6">
         <v>62</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C63" s="18" t="s">
+      <c r="C63" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="D63" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E63" s="5" t="s">
+      <c r="E63" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="F63" s="5" t="s">
+      <c r="F63" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5" t="s">
+      <c r="G63" s="6"/>
+      <c r="H63" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I63" s="5"/>
+      <c r="I63" s="6"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="5">
+      <c r="A64" s="6">
         <v>63</v>
       </c>
-      <c r="B64" s="6"/>
-      <c r="C64" s="18"/>
-      <c r="D64" s="5" t="s">
+      <c r="B64" s="7"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E64" s="5" t="s">
+      <c r="E64" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="F64" s="5" t="s">
+      <c r="F64" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="G64" s="5"/>
-      <c r="H64" s="5" t="s">
+      <c r="G64" s="6"/>
+      <c r="H64" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I64" s="5"/>
+      <c r="I64" s="6"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="5">
+      <c r="A65" s="6">
         <v>64</v>
       </c>
-      <c r="B65" s="6"/>
-      <c r="C65" s="18"/>
-      <c r="D65" s="5" t="s">
+      <c r="B65" s="7"/>
+      <c r="C65" s="19"/>
+      <c r="D65" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E65" s="5" t="s">
+      <c r="E65" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="F65" s="5" t="s">
+      <c r="F65" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="G65" s="5"/>
-      <c r="H65" s="5" t="s">
+      <c r="G65" s="6"/>
+      <c r="H65" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I65" s="5"/>
+      <c r="I65" s="6"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="5">
+      <c r="A66" s="6">
         <v>65</v>
       </c>
-      <c r="B66" s="6"/>
-      <c r="C66" s="18" t="s">
+      <c r="B66" s="7"/>
+      <c r="C66" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="D66" s="5" t="s">
+      <c r="D66" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="E66" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="F66" s="5" t="s">
+      <c r="F66" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="G66" s="5"/>
-      <c r="H66" s="5" t="s">
+      <c r="G66" s="6"/>
+      <c r="H66" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I66" s="5" t="s">
+      <c r="I66" s="6" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="5">
+      <c r="A67" s="6">
         <v>66</v>
       </c>
-      <c r="B67" s="6"/>
-      <c r="C67" s="18"/>
-      <c r="D67" s="5" t="s">
+      <c r="B67" s="7"/>
+      <c r="C67" s="19"/>
+      <c r="D67" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E67" s="5" t="s">
+      <c r="E67" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="F67" s="5" t="s">
+      <c r="F67" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="G67" s="5"/>
-      <c r="H67" s="5" t="s">
+      <c r="G67" s="6"/>
+      <c r="H67" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I67" s="5"/>
+      <c r="I67" s="6"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="5">
+      <c r="A68" s="6">
         <v>67</v>
       </c>
-      <c r="B68" s="6"/>
-      <c r="C68" s="10" t="s">
+      <c r="B68" s="7"/>
+      <c r="C68" s="11" t="s">
         <v>375</v>
       </c>
-      <c r="D68" s="5" t="s">
+      <c r="D68" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E68" s="5" t="s">
+      <c r="E68" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="F68" s="5" t="s">
+      <c r="F68" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="G68" s="5"/>
-      <c r="H68" s="5" t="s">
+      <c r="G68" s="6"/>
+      <c r="H68" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I68" s="5"/>
+      <c r="I68" s="6"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="5">
+      <c r="A69" s="6">
         <v>68</v>
       </c>
-      <c r="B69" s="6"/>
-      <c r="C69" s="10"/>
-      <c r="D69" s="5" t="s">
+      <c r="B69" s="7"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E69" s="5" t="s">
+      <c r="E69" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="F69" s="5" t="s">
+      <c r="F69" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="G69" s="5"/>
-      <c r="H69" s="5" t="s">
+      <c r="G69" s="6"/>
+      <c r="H69" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I69" s="5"/>
+      <c r="I69" s="6"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="5">
+      <c r="A70" s="6">
         <v>69</v>
       </c>
-      <c r="B70" s="6"/>
-      <c r="C70" s="10"/>
-      <c r="D70" s="5" t="s">
+      <c r="B70" s="7"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E70" s="5" t="s">
+      <c r="E70" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="F70" s="5" t="s">
+      <c r="F70" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="G70" s="5"/>
-      <c r="H70" s="5" t="s">
+      <c r="G70" s="6"/>
+      <c r="H70" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I70" s="5"/>
+      <c r="I70" s="6"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="5">
+      <c r="A71" s="6">
         <v>70</v>
       </c>
-      <c r="B71" s="6"/>
-      <c r="C71" s="10"/>
-      <c r="D71" s="5" t="s">
+      <c r="B71" s="7"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E71" s="5" t="s">
+      <c r="E71" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F71" s="5" t="s">
+      <c r="F71" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="G71" s="5"/>
-      <c r="H71" s="5" t="s">
+      <c r="G71" s="6"/>
+      <c r="H71" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I71" s="5"/>
+      <c r="I71" s="6"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="5">
+      <c r="A72" s="6">
         <v>71</v>
       </c>
-      <c r="B72" s="6"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="5" t="s">
+      <c r="B72" s="7"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E72" s="5" t="s">
+      <c r="E72" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="F72" s="5" t="s">
+      <c r="F72" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5" t="s">
+      <c r="G72" s="6"/>
+      <c r="H72" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I72" s="5"/>
+      <c r="I72" s="6"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="5">
+      <c r="A73" s="6">
         <v>72</v>
       </c>
-      <c r="B73" s="6"/>
-      <c r="C73" s="10"/>
-      <c r="D73" s="5" t="s">
+      <c r="B73" s="7"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="E73" s="5" t="s">
+      <c r="E73" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F73" s="5" t="s">
+      <c r="F73" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="G73" s="5"/>
-      <c r="H73" s="5" t="s">
+      <c r="G73" s="6"/>
+      <c r="H73" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I73" s="5"/>
+      <c r="I73" s="6"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="5">
+      <c r="A74" s="6">
         <v>73</v>
       </c>
-      <c r="B74" s="6"/>
-      <c r="C74" s="10" t="s">
+      <c r="B74" s="7"/>
+      <c r="C74" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="D74" s="5" t="s">
+      <c r="D74" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E74" s="5" t="s">
+      <c r="E74" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="F74" s="5" t="s">
+      <c r="F74" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5" t="s">
+      <c r="G74" s="6"/>
+      <c r="H74" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I74" s="5"/>
+      <c r="I74" s="6"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="5">
+      <c r="A75" s="6">
         <v>74</v>
       </c>
-      <c r="B75" s="6"/>
-      <c r="C75" s="10"/>
-      <c r="D75" s="5" t="s">
+      <c r="B75" s="7"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="E75" s="5" t="s">
+      <c r="E75" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="F75" s="5" t="s">
+      <c r="F75" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="G75" s="5"/>
-      <c r="H75" s="5" t="s">
+      <c r="G75" s="6"/>
+      <c r="H75" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I75" s="5"/>
+      <c r="I75" s="6"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="5">
+      <c r="A76" s="6">
         <v>75</v>
       </c>
-      <c r="B76" s="6"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="5" t="s">
+      <c r="B76" s="7"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E76" s="5" t="s">
+      <c r="E76" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="F76" s="5" t="s">
+      <c r="F76" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="G76" s="5"/>
-      <c r="H76" s="5" t="s">
+      <c r="G76" s="6"/>
+      <c r="H76" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I76" s="5"/>
+      <c r="I76" s="6"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="5">
+      <c r="A77" s="6">
         <v>76</v>
       </c>
-      <c r="B77" s="6"/>
-      <c r="C77" s="10"/>
-      <c r="D77" s="5" t="s">
+      <c r="B77" s="7"/>
+      <c r="C77" s="11"/>
+      <c r="D77" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E77" s="5" t="s">
+      <c r="E77" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F77" s="5" t="s">
+      <c r="F77" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="G77" s="5"/>
-      <c r="H77" s="5" t="s">
+      <c r="G77" s="6"/>
+      <c r="H77" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I77" s="5"/>
+      <c r="I77" s="6"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="5">
+      <c r="A78" s="6">
         <v>77</v>
       </c>
-      <c r="B78" s="6"/>
-      <c r="C78" s="10"/>
-      <c r="D78" s="5" t="s">
+      <c r="B78" s="7"/>
+      <c r="C78" s="11"/>
+      <c r="D78" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="E78" s="5" t="s">
+      <c r="E78" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="F78" s="5" t="s">
+      <c r="F78" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="G78" s="5"/>
-      <c r="H78" s="5" t="s">
+      <c r="G78" s="6"/>
+      <c r="H78" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I78" s="5"/>
+      <c r="I78" s="6"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="5">
+      <c r="A79" s="6">
         <v>78</v>
       </c>
-      <c r="B79" s="6" t="s">
+      <c r="B79" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C79" s="7" t="s">
+      <c r="C79" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D79" s="5" t="s">
+      <c r="D79" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E79" s="9" t="s">
+      <c r="E79" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="F79" s="5" t="s">
+      <c r="F79" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="G79" s="5"/>
-      <c r="H79" s="5" t="s">
+      <c r="G79" s="6"/>
+      <c r="H79" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I79" s="5"/>
+      <c r="I79" s="6"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="5">
+      <c r="A80" s="6">
         <v>79</v>
       </c>
-      <c r="B80" s="6"/>
-      <c r="C80" s="7"/>
-      <c r="D80" s="5" t="s">
+      <c r="B80" s="7"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E80" s="9" t="s">
+      <c r="E80" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="F80" s="5" t="s">
+      <c r="F80" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="G80" s="5"/>
-      <c r="H80" s="5" t="s">
+      <c r="G80" s="6"/>
+      <c r="H80" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I80" s="5"/>
+      <c r="I80" s="6"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="5">
+      <c r="A81" s="6">
         <v>80</v>
       </c>
-      <c r="B81" s="6"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="5" t="s">
+      <c r="B81" s="7"/>
+      <c r="C81" s="8"/>
+      <c r="D81" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E81" s="9" t="s">
+      <c r="E81" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="F81" s="5" t="s">
+      <c r="F81" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="G81" s="5"/>
-      <c r="H81" s="5" t="s">
+      <c r="G81" s="6"/>
+      <c r="H81" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I81" s="5"/>
+      <c r="I81" s="6"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="5">
+      <c r="A82" s="6">
         <v>81</v>
       </c>
-      <c r="B82" s="6"/>
-      <c r="C82" s="7" t="s">
+      <c r="B82" s="7"/>
+      <c r="C82" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D82" s="5" t="s">
+      <c r="D82" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E82" s="9" t="s">
+      <c r="E82" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="F82" s="5" t="s">
+      <c r="F82" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="G82" s="5"/>
-      <c r="H82" s="5" t="s">
+      <c r="G82" s="6"/>
+      <c r="H82" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I82" s="5"/>
+      <c r="I82" s="6"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" s="5">
+      <c r="A83" s="6">
         <v>82</v>
       </c>
-      <c r="B83" s="6"/>
-      <c r="C83" s="7"/>
-      <c r="D83" s="5" t="s">
+      <c r="B83" s="7"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E83" s="9" t="s">
+      <c r="E83" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="F83" s="5" t="s">
+      <c r="F83" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="G83" s="5"/>
-      <c r="H83" s="5" t="s">
+      <c r="G83" s="6"/>
+      <c r="H83" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I83" s="5"/>
+      <c r="I83" s="6"/>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="5">
+      <c r="A84" s="6">
         <v>83</v>
       </c>
-      <c r="B84" s="6"/>
-      <c r="C84" s="7"/>
-      <c r="D84" s="5" t="s">
+      <c r="B84" s="7"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E84" s="9" t="s">
+      <c r="E84" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="F84" s="5" t="s">
+      <c r="F84" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="G84" s="5"/>
-      <c r="H84" s="5" t="s">
+      <c r="G84" s="6"/>
+      <c r="H84" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I84" s="5"/>
+      <c r="I84" s="6"/>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" s="5">
+      <c r="A85" s="6">
         <v>84</v>
       </c>
-      <c r="B85" s="6"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="5" t="s">
+      <c r="B85" s="7"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="E85" s="9" t="s">
+      <c r="E85" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="F85" s="5" t="s">
+      <c r="F85" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="G85" s="5"/>
-      <c r="H85" s="5" t="s">
+      <c r="G85" s="6"/>
+      <c r="H85" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I85" s="5"/>
+      <c r="I85" s="6"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="5">
+      <c r="A86" s="6">
         <v>85</v>
       </c>
-      <c r="B86" s="6"/>
-      <c r="C86" s="7"/>
-      <c r="D86" s="5" t="s">
+      <c r="B86" s="7"/>
+      <c r="C86" s="8"/>
+      <c r="D86" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E86" s="9" t="s">
+      <c r="E86" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="F86" s="5" t="s">
+      <c r="F86" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="G86" s="5"/>
-      <c r="H86" s="5" t="s">
+      <c r="G86" s="6"/>
+      <c r="H86" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I86" s="5"/>
+      <c r="I86" s="6"/>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="5">
+      <c r="A87" s="6">
         <v>86</v>
       </c>
-      <c r="B87" s="6"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="5" t="s">
+      <c r="B87" s="7"/>
+      <c r="C87" s="8"/>
+      <c r="D87" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="E87" s="9" t="s">
+      <c r="E87" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="F87" s="5" t="s">
+      <c r="F87" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="G87" s="5"/>
-      <c r="H87" s="5" t="s">
+      <c r="G87" s="6"/>
+      <c r="H87" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I87" s="5"/>
+      <c r="I87" s="6"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="5">
+      <c r="A88" s="6">
         <v>87</v>
       </c>
-      <c r="B88" s="6"/>
-      <c r="C88" s="7"/>
-      <c r="D88" s="5" t="s">
+      <c r="B88" s="7"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="E88" s="9" t="s">
+      <c r="E88" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="F88" s="5" t="s">
+      <c r="F88" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="G88" s="5"/>
-      <c r="H88" s="5" t="s">
+      <c r="G88" s="6"/>
+      <c r="H88" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I88" s="5"/>
+      <c r="I88" s="6"/>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="5">
+      <c r="A89" s="6">
         <v>88</v>
       </c>
-      <c r="B89" s="6"/>
-      <c r="C89" s="7" t="s">
+      <c r="B89" s="7"/>
+      <c r="C89" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D89" s="5" t="s">
+      <c r="D89" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="E89" s="9" t="s">
+      <c r="E89" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="F89" s="5" t="s">
+      <c r="F89" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="G89" s="5"/>
-      <c r="H89" s="5" t="s">
+      <c r="G89" s="6"/>
+      <c r="H89" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I89" s="5"/>
+      <c r="I89" s="6"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="5">
+      <c r="A90" s="6">
         <v>89</v>
       </c>
-      <c r="B90" s="6"/>
-      <c r="C90" s="7"/>
-      <c r="D90" s="5" t="s">
+      <c r="B90" s="7"/>
+      <c r="C90" s="8"/>
+      <c r="D90" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E90" s="9" t="s">
+      <c r="E90" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="F90" s="5" t="s">
+      <c r="F90" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="G90" s="5"/>
-      <c r="H90" s="5" t="s">
+      <c r="G90" s="6"/>
+      <c r="H90" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I90" s="5"/>
+      <c r="I90" s="6"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" s="5">
+      <c r="A91" s="6">
         <v>90</v>
       </c>
-      <c r="B91" s="6" t="s">
+      <c r="B91" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C91" s="7" t="s">
+      <c r="C91" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D91" s="5" t="s">
+      <c r="D91" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E91" s="9" t="s">
+      <c r="E91" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="F91" s="5" t="s">
+      <c r="F91" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="G91" s="5"/>
-      <c r="H91" s="5" t="s">
+      <c r="G91" s="6"/>
+      <c r="H91" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I91" s="5"/>
+      <c r="I91" s="6"/>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="5">
+      <c r="A92" s="6">
         <v>91</v>
       </c>
-      <c r="B92" s="6"/>
-      <c r="C92" s="7"/>
-      <c r="D92" s="5" t="s">
+      <c r="B92" s="7"/>
+      <c r="C92" s="8"/>
+      <c r="D92" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E92" s="9" t="s">
+      <c r="E92" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="F92" s="5" t="s">
+      <c r="F92" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="G92" s="5"/>
-      <c r="H92" s="5" t="s">
+      <c r="G92" s="6"/>
+      <c r="H92" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I92" s="5"/>
+      <c r="I92" s="6"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="5">
+      <c r="A93" s="6">
         <v>92</v>
       </c>
-      <c r="B93" s="6" t="s">
+      <c r="B93" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C93" s="7" t="s">
+      <c r="C93" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="D93" s="5" t="s">
+      <c r="D93" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E93" s="9" t="s">
+      <c r="E93" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="F93" s="5" t="s">
+      <c r="F93" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="G93" s="5"/>
-      <c r="H93" s="5" t="s">
+      <c r="G93" s="6"/>
+      <c r="H93" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I93" s="5"/>
+      <c r="I93" s="6"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" s="5">
+      <c r="A94" s="6">
         <v>93</v>
       </c>
-      <c r="B94" s="6"/>
-      <c r="C94" s="7"/>
-      <c r="D94" s="5" t="s">
+      <c r="B94" s="7"/>
+      <c r="C94" s="8"/>
+      <c r="D94" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E94" s="9" t="s">
+      <c r="E94" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="F94" s="5" t="s">
+      <c r="F94" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="G94" s="5"/>
-      <c r="H94" s="5" t="s">
+      <c r="G94" s="6"/>
+      <c r="H94" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I94" s="5"/>
+      <c r="I94" s="6"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="5">
+      <c r="A95" s="6">
         <v>94</v>
       </c>
-      <c r="B95" s="6"/>
-      <c r="C95" s="7"/>
-      <c r="D95" s="5" t="s">
+      <c r="B95" s="7"/>
+      <c r="C95" s="8"/>
+      <c r="D95" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E95" s="9" t="s">
+      <c r="E95" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="F95" s="5" t="s">
+      <c r="F95" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="G95" s="5"/>
-      <c r="H95" s="5" t="s">
+      <c r="G95" s="6"/>
+      <c r="H95" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I95" s="5"/>
+      <c r="I95" s="6"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="5">
+      <c r="A96" s="6">
         <v>95</v>
       </c>
-      <c r="B96" s="6"/>
-      <c r="C96" s="8" t="s">
+      <c r="B96" s="7"/>
+      <c r="C96" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="D96" s="5" t="s">
+      <c r="D96" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="E96" s="9" t="s">
+      <c r="E96" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="F96" s="9" t="s">
+      <c r="F96" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="G96" s="5"/>
-      <c r="H96" s="5" t="s">
+      <c r="G96" s="6"/>
+      <c r="H96" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I96" s="5"/>
+      <c r="I96" s="6"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="5">
+      <c r="A97" s="6">
         <v>96</v>
       </c>
-      <c r="B97" s="6" t="s">
+      <c r="B97" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="C97" s="7" t="s">
+      <c r="C97" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D97" s="5" t="s">
+      <c r="D97" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E97" s="9" t="s">
+      <c r="E97" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="F97" s="9" t="s">
+      <c r="F97" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="G97" s="5"/>
-      <c r="H97" s="5" t="s">
+      <c r="G97" s="6"/>
+      <c r="H97" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I97" s="5"/>
+      <c r="I97" s="6"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="5">
+      <c r="A98" s="6">
         <v>97</v>
       </c>
-      <c r="B98" s="6"/>
-      <c r="C98" s="7"/>
-      <c r="D98" s="5" t="s">
+      <c r="B98" s="7"/>
+      <c r="C98" s="8"/>
+      <c r="D98" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="E98" s="9" t="s">
+      <c r="E98" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="F98" s="9" t="s">
+      <c r="F98" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="G98" s="5"/>
-      <c r="H98" s="5" t="s">
+      <c r="G98" s="6"/>
+      <c r="H98" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I98" s="5"/>
+      <c r="I98" s="6"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" s="5">
+      <c r="A99" s="6">
         <v>98</v>
       </c>
-      <c r="B99" s="6"/>
-      <c r="C99" s="7"/>
-      <c r="D99" s="5" t="s">
+      <c r="B99" s="7"/>
+      <c r="C99" s="8"/>
+      <c r="D99" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E99" s="9" t="s">
+      <c r="E99" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="F99" s="9" t="s">
+      <c r="F99" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="G99" s="5"/>
-      <c r="H99" s="5" t="s">
+      <c r="G99" s="6"/>
+      <c r="H99" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I99" s="5"/>
+      <c r="I99" s="6"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="5">
+      <c r="A100" s="6">
         <v>99</v>
       </c>
-      <c r="B100" s="6"/>
-      <c r="C100" s="7" t="s">
+      <c r="B100" s="7"/>
+      <c r="C100" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="D100" s="5" t="s">
+      <c r="D100" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E100" s="5" t="s">
+      <c r="E100" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F100" s="5" t="s">
+      <c r="F100" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="G100" s="5"/>
-      <c r="H100" s="5" t="s">
+      <c r="G100" s="6"/>
+      <c r="H100" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I100" s="5"/>
+      <c r="I100" s="6"/>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="5">
+      <c r="A101" s="6">
         <v>100</v>
       </c>
-      <c r="B101" s="6"/>
-      <c r="C101" s="7"/>
-      <c r="D101" s="5" t="s">
+      <c r="B101" s="7"/>
+      <c r="C101" s="8"/>
+      <c r="D101" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E101" s="5" t="s">
+      <c r="E101" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="F101" s="5" t="s">
+      <c r="F101" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="G101" s="5"/>
-      <c r="H101" s="5" t="s">
+      <c r="G101" s="6"/>
+      <c r="H101" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I101" s="5"/>
+      <c r="I101" s="6"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" s="5">
+      <c r="A102" s="6">
         <v>101</v>
       </c>
-      <c r="B102" s="6"/>
-      <c r="C102" s="7"/>
-      <c r="D102" s="5" t="s">
+      <c r="B102" s="7"/>
+      <c r="C102" s="8"/>
+      <c r="D102" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="E102" s="5" t="s">
+      <c r="E102" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="F102" s="5" t="s">
+      <c r="F102" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="G102" s="5"/>
-      <c r="H102" s="5" t="s">
+      <c r="G102" s="6"/>
+      <c r="H102" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I102" s="5"/>
+      <c r="I102" s="6"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="5">
+      <c r="A103" s="6">
         <v>102</v>
       </c>
-      <c r="B103" s="6" t="s">
+      <c r="B103" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="C103" s="7" t="s">
+      <c r="C103" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="D103" s="5" t="s">
+      <c r="D103" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E103" s="5" t="s">
+      <c r="E103" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="F103" s="5" t="s">
+      <c r="F103" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G103" s="5"/>
-      <c r="H103" s="5" t="s">
+      <c r="G103" s="6"/>
+      <c r="H103" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I103" s="5"/>
+      <c r="I103" s="6"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="5">
+      <c r="A104" s="6">
         <v>103</v>
       </c>
-      <c r="B104" s="6"/>
-      <c r="C104" s="7"/>
-      <c r="D104" s="5" t="s">
+      <c r="B104" s="7"/>
+      <c r="C104" s="8"/>
+      <c r="D104" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="E104" s="5" t="s">
+      <c r="E104" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="F104" s="5" t="s">
+      <c r="F104" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G104" s="5"/>
-      <c r="H104" s="5" t="s">
+      <c r="G104" s="6"/>
+      <c r="H104" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I104" s="5"/>
+      <c r="I104" s="6"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="5">
+      <c r="A105" s="6">
         <v>104</v>
       </c>
-      <c r="B105" s="6"/>
-      <c r="C105" s="7"/>
-      <c r="D105" s="5" t="s">
+      <c r="B105" s="7"/>
+      <c r="C105" s="8"/>
+      <c r="D105" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="E105" s="5" t="s">
+      <c r="E105" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="F105" s="5" t="s">
+      <c r="F105" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G105" s="5"/>
-      <c r="H105" s="5" t="s">
+      <c r="G105" s="6"/>
+      <c r="H105" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I105" s="5"/>
+      <c r="I105" s="6"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" s="5">
+      <c r="A106" s="6">
         <v>105</v>
       </c>
-      <c r="B106" s="6"/>
-      <c r="C106" s="10" t="s">
+      <c r="B106" s="7"/>
+      <c r="C106" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="D106" s="5" t="s">
+      <c r="D106" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="E106" s="5" t="s">
+      <c r="E106" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="F106" s="5" t="s">
+      <c r="F106" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="G106" s="5"/>
-      <c r="H106" s="5" t="s">
+      <c r="G106" s="6"/>
+      <c r="H106" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I106" s="5"/>
+      <c r="I106" s="6"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="5">
+      <c r="A107" s="6">
         <v>106</v>
       </c>
-      <c r="B107" s="6"/>
-      <c r="C107" s="10"/>
-      <c r="D107" s="5" t="s">
+      <c r="B107" s="7"/>
+      <c r="C107" s="11"/>
+      <c r="D107" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="E107" s="5" t="s">
+      <c r="E107" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="F107" s="5" t="s">
+      <c r="F107" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G107" s="5"/>
-      <c r="H107" s="5" t="s">
+      <c r="G107" s="6"/>
+      <c r="H107" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I107" s="5"/>
+      <c r="I107" s="6"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" s="5">
+      <c r="A108" s="6">
         <v>107</v>
       </c>
-      <c r="B108" s="6"/>
-      <c r="C108" s="10" t="s">
+      <c r="B108" s="7"/>
+      <c r="C108" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="D108" s="5" t="s">
+      <c r="D108" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="E108" s="5" t="s">
+      <c r="E108" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="F108" s="5" t="s">
+      <c r="F108" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="G108" s="5"/>
-      <c r="H108" s="5" t="s">
+      <c r="G108" s="6"/>
+      <c r="H108" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I108" s="5"/>
+      <c r="I108" s="6"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="5">
+      <c r="A109" s="6">
         <v>108</v>
       </c>
-      <c r="B109" s="6"/>
-      <c r="C109" s="10"/>
-      <c r="D109" s="5" t="s">
+      <c r="B109" s="7"/>
+      <c r="C109" s="11"/>
+      <c r="D109" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="E109" s="5" t="s">
+      <c r="E109" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="F109" s="5" t="s">
+      <c r="F109" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="G109" s="5"/>
-      <c r="H109" s="5" t="s">
+      <c r="G109" s="6"/>
+      <c r="H109" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I109" s="5"/>
+      <c r="I109" s="6"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="5">
+      <c r="A110" s="6">
         <v>109</v>
       </c>
-      <c r="B110" s="6"/>
-      <c r="C110" s="10"/>
-      <c r="D110" s="5" t="s">
+      <c r="B110" s="7"/>
+      <c r="C110" s="11"/>
+      <c r="D110" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="E110" s="5" t="s">
+      <c r="E110" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="F110" s="5" t="s">
+      <c r="F110" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="G110" s="5"/>
-      <c r="H110" s="5" t="s">
+      <c r="G110" s="6"/>
+      <c r="H110" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I110" s="5"/>
+      <c r="I110" s="6"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="5">
+      <c r="A111" s="6">
         <v>110</v>
       </c>
-      <c r="B111" s="6"/>
-      <c r="C111" s="10" t="s">
+      <c r="B111" s="7"/>
+      <c r="C111" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="D111" s="5" t="s">
+      <c r="D111" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="E111" s="5" t="s">
+      <c r="E111" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="F111" s="5" t="s">
+      <c r="F111" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="G111" s="5"/>
-      <c r="H111" s="5" t="s">
+      <c r="G111" s="6"/>
+      <c r="H111" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I111" s="5"/>
+      <c r="I111" s="6"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="5">
+      <c r="A112" s="6">
         <v>111</v>
       </c>
-      <c r="B112" s="6"/>
-      <c r="C112" s="10"/>
-      <c r="D112" s="5" t="s">
+      <c r="B112" s="7"/>
+      <c r="C112" s="11"/>
+      <c r="D112" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="E112" s="5" t="s">
+      <c r="E112" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="F112" s="5" t="s">
+      <c r="F112" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="G112" s="5"/>
-      <c r="H112" s="5" t="s">
+      <c r="G112" s="6"/>
+      <c r="H112" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I112" s="5"/>
+      <c r="I112" s="6"/>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" s="5">
+      <c r="A113" s="6">
         <v>112</v>
       </c>
-      <c r="B113" s="6"/>
-      <c r="C113" s="10" t="s">
+      <c r="B113" s="7"/>
+      <c r="C113" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="D113" s="5" t="s">
+      <c r="D113" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="E113" s="5" t="s">
+      <c r="E113" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="F113" s="5" t="s">
+      <c r="F113" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="G113" s="5"/>
-      <c r="H113" s="5" t="s">
+      <c r="G113" s="6"/>
+      <c r="H113" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I113" s="5"/>
+      <c r="I113" s="6"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="5">
+      <c r="A114" s="6">
         <v>113</v>
       </c>
-      <c r="B114" s="6"/>
-      <c r="C114" s="10"/>
-      <c r="D114" s="5" t="s">
+      <c r="B114" s="7"/>
+      <c r="C114" s="11"/>
+      <c r="D114" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="E114" s="5" t="s">
+      <c r="E114" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="F114" s="5" t="s">
+      <c r="F114" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="G114" s="5"/>
-      <c r="H114" s="5" t="s">
+      <c r="G114" s="6"/>
+      <c r="H114" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I114" s="5"/>
+      <c r="I114" s="6"/>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="5">
+      <c r="A115" s="6">
         <v>114</v>
       </c>
-      <c r="B115" s="6"/>
-      <c r="C115" s="10"/>
-      <c r="D115" s="5" t="s">
+      <c r="B115" s="7"/>
+      <c r="C115" s="11"/>
+      <c r="D115" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E115" s="5" t="s">
+      <c r="E115" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="F115" s="5" t="s">
+      <c r="F115" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="G115" s="5"/>
-      <c r="H115" s="5" t="s">
+      <c r="G115" s="6"/>
+      <c r="H115" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I115" s="5"/>
+      <c r="I115" s="6"/>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" s="5">
+      <c r="A116" s="6">
         <v>115</v>
       </c>
-      <c r="B116" s="6"/>
-      <c r="C116" s="5" t="s">
+      <c r="B116" s="7"/>
+      <c r="C116" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="D116" s="5" t="s">
+      <c r="D116" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="E116" s="5" t="s">
+      <c r="E116" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="F116" s="5" t="s">
+      <c r="F116" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="G116" s="5"/>
-      <c r="H116" s="5" t="s">
+      <c r="G116" s="6"/>
+      <c r="H116" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I116" s="5"/>
+      <c r="I116" s="6"/>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="5">
+      <c r="A117" s="6">
         <v>116</v>
       </c>
-      <c r="B117" s="6"/>
-      <c r="C117" s="10" t="s">
+      <c r="B117" s="7"/>
+      <c r="C117" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="D117" s="5" t="s">
+      <c r="D117" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="E117" s="5" t="s">
+      <c r="E117" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F117" s="5" t="s">
+      <c r="F117" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="G117" s="5"/>
-      <c r="H117" s="5" t="s">
+      <c r="G117" s="6"/>
+      <c r="H117" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I117" s="5"/>
+      <c r="I117" s="6"/>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" s="5">
+      <c r="A118" s="6">
         <v>117</v>
       </c>
-      <c r="B118" s="6"/>
-      <c r="C118" s="10"/>
-      <c r="D118" s="5" t="s">
+      <c r="B118" s="7"/>
+      <c r="C118" s="11"/>
+      <c r="D118" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="E118" s="5" t="s">
+      <c r="E118" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F118" s="5" t="s">
+      <c r="F118" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="G118" s="5"/>
-      <c r="H118" s="5" t="s">
+      <c r="G118" s="6"/>
+      <c r="H118" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I118" s="5"/>
+      <c r="I118" s="6"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" s="5">
+      <c r="A119" s="6">
         <v>118</v>
       </c>
-      <c r="B119" s="6"/>
-      <c r="C119" s="10"/>
-      <c r="D119" s="5" t="s">
+      <c r="B119" s="7"/>
+      <c r="C119" s="11"/>
+      <c r="D119" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="E119" s="5" t="s">
+      <c r="E119" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F119" s="5" t="s">
+      <c r="F119" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="G119" s="5"/>
-      <c r="H119" s="5" t="s">
+      <c r="G119" s="6"/>
+      <c r="H119" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I119" s="5"/>
+      <c r="I119" s="6"/>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120" s="5">
+      <c r="A120" s="6">
         <v>119</v>
       </c>
-      <c r="B120" s="6"/>
-      <c r="C120" s="10"/>
-      <c r="D120" s="5" t="s">
+      <c r="B120" s="7"/>
+      <c r="C120" s="11"/>
+      <c r="D120" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E120" s="5" t="s">
+      <c r="E120" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="F120" s="5" t="s">
+      <c r="F120" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="G120" s="5"/>
-      <c r="H120" s="5" t="s">
+      <c r="G120" s="6"/>
+      <c r="H120" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I120" s="5"/>
+      <c r="I120" s="6"/>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" s="5">
+      <c r="A121" s="6">
         <v>120</v>
       </c>
-      <c r="B121" s="6" t="s">
+      <c r="B121" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C121" s="10" t="s">
+      <c r="C121" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="D121" s="5" t="s">
+      <c r="D121" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="E121" s="5" t="s">
+      <c r="E121" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="F121" s="5" t="s">
+      <c r="F121" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="G121" s="5"/>
-      <c r="H121" s="5" t="s">
+      <c r="G121" s="6"/>
+      <c r="H121" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I121" s="5"/>
+      <c r="I121" s="6"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="5">
+      <c r="A122" s="6">
         <v>121</v>
       </c>
-      <c r="B122" s="6"/>
-      <c r="C122" s="10"/>
-      <c r="D122" s="5" t="s">
+      <c r="B122" s="7"/>
+      <c r="C122" s="11"/>
+      <c r="D122" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="E122" s="5" t="s">
+      <c r="E122" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="F122" s="5" t="s">
+      <c r="F122" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="G122" s="5"/>
-      <c r="H122" s="5" t="s">
+      <c r="G122" s="6"/>
+      <c r="H122" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I122" s="5"/>
+      <c r="I122" s="6"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="5">
+      <c r="A123" s="6">
         <v>122</v>
       </c>
-      <c r="B123" s="6"/>
-      <c r="C123" s="10"/>
-      <c r="D123" s="5" t="s">
+      <c r="B123" s="7"/>
+      <c r="C123" s="11"/>
+      <c r="D123" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E123" s="5" t="s">
+      <c r="E123" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="F123" s="5" t="s">
+      <c r="F123" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="G123" s="5"/>
-      <c r="H123" s="5" t="s">
+      <c r="G123" s="6"/>
+      <c r="H123" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I123" s="5"/>
+      <c r="I123" s="6"/>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" s="5">
+      <c r="A124" s="6">
         <v>123</v>
       </c>
-      <c r="B124" s="6" t="s">
+      <c r="B124" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="C124" s="12" t="s">
+      <c r="C124" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="D124" s="5" t="s">
+      <c r="D124" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="E124" s="5" t="s">
+      <c r="E124" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="F124" s="5" t="s">
+      <c r="F124" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="G124" s="5"/>
-      <c r="H124" s="5" t="s">
+      <c r="G124" s="6"/>
+      <c r="H124" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I124" s="5"/>
+      <c r="I124" s="6"/>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A125" s="5">
+      <c r="A125" s="6">
         <v>124</v>
       </c>
-      <c r="B125" s="6"/>
-      <c r="C125" s="12" t="s">
+      <c r="B125" s="7"/>
+      <c r="C125" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="D125" s="5" t="s">
+      <c r="D125" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="E125" s="5" t="s">
+      <c r="E125" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="F125" s="5" t="s">
+      <c r="F125" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="G125" s="5"/>
-      <c r="H125" s="5" t="s">
+      <c r="G125" s="6"/>
+      <c r="H125" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I125" s="5"/>
+      <c r="I125" s="6"/>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A126" s="5">
+      <c r="A126" s="6">
         <v>125</v>
       </c>
-      <c r="B126" s="6"/>
-      <c r="C126" s="5" t="s">
+      <c r="B126" s="7"/>
+      <c r="C126" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D126" s="5" t="s">
+      <c r="D126" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="E126" s="5" t="s">
+      <c r="E126" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="F126" s="5" t="s">
+      <c r="F126" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="G126" s="5"/>
-      <c r="H126" s="5" t="s">
+      <c r="G126" s="6"/>
+      <c r="H126" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I126" s="5"/>
+      <c r="I126" s="6"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A127" s="5">
+      <c r="A127" s="6">
         <v>126</v>
       </c>
-      <c r="B127" s="6"/>
-      <c r="C127" s="5" t="s">
+      <c r="B127" s="7"/>
+      <c r="C127" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="D127" s="5" t="s">
+      <c r="D127" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="E127" s="5" t="s">
+      <c r="E127" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="F127" s="5" t="s">
+      <c r="F127" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="G127" s="5"/>
-      <c r="H127" s="5" t="s">
+      <c r="G127" s="6"/>
+      <c r="H127" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I127" s="5"/>
+      <c r="I127" s="6"/>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A128" s="5">
+      <c r="A128" s="6">
         <v>127</v>
       </c>
-      <c r="B128" s="6"/>
-      <c r="C128" s="5" t="s">
+      <c r="B128" s="7"/>
+      <c r="C128" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D128" s="5" t="s">
+      <c r="D128" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="E128" s="5" t="s">
+      <c r="E128" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="F128" s="5" t="s">
+      <c r="F128" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="G128" s="5"/>
-      <c r="H128" s="5" t="s">
+      <c r="G128" s="6"/>
+      <c r="H128" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I128" s="5"/>
+      <c r="I128" s="6"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A129" s="5">
+      <c r="A129" s="6">
         <v>128</v>
       </c>
-      <c r="B129" s="6"/>
-      <c r="C129" s="10" t="s">
+      <c r="B129" s="7"/>
+      <c r="C129" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="D129" s="5" t="s">
+      <c r="D129" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E129" s="5" t="s">
+      <c r="E129" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="F129" s="5" t="s">
+      <c r="F129" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="G129" s="5"/>
-      <c r="H129" s="5" t="s">
+      <c r="G129" s="6"/>
+      <c r="H129" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I129" s="5"/>
+      <c r="I129" s="6"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A130" s="5">
+      <c r="A130" s="6">
         <v>129</v>
       </c>
-      <c r="B130" s="6"/>
-      <c r="C130" s="10"/>
-      <c r="D130" s="5" t="s">
+      <c r="B130" s="7"/>
+      <c r="C130" s="11"/>
+      <c r="D130" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="E130" s="5" t="s">
+      <c r="E130" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="F130" s="5" t="s">
+      <c r="F130" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="G130" s="5"/>
-      <c r="H130" s="5" t="s">
+      <c r="G130" s="6"/>
+      <c r="H130" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I130" s="5"/>
+      <c r="I130" s="6"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A131" s="5">
+      <c r="A131" s="6">
         <v>130</v>
       </c>
-      <c r="B131" s="6"/>
-      <c r="C131" s="10"/>
-      <c r="D131" s="5" t="s">
+      <c r="B131" s="7"/>
+      <c r="C131" s="11"/>
+      <c r="D131" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E131" s="5" t="s">
+      <c r="E131" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="F131" s="5" t="s">
+      <c r="F131" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="G131" s="5"/>
-      <c r="H131" s="5" t="s">
+      <c r="G131" s="6"/>
+      <c r="H131" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I131" s="5"/>
+      <c r="I131" s="6"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="5">
+      <c r="A132" s="6">
         <v>131</v>
       </c>
-      <c r="B132" s="6"/>
-      <c r="C132" s="10" t="s">
+      <c r="B132" s="7"/>
+      <c r="C132" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="D132" s="5" t="s">
+      <c r="D132" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E132" s="5" t="s">
+      <c r="E132" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="F132" s="5" t="s">
+      <c r="F132" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="G132" s="5"/>
-      <c r="H132" s="5" t="s">
+      <c r="G132" s="6"/>
+      <c r="H132" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I132" s="5"/>
+      <c r="I132" s="6"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A133" s="5">
+      <c r="A133" s="6">
         <v>132</v>
       </c>
-      <c r="B133" s="6"/>
-      <c r="C133" s="10"/>
-      <c r="D133" s="5" t="s">
+      <c r="B133" s="7"/>
+      <c r="C133" s="11"/>
+      <c r="D133" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="E133" s="5" t="s">
+      <c r="E133" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="F133" s="5" t="s">
+      <c r="F133" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="G133" s="5"/>
-      <c r="H133" s="5" t="s">
+      <c r="G133" s="6"/>
+      <c r="H133" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I133" s="5"/>
+      <c r="I133" s="6"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A134" s="5">
+      <c r="A134" s="6">
         <v>133</v>
       </c>
-      <c r="B134" s="6"/>
-      <c r="C134" s="10"/>
-      <c r="D134" s="5" t="s">
+      <c r="B134" s="7"/>
+      <c r="C134" s="11"/>
+      <c r="D134" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E134" s="5" t="s">
+      <c r="E134" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="F134" s="5" t="s">
+      <c r="F134" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="G134" s="5"/>
-      <c r="H134" s="5" t="s">
+      <c r="G134" s="6"/>
+      <c r="H134" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I134" s="5"/>
+      <c r="I134" s="6"/>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A135" s="5">
+      <c r="A135" s="6">
         <v>134</v>
       </c>
-      <c r="B135" s="6"/>
-      <c r="C135" s="10" t="s">
+      <c r="B135" s="7"/>
+      <c r="C135" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="D135" s="5" t="s">
+      <c r="D135" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E135" s="5" t="s">
+      <c r="E135" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="F135" s="5" t="s">
+      <c r="F135" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="G135" s="5"/>
-      <c r="H135" s="5" t="s">
+      <c r="G135" s="6"/>
+      <c r="H135" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I135" s="5"/>
+      <c r="I135" s="6"/>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A136" s="5">
+      <c r="A136" s="6">
         <v>135</v>
       </c>
-      <c r="B136" s="6"/>
-      <c r="C136" s="10"/>
-      <c r="D136" s="5" t="s">
+      <c r="B136" s="7"/>
+      <c r="C136" s="11"/>
+      <c r="D136" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="E136" s="5" t="s">
+      <c r="E136" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="F136" s="5" t="s">
+      <c r="F136" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="G136" s="5"/>
-      <c r="H136" s="5" t="s">
+      <c r="G136" s="6"/>
+      <c r="H136" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I136" s="5"/>
+      <c r="I136" s="6"/>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A137" s="5">
+      <c r="A137" s="6">
         <v>136</v>
       </c>
-      <c r="B137" s="6"/>
-      <c r="C137" s="10"/>
-      <c r="D137" s="5" t="s">
+      <c r="B137" s="7"/>
+      <c r="C137" s="11"/>
+      <c r="D137" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E137" s="5" t="s">
+      <c r="E137" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="F137" s="5" t="s">
+      <c r="F137" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="G137" s="5"/>
-      <c r="H137" s="5" t="s">
+      <c r="G137" s="6"/>
+      <c r="H137" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I137" s="5"/>
+      <c r="I137" s="6"/>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A138" s="5">
+      <c r="A138" s="6">
         <v>137</v>
       </c>
-      <c r="B138" s="6"/>
-      <c r="C138" s="10" t="s">
+      <c r="B138" s="7"/>
+      <c r="C138" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="D138" s="5" t="s">
+      <c r="D138" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="E138" s="5" t="s">
+      <c r="E138" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="F138" s="5" t="s">
+      <c r="F138" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="G138" s="5"/>
-      <c r="H138" s="5" t="s">
+      <c r="G138" s="6"/>
+      <c r="H138" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I138" s="5"/>
+      <c r="I138" s="6"/>
     </row>
     <row r="139" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A139" s="5">
+      <c r="A139" s="6">
         <v>138</v>
       </c>
-      <c r="B139" s="6"/>
-      <c r="C139" s="10"/>
-      <c r="D139" s="11" t="s">
+      <c r="B139" s="7"/>
+      <c r="C139" s="11"/>
+      <c r="D139" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="E139" s="5" t="s">
+      <c r="E139" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="F139" s="5" t="s">
+      <c r="F139" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="G139" s="5"/>
-      <c r="H139" s="5" t="s">
+      <c r="G139" s="6"/>
+      <c r="H139" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I139" s="5"/>
+      <c r="I139" s="6"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A140" s="5">
+      <c r="A140" s="6">
         <v>139</v>
       </c>
-      <c r="B140" s="6"/>
-      <c r="C140" s="10"/>
-      <c r="D140" s="8" t="s">
+      <c r="B140" s="7"/>
+      <c r="C140" s="11"/>
+      <c r="D140" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="E140" s="5" t="s">
+      <c r="E140" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="F140" s="5" t="s">
+      <c r="F140" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="G140" s="5"/>
-      <c r="H140" s="5" t="s">
+      <c r="G140" s="6"/>
+      <c r="H140" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I140" s="5"/>
+      <c r="I140" s="6"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A141" s="5">
+      <c r="A141" s="6">
         <v>140</v>
       </c>
-      <c r="B141" s="6"/>
-      <c r="C141" s="10"/>
-      <c r="D141" s="8" t="s">
+      <c r="B141" s="7"/>
+      <c r="C141" s="11"/>
+      <c r="D141" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="E141" s="5" t="s">
+      <c r="E141" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="F141" s="5" t="s">
+      <c r="F141" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="G141" s="5"/>
-      <c r="H141" s="5" t="s">
+      <c r="G141" s="6"/>
+      <c r="H141" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I141" s="5"/>
+      <c r="I141" s="6"/>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A142" s="5">
+      <c r="A142" s="6">
         <v>141</v>
       </c>
-      <c r="B142" s="6"/>
-      <c r="C142" s="10"/>
-      <c r="D142" s="8" t="s">
+      <c r="B142" s="7"/>
+      <c r="C142" s="11"/>
+      <c r="D142" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="E142" s="5" t="s">
+      <c r="E142" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="F142" s="5" t="s">
+      <c r="F142" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="G142" s="5"/>
-      <c r="H142" s="5" t="s">
+      <c r="G142" s="6"/>
+      <c r="H142" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I142" s="5"/>
+      <c r="I142" s="6"/>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A143" s="5">
+      <c r="A143" s="6">
         <v>142</v>
       </c>
-      <c r="B143" s="6" t="s">
+      <c r="B143" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C143" s="5" t="s">
+      <c r="C143" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="D143" s="5" t="s">
+      <c r="D143" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="E143" s="5" t="s">
+      <c r="E143" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="F143" s="5" t="s">
+      <c r="F143" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="G143" s="5"/>
-      <c r="H143" s="5" t="s">
+      <c r="G143" s="6"/>
+      <c r="H143" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I143" s="5"/>
+      <c r="I143" s="6"/>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A144" s="5">
+      <c r="A144" s="6">
         <v>143</v>
       </c>
-      <c r="B144" s="6"/>
-      <c r="C144" s="5" t="s">
+      <c r="B144" s="7"/>
+      <c r="C144" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="D144" s="5" t="s">
+      <c r="D144" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="E144" s="5" t="s">
+      <c r="E144" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="F144" s="5" t="s">
+      <c r="F144" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="G144" s="5"/>
-      <c r="H144" s="5" t="s">
+      <c r="G144" s="6"/>
+      <c r="H144" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I144" s="5"/>
+      <c r="I144" s="6"/>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A145" s="5">
+      <c r="A145" s="6">
         <v>144</v>
       </c>
-      <c r="B145" s="13" t="s">
+      <c r="B145" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="C145" s="5" t="s">
+      <c r="C145" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="D145" s="5" t="s">
+      <c r="D145" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="E145" s="5" t="s">
+      <c r="E145" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="F145" s="5" t="s">
+      <c r="F145" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="G145" s="5"/>
-      <c r="H145" s="5" t="s">
+      <c r="G145" s="6"/>
+      <c r="H145" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I145" s="5"/>
+      <c r="I145" s="6"/>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A146" s="5">
+      <c r="A146" s="6">
         <v>145</v>
       </c>
-      <c r="B146" s="6" t="s">
+      <c r="B146" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C146" s="10" t="s">
+      <c r="C146" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="D146" s="5" t="s">
+      <c r="D146" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="E146" s="5" t="s">
+      <c r="E146" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="F146" s="5" t="s">
+      <c r="F146" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="G146" s="5"/>
-      <c r="H146" s="5" t="s">
+      <c r="G146" s="6"/>
+      <c r="H146" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I146" s="5"/>
+      <c r="I146" s="6"/>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A147" s="5">
+      <c r="A147" s="6">
         <v>146</v>
       </c>
-      <c r="B147" s="6"/>
-      <c r="C147" s="10"/>
-      <c r="D147" s="5" t="s">
+      <c r="B147" s="7"/>
+      <c r="C147" s="11"/>
+      <c r="D147" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="E147" s="5" t="s">
+      <c r="E147" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="F147" s="5" t="s">
+      <c r="F147" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="G147" s="5"/>
-      <c r="H147" s="5" t="s">
+      <c r="G147" s="6"/>
+      <c r="H147" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I147" s="5"/>
+      <c r="I147" s="6"/>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A148" s="5">
+      <c r="A148" s="6">
         <v>147</v>
       </c>
-      <c r="B148" s="6"/>
-      <c r="C148" s="10"/>
-      <c r="D148" s="5" t="s">
+      <c r="B148" s="7"/>
+      <c r="C148" s="11"/>
+      <c r="D148" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E148" s="5" t="s">
+      <c r="E148" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="F148" s="5" t="s">
+      <c r="F148" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="G148" s="5"/>
-      <c r="H148" s="5" t="s">
+      <c r="G148" s="6"/>
+      <c r="H148" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I148" s="5"/>
+      <c r="I148" s="6"/>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A149" s="5">
+      <c r="A149" s="6">
         <v>148</v>
       </c>
-      <c r="B149" s="6"/>
-      <c r="C149" s="10" t="s">
+      <c r="B149" s="7"/>
+      <c r="C149" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="D149" s="5" t="s">
+      <c r="D149" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="E149" s="5" t="s">
+      <c r="E149" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="F149" s="5" t="s">
+      <c r="F149" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="G149" s="5"/>
-      <c r="H149" s="5" t="s">
+      <c r="G149" s="6"/>
+      <c r="H149" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I149" s="5"/>
+      <c r="I149" s="6"/>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A150" s="5">
+      <c r="A150" s="6">
         <v>149</v>
       </c>
-      <c r="B150" s="6"/>
-      <c r="C150" s="10"/>
-      <c r="D150" s="5" t="s">
+      <c r="B150" s="7"/>
+      <c r="C150" s="11"/>
+      <c r="D150" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="E150" s="5" t="s">
+      <c r="E150" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="F150" s="5" t="s">
+      <c r="F150" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="G150" s="5"/>
-      <c r="H150" s="5" t="s">
+      <c r="G150" s="6"/>
+      <c r="H150" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I150" s="5"/>
+      <c r="I150" s="6"/>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A151" s="5">
+      <c r="A151" s="6">
         <v>150</v>
       </c>
-      <c r="B151" s="6"/>
-      <c r="C151" s="10"/>
-      <c r="D151" s="5" t="s">
+      <c r="B151" s="7"/>
+      <c r="C151" s="11"/>
+      <c r="D151" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="E151" s="5" t="s">
+      <c r="E151" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="F151" s="5" t="s">
+      <c r="F151" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="G151" s="5"/>
-      <c r="H151" s="5" t="s">
+      <c r="G151" s="6"/>
+      <c r="H151" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I151" s="5"/>
+      <c r="I151" s="6"/>
     </row>
     <row r="152" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A152" s="5">
+      <c r="A152" s="6">
         <v>151</v>
       </c>
-      <c r="B152" s="13" t="s">
+      <c r="B152" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="C152" s="14" t="s">
+      <c r="C152" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="D152" s="5" t="s">
+      <c r="D152" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="E152" s="5" t="s">
+      <c r="E152" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="F152" s="5" t="s">
+      <c r="F152" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="G152" s="5"/>
-      <c r="H152" s="5" t="s">
+      <c r="G152" s="6"/>
+      <c r="H152" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I152" s="5"/>
+      <c r="I152" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="52">
@@ -5464,7 +5483,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CF7B26D-E2A8-4887-8F63-92439D43C540}">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
@@ -5478,392 +5497,392 @@
     <col min="9" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="17" customFormat="1" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:9" s="18" customFormat="1" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="10" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="6"/>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="10" t="s">
         <v>317</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="10" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="6"/>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="7"/>
+      <c r="C8" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="10" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="6"/>
-      <c r="C9" s="8" t="s">
+      <c r="B9" s="7"/>
+      <c r="C9" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="10" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="6"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="6"/>
-      <c r="C11" s="6" t="s">
+      <c r="B11" s="7"/>
+      <c r="C11" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="10" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="9" t="s">
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="10" t="s">
         <v>338</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="10" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="9" t="s">
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="10" t="s">
         <v>338</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="10" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="6"/>
-      <c r="C14" s="13" t="s">
+      <c r="B14" s="7"/>
+      <c r="C14" s="14" t="s">
         <v>341</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="10" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="6"/>
-      <c r="C15" s="6" t="s">
+      <c r="B15" s="7"/>
+      <c r="C15" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="10" t="s">
         <v>345</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="10" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="9" t="s">
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="10" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="9" t="s">
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="10" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="9" t="s">
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="10" t="s">
         <v>350</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="10" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="6"/>
-      <c r="C19" s="6" t="s">
+      <c r="B19" s="7"/>
+      <c r="C19" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="10" t="s">
         <v>351</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="10" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="9" t="s">
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="10" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="9" t="s">
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="10" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="6"/>
-      <c r="C22" s="6" t="s">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="10" t="s">
         <v>356</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="10" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="9" t="s">
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="10" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="9" t="s">
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="10" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="9" t="s">
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="10" t="s">
         <v>365</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="10" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="9" t="s">
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="10" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="9" t="s">
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="10" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B28" s="6"/>
-      <c r="C28" s="13" t="s">
+      <c r="B28" s="7"/>
+      <c r="C28" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="10" t="s">
         <v>368</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="10" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B29" s="6"/>
-      <c r="C29" s="6" t="s">
+      <c r="B29" s="7"/>
+      <c r="C29" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="10" t="s">
         <v>371</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="10" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="9" t="s">
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="10" t="s">
         <v>373</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="10" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E31" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="F31" s="10" t="s">
         <v>326</v>
       </c>
     </row>
@@ -5913,7 +5932,7 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C39" t="s">
+      <c r="C39" s="5" t="s">
         <v>386</v>
       </c>
       <c r="D39" t="s">
@@ -5927,6 +5946,7 @@
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C40" s="5"/>
       <c r="D40" t="s">
         <v>391</v>
       </c>
@@ -5937,8 +5957,23 @@
         <v>389</v>
       </c>
     </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
+        <v>393</v>
+      </c>
+      <c r="D41" t="s">
+        <v>394</v>
+      </c>
+      <c r="E41" t="s">
+        <v>395</v>
+      </c>
+      <c r="F41" t="s">
+        <v>396</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="B6:B30"/>
     <mergeCell ref="C11:C13"/>
     <mergeCell ref="C15:C18"/>

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F851F0-A23D-488D-B0AD-824C1E18519E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AA6F02F-7FF0-4A6C-BC2F-58ADF107E4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{F425FBA8-E65A-4F03-9270-551F3EA7C4F5}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="412">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1599,6 +1599,66 @@
   </si>
   <si>
     <t>页面显示数据正常</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>双倍加分使用规则</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>次数刷新清空规则</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用限制段位校验</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用规则-参与玩法</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用规则-消耗限制</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>查看次数消耗清空</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间进入排位赛首胜一局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗成功，次数-1，积分增加</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用规则-消耗方式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>胜利后自动消耗</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>有双倍加分次数2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>有双倍加分次数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>排位赛首胜一局，查看次数消耗方式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>第二次无消耗</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当日排位赛胜利2局，查看是否可消耗</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1711,7 +1771,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1722,9 +1782,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2127,3293 +2184,3293 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I2" s="6"/>
+      <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="6" t="s">
+      <c r="B3" s="6"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I3" s="6"/>
+      <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="6" t="s">
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6" t="s">
+      <c r="G4" s="5"/>
+      <c r="H4" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I4" s="6"/>
+      <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6" t="s">
+      <c r="G5" s="5"/>
+      <c r="H5" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I5" s="6"/>
+      <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="6" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6" t="s">
+      <c r="G6" s="5"/>
+      <c r="H6" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I6" s="6"/>
+      <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="6" t="s">
+      <c r="B7" s="6"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6" t="s">
+      <c r="G7" s="5"/>
+      <c r="H7" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I7" s="6"/>
+      <c r="I7" s="5"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="9" t="s">
+      <c r="B8" s="6"/>
+      <c r="C8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6" t="s">
+      <c r="G8" s="5"/>
+      <c r="H8" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="I8" s="6"/>
+      <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="8" t="s">
+      <c r="B9" s="6"/>
+      <c r="C9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6" t="s">
+      <c r="G9" s="5"/>
+      <c r="H9" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="5" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="6" t="s">
+      <c r="B10" s="6"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6" t="s">
+      <c r="G10" s="5"/>
+      <c r="H10" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I10" s="6"/>
+      <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="6" t="s">
+      <c r="B11" s="6"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6" t="s">
+      <c r="G11" s="5"/>
+      <c r="H11" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I11" s="6"/>
+      <c r="I11" s="5"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+      <c r="A12" s="5">
         <v>11</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="9" t="s">
+      <c r="B12" s="6"/>
+      <c r="C12" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6" t="s">
+      <c r="G12" s="5"/>
+      <c r="H12" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I12" s="6"/>
+      <c r="I12" s="5"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+      <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6" t="s">
+      <c r="G13" s="5"/>
+      <c r="H13" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I13" s="6"/>
+      <c r="I13" s="5"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
+      <c r="A14" s="5">
         <v>13</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="9" t="s">
+      <c r="B14" s="6"/>
+      <c r="C14" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6" t="s">
+      <c r="G14" s="5"/>
+      <c r="H14" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I14" s="6"/>
+      <c r="I14" s="5"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
+      <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="9" t="s">
+      <c r="B15" s="6"/>
+      <c r="C15" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6" t="s">
+      <c r="G15" s="5"/>
+      <c r="H15" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I15" s="6"/>
+      <c r="I15" s="5"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
+      <c r="A16" s="5">
         <v>15</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="9" t="s">
+      <c r="B16" s="6"/>
+      <c r="C16" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6" t="s">
+      <c r="G16" s="5"/>
+      <c r="H16" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I16" s="6"/>
+      <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+      <c r="A17" s="5">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6" t="s">
+      <c r="G17" s="5"/>
+      <c r="H17" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I17" s="6"/>
+      <c r="I17" s="5"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+      <c r="A18" s="5">
         <v>17</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="6" t="s">
+      <c r="B18" s="6"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6" t="s">
+      <c r="G18" s="5"/>
+      <c r="H18" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I18" s="6"/>
+      <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+      <c r="A19" s="5">
         <v>18</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="6" t="s">
+      <c r="B19" s="6"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6" t="s">
+      <c r="G19" s="5"/>
+      <c r="H19" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I19" s="6"/>
+      <c r="I19" s="5"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+      <c r="A20" s="5">
         <v>19</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="9" t="s">
+      <c r="B20" s="6"/>
+      <c r="C20" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6" t="s">
+      <c r="G20" s="5"/>
+      <c r="H20" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I20" s="6"/>
+      <c r="I20" s="5"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+      <c r="A21" s="5">
         <v>20</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="9" t="s">
+      <c r="B21" s="6"/>
+      <c r="C21" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6" t="s">
+      <c r="G21" s="5"/>
+      <c r="H21" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="I21" s="6"/>
+      <c r="I21" s="5"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
+      <c r="A22" s="5">
         <v>21</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="9" t="s">
+      <c r="B22" s="6"/>
+      <c r="C22" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6" t="s">
+      <c r="G22" s="5"/>
+      <c r="H22" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="I22" s="6"/>
+      <c r="I22" s="5"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
+      <c r="A23" s="5">
         <v>22</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="9" t="s">
+      <c r="B23" s="6"/>
+      <c r="C23" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6" t="s">
+      <c r="G23" s="5"/>
+      <c r="H23" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I23" s="6"/>
+      <c r="I23" s="5"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
+      <c r="A24" s="5">
         <v>23</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="8" t="s">
+      <c r="B24" s="6"/>
+      <c r="C24" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6" t="s">
+      <c r="G24" s="5"/>
+      <c r="H24" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I24" s="6"/>
+      <c r="I24" s="5"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="6">
+      <c r="A25" s="5">
         <v>24</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="6" t="s">
+      <c r="B25" s="6"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6" t="s">
+      <c r="G25" s="5"/>
+      <c r="H25" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I25" s="6"/>
+      <c r="I25" s="5"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
+      <c r="A26" s="5">
         <v>25</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="6" t="s">
+      <c r="B26" s="6"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="F26" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6" t="s">
+      <c r="G26" s="5"/>
+      <c r="H26" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I26" s="6"/>
+      <c r="I26" s="5"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
+      <c r="A27" s="5">
         <v>26</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="11" t="s">
+      <c r="B27" s="6"/>
+      <c r="C27" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6" t="s">
+      <c r="G27" s="5"/>
+      <c r="H27" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I27" s="6"/>
+      <c r="I27" s="5"/>
     </row>
     <row r="28" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
+      <c r="A28" s="5">
         <v>27</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="12" t="s">
+      <c r="B28" s="6"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6" t="s">
+      <c r="G28" s="5"/>
+      <c r="H28" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I28" s="6"/>
+      <c r="I28" s="5"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
+      <c r="A29" s="5">
         <v>28</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="F29" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6" t="s">
+      <c r="G29" s="5"/>
+      <c r="H29" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="I29" s="6"/>
+      <c r="I29" s="5"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
+      <c r="A30" s="5">
         <v>29</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="9" t="s">
+      <c r="B30" s="6"/>
+      <c r="C30" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="F30" s="9" t="s">
         <v>309</v>
       </c>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6" t="s">
+      <c r="G30" s="5"/>
+      <c r="H30" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="I30" s="6"/>
+      <c r="I30" s="5"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
+      <c r="A31" s="5">
         <v>30</v>
       </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="9" t="s">
+      <c r="B31" s="6"/>
+      <c r="C31" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E31" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="F31" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6" t="s">
+      <c r="G31" s="5"/>
+      <c r="H31" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="I31" s="6"/>
+      <c r="I31" s="5"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
+      <c r="A32" s="5">
         <v>31</v>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="8" t="s">
+      <c r="B32" s="6"/>
+      <c r="C32" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="F32" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6" t="s">
+      <c r="G32" s="5"/>
+      <c r="H32" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I32" s="6"/>
+      <c r="I32" s="5"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
+      <c r="A33" s="5">
         <v>32</v>
       </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="6" t="s">
+      <c r="B33" s="6"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E33" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="F33" s="10" t="s">
+      <c r="F33" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6" t="s">
+      <c r="G33" s="5"/>
+      <c r="H33" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I33" s="6"/>
+      <c r="I33" s="5"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
+      <c r="A34" s="5">
         <v>33</v>
       </c>
-      <c r="B34" s="7"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="6" t="s">
+      <c r="B34" s="6"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E34" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="F34" s="10" t="s">
+      <c r="F34" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6" t="s">
+      <c r="G34" s="5"/>
+      <c r="H34" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I34" s="6"/>
+      <c r="I34" s="5"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="6">
+      <c r="A35" s="5">
         <v>34</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="8" t="s">
+      <c r="B35" s="6"/>
+      <c r="C35" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="E35" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="F35" s="10" t="s">
+      <c r="F35" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6" t="s">
+      <c r="G35" s="5"/>
+      <c r="H35" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I35" s="6"/>
+      <c r="I35" s="5"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
+      <c r="A36" s="5">
         <v>35</v>
       </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="6" t="s">
+      <c r="B36" s="6"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E36" s="10" t="s">
+      <c r="E36" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="F36" s="10" t="s">
+      <c r="F36" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6" t="s">
+      <c r="G36" s="5"/>
+      <c r="H36" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I36" s="6"/>
+      <c r="I36" s="5"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="6">
+      <c r="A37" s="5">
         <v>36</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="8" t="s">
         <v>333</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D37" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="F37" s="10" t="s">
+      <c r="F37" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
+      <c r="A38" s="5">
         <v>37</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="9" t="s">
+      <c r="B38" s="6"/>
+      <c r="C38" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="E38" s="9" t="s">
         <v>317</v>
       </c>
-      <c r="F38" s="10" t="s">
+      <c r="F38" s="9" t="s">
         <v>318</v>
       </c>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="6">
+      <c r="A39" s="5">
         <v>38</v>
       </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="9" t="s">
+      <c r="B39" s="6"/>
+      <c r="C39" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="E39" s="10" t="s">
+      <c r="E39" s="9" t="s">
         <v>319</v>
       </c>
-      <c r="F39" s="10" t="s">
+      <c r="F39" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="6">
+      <c r="A40" s="5">
         <v>39</v>
       </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="9" t="s">
+      <c r="B40" s="6"/>
+      <c r="C40" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="E40" s="10" t="s">
+      <c r="E40" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="F40" s="10" t="s">
+      <c r="F40" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="6">
+      <c r="A41" s="5">
         <v>40</v>
       </c>
-      <c r="B41" s="7"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="6">
+      <c r="A42" s="5">
         <v>41</v>
       </c>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7" t="s">
+      <c r="B42" s="6"/>
+      <c r="C42" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D42" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="E42" s="10" t="s">
+      <c r="E42" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="F42" s="10" t="s">
+      <c r="F42" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="6">
+      <c r="A43" s="5">
         <v>42</v>
       </c>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="10" t="s">
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="E43" s="10" t="s">
+      <c r="E43" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="F43" s="10" t="s">
+      <c r="F43" s="9" t="s">
         <v>318</v>
       </c>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="6">
+      <c r="A44" s="5">
         <v>43</v>
       </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="10" t="s">
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="E44" s="10" t="s">
+      <c r="E44" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="F44" s="10" t="s">
+      <c r="F44" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="6">
+      <c r="A45" s="5">
         <v>44</v>
       </c>
-      <c r="B45" s="7"/>
-      <c r="C45" s="14" t="s">
+      <c r="B45" s="6"/>
+      <c r="C45" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D45" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E45" s="9" t="s">
         <v>342</v>
       </c>
-      <c r="F45" s="10" t="s">
+      <c r="F45" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="6">
+      <c r="A46" s="5">
         <v>45</v>
       </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7" t="s">
+      <c r="B46" s="6"/>
+      <c r="C46" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="D46" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="E46" s="10" t="s">
+      <c r="E46" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="F46" s="10" t="s">
+      <c r="F46" s="9" t="s">
         <v>346</v>
       </c>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="6">
+      <c r="A47" s="5">
         <v>46</v>
       </c>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="10" t="s">
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="E47" s="10" t="s">
+      <c r="E47" s="9" t="s">
         <v>347</v>
       </c>
-      <c r="F47" s="10" t="s">
+      <c r="F47" s="9" t="s">
         <v>346</v>
       </c>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="6">
+      <c r="A48" s="5">
         <v>47</v>
       </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="10" t="s">
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="E48" s="10" t="s">
+      <c r="E48" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="F48" s="10" t="s">
+      <c r="F48" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="6">
+      <c r="A49" s="5">
         <v>48</v>
       </c>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="10" t="s">
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="E49" s="10" t="s">
+      <c r="E49" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="F49" s="10" t="s">
+      <c r="F49" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="6">
+      <c r="A50" s="5">
         <v>49</v>
       </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7" t="s">
+      <c r="B50" s="6"/>
+      <c r="C50" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="D50" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="E50" s="10" t="s">
+      <c r="E50" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="F50" s="10" t="s">
+      <c r="F50" s="9" t="s">
         <v>346</v>
       </c>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="6">
+      <c r="A51" s="5">
         <v>50</v>
       </c>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="10" t="s">
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="E51" s="10" t="s">
+      <c r="E51" s="9" t="s">
         <v>352</v>
       </c>
-      <c r="F51" s="10" t="s">
+      <c r="F51" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="6">
+      <c r="A52" s="5">
         <v>51</v>
       </c>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="10" t="s">
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="E52" s="10" t="s">
+      <c r="E52" s="9" t="s">
         <v>353</v>
       </c>
-      <c r="F52" s="10" t="s">
+      <c r="F52" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="6">
+      <c r="A53" s="5">
         <v>52</v>
       </c>
-      <c r="B53" s="7"/>
-      <c r="C53" s="7" t="s">
+      <c r="B53" s="6"/>
+      <c r="C53" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="D53" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="E53" s="9" t="s">
         <v>356</v>
       </c>
-      <c r="F53" s="10" t="s">
+      <c r="F53" s="9" t="s">
         <v>355</v>
       </c>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="6">
+      <c r="A54" s="5">
         <v>53</v>
       </c>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="10" t="s">
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="E54" s="10" t="s">
+      <c r="E54" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="F54" s="10" t="s">
+      <c r="F54" s="9" t="s">
         <v>360</v>
       </c>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="6">
+      <c r="A55" s="5">
         <v>54</v>
       </c>
-      <c r="B55" s="7"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="10" t="s">
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="E55" s="10" t="s">
+      <c r="E55" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="F55" s="10" t="s">
+      <c r="F55" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="6">
+      <c r="A56" s="5">
         <v>55</v>
       </c>
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="10" t="s">
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="E56" s="10" t="s">
+      <c r="E56" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="F56" s="10" t="s">
+      <c r="F56" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="6">
+      <c r="A57" s="5">
         <v>56</v>
       </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="10" t="s">
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="E57" s="10" t="s">
+      <c r="E57" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="F57" s="10" t="s">
+      <c r="F57" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="6">
+      <c r="A58" s="5">
         <v>57</v>
       </c>
-      <c r="B58" s="7"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="10" t="s">
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="E58" s="10" t="s">
+      <c r="E58" s="9" t="s">
         <v>366</v>
       </c>
-      <c r="F58" s="10" t="s">
+      <c r="F58" s="9" t="s">
         <v>364</v>
       </c>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="6">
+      <c r="A59" s="5">
         <v>58</v>
       </c>
-      <c r="B59" s="7"/>
-      <c r="C59" s="14" t="s">
+      <c r="B59" s="6"/>
+      <c r="C59" s="13" t="s">
         <v>367</v>
       </c>
-      <c r="D59" s="10" t="s">
+      <c r="D59" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="E59" s="10" t="s">
+      <c r="E59" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="F59" s="10" t="s">
+      <c r="F59" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="6">
+      <c r="A60" s="5">
         <v>59</v>
       </c>
-      <c r="B60" s="7"/>
-      <c r="C60" s="7" t="s">
+      <c r="B60" s="6"/>
+      <c r="C60" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="D60" s="10" t="s">
+      <c r="D60" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="E60" s="10" t="s">
+      <c r="E60" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="F60" s="10" t="s">
+      <c r="F60" s="9" t="s">
         <v>372</v>
       </c>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="5"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="6">
+      <c r="A61" s="5">
         <v>60</v>
       </c>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="10" t="s">
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="E61" s="10" t="s">
+      <c r="E61" s="9" t="s">
         <v>373</v>
       </c>
-      <c r="F61" s="10" t="s">
+      <c r="F61" s="9" t="s">
         <v>372</v>
       </c>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="6">
+      <c r="A62" s="5">
         <v>61</v>
       </c>
-      <c r="B62" s="14" t="s">
+      <c r="B62" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="C62" s="14" t="s">
+      <c r="C62" s="13" t="s">
         <v>323</v>
       </c>
-      <c r="D62" s="10" t="s">
+      <c r="D62" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="E62" s="10" t="s">
+      <c r="E62" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="F62" s="10" t="s">
+      <c r="F62" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="6">
+      <c r="A63" s="5">
         <v>62</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B63" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C63" s="19" t="s">
+      <c r="C63" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D63" s="6" t="s">
+      <c r="D63" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E63" s="6" t="s">
+      <c r="E63" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="F63" s="6" t="s">
+      <c r="F63" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6" t="s">
+      <c r="G63" s="5"/>
+      <c r="H63" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I63" s="6"/>
+      <c r="I63" s="5"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="6">
+      <c r="A64" s="5">
         <v>63</v>
       </c>
-      <c r="B64" s="7"/>
-      <c r="C64" s="19"/>
-      <c r="D64" s="6" t="s">
+      <c r="B64" s="6"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E64" s="6" t="s">
+      <c r="E64" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="F64" s="6" t="s">
+      <c r="F64" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="G64" s="6"/>
-      <c r="H64" s="6" t="s">
+      <c r="G64" s="5"/>
+      <c r="H64" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I64" s="6"/>
+      <c r="I64" s="5"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="6">
+      <c r="A65" s="5">
         <v>64</v>
       </c>
-      <c r="B65" s="7"/>
-      <c r="C65" s="19"/>
-      <c r="D65" s="6" t="s">
+      <c r="B65" s="6"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E65" s="6" t="s">
+      <c r="E65" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="F65" s="6" t="s">
+      <c r="F65" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="G65" s="6"/>
-      <c r="H65" s="6" t="s">
+      <c r="G65" s="5"/>
+      <c r="H65" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I65" s="6"/>
+      <c r="I65" s="5"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="6">
+      <c r="A66" s="5">
         <v>65</v>
       </c>
-      <c r="B66" s="7"/>
-      <c r="C66" s="19" t="s">
+      <c r="B66" s="6"/>
+      <c r="C66" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D66" s="6" t="s">
+      <c r="D66" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E66" s="6" t="s">
+      <c r="E66" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="F66" s="6" t="s">
+      <c r="F66" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="G66" s="6"/>
-      <c r="H66" s="6" t="s">
+      <c r="G66" s="5"/>
+      <c r="H66" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I66" s="6" t="s">
+      <c r="I66" s="5" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="6">
+      <c r="A67" s="5">
         <v>66</v>
       </c>
-      <c r="B67" s="7"/>
-      <c r="C67" s="19"/>
-      <c r="D67" s="6" t="s">
+      <c r="B67" s="6"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E67" s="6" t="s">
+      <c r="E67" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="F67" s="6" t="s">
+      <c r="F67" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="G67" s="6"/>
-      <c r="H67" s="6" t="s">
+      <c r="G67" s="5"/>
+      <c r="H67" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I67" s="6"/>
+      <c r="I67" s="5"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="6">
+      <c r="A68" s="5">
         <v>67</v>
       </c>
-      <c r="B68" s="7"/>
-      <c r="C68" s="11" t="s">
+      <c r="B68" s="6"/>
+      <c r="C68" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="D68" s="6" t="s">
+      <c r="D68" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E68" s="6" t="s">
+      <c r="E68" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="F68" s="6" t="s">
+      <c r="F68" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="G68" s="6"/>
-      <c r="H68" s="6" t="s">
+      <c r="G68" s="5"/>
+      <c r="H68" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I68" s="6"/>
+      <c r="I68" s="5"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="6">
+      <c r="A69" s="5">
         <v>68</v>
       </c>
-      <c r="B69" s="7"/>
-      <c r="C69" s="11"/>
-      <c r="D69" s="6" t="s">
+      <c r="B69" s="6"/>
+      <c r="C69" s="10"/>
+      <c r="D69" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E69" s="6" t="s">
+      <c r="E69" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="F69" s="6" t="s">
+      <c r="F69" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="G69" s="6"/>
-      <c r="H69" s="6" t="s">
+      <c r="G69" s="5"/>
+      <c r="H69" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I69" s="6"/>
+      <c r="I69" s="5"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="6">
+      <c r="A70" s="5">
         <v>69</v>
       </c>
-      <c r="B70" s="7"/>
-      <c r="C70" s="11"/>
-      <c r="D70" s="6" t="s">
+      <c r="B70" s="6"/>
+      <c r="C70" s="10"/>
+      <c r="D70" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E70" s="6" t="s">
+      <c r="E70" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="F70" s="6" t="s">
+      <c r="F70" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6" t="s">
+      <c r="G70" s="5"/>
+      <c r="H70" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I70" s="6"/>
+      <c r="I70" s="5"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="6">
+      <c r="A71" s="5">
         <v>70</v>
       </c>
-      <c r="B71" s="7"/>
-      <c r="C71" s="11"/>
-      <c r="D71" s="6" t="s">
+      <c r="B71" s="6"/>
+      <c r="C71" s="10"/>
+      <c r="D71" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E71" s="6" t="s">
+      <c r="E71" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="F71" s="6" t="s">
+      <c r="F71" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6" t="s">
+      <c r="G71" s="5"/>
+      <c r="H71" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I71" s="6"/>
+      <c r="I71" s="5"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="6">
+      <c r="A72" s="5">
         <v>71</v>
       </c>
-      <c r="B72" s="7"/>
-      <c r="C72" s="11"/>
-      <c r="D72" s="6" t="s">
+      <c r="B72" s="6"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E72" s="6" t="s">
+      <c r="E72" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="F72" s="6" t="s">
+      <c r="F72" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6" t="s">
+      <c r="G72" s="5"/>
+      <c r="H72" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I72" s="6"/>
+      <c r="I72" s="5"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="6">
+      <c r="A73" s="5">
         <v>72</v>
       </c>
-      <c r="B73" s="7"/>
-      <c r="C73" s="11"/>
-      <c r="D73" s="6" t="s">
+      <c r="B73" s="6"/>
+      <c r="C73" s="10"/>
+      <c r="D73" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="E73" s="6" t="s">
+      <c r="E73" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="F73" s="6" t="s">
+      <c r="F73" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="G73" s="6"/>
-      <c r="H73" s="6" t="s">
+      <c r="G73" s="5"/>
+      <c r="H73" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I73" s="6"/>
+      <c r="I73" s="5"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="6">
+      <c r="A74" s="5">
         <v>73</v>
       </c>
-      <c r="B74" s="7"/>
-      <c r="C74" s="11" t="s">
+      <c r="B74" s="6"/>
+      <c r="C74" s="10" t="s">
         <v>374</v>
       </c>
-      <c r="D74" s="6" t="s">
+      <c r="D74" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E74" s="6" t="s">
+      <c r="E74" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="F74" s="6" t="s">
+      <c r="F74" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6" t="s">
+      <c r="G74" s="5"/>
+      <c r="H74" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I74" s="6"/>
+      <c r="I74" s="5"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="6">
+      <c r="A75" s="5">
         <v>74</v>
       </c>
-      <c r="B75" s="7"/>
-      <c r="C75" s="11"/>
-      <c r="D75" s="6" t="s">
+      <c r="B75" s="6"/>
+      <c r="C75" s="10"/>
+      <c r="D75" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="E75" s="6" t="s">
+      <c r="E75" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="F75" s="6" t="s">
+      <c r="F75" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="G75" s="6"/>
-      <c r="H75" s="6" t="s">
+      <c r="G75" s="5"/>
+      <c r="H75" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I75" s="6"/>
+      <c r="I75" s="5"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="6">
+      <c r="A76" s="5">
         <v>75</v>
       </c>
-      <c r="B76" s="7"/>
-      <c r="C76" s="11"/>
-      <c r="D76" s="6" t="s">
+      <c r="B76" s="6"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E76" s="6" t="s">
+      <c r="E76" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="F76" s="6" t="s">
+      <c r="F76" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="G76" s="6"/>
-      <c r="H76" s="6" t="s">
+      <c r="G76" s="5"/>
+      <c r="H76" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I76" s="6"/>
+      <c r="I76" s="5"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="6">
+      <c r="A77" s="5">
         <v>76</v>
       </c>
-      <c r="B77" s="7"/>
-      <c r="C77" s="11"/>
-      <c r="D77" s="6" t="s">
+      <c r="B77" s="6"/>
+      <c r="C77" s="10"/>
+      <c r="D77" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E77" s="6" t="s">
+      <c r="E77" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="F77" s="6" t="s">
+      <c r="F77" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="G77" s="6"/>
-      <c r="H77" s="6" t="s">
+      <c r="G77" s="5"/>
+      <c r="H77" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I77" s="6"/>
+      <c r="I77" s="5"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="6">
+      <c r="A78" s="5">
         <v>77</v>
       </c>
-      <c r="B78" s="7"/>
-      <c r="C78" s="11"/>
-      <c r="D78" s="6" t="s">
+      <c r="B78" s="6"/>
+      <c r="C78" s="10"/>
+      <c r="D78" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E78" s="6" t="s">
+      <c r="E78" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="F78" s="6" t="s">
+      <c r="F78" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="G78" s="6"/>
-      <c r="H78" s="6" t="s">
+      <c r="G78" s="5"/>
+      <c r="H78" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I78" s="6"/>
+      <c r="I78" s="5"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="6">
+      <c r="A79" s="5">
         <v>78</v>
       </c>
-      <c r="B79" s="7" t="s">
+      <c r="B79" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C79" s="8" t="s">
+      <c r="C79" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D79" s="6" t="s">
+      <c r="D79" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E79" s="10" t="s">
+      <c r="E79" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="F79" s="6" t="s">
+      <c r="F79" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="G79" s="6"/>
-      <c r="H79" s="6" t="s">
+      <c r="G79" s="5"/>
+      <c r="H79" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I79" s="6"/>
+      <c r="I79" s="5"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="6">
+      <c r="A80" s="5">
         <v>79</v>
       </c>
-      <c r="B80" s="7"/>
-      <c r="C80" s="8"/>
-      <c r="D80" s="6" t="s">
+      <c r="B80" s="6"/>
+      <c r="C80" s="7"/>
+      <c r="D80" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E80" s="10" t="s">
+      <c r="E80" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="F80" s="6" t="s">
+      <c r="F80" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="G80" s="6"/>
-      <c r="H80" s="6" t="s">
+      <c r="G80" s="5"/>
+      <c r="H80" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I80" s="6"/>
+      <c r="I80" s="5"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="6">
+      <c r="A81" s="5">
         <v>80</v>
       </c>
-      <c r="B81" s="7"/>
-      <c r="C81" s="8"/>
-      <c r="D81" s="6" t="s">
+      <c r="B81" s="6"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E81" s="10" t="s">
+      <c r="E81" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="F81" s="6" t="s">
+      <c r="F81" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="G81" s="6"/>
-      <c r="H81" s="6" t="s">
+      <c r="G81" s="5"/>
+      <c r="H81" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I81" s="6"/>
+      <c r="I81" s="5"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="6">
+      <c r="A82" s="5">
         <v>81</v>
       </c>
-      <c r="B82" s="7"/>
-      <c r="C82" s="8" t="s">
+      <c r="B82" s="6"/>
+      <c r="C82" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D82" s="6" t="s">
+      <c r="D82" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E82" s="10" t="s">
+      <c r="E82" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="F82" s="6" t="s">
+      <c r="F82" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="G82" s="6"/>
-      <c r="H82" s="6" t="s">
+      <c r="G82" s="5"/>
+      <c r="H82" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I82" s="6"/>
+      <c r="I82" s="5"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" s="6">
+      <c r="A83" s="5">
         <v>82</v>
       </c>
-      <c r="B83" s="7"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="6" t="s">
+      <c r="B83" s="6"/>
+      <c r="C83" s="7"/>
+      <c r="D83" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E83" s="10" t="s">
+      <c r="E83" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="F83" s="6" t="s">
+      <c r="F83" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="G83" s="6"/>
-      <c r="H83" s="6" t="s">
+      <c r="G83" s="5"/>
+      <c r="H83" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I83" s="6"/>
+      <c r="I83" s="5"/>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="6">
+      <c r="A84" s="5">
         <v>83</v>
       </c>
-      <c r="B84" s="7"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="6" t="s">
+      <c r="B84" s="6"/>
+      <c r="C84" s="7"/>
+      <c r="D84" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E84" s="10" t="s">
+      <c r="E84" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="F84" s="6" t="s">
+      <c r="F84" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="G84" s="6"/>
-      <c r="H84" s="6" t="s">
+      <c r="G84" s="5"/>
+      <c r="H84" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I84" s="6"/>
+      <c r="I84" s="5"/>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" s="6">
+      <c r="A85" s="5">
         <v>84</v>
       </c>
-      <c r="B85" s="7"/>
-      <c r="C85" s="8"/>
-      <c r="D85" s="6" t="s">
+      <c r="B85" s="6"/>
+      <c r="C85" s="7"/>
+      <c r="D85" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="E85" s="10" t="s">
+      <c r="E85" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="F85" s="6" t="s">
+      <c r="F85" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="G85" s="6"/>
-      <c r="H85" s="6" t="s">
+      <c r="G85" s="5"/>
+      <c r="H85" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I85" s="6"/>
+      <c r="I85" s="5"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="6">
+      <c r="A86" s="5">
         <v>85</v>
       </c>
-      <c r="B86" s="7"/>
-      <c r="C86" s="8"/>
-      <c r="D86" s="6" t="s">
+      <c r="B86" s="6"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="E86" s="10" t="s">
+      <c r="E86" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="F86" s="6" t="s">
+      <c r="F86" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="G86" s="6"/>
-      <c r="H86" s="6" t="s">
+      <c r="G86" s="5"/>
+      <c r="H86" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I86" s="6"/>
+      <c r="I86" s="5"/>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="6">
+      <c r="A87" s="5">
         <v>86</v>
       </c>
-      <c r="B87" s="7"/>
-      <c r="C87" s="8"/>
-      <c r="D87" s="6" t="s">
+      <c r="B87" s="6"/>
+      <c r="C87" s="7"/>
+      <c r="D87" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E87" s="10" t="s">
+      <c r="E87" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="F87" s="6" t="s">
+      <c r="F87" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="G87" s="6"/>
-      <c r="H87" s="6" t="s">
+      <c r="G87" s="5"/>
+      <c r="H87" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I87" s="6"/>
+      <c r="I87" s="5"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="6">
+      <c r="A88" s="5">
         <v>87</v>
       </c>
-      <c r="B88" s="7"/>
-      <c r="C88" s="8"/>
-      <c r="D88" s="6" t="s">
+      <c r="B88" s="6"/>
+      <c r="C88" s="7"/>
+      <c r="D88" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E88" s="10" t="s">
+      <c r="E88" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="F88" s="6" t="s">
+      <c r="F88" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="G88" s="6"/>
-      <c r="H88" s="6" t="s">
+      <c r="G88" s="5"/>
+      <c r="H88" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I88" s="6"/>
+      <c r="I88" s="5"/>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="6">
+      <c r="A89" s="5">
         <v>88</v>
       </c>
-      <c r="B89" s="7"/>
-      <c r="C89" s="8" t="s">
+      <c r="B89" s="6"/>
+      <c r="C89" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D89" s="6" t="s">
+      <c r="D89" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E89" s="10" t="s">
+      <c r="E89" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="F89" s="6" t="s">
+      <c r="F89" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="G89" s="6"/>
-      <c r="H89" s="6" t="s">
+      <c r="G89" s="5"/>
+      <c r="H89" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I89" s="6"/>
+      <c r="I89" s="5"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="6">
+      <c r="A90" s="5">
         <v>89</v>
       </c>
-      <c r="B90" s="7"/>
-      <c r="C90" s="8"/>
-      <c r="D90" s="6" t="s">
+      <c r="B90" s="6"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E90" s="10" t="s">
+      <c r="E90" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="F90" s="6" t="s">
+      <c r="F90" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="G90" s="6"/>
-      <c r="H90" s="6" t="s">
+      <c r="G90" s="5"/>
+      <c r="H90" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I90" s="6"/>
+      <c r="I90" s="5"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" s="6">
+      <c r="A91" s="5">
         <v>90</v>
       </c>
-      <c r="B91" s="7" t="s">
+      <c r="B91" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C91" s="8" t="s">
+      <c r="C91" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="D91" s="6" t="s">
+      <c r="D91" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E91" s="10" t="s">
+      <c r="E91" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="F91" s="6" t="s">
+      <c r="F91" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="G91" s="6"/>
-      <c r="H91" s="6" t="s">
+      <c r="G91" s="5"/>
+      <c r="H91" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I91" s="6"/>
+      <c r="I91" s="5"/>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="6">
+      <c r="A92" s="5">
         <v>91</v>
       </c>
-      <c r="B92" s="7"/>
-      <c r="C92" s="8"/>
-      <c r="D92" s="6" t="s">
+      <c r="B92" s="6"/>
+      <c r="C92" s="7"/>
+      <c r="D92" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E92" s="10" t="s">
+      <c r="E92" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="F92" s="6" t="s">
+      <c r="F92" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="G92" s="6"/>
-      <c r="H92" s="6" t="s">
+      <c r="G92" s="5"/>
+      <c r="H92" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I92" s="6"/>
+      <c r="I92" s="5"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="6">
+      <c r="A93" s="5">
         <v>92</v>
       </c>
-      <c r="B93" s="7" t="s">
+      <c r="B93" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C93" s="8" t="s">
+      <c r="C93" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="D93" s="6" t="s">
+      <c r="D93" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E93" s="10" t="s">
+      <c r="E93" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="F93" s="6" t="s">
+      <c r="F93" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="G93" s="6"/>
-      <c r="H93" s="6" t="s">
+      <c r="G93" s="5"/>
+      <c r="H93" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I93" s="6"/>
+      <c r="I93" s="5"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" s="6">
+      <c r="A94" s="5">
         <v>93</v>
       </c>
-      <c r="B94" s="7"/>
-      <c r="C94" s="8"/>
-      <c r="D94" s="6" t="s">
+      <c r="B94" s="6"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="E94" s="10" t="s">
+      <c r="E94" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="F94" s="6" t="s">
+      <c r="F94" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="G94" s="6"/>
-      <c r="H94" s="6" t="s">
+      <c r="G94" s="5"/>
+      <c r="H94" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I94" s="6"/>
+      <c r="I94" s="5"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="6">
+      <c r="A95" s="5">
         <v>94</v>
       </c>
-      <c r="B95" s="7"/>
-      <c r="C95" s="8"/>
-      <c r="D95" s="6" t="s">
+      <c r="B95" s="6"/>
+      <c r="C95" s="7"/>
+      <c r="D95" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E95" s="10" t="s">
+      <c r="E95" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="F95" s="6" t="s">
+      <c r="F95" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="G95" s="6"/>
-      <c r="H95" s="6" t="s">
+      <c r="G95" s="5"/>
+      <c r="H95" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I95" s="6"/>
+      <c r="I95" s="5"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="6">
+      <c r="A96" s="5">
         <v>95</v>
       </c>
-      <c r="B96" s="7"/>
-      <c r="C96" s="9" t="s">
+      <c r="B96" s="6"/>
+      <c r="C96" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D96" s="6" t="s">
+      <c r="D96" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E96" s="10" t="s">
+      <c r="E96" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F96" s="10" t="s">
+      <c r="F96" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="G96" s="6"/>
-      <c r="H96" s="6" t="s">
+      <c r="G96" s="5"/>
+      <c r="H96" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I96" s="6"/>
+      <c r="I96" s="5"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="6">
+      <c r="A97" s="5">
         <v>96</v>
       </c>
-      <c r="B97" s="7" t="s">
+      <c r="B97" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="C97" s="8" t="s">
+      <c r="C97" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="D97" s="6" t="s">
+      <c r="D97" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E97" s="10" t="s">
+      <c r="E97" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="F97" s="10" t="s">
+      <c r="F97" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="G97" s="6"/>
-      <c r="H97" s="6" t="s">
+      <c r="G97" s="5"/>
+      <c r="H97" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I97" s="6"/>
+      <c r="I97" s="5"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="6">
+      <c r="A98" s="5">
         <v>97</v>
       </c>
-      <c r="B98" s="7"/>
-      <c r="C98" s="8"/>
-      <c r="D98" s="6" t="s">
+      <c r="B98" s="6"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E98" s="10" t="s">
+      <c r="E98" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="F98" s="10" t="s">
+      <c r="F98" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="G98" s="6"/>
-      <c r="H98" s="6" t="s">
+      <c r="G98" s="5"/>
+      <c r="H98" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I98" s="6"/>
+      <c r="I98" s="5"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" s="6">
+      <c r="A99" s="5">
         <v>98</v>
       </c>
-      <c r="B99" s="7"/>
-      <c r="C99" s="8"/>
-      <c r="D99" s="6" t="s">
+      <c r="B99" s="6"/>
+      <c r="C99" s="7"/>
+      <c r="D99" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="E99" s="10" t="s">
+      <c r="E99" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="F99" s="10" t="s">
+      <c r="F99" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="G99" s="6"/>
-      <c r="H99" s="6" t="s">
+      <c r="G99" s="5"/>
+      <c r="H99" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I99" s="6"/>
+      <c r="I99" s="5"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="6">
+      <c r="A100" s="5">
         <v>99</v>
       </c>
-      <c r="B100" s="7"/>
-      <c r="C100" s="8" t="s">
+      <c r="B100" s="6"/>
+      <c r="C100" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D100" s="6" t="s">
+      <c r="D100" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E100" s="6" t="s">
+      <c r="E100" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F100" s="6" t="s">
+      <c r="F100" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="G100" s="6"/>
-      <c r="H100" s="6" t="s">
+      <c r="G100" s="5"/>
+      <c r="H100" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I100" s="6"/>
+      <c r="I100" s="5"/>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="6">
+      <c r="A101" s="5">
         <v>100</v>
       </c>
-      <c r="B101" s="7"/>
-      <c r="C101" s="8"/>
-      <c r="D101" s="6" t="s">
+      <c r="B101" s="6"/>
+      <c r="C101" s="7"/>
+      <c r="D101" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="E101" s="6" t="s">
+      <c r="E101" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="F101" s="6" t="s">
+      <c r="F101" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="G101" s="6"/>
-      <c r="H101" s="6" t="s">
+      <c r="G101" s="5"/>
+      <c r="H101" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I101" s="6"/>
+      <c r="I101" s="5"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" s="6">
+      <c r="A102" s="5">
         <v>101</v>
       </c>
-      <c r="B102" s="7"/>
-      <c r="C102" s="8"/>
-      <c r="D102" s="6" t="s">
+      <c r="B102" s="6"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E102" s="6" t="s">
+      <c r="E102" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F102" s="6" t="s">
+      <c r="F102" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G102" s="6"/>
-      <c r="H102" s="6" t="s">
+      <c r="G102" s="5"/>
+      <c r="H102" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I102" s="6"/>
+      <c r="I102" s="5"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="6">
+      <c r="A103" s="5">
         <v>102</v>
       </c>
-      <c r="B103" s="7" t="s">
+      <c r="B103" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C103" s="8" t="s">
+      <c r="C103" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="D103" s="6" t="s">
+      <c r="D103" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E103" s="6" t="s">
+      <c r="E103" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="F103" s="6" t="s">
+      <c r="F103" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="G103" s="6"/>
-      <c r="H103" s="6" t="s">
+      <c r="G103" s="5"/>
+      <c r="H103" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I103" s="6"/>
+      <c r="I103" s="5"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="6">
+      <c r="A104" s="5">
         <v>103</v>
       </c>
-      <c r="B104" s="7"/>
-      <c r="C104" s="8"/>
-      <c r="D104" s="6" t="s">
+      <c r="B104" s="6"/>
+      <c r="C104" s="7"/>
+      <c r="D104" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E104" s="6" t="s">
+      <c r="E104" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="F104" s="6" t="s">
+      <c r="F104" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="G104" s="6"/>
-      <c r="H104" s="6" t="s">
+      <c r="G104" s="5"/>
+      <c r="H104" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I104" s="6"/>
+      <c r="I104" s="5"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="6">
+      <c r="A105" s="5">
         <v>104</v>
       </c>
-      <c r="B105" s="7"/>
-      <c r="C105" s="8"/>
-      <c r="D105" s="6" t="s">
+      <c r="B105" s="6"/>
+      <c r="C105" s="7"/>
+      <c r="D105" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E105" s="6" t="s">
+      <c r="E105" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="F105" s="6" t="s">
+      <c r="F105" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="G105" s="6"/>
-      <c r="H105" s="6" t="s">
+      <c r="G105" s="5"/>
+      <c r="H105" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I105" s="6"/>
+      <c r="I105" s="5"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" s="6">
+      <c r="A106" s="5">
         <v>105</v>
       </c>
-      <c r="B106" s="7"/>
-      <c r="C106" s="11" t="s">
+      <c r="B106" s="6"/>
+      <c r="C106" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="D106" s="6" t="s">
+      <c r="D106" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E106" s="6" t="s">
+      <c r="E106" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="F106" s="6" t="s">
+      <c r="F106" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="G106" s="6"/>
-      <c r="H106" s="6" t="s">
+      <c r="G106" s="5"/>
+      <c r="H106" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I106" s="6"/>
+      <c r="I106" s="5"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="6">
+      <c r="A107" s="5">
         <v>106</v>
       </c>
-      <c r="B107" s="7"/>
-      <c r="C107" s="11"/>
-      <c r="D107" s="6" t="s">
+      <c r="B107" s="6"/>
+      <c r="C107" s="10"/>
+      <c r="D107" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E107" s="6" t="s">
+      <c r="E107" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="F107" s="6" t="s">
+      <c r="F107" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="G107" s="6"/>
-      <c r="H107" s="6" t="s">
+      <c r="G107" s="5"/>
+      <c r="H107" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I107" s="6"/>
+      <c r="I107" s="5"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" s="6">
+      <c r="A108" s="5">
         <v>107</v>
       </c>
-      <c r="B108" s="7"/>
-      <c r="C108" s="11" t="s">
+      <c r="B108" s="6"/>
+      <c r="C108" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="D108" s="6" t="s">
+      <c r="D108" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="E108" s="6" t="s">
+      <c r="E108" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="F108" s="6" t="s">
+      <c r="F108" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="G108" s="6"/>
-      <c r="H108" s="6" t="s">
+      <c r="G108" s="5"/>
+      <c r="H108" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I108" s="6"/>
+      <c r="I108" s="5"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="6">
+      <c r="A109" s="5">
         <v>108</v>
       </c>
-      <c r="B109" s="7"/>
-      <c r="C109" s="11"/>
-      <c r="D109" s="6" t="s">
+      <c r="B109" s="6"/>
+      <c r="C109" s="10"/>
+      <c r="D109" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="E109" s="6" t="s">
+      <c r="E109" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="F109" s="6" t="s">
+      <c r="F109" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="G109" s="6"/>
-      <c r="H109" s="6" t="s">
+      <c r="G109" s="5"/>
+      <c r="H109" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I109" s="6"/>
+      <c r="I109" s="5"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="6">
+      <c r="A110" s="5">
         <v>109</v>
       </c>
-      <c r="B110" s="7"/>
-      <c r="C110" s="11"/>
-      <c r="D110" s="6" t="s">
+      <c r="B110" s="6"/>
+      <c r="C110" s="10"/>
+      <c r="D110" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="E110" s="6" t="s">
+      <c r="E110" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="F110" s="6" t="s">
+      <c r="F110" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="G110" s="6"/>
-      <c r="H110" s="6" t="s">
+      <c r="G110" s="5"/>
+      <c r="H110" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I110" s="6"/>
+      <c r="I110" s="5"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="6">
+      <c r="A111" s="5">
         <v>110</v>
       </c>
-      <c r="B111" s="7"/>
-      <c r="C111" s="11" t="s">
+      <c r="B111" s="6"/>
+      <c r="C111" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="D111" s="6" t="s">
+      <c r="D111" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E111" s="6" t="s">
+      <c r="E111" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="F111" s="6" t="s">
+      <c r="F111" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="G111" s="6"/>
-      <c r="H111" s="6" t="s">
+      <c r="G111" s="5"/>
+      <c r="H111" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I111" s="6"/>
+      <c r="I111" s="5"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="6">
+      <c r="A112" s="5">
         <v>111</v>
       </c>
-      <c r="B112" s="7"/>
-      <c r="C112" s="11"/>
-      <c r="D112" s="6" t="s">
+      <c r="B112" s="6"/>
+      <c r="C112" s="10"/>
+      <c r="D112" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E112" s="6" t="s">
+      <c r="E112" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="F112" s="6" t="s">
+      <c r="F112" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="G112" s="6"/>
-      <c r="H112" s="6" t="s">
+      <c r="G112" s="5"/>
+      <c r="H112" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I112" s="6"/>
+      <c r="I112" s="5"/>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" s="6">
+      <c r="A113" s="5">
         <v>112</v>
       </c>
-      <c r="B113" s="7"/>
-      <c r="C113" s="11" t="s">
+      <c r="B113" s="6"/>
+      <c r="C113" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="D113" s="6" t="s">
+      <c r="D113" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="E113" s="6" t="s">
+      <c r="E113" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="F113" s="6" t="s">
+      <c r="F113" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="G113" s="6"/>
-      <c r="H113" s="6" t="s">
+      <c r="G113" s="5"/>
+      <c r="H113" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I113" s="6"/>
+      <c r="I113" s="5"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="6">
+      <c r="A114" s="5">
         <v>113</v>
       </c>
-      <c r="B114" s="7"/>
-      <c r="C114" s="11"/>
-      <c r="D114" s="6" t="s">
+      <c r="B114" s="6"/>
+      <c r="C114" s="10"/>
+      <c r="D114" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="E114" s="6" t="s">
+      <c r="E114" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="F114" s="6" t="s">
+      <c r="F114" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="G114" s="6"/>
-      <c r="H114" s="6" t="s">
+      <c r="G114" s="5"/>
+      <c r="H114" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I114" s="6"/>
+      <c r="I114" s="5"/>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="6">
+      <c r="A115" s="5">
         <v>114</v>
       </c>
-      <c r="B115" s="7"/>
-      <c r="C115" s="11"/>
-      <c r="D115" s="6" t="s">
+      <c r="B115" s="6"/>
+      <c r="C115" s="10"/>
+      <c r="D115" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="E115" s="6" t="s">
+      <c r="E115" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="F115" s="6" t="s">
+      <c r="F115" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="G115" s="6"/>
-      <c r="H115" s="6" t="s">
+      <c r="G115" s="5"/>
+      <c r="H115" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I115" s="6"/>
+      <c r="I115" s="5"/>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" s="6">
+      <c r="A116" s="5">
         <v>115</v>
       </c>
-      <c r="B116" s="7"/>
-      <c r="C116" s="6" t="s">
+      <c r="B116" s="6"/>
+      <c r="C116" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D116" s="6" t="s">
+      <c r="D116" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E116" s="6" t="s">
+      <c r="E116" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="F116" s="6" t="s">
+      <c r="F116" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="G116" s="6"/>
-      <c r="H116" s="6" t="s">
+      <c r="G116" s="5"/>
+      <c r="H116" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I116" s="6"/>
+      <c r="I116" s="5"/>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="6">
+      <c r="A117" s="5">
         <v>116</v>
       </c>
-      <c r="B117" s="7"/>
-      <c r="C117" s="11" t="s">
+      <c r="B117" s="6"/>
+      <c r="C117" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="D117" s="6" t="s">
+      <c r="D117" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="E117" s="6" t="s">
+      <c r="E117" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="F117" s="6" t="s">
+      <c r="F117" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="G117" s="6"/>
-      <c r="H117" s="6" t="s">
+      <c r="G117" s="5"/>
+      <c r="H117" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I117" s="6"/>
+      <c r="I117" s="5"/>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" s="6">
+      <c r="A118" s="5">
         <v>117</v>
       </c>
-      <c r="B118" s="7"/>
-      <c r="C118" s="11"/>
-      <c r="D118" s="6" t="s">
+      <c r="B118" s="6"/>
+      <c r="C118" s="10"/>
+      <c r="D118" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="E118" s="6" t="s">
+      <c r="E118" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="F118" s="6" t="s">
+      <c r="F118" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="G118" s="6"/>
-      <c r="H118" s="6" t="s">
+      <c r="G118" s="5"/>
+      <c r="H118" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I118" s="6"/>
+      <c r="I118" s="5"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" s="6">
+      <c r="A119" s="5">
         <v>118</v>
       </c>
-      <c r="B119" s="7"/>
-      <c r="C119" s="11"/>
-      <c r="D119" s="6" t="s">
+      <c r="B119" s="6"/>
+      <c r="C119" s="10"/>
+      <c r="D119" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="E119" s="6" t="s">
+      <c r="E119" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="F119" s="6" t="s">
+      <c r="F119" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="G119" s="6"/>
-      <c r="H119" s="6" t="s">
+      <c r="G119" s="5"/>
+      <c r="H119" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I119" s="6"/>
+      <c r="I119" s="5"/>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120" s="6">
+      <c r="A120" s="5">
         <v>119</v>
       </c>
-      <c r="B120" s="7"/>
-      <c r="C120" s="11"/>
-      <c r="D120" s="6" t="s">
+      <c r="B120" s="6"/>
+      <c r="C120" s="10"/>
+      <c r="D120" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="E120" s="6" t="s">
+      <c r="E120" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="F120" s="6" t="s">
+      <c r="F120" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="G120" s="6"/>
-      <c r="H120" s="6" t="s">
+      <c r="G120" s="5"/>
+      <c r="H120" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I120" s="6"/>
+      <c r="I120" s="5"/>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" s="6">
+      <c r="A121" s="5">
         <v>120</v>
       </c>
-      <c r="B121" s="7" t="s">
+      <c r="B121" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C121" s="11" t="s">
+      <c r="C121" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="D121" s="6" t="s">
+      <c r="D121" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="E121" s="6" t="s">
+      <c r="E121" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="F121" s="6" t="s">
+      <c r="F121" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="G121" s="6"/>
-      <c r="H121" s="6" t="s">
+      <c r="G121" s="5"/>
+      <c r="H121" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I121" s="6"/>
+      <c r="I121" s="5"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="6">
+      <c r="A122" s="5">
         <v>121</v>
       </c>
-      <c r="B122" s="7"/>
-      <c r="C122" s="11"/>
-      <c r="D122" s="6" t="s">
+      <c r="B122" s="6"/>
+      <c r="C122" s="10"/>
+      <c r="D122" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="E122" s="6" t="s">
+      <c r="E122" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="F122" s="6" t="s">
+      <c r="F122" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="G122" s="6"/>
-      <c r="H122" s="6" t="s">
+      <c r="G122" s="5"/>
+      <c r="H122" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I122" s="6"/>
+      <c r="I122" s="5"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="6">
+      <c r="A123" s="5">
         <v>122</v>
       </c>
-      <c r="B123" s="7"/>
-      <c r="C123" s="11"/>
-      <c r="D123" s="6" t="s">
+      <c r="B123" s="6"/>
+      <c r="C123" s="10"/>
+      <c r="D123" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="E123" s="6" t="s">
+      <c r="E123" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="F123" s="6" t="s">
+      <c r="F123" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="G123" s="6"/>
-      <c r="H123" s="6" t="s">
+      <c r="G123" s="5"/>
+      <c r="H123" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I123" s="6"/>
+      <c r="I123" s="5"/>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" s="6">
+      <c r="A124" s="5">
         <v>123</v>
       </c>
-      <c r="B124" s="7" t="s">
+      <c r="B124" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C124" s="13" t="s">
+      <c r="C124" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="D124" s="6" t="s">
+      <c r="D124" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E124" s="6" t="s">
+      <c r="E124" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="F124" s="6" t="s">
+      <c r="F124" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="G124" s="6"/>
-      <c r="H124" s="6" t="s">
+      <c r="G124" s="5"/>
+      <c r="H124" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I124" s="6"/>
+      <c r="I124" s="5"/>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A125" s="6">
+      <c r="A125" s="5">
         <v>124</v>
       </c>
-      <c r="B125" s="7"/>
-      <c r="C125" s="13" t="s">
+      <c r="B125" s="6"/>
+      <c r="C125" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="D125" s="6" t="s">
+      <c r="D125" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="E125" s="6" t="s">
+      <c r="E125" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="F125" s="6" t="s">
+      <c r="F125" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="G125" s="6"/>
-      <c r="H125" s="6" t="s">
+      <c r="G125" s="5"/>
+      <c r="H125" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I125" s="6"/>
+      <c r="I125" s="5"/>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A126" s="6">
+      <c r="A126" s="5">
         <v>125</v>
       </c>
-      <c r="B126" s="7"/>
-      <c r="C126" s="6" t="s">
+      <c r="B126" s="6"/>
+      <c r="C126" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D126" s="6" t="s">
+      <c r="D126" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="E126" s="6" t="s">
+      <c r="E126" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="F126" s="6" t="s">
+      <c r="F126" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="G126" s="6"/>
-      <c r="H126" s="6" t="s">
+      <c r="G126" s="5"/>
+      <c r="H126" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I126" s="6"/>
+      <c r="I126" s="5"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A127" s="6">
+      <c r="A127" s="5">
         <v>126</v>
       </c>
-      <c r="B127" s="7"/>
-      <c r="C127" s="6" t="s">
+      <c r="B127" s="6"/>
+      <c r="C127" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="D127" s="6" t="s">
+      <c r="D127" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="E127" s="6" t="s">
+      <c r="E127" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="F127" s="6" t="s">
+      <c r="F127" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="G127" s="6"/>
-      <c r="H127" s="6" t="s">
+      <c r="G127" s="5"/>
+      <c r="H127" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I127" s="6"/>
+      <c r="I127" s="5"/>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A128" s="6">
+      <c r="A128" s="5">
         <v>127</v>
       </c>
-      <c r="B128" s="7"/>
-      <c r="C128" s="6" t="s">
+      <c r="B128" s="6"/>
+      <c r="C128" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D128" s="6" t="s">
+      <c r="D128" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="E128" s="6" t="s">
+      <c r="E128" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="F128" s="6" t="s">
+      <c r="F128" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="G128" s="6"/>
-      <c r="H128" s="6" t="s">
+      <c r="G128" s="5"/>
+      <c r="H128" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I128" s="6"/>
+      <c r="I128" s="5"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A129" s="6">
+      <c r="A129" s="5">
         <v>128</v>
       </c>
-      <c r="B129" s="7"/>
-      <c r="C129" s="11" t="s">
+      <c r="B129" s="6"/>
+      <c r="C129" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="D129" s="6" t="s">
+      <c r="D129" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E129" s="6" t="s">
+      <c r="E129" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="F129" s="6" t="s">
+      <c r="F129" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="G129" s="6"/>
-      <c r="H129" s="6" t="s">
+      <c r="G129" s="5"/>
+      <c r="H129" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I129" s="6"/>
+      <c r="I129" s="5"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A130" s="6">
+      <c r="A130" s="5">
         <v>129</v>
       </c>
-      <c r="B130" s="7"/>
-      <c r="C130" s="11"/>
-      <c r="D130" s="6" t="s">
+      <c r="B130" s="6"/>
+      <c r="C130" s="10"/>
+      <c r="D130" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="E130" s="6" t="s">
+      <c r="E130" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="F130" s="6" t="s">
+      <c r="F130" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="G130" s="6"/>
-      <c r="H130" s="6" t="s">
+      <c r="G130" s="5"/>
+      <c r="H130" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I130" s="6"/>
+      <c r="I130" s="5"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A131" s="6">
+      <c r="A131" s="5">
         <v>130</v>
       </c>
-      <c r="B131" s="7"/>
-      <c r="C131" s="11"/>
-      <c r="D131" s="6" t="s">
+      <c r="B131" s="6"/>
+      <c r="C131" s="10"/>
+      <c r="D131" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E131" s="6" t="s">
+      <c r="E131" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="F131" s="6" t="s">
+      <c r="F131" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="G131" s="6"/>
-      <c r="H131" s="6" t="s">
+      <c r="G131" s="5"/>
+      <c r="H131" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I131" s="6"/>
+      <c r="I131" s="5"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="6">
+      <c r="A132" s="5">
         <v>131</v>
       </c>
-      <c r="B132" s="7"/>
-      <c r="C132" s="11" t="s">
+      <c r="B132" s="6"/>
+      <c r="C132" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="D132" s="6" t="s">
+      <c r="D132" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E132" s="6" t="s">
+      <c r="E132" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="F132" s="6" t="s">
+      <c r="F132" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="G132" s="6"/>
-      <c r="H132" s="6" t="s">
+      <c r="G132" s="5"/>
+      <c r="H132" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I132" s="6"/>
+      <c r="I132" s="5"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A133" s="6">
+      <c r="A133" s="5">
         <v>132</v>
       </c>
-      <c r="B133" s="7"/>
-      <c r="C133" s="11"/>
-      <c r="D133" s="6" t="s">
+      <c r="B133" s="6"/>
+      <c r="C133" s="10"/>
+      <c r="D133" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="E133" s="6" t="s">
+      <c r="E133" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="F133" s="6" t="s">
+      <c r="F133" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="G133" s="6"/>
-      <c r="H133" s="6" t="s">
+      <c r="G133" s="5"/>
+      <c r="H133" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I133" s="6"/>
+      <c r="I133" s="5"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A134" s="6">
+      <c r="A134" s="5">
         <v>133</v>
       </c>
-      <c r="B134" s="7"/>
-      <c r="C134" s="11"/>
-      <c r="D134" s="6" t="s">
+      <c r="B134" s="6"/>
+      <c r="C134" s="10"/>
+      <c r="D134" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E134" s="6" t="s">
+      <c r="E134" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="F134" s="6" t="s">
+      <c r="F134" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="G134" s="6"/>
-      <c r="H134" s="6" t="s">
+      <c r="G134" s="5"/>
+      <c r="H134" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I134" s="6"/>
+      <c r="I134" s="5"/>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A135" s="6">
+      <c r="A135" s="5">
         <v>134</v>
       </c>
-      <c r="B135" s="7"/>
-      <c r="C135" s="11" t="s">
+      <c r="B135" s="6"/>
+      <c r="C135" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="D135" s="6" t="s">
+      <c r="D135" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E135" s="6" t="s">
+      <c r="E135" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="F135" s="6" t="s">
+      <c r="F135" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="G135" s="6"/>
-      <c r="H135" s="6" t="s">
+      <c r="G135" s="5"/>
+      <c r="H135" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I135" s="6"/>
+      <c r="I135" s="5"/>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A136" s="6">
+      <c r="A136" s="5">
         <v>135</v>
       </c>
-      <c r="B136" s="7"/>
-      <c r="C136" s="11"/>
-      <c r="D136" s="6" t="s">
+      <c r="B136" s="6"/>
+      <c r="C136" s="10"/>
+      <c r="D136" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="E136" s="6" t="s">
+      <c r="E136" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="F136" s="6" t="s">
+      <c r="F136" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="G136" s="6"/>
-      <c r="H136" s="6" t="s">
+      <c r="G136" s="5"/>
+      <c r="H136" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I136" s="6"/>
+      <c r="I136" s="5"/>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A137" s="6">
+      <c r="A137" s="5">
         <v>136</v>
       </c>
-      <c r="B137" s="7"/>
-      <c r="C137" s="11"/>
-      <c r="D137" s="6" t="s">
+      <c r="B137" s="6"/>
+      <c r="C137" s="10"/>
+      <c r="D137" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E137" s="6" t="s">
+      <c r="E137" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="F137" s="6" t="s">
+      <c r="F137" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="G137" s="6"/>
-      <c r="H137" s="6" t="s">
+      <c r="G137" s="5"/>
+      <c r="H137" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I137" s="6"/>
+      <c r="I137" s="5"/>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A138" s="6">
+      <c r="A138" s="5">
         <v>137</v>
       </c>
-      <c r="B138" s="7"/>
-      <c r="C138" s="11" t="s">
+      <c r="B138" s="6"/>
+      <c r="C138" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="D138" s="6" t="s">
+      <c r="D138" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E138" s="6" t="s">
+      <c r="E138" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="F138" s="6" t="s">
+      <c r="F138" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="G138" s="6"/>
-      <c r="H138" s="6" t="s">
+      <c r="G138" s="5"/>
+      <c r="H138" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I138" s="6"/>
+      <c r="I138" s="5"/>
     </row>
     <row r="139" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A139" s="6">
+      <c r="A139" s="5">
         <v>138</v>
       </c>
-      <c r="B139" s="7"/>
-      <c r="C139" s="11"/>
-      <c r="D139" s="12" t="s">
+      <c r="B139" s="6"/>
+      <c r="C139" s="10"/>
+      <c r="D139" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="E139" s="6" t="s">
+      <c r="E139" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="F139" s="6" t="s">
+      <c r="F139" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="G139" s="6"/>
-      <c r="H139" s="6" t="s">
+      <c r="G139" s="5"/>
+      <c r="H139" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I139" s="6"/>
+      <c r="I139" s="5"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A140" s="6">
+      <c r="A140" s="5">
         <v>139</v>
       </c>
-      <c r="B140" s="7"/>
-      <c r="C140" s="11"/>
-      <c r="D140" s="9" t="s">
+      <c r="B140" s="6"/>
+      <c r="C140" s="10"/>
+      <c r="D140" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="E140" s="6" t="s">
+      <c r="E140" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="F140" s="6" t="s">
+      <c r="F140" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="G140" s="6"/>
-      <c r="H140" s="6" t="s">
+      <c r="G140" s="5"/>
+      <c r="H140" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I140" s="6"/>
+      <c r="I140" s="5"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A141" s="6">
+      <c r="A141" s="5">
         <v>140</v>
       </c>
-      <c r="B141" s="7"/>
-      <c r="C141" s="11"/>
-      <c r="D141" s="9" t="s">
+      <c r="B141" s="6"/>
+      <c r="C141" s="10"/>
+      <c r="D141" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="E141" s="6" t="s">
+      <c r="E141" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="F141" s="6" t="s">
+      <c r="F141" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="G141" s="6"/>
-      <c r="H141" s="6" t="s">
+      <c r="G141" s="5"/>
+      <c r="H141" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I141" s="6"/>
+      <c r="I141" s="5"/>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A142" s="6">
+      <c r="A142" s="5">
         <v>141</v>
       </c>
-      <c r="B142" s="7"/>
-      <c r="C142" s="11"/>
-      <c r="D142" s="9" t="s">
+      <c r="B142" s="6"/>
+      <c r="C142" s="10"/>
+      <c r="D142" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="E142" s="6" t="s">
+      <c r="E142" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="F142" s="6" t="s">
+      <c r="F142" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="G142" s="6"/>
-      <c r="H142" s="6" t="s">
+      <c r="G142" s="5"/>
+      <c r="H142" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I142" s="6"/>
+      <c r="I142" s="5"/>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A143" s="6">
+      <c r="A143" s="5">
         <v>142</v>
       </c>
-      <c r="B143" s="7" t="s">
+      <c r="B143" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="C143" s="6" t="s">
+      <c r="C143" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D143" s="6" t="s">
+      <c r="D143" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="E143" s="6" t="s">
+      <c r="E143" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="F143" s="6" t="s">
+      <c r="F143" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="G143" s="6"/>
-      <c r="H143" s="6" t="s">
+      <c r="G143" s="5"/>
+      <c r="H143" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I143" s="6"/>
+      <c r="I143" s="5"/>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A144" s="6">
+      <c r="A144" s="5">
         <v>143</v>
       </c>
-      <c r="B144" s="7"/>
-      <c r="C144" s="6" t="s">
+      <c r="B144" s="6"/>
+      <c r="C144" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="D144" s="6" t="s">
+      <c r="D144" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="E144" s="6" t="s">
+      <c r="E144" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="F144" s="6" t="s">
+      <c r="F144" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="G144" s="6"/>
-      <c r="H144" s="6" t="s">
+      <c r="G144" s="5"/>
+      <c r="H144" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I144" s="6"/>
+      <c r="I144" s="5"/>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A145" s="6">
+      <c r="A145" s="5">
         <v>144</v>
       </c>
-      <c r="B145" s="14" t="s">
+      <c r="B145" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="C145" s="6" t="s">
+      <c r="C145" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="D145" s="6" t="s">
+      <c r="D145" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E145" s="6" t="s">
+      <c r="E145" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="F145" s="6" t="s">
+      <c r="F145" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="G145" s="6"/>
-      <c r="H145" s="6" t="s">
+      <c r="G145" s="5"/>
+      <c r="H145" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I145" s="6"/>
+      <c r="I145" s="5"/>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A146" s="6">
+      <c r="A146" s="5">
         <v>145</v>
       </c>
-      <c r="B146" s="7" t="s">
+      <c r="B146" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C146" s="11" t="s">
+      <c r="C146" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="D146" s="6" t="s">
+      <c r="D146" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="E146" s="6" t="s">
+      <c r="E146" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="F146" s="6" t="s">
+      <c r="F146" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="G146" s="6"/>
-      <c r="H146" s="6" t="s">
+      <c r="G146" s="5"/>
+      <c r="H146" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I146" s="6"/>
+      <c r="I146" s="5"/>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A147" s="6">
+      <c r="A147" s="5">
         <v>146</v>
       </c>
-      <c r="B147" s="7"/>
-      <c r="C147" s="11"/>
-      <c r="D147" s="6" t="s">
+      <c r="B147" s="6"/>
+      <c r="C147" s="10"/>
+      <c r="D147" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="E147" s="6" t="s">
+      <c r="E147" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="F147" s="6" t="s">
+      <c r="F147" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="G147" s="6"/>
-      <c r="H147" s="6" t="s">
+      <c r="G147" s="5"/>
+      <c r="H147" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I147" s="6"/>
+      <c r="I147" s="5"/>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A148" s="6">
+      <c r="A148" s="5">
         <v>147</v>
       </c>
-      <c r="B148" s="7"/>
-      <c r="C148" s="11"/>
-      <c r="D148" s="6" t="s">
+      <c r="B148" s="6"/>
+      <c r="C148" s="10"/>
+      <c r="D148" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="E148" s="6" t="s">
+      <c r="E148" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="F148" s="6" t="s">
+      <c r="F148" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="G148" s="6"/>
-      <c r="H148" s="6" t="s">
+      <c r="G148" s="5"/>
+      <c r="H148" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I148" s="6"/>
+      <c r="I148" s="5"/>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A149" s="6">
+      <c r="A149" s="5">
         <v>148</v>
       </c>
-      <c r="B149" s="7"/>
-      <c r="C149" s="11" t="s">
+      <c r="B149" s="6"/>
+      <c r="C149" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="D149" s="6" t="s">
+      <c r="D149" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="E149" s="6" t="s">
+      <c r="E149" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="F149" s="6" t="s">
+      <c r="F149" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="G149" s="6"/>
-      <c r="H149" s="6" t="s">
+      <c r="G149" s="5"/>
+      <c r="H149" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I149" s="6"/>
+      <c r="I149" s="5"/>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A150" s="6">
+      <c r="A150" s="5">
         <v>149</v>
       </c>
-      <c r="B150" s="7"/>
-      <c r="C150" s="11"/>
-      <c r="D150" s="6" t="s">
+      <c r="B150" s="6"/>
+      <c r="C150" s="10"/>
+      <c r="D150" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="E150" s="6" t="s">
+      <c r="E150" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="F150" s="6" t="s">
+      <c r="F150" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="G150" s="6"/>
-      <c r="H150" s="6" t="s">
+      <c r="G150" s="5"/>
+      <c r="H150" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I150" s="6"/>
+      <c r="I150" s="5"/>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A151" s="6">
+      <c r="A151" s="5">
         <v>150</v>
       </c>
-      <c r="B151" s="7"/>
-      <c r="C151" s="11"/>
-      <c r="D151" s="6" t="s">
+      <c r="B151" s="6"/>
+      <c r="C151" s="10"/>
+      <c r="D151" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="E151" s="6" t="s">
+      <c r="E151" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="F151" s="6" t="s">
+      <c r="F151" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="G151" s="6"/>
-      <c r="H151" s="6" t="s">
+      <c r="G151" s="5"/>
+      <c r="H151" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I151" s="6"/>
+      <c r="I151" s="5"/>
     </row>
     <row r="152" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A152" s="6">
+      <c r="A152" s="5">
         <v>151</v>
       </c>
-      <c r="B152" s="14" t="s">
+      <c r="B152" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="C152" s="15" t="s">
+      <c r="C152" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="D152" s="6" t="s">
+      <c r="D152" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="E152" s="6" t="s">
+      <c r="E152" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="F152" s="6" t="s">
+      <c r="F152" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="G152" s="6"/>
-      <c r="H152" s="6" t="s">
+      <c r="G152" s="5"/>
+      <c r="H152" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="I152" s="6"/>
+      <c r="I152" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="52">
@@ -5483,7 +5540,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CF7B26D-E2A8-4887-8F63-92439D43C540}">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
@@ -5497,392 +5554,392 @@
     <col min="9" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="18" customFormat="1" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:9" s="17" customFormat="1" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>333</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="9" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="7"/>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="6"/>
+      <c r="C7" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="9" t="s">
         <v>317</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="9" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="7"/>
-      <c r="C8" s="9" t="s">
+      <c r="B8" s="6"/>
+      <c r="C8" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="9" t="s">
         <v>319</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="9" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="7"/>
-      <c r="C9" s="9" t="s">
+      <c r="B9" s="6"/>
+      <c r="C9" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="9" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="7"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="7"/>
-      <c r="C11" s="7" t="s">
+      <c r="B11" s="6"/>
+      <c r="C11" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="9" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="10" t="s">
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="9" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="10" t="s">
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="9" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="7"/>
-      <c r="C14" s="14" t="s">
+      <c r="B14" s="6"/>
+      <c r="C14" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="9" t="s">
         <v>342</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="9" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="7"/>
-      <c r="C15" s="7" t="s">
+      <c r="B15" s="6"/>
+      <c r="C15" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="9" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="10" t="s">
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="9" t="s">
         <v>347</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="9" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="10" t="s">
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="9" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="10" t="s">
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="9" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="7"/>
-      <c r="C19" s="7" t="s">
+      <c r="B19" s="6"/>
+      <c r="C19" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="9" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="10" t="s">
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="9" t="s">
         <v>352</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="9" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="10" t="s">
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="9" t="s">
         <v>353</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="9" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7" t="s">
+      <c r="B22" s="6"/>
+      <c r="C22" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="9" t="s">
         <v>356</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="9" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="10" t="s">
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="9" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="10" t="s">
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="9" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="10" t="s">
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="9" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="10" t="s">
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="F26" s="9" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="10" t="s">
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="9" t="s">
         <v>366</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="9" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B28" s="7"/>
-      <c r="C28" s="14" t="s">
+      <c r="B28" s="6"/>
+      <c r="C28" s="13" t="s">
         <v>367</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="9" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B29" s="7"/>
-      <c r="C29" s="7" t="s">
+      <c r="B29" s="6"/>
+      <c r="C29" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="F29" s="9" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="10" t="s">
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="9" t="s">
         <v>373</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="F30" s="9" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="13" t="s">
         <v>323</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E31" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="F31" s="9" t="s">
         <v>326</v>
       </c>
     </row>
@@ -5904,6 +5961,7 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="4"/>
       <c r="C37" t="s">
         <v>382</v>
       </c>
@@ -5918,6 +5976,7 @@
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="4"/>
       <c r="C38" t="s">
         <v>385</v>
       </c>
@@ -5932,7 +5991,8 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C39" s="5" t="s">
+      <c r="B39" s="4"/>
+      <c r="C39" s="4" t="s">
         <v>386</v>
       </c>
       <c r="D39" t="s">
@@ -5946,7 +6006,8 @@
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C40" s="5"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
       <c r="D40" t="s">
         <v>391</v>
       </c>
@@ -5958,6 +6019,7 @@
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B41" s="4"/>
       <c r="C41" t="s">
         <v>393</v>
       </c>
@@ -5971,9 +6033,65 @@
         <v>396</v>
       </c>
     </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>397</v>
+      </c>
+      <c r="C43" t="s">
+        <v>400</v>
+      </c>
+      <c r="D43" t="s">
+        <v>403</v>
+      </c>
+      <c r="E43" t="s">
+        <v>402</v>
+      </c>
+      <c r="F43" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C44" t="s">
+        <v>405</v>
+      </c>
+      <c r="D44" t="s">
+        <v>408</v>
+      </c>
+      <c r="E44" t="s">
+        <v>409</v>
+      </c>
+      <c r="F44" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C45" t="s">
+        <v>401</v>
+      </c>
+      <c r="D45" t="s">
+        <v>407</v>
+      </c>
+      <c r="E45" t="s">
+        <v>411</v>
+      </c>
+      <c r="F45" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C47" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="51" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C51" t="s">
+        <v>398</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="C39:C40"/>
+    <mergeCell ref="B36:B41"/>
     <mergeCell ref="B6:B30"/>
     <mergeCell ref="C11:C13"/>
     <mergeCell ref="C15:C18"/>

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFC6153-091F-41EA-8670-7F5FC6AB5D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C53825F-D49D-4FC4-BF9B-38BC0B83CDC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{F425FBA8-E65A-4F03-9270-551F3EA7C4F5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="393">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1576,6 +1576,14 @@
   </si>
   <si>
     <t>有安卓设备</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家修改头像</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家修改昵称</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1740,7 +1748,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1768,6 +1776,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1777,15 +1791,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1794,6 +1799,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2109,7 +2120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DF7E13A-4D63-4E82-9598-D598C8858D86}">
-  <dimension ref="A1:I143"/>
+  <dimension ref="A1:I145"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
@@ -2153,10 +2164,10 @@
       <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="17" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="4" t="s">
@@ -2178,8 +2189,8 @@
       <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
       <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
@@ -2199,8 +2210,8 @@
       <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
       <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
@@ -2220,8 +2231,8 @@
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13" t="s">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="4" t="s">
@@ -2243,8 +2254,8 @@
       <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
       <c r="D6" s="4" t="s">
         <v>309</v>
       </c>
@@ -2264,8 +2275,8 @@
       <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
       <c r="D7" s="4" t="s">
         <v>16</v>
       </c>
@@ -2285,7 +2296,7 @@
       <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="13"/>
+      <c r="B8" s="17"/>
       <c r="C8" s="7" t="s">
         <v>32</v>
       </c>
@@ -2308,8 +2319,8 @@
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13" t="s">
+      <c r="B9" s="17"/>
+      <c r="C9" s="17" t="s">
         <v>17</v>
       </c>
       <c r="D9" s="4" t="s">
@@ -2333,8 +2344,8 @@
       <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
       <c r="D10" s="4" t="s">
         <v>19</v>
       </c>
@@ -2354,8 +2365,8 @@
       <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
       <c r="D11" s="4" t="s">
         <v>20</v>
       </c>
@@ -2375,7 +2386,7 @@
       <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="13"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="7" t="s">
         <v>44</v>
       </c>
@@ -2398,7 +2409,7 @@
       <c r="A13" s="4">
         <v>12</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="17" t="s">
         <v>21</v>
       </c>
       <c r="C13" s="7" t="s">
@@ -2423,7 +2434,7 @@
       <c r="A14" s="4">
         <v>13</v>
       </c>
-      <c r="B14" s="13"/>
+      <c r="B14" s="17"/>
       <c r="C14" s="7" t="s">
         <v>24</v>
       </c>
@@ -2446,7 +2457,7 @@
       <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="13"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="7" t="s">
         <v>27</v>
       </c>
@@ -2469,7 +2480,7 @@
       <c r="A16" s="4">
         <v>15</v>
       </c>
-      <c r="B16" s="13"/>
+      <c r="B16" s="17"/>
       <c r="C16" s="7" t="s">
         <v>26</v>
       </c>
@@ -2492,10 +2503,10 @@
       <c r="A17" s="4">
         <v>16</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="17" t="s">
         <v>30</v>
       </c>
       <c r="D17" s="4" t="s">
@@ -2517,8 +2528,8 @@
       <c r="A18" s="4">
         <v>17</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
       <c r="D18" s="4" t="s">
         <v>12</v>
       </c>
@@ -2538,8 +2549,8 @@
       <c r="A19" s="4">
         <v>18</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
       <c r="D19" s="4" t="s">
         <v>13</v>
       </c>
@@ -2559,7 +2570,7 @@
       <c r="A20" s="4">
         <v>19</v>
       </c>
-      <c r="B20" s="13"/>
+      <c r="B20" s="17"/>
       <c r="C20" s="7" t="s">
         <v>233</v>
       </c>
@@ -2582,7 +2593,7 @@
       <c r="A21" s="4">
         <v>20</v>
       </c>
-      <c r="B21" s="13"/>
+      <c r="B21" s="17"/>
       <c r="C21" s="7" t="s">
         <v>37</v>
       </c>
@@ -2605,7 +2616,7 @@
       <c r="A22" s="4">
         <v>21</v>
       </c>
-      <c r="B22" s="13"/>
+      <c r="B22" s="17"/>
       <c r="C22" s="7" t="s">
         <v>36</v>
       </c>
@@ -2628,7 +2639,7 @@
       <c r="A23" s="4">
         <v>22</v>
       </c>
-      <c r="B23" s="13"/>
+      <c r="B23" s="17"/>
       <c r="C23" s="7" t="s">
         <v>34</v>
       </c>
@@ -2651,8 +2662,8 @@
       <c r="A24" s="4">
         <v>23</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13" t="s">
+      <c r="B24" s="17"/>
+      <c r="C24" s="17" t="s">
         <v>31</v>
       </c>
       <c r="D24" s="4" t="s">
@@ -2674,8 +2685,8 @@
       <c r="A25" s="4">
         <v>24</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
       <c r="D25" s="4" t="s">
         <v>19</v>
       </c>
@@ -2695,8 +2706,8 @@
       <c r="A26" s="4">
         <v>25</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
       <c r="D26" s="4" t="s">
         <v>20</v>
       </c>
@@ -2716,8 +2727,8 @@
       <c r="A27" s="4">
         <v>26</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13" t="s">
+      <c r="B27" s="17"/>
+      <c r="C27" s="17" t="s">
         <v>44</v>
       </c>
       <c r="D27" s="4" t="s">
@@ -2739,8 +2750,8 @@
       <c r="A28" s="4">
         <v>27</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
       <c r="D28" s="6" t="s">
         <v>227</v>
       </c>
@@ -2760,7 +2771,7 @@
       <c r="A29" s="4">
         <v>28</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="17" t="s">
         <v>39</v>
       </c>
       <c r="C29" s="7" t="s">
@@ -2785,7 +2796,7 @@
       <c r="A30" s="4">
         <v>29</v>
       </c>
-      <c r="B30" s="13"/>
+      <c r="B30" s="17"/>
       <c r="C30" s="7" t="s">
         <v>42</v>
       </c>
@@ -2808,7 +2819,7 @@
       <c r="A31" s="4">
         <v>30</v>
       </c>
-      <c r="B31" s="13"/>
+      <c r="B31" s="17"/>
       <c r="C31" s="7" t="s">
         <v>43</v>
       </c>
@@ -2831,8 +2842,8 @@
       <c r="A32" s="4">
         <v>31</v>
       </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13" t="s">
+      <c r="B32" s="17"/>
+      <c r="C32" s="17" t="s">
         <v>50</v>
       </c>
       <c r="D32" s="4" t="s">
@@ -2854,8 +2865,8 @@
       <c r="A33" s="4">
         <v>32</v>
       </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
       <c r="D33" s="4" t="s">
         <v>48</v>
       </c>
@@ -2875,8 +2886,8 @@
       <c r="A34" s="4">
         <v>33</v>
       </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
       <c r="D34" s="4" t="s">
         <v>49</v>
       </c>
@@ -2896,8 +2907,8 @@
       <c r="A35" s="4">
         <v>34</v>
       </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13" t="s">
+      <c r="B35" s="17"/>
+      <c r="C35" s="17" t="s">
         <v>46</v>
       </c>
       <c r="D35" s="4" t="s">
@@ -2919,8 +2930,8 @@
       <c r="A36" s="4">
         <v>35</v>
       </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
       <c r="D36" s="4" t="s">
         <v>390</v>
       </c>
@@ -2940,7 +2951,7 @@
       <c r="A37" s="4">
         <v>36</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="17" t="s">
         <v>246</v>
       </c>
       <c r="C37" s="7" t="s">
@@ -2963,7 +2974,7 @@
       <c r="A38" s="4">
         <v>37</v>
       </c>
-      <c r="B38" s="13"/>
+      <c r="B38" s="17"/>
       <c r="C38" s="7" t="s">
         <v>266</v>
       </c>
@@ -2984,7 +2995,7 @@
       <c r="A39" s="4">
         <v>38</v>
       </c>
-      <c r="B39" s="13"/>
+      <c r="B39" s="17"/>
       <c r="C39" s="7" t="s">
         <v>266</v>
       </c>
@@ -3005,7 +3016,7 @@
       <c r="A40" s="4">
         <v>39</v>
       </c>
-      <c r="B40" s="13"/>
+      <c r="B40" s="17"/>
       <c r="C40" s="7" t="s">
         <v>267</v>
       </c>
@@ -3026,8 +3037,8 @@
       <c r="A41" s="4">
         <v>40</v>
       </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13" t="s">
+      <c r="B41" s="17"/>
+      <c r="C41" s="17" t="s">
         <v>260</v>
       </c>
       <c r="D41" s="5" t="s">
@@ -3047,8 +3058,8 @@
       <c r="A42" s="4">
         <v>41</v>
       </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
       <c r="D42" s="5" t="s">
         <v>268</v>
       </c>
@@ -3066,8 +3077,8 @@
       <c r="A43" s="4">
         <v>42</v>
       </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="17"/>
       <c r="D43" s="5" t="s">
         <v>268</v>
       </c>
@@ -3085,7 +3096,7 @@
       <c r="A44" s="4">
         <v>43</v>
       </c>
-      <c r="B44" s="13"/>
+      <c r="B44" s="17"/>
       <c r="C44" s="7" t="s">
         <v>273</v>
       </c>
@@ -3106,8 +3117,8 @@
       <c r="A45" s="4">
         <v>44</v>
       </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13" t="s">
+      <c r="B45" s="17"/>
+      <c r="C45" s="17" t="s">
         <v>261</v>
       </c>
       <c r="D45" s="5" t="s">
@@ -3127,8 +3138,8 @@
       <c r="A46" s="4">
         <v>45</v>
       </c>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
       <c r="D46" s="5" t="s">
         <v>276</v>
       </c>
@@ -3146,8 +3157,8 @@
       <c r="A47" s="4">
         <v>46</v>
       </c>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
       <c r="D47" s="5" t="s">
         <v>276</v>
       </c>
@@ -3165,8 +3176,8 @@
       <c r="A48" s="4">
         <v>47</v>
       </c>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
       <c r="D48" s="5" t="s">
         <v>276</v>
       </c>
@@ -3184,8 +3195,8 @@
       <c r="A49" s="4">
         <v>48</v>
       </c>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13" t="s">
+      <c r="B49" s="17"/>
+      <c r="C49" s="17" t="s">
         <v>262</v>
       </c>
       <c r="D49" s="5" t="s">
@@ -3205,8 +3216,8 @@
       <c r="A50" s="4">
         <v>49</v>
       </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
       <c r="D50" s="5" t="s">
         <v>276</v>
       </c>
@@ -3224,8 +3235,8 @@
       <c r="A51" s="4">
         <v>50</v>
       </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="13"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="17"/>
       <c r="D51" s="5" t="s">
         <v>276</v>
       </c>
@@ -3243,8 +3254,8 @@
       <c r="A52" s="4">
         <v>51</v>
       </c>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13" t="s">
+      <c r="B52" s="17"/>
+      <c r="C52" s="17" t="s">
         <v>263</v>
       </c>
       <c r="D52" s="5" t="s">
@@ -3264,8 +3275,8 @@
       <c r="A53" s="4">
         <v>52</v>
       </c>
-      <c r="B53" s="13"/>
-      <c r="C53" s="13"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="17"/>
       <c r="D53" s="5" t="s">
         <v>286</v>
       </c>
@@ -3283,8 +3294,8 @@
       <c r="A54" s="4">
         <v>53</v>
       </c>
-      <c r="B54" s="13"/>
-      <c r="C54" s="13"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
       <c r="D54" s="5" t="s">
         <v>286</v>
       </c>
@@ -3302,8 +3313,8 @@
       <c r="A55" s="4">
         <v>54</v>
       </c>
-      <c r="B55" s="13"/>
-      <c r="C55" s="13"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="17"/>
       <c r="D55" s="5" t="s">
         <v>286</v>
       </c>
@@ -3321,8 +3332,8 @@
       <c r="A56" s="4">
         <v>55</v>
       </c>
-      <c r="B56" s="13"/>
-      <c r="C56" s="13"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
       <c r="D56" s="5" t="s">
         <v>286</v>
       </c>
@@ -3340,8 +3351,8 @@
       <c r="A57" s="4">
         <v>56</v>
       </c>
-      <c r="B57" s="13"/>
-      <c r="C57" s="13"/>
+      <c r="B57" s="17"/>
+      <c r="C57" s="17"/>
       <c r="D57" s="5" t="s">
         <v>286</v>
       </c>
@@ -3359,7 +3370,7 @@
       <c r="A58" s="4">
         <v>57</v>
       </c>
-      <c r="B58" s="13"/>
+      <c r="B58" s="17"/>
       <c r="C58" s="7" t="s">
         <v>299</v>
       </c>
@@ -3380,8 +3391,8 @@
       <c r="A59" s="4">
         <v>58</v>
       </c>
-      <c r="B59" s="13"/>
-      <c r="C59" s="13" t="s">
+      <c r="B59" s="17"/>
+      <c r="C59" s="17" t="s">
         <v>264</v>
       </c>
       <c r="D59" s="5" t="s">
@@ -3401,8 +3412,8 @@
       <c r="A60" s="4">
         <v>59</v>
       </c>
-      <c r="B60" s="13"/>
-      <c r="C60" s="13"/>
+      <c r="B60" s="17"/>
+      <c r="C60" s="17"/>
       <c r="D60" s="5" t="s">
         <v>302</v>
       </c>
@@ -3443,7 +3454,7 @@
       <c r="A62" s="4">
         <v>61</v>
       </c>
-      <c r="B62" s="13" t="s">
+      <c r="B62" s="17" t="s">
         <v>310</v>
       </c>
       <c r="C62" s="7" t="s">
@@ -3468,7 +3479,7 @@
       <c r="A63" s="4">
         <v>62</v>
       </c>
-      <c r="B63" s="13"/>
+      <c r="B63" s="17"/>
       <c r="C63" s="7" t="s">
         <v>312</v>
       </c>
@@ -3491,7 +3502,7 @@
       <c r="A64" s="4">
         <v>63</v>
       </c>
-      <c r="B64" s="13"/>
+      <c r="B64" s="17"/>
       <c r="C64" s="7" t="s">
         <v>315</v>
       </c>
@@ -3514,8 +3525,8 @@
       <c r="A65" s="4">
         <v>64</v>
       </c>
-      <c r="B65" s="13"/>
-      <c r="C65" s="13" t="s">
+      <c r="B65" s="17"/>
+      <c r="C65" s="17" t="s">
         <v>316</v>
       </c>
       <c r="D65" s="4" t="s">
@@ -3539,8 +3550,8 @@
       <c r="A66" s="4">
         <v>65</v>
       </c>
-      <c r="B66" s="13"/>
-      <c r="C66" s="13"/>
+      <c r="B66" s="17"/>
+      <c r="C66" s="17"/>
       <c r="D66" s="4" t="s">
         <v>321</v>
       </c>
@@ -3560,7 +3571,7 @@
       <c r="A67" s="4">
         <v>66</v>
       </c>
-      <c r="B67" s="13"/>
+      <c r="B67" s="17"/>
       <c r="C67" s="7" t="s">
         <v>323</v>
       </c>
@@ -3583,7 +3594,7 @@
       <c r="A68" s="4">
         <v>67</v>
       </c>
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="18" t="s">
         <v>347</v>
       </c>
       <c r="C68" s="7" t="s">
@@ -3608,7 +3619,7 @@
       <c r="A69" s="4">
         <v>68</v>
       </c>
-      <c r="B69" s="12"/>
+      <c r="B69" s="18"/>
       <c r="C69" s="7" t="s">
         <v>306</v>
       </c>
@@ -3631,7 +3642,7 @@
       <c r="A70" s="4">
         <v>69</v>
       </c>
-      <c r="B70" s="12"/>
+      <c r="B70" s="18"/>
       <c r="C70" s="7" t="s">
         <v>351</v>
       </c>
@@ -3654,7 +3665,7 @@
       <c r="A71" s="4">
         <v>70</v>
       </c>
-      <c r="B71" s="12"/>
+      <c r="B71" s="18"/>
       <c r="C71" s="7" t="s">
         <v>129</v>
       </c>
@@ -3677,7 +3688,7 @@
       <c r="A72" s="4">
         <v>71</v>
       </c>
-      <c r="B72" s="9" t="s">
+      <c r="B72" s="11" t="s">
         <v>327</v>
       </c>
       <c r="C72" s="7" t="s">
@@ -3702,7 +3713,7 @@
       <c r="A73" s="4">
         <v>72</v>
       </c>
-      <c r="B73" s="10"/>
+      <c r="B73" s="12"/>
       <c r="C73" s="7" t="s">
         <v>334</v>
       </c>
@@ -3725,7 +3736,7 @@
       <c r="A74" s="4">
         <v>73</v>
       </c>
-      <c r="B74" s="10"/>
+      <c r="B74" s="12"/>
       <c r="C74" s="7" t="s">
         <v>330</v>
       </c>
@@ -3748,8 +3759,8 @@
       <c r="A75" s="4">
         <v>74</v>
       </c>
-      <c r="B75" s="10"/>
-      <c r="C75" s="9" t="s">
+      <c r="B75" s="12"/>
+      <c r="C75" s="11" t="s">
         <v>328</v>
       </c>
       <c r="D75" s="4" t="s">
@@ -3771,8 +3782,8 @@
       <c r="A76" s="4">
         <v>75</v>
       </c>
-      <c r="B76" s="10"/>
-      <c r="C76" s="10"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="12"/>
       <c r="D76" s="4" t="s">
         <v>354</v>
       </c>
@@ -3792,8 +3803,8 @@
       <c r="A77" s="4">
         <v>76</v>
       </c>
-      <c r="B77" s="11"/>
-      <c r="C77" s="11"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="13"/>
       <c r="D77" s="4" t="s">
         <v>344</v>
       </c>
@@ -3813,7 +3824,7 @@
       <c r="A78" s="4">
         <v>77</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="B78" s="11" t="s">
         <v>342</v>
       </c>
       <c r="C78" s="7" t="s">
@@ -3838,7 +3849,7 @@
       <c r="A79" s="4">
         <v>78</v>
       </c>
-      <c r="B79" s="10"/>
+      <c r="B79" s="12"/>
       <c r="C79" s="7" t="s">
         <v>51</v>
       </c>
@@ -3861,7 +3872,7 @@
       <c r="A80" s="4">
         <v>79</v>
       </c>
-      <c r="B80" s="10"/>
+      <c r="B80" s="12"/>
       <c r="C80" s="7" t="s">
         <v>53</v>
       </c>
@@ -3884,7 +3895,7 @@
       <c r="A81" s="4">
         <v>80</v>
       </c>
-      <c r="B81" s="10"/>
+      <c r="B81" s="12"/>
       <c r="C81" s="7" t="s">
         <v>54</v>
       </c>
@@ -3907,7 +3918,7 @@
       <c r="A82" s="4">
         <v>81</v>
       </c>
-      <c r="B82" s="11"/>
+      <c r="B82" s="13"/>
       <c r="C82" s="7" t="s">
         <v>55</v>
       </c>
@@ -3930,10 +3941,10 @@
       <c r="A83" s="4">
         <v>82</v>
       </c>
-      <c r="B83" s="13" t="s">
+      <c r="B83" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="C83" s="13" t="s">
+      <c r="C83" s="17" t="s">
         <v>61</v>
       </c>
       <c r="D83" s="4" t="s">
@@ -3955,8 +3966,8 @@
       <c r="A84" s="4">
         <v>83</v>
       </c>
-      <c r="B84" s="13"/>
-      <c r="C84" s="13"/>
+      <c r="B84" s="17"/>
+      <c r="C84" s="17"/>
       <c r="D84" s="4" t="s">
         <v>63</v>
       </c>
@@ -3976,10 +3987,10 @@
       <c r="A85" s="4">
         <v>84</v>
       </c>
-      <c r="B85" s="9" t="s">
+      <c r="B85" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="C85" s="13" t="s">
+      <c r="C85" s="17" t="s">
         <v>358</v>
       </c>
       <c r="D85" s="4" t="s">
@@ -4001,8 +4012,8 @@
       <c r="A86" s="4">
         <v>85</v>
       </c>
-      <c r="B86" s="10"/>
-      <c r="C86" s="13"/>
+      <c r="B86" s="12"/>
+      <c r="C86" s="17"/>
       <c r="D86" s="4" t="s">
         <v>58</v>
       </c>
@@ -4022,8 +4033,8 @@
       <c r="A87" s="4">
         <v>86</v>
       </c>
-      <c r="B87" s="11"/>
-      <c r="C87" s="13"/>
+      <c r="B87" s="13"/>
+      <c r="C87" s="17"/>
       <c r="D87" s="4" t="s">
         <v>59</v>
       </c>
@@ -4068,10 +4079,10 @@
       <c r="A89" s="4">
         <v>88</v>
       </c>
-      <c r="B89" s="13" t="s">
+      <c r="B89" s="17" t="s">
         <v>341</v>
       </c>
-      <c r="C89" s="13" t="s">
+      <c r="C89" s="17" t="s">
         <v>377</v>
       </c>
       <c r="D89" s="4" t="s">
@@ -4093,8 +4104,8 @@
       <c r="A90" s="4">
         <v>89</v>
       </c>
-      <c r="B90" s="13"/>
-      <c r="C90" s="13"/>
+      <c r="B90" s="17"/>
+      <c r="C90" s="17"/>
       <c r="D90" s="4" t="s">
         <v>65</v>
       </c>
@@ -4114,8 +4125,8 @@
       <c r="A91" s="4">
         <v>90</v>
       </c>
-      <c r="B91" s="13"/>
-      <c r="C91" s="13"/>
+      <c r="B91" s="17"/>
+      <c r="C91" s="17"/>
       <c r="D91" s="4" t="s">
         <v>66</v>
       </c>
@@ -4135,8 +4146,8 @@
       <c r="A92" s="4">
         <v>91</v>
       </c>
-      <c r="B92" s="13"/>
-      <c r="C92" s="13" t="s">
+      <c r="B92" s="17"/>
+      <c r="C92" s="17" t="s">
         <v>359</v>
       </c>
       <c r="D92" s="4" t="s">
@@ -4158,8 +4169,8 @@
       <c r="A93" s="4">
         <v>92</v>
       </c>
-      <c r="B93" s="13"/>
-      <c r="C93" s="13"/>
+      <c r="B93" s="17"/>
+      <c r="C93" s="17"/>
       <c r="D93" s="4" t="s">
         <v>70</v>
       </c>
@@ -4179,8 +4190,8 @@
       <c r="A94" s="4">
         <v>93</v>
       </c>
-      <c r="B94" s="13"/>
-      <c r="C94" s="13"/>
+      <c r="B94" s="17"/>
+      <c r="C94" s="17"/>
       <c r="D94" s="4" t="s">
         <v>73</v>
       </c>
@@ -4200,7 +4211,7 @@
       <c r="A95" s="4">
         <v>94</v>
       </c>
-      <c r="B95" s="9" t="s">
+      <c r="B95" s="11" t="s">
         <v>76</v>
       </c>
       <c r="C95" s="7" t="s">
@@ -4225,8 +4236,8 @@
       <c r="A96" s="4">
         <v>95</v>
       </c>
-      <c r="B96" s="10"/>
-      <c r="C96" s="13" t="s">
+      <c r="B96" s="12"/>
+      <c r="C96" s="17" t="s">
         <v>378</v>
       </c>
       <c r="D96" s="4" t="s">
@@ -4248,8 +4259,8 @@
       <c r="A97" s="4">
         <v>96</v>
       </c>
-      <c r="B97" s="10"/>
-      <c r="C97" s="13"/>
+      <c r="B97" s="12"/>
+      <c r="C97" s="17"/>
       <c r="D97" s="4" t="s">
         <v>78</v>
       </c>
@@ -4269,8 +4280,8 @@
       <c r="A98" s="4">
         <v>97</v>
       </c>
-      <c r="B98" s="10"/>
-      <c r="C98" s="13"/>
+      <c r="B98" s="12"/>
+      <c r="C98" s="17"/>
       <c r="D98" s="4" t="s">
         <v>79</v>
       </c>
@@ -4290,8 +4301,8 @@
       <c r="A99" s="4">
         <v>98</v>
       </c>
-      <c r="B99" s="10"/>
-      <c r="C99" s="13" t="s">
+      <c r="B99" s="12"/>
+      <c r="C99" s="17" t="s">
         <v>81</v>
       </c>
       <c r="D99" s="4" t="s">
@@ -4313,8 +4324,8 @@
       <c r="A100" s="4">
         <v>99</v>
       </c>
-      <c r="B100" s="10"/>
-      <c r="C100" s="13"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="17"/>
       <c r="D100" s="4" t="s">
         <v>87</v>
       </c>
@@ -4334,8 +4345,8 @@
       <c r="A101" s="4">
         <v>100</v>
       </c>
-      <c r="B101" s="10"/>
-      <c r="C101" s="13" t="s">
+      <c r="B101" s="12"/>
+      <c r="C101" s="17" t="s">
         <v>379</v>
       </c>
       <c r="D101" s="4" t="s">
@@ -4357,8 +4368,8 @@
       <c r="A102" s="4">
         <v>101</v>
       </c>
-      <c r="B102" s="10"/>
-      <c r="C102" s="13"/>
+      <c r="B102" s="12"/>
+      <c r="C102" s="17"/>
       <c r="D102" s="4" t="s">
         <v>96</v>
       </c>
@@ -4378,8 +4389,8 @@
       <c r="A103" s="4">
         <v>102</v>
       </c>
-      <c r="B103" s="10"/>
-      <c r="C103" s="13"/>
+      <c r="B103" s="12"/>
+      <c r="C103" s="17"/>
       <c r="D103" s="4" t="s">
         <v>97</v>
       </c>
@@ -4396,65 +4407,47 @@
       <c r="I103" s="4"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="4">
-        <v>103</v>
-      </c>
-      <c r="B104" s="10"/>
-      <c r="C104" s="13" t="s">
-        <v>84</v>
-      </c>
+      <c r="A104" s="4"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="9"/>
       <c r="D104" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E104" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="F104" s="4" t="s">
-        <v>85</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4"/>
       <c r="G104" s="4"/>
-      <c r="H104" s="4" t="s">
-        <v>142</v>
-      </c>
+      <c r="H104" s="4"/>
       <c r="I104" s="4"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="4">
-        <v>104</v>
-      </c>
-      <c r="B105" s="10"/>
-      <c r="C105" s="13"/>
+      <c r="A105" s="4"/>
+      <c r="B105" s="12"/>
+      <c r="C105" s="9"/>
       <c r="D105" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>86</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="E105" s="4"/>
+      <c r="F105" s="4"/>
       <c r="G105" s="4"/>
-      <c r="H105" s="4" t="s">
-        <v>142</v>
-      </c>
+      <c r="H105" s="4"/>
       <c r="I105" s="4"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
-        <v>105</v>
-      </c>
-      <c r="B106" s="10"/>
-      <c r="C106" s="13" t="s">
-        <v>370</v>
+        <v>103</v>
+      </c>
+      <c r="B106" s="12"/>
+      <c r="C106" s="17" t="s">
+        <v>84</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>171</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>172</v>
+        <v>85</v>
       </c>
       <c r="G106" s="4"/>
       <c r="H106" s="4" t="s">
@@ -4464,33 +4457,35 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
-        <v>106</v>
-      </c>
-      <c r="B107" s="10"/>
-      <c r="C107" s="13"/>
+        <v>104</v>
+      </c>
+      <c r="B107" s="12"/>
+      <c r="C107" s="17"/>
       <c r="D107" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>171</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>172</v>
+        <v>86</v>
       </c>
       <c r="G107" s="4"/>
       <c r="H107" s="4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="I107" s="4"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
-        <v>107</v>
-      </c>
-      <c r="B108" s="10"/>
-      <c r="C108" s="13"/>
+        <v>105</v>
+      </c>
+      <c r="B108" s="12"/>
+      <c r="C108" s="17" t="s">
+        <v>370</v>
+      </c>
       <c r="D108" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>171</v>
@@ -4506,45 +4501,39 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
-        <v>108</v>
-      </c>
-      <c r="B109" s="11"/>
-      <c r="C109" s="7" t="s">
-        <v>380</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="B109" s="12"/>
+      <c r="C109" s="17"/>
       <c r="D109" s="4" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="E109" s="4" t="s">
         <v>171</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G109" s="4"/>
       <c r="H109" s="4" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="I109" s="4"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
-        <v>109</v>
-      </c>
-      <c r="B110" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="D110" s="8" t="s">
-        <v>383</v>
+        <v>107</v>
+      </c>
+      <c r="B110" s="12"/>
+      <c r="C110" s="17"/>
+      <c r="D110" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G110" s="4"/>
       <c r="H110" s="4" t="s">
@@ -4554,20 +4543,20 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
-        <v>110</v>
-      </c>
-      <c r="B111" s="16"/>
-      <c r="C111" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="D111" s="8" t="s">
-        <v>383</v>
+        <v>108</v>
+      </c>
+      <c r="B111" s="13"/>
+      <c r="C111" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="4" t="s">
@@ -4577,11 +4566,13 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
-        <v>111</v>
-      </c>
-      <c r="B112" s="16"/>
-      <c r="C112" s="4" t="s">
-        <v>89</v>
+        <v>109</v>
+      </c>
+      <c r="B112" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C112" s="9" t="s">
+        <v>218</v>
       </c>
       <c r="D112" s="8" t="s">
         <v>383</v>
@@ -4600,45 +4591,43 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
-        <v>112</v>
-      </c>
-      <c r="B113" s="17"/>
-      <c r="C113" s="4" t="s">
-        <v>101</v>
+        <v>110</v>
+      </c>
+      <c r="B113" s="15"/>
+      <c r="C113" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>231</v>
+        <v>176</v>
       </c>
       <c r="G113" s="4"/>
       <c r="H113" s="4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="I113" s="4"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="4">
-        <v>113</v>
-      </c>
-      <c r="B114" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C114" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="D114" s="4" t="s">
-        <v>92</v>
+        <v>111</v>
+      </c>
+      <c r="B114" s="15"/>
+      <c r="C114" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D114" s="8" t="s">
+        <v>383</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G114" s="4"/>
       <c r="H114" s="4" t="s">
@@ -4648,18 +4637,20 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
-        <v>114</v>
-      </c>
-      <c r="B115" s="13"/>
-      <c r="C115" s="13"/>
-      <c r="D115" s="4" t="s">
-        <v>91</v>
+        <v>112</v>
+      </c>
+      <c r="B115" s="16"/>
+      <c r="C115" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D115" s="8" t="s">
+        <v>384</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>90</v>
+        <v>231</v>
       </c>
       <c r="G115" s="4"/>
       <c r="H115" s="4" t="s">
@@ -4669,18 +4660,22 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
-        <v>115</v>
-      </c>
-      <c r="B116" s="13"/>
-      <c r="C116" s="13"/>
+        <v>113</v>
+      </c>
+      <c r="B116" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C116" s="17" t="s">
+        <v>94</v>
+      </c>
       <c r="D116" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E116" s="4" t="s">
         <v>177</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>90</v>
+        <v>178</v>
       </c>
       <c r="G116" s="4"/>
       <c r="H116" s="4" t="s">
@@ -4690,22 +4685,18 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
-        <v>116</v>
-      </c>
-      <c r="B117" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C117" s="7" t="s">
-        <v>371</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="B117" s="17"/>
+      <c r="C117" s="17"/>
       <c r="D117" s="4" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>179</v>
+        <v>90</v>
       </c>
       <c r="G117" s="4"/>
       <c r="H117" s="4" t="s">
@@ -4715,40 +4706,40 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="4">
-        <v>117</v>
-      </c>
-      <c r="B118" s="10"/>
-      <c r="C118" s="7" t="s">
-        <v>105</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="B118" s="17"/>
+      <c r="C118" s="17"/>
       <c r="D118" s="4" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>181</v>
+        <v>90</v>
       </c>
       <c r="G118" s="4"/>
       <c r="H118" s="4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="I118" s="4"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
-        <v>118</v>
-      </c>
-      <c r="B119" s="10"/>
+        <v>116</v>
+      </c>
+      <c r="B119" s="11" t="s">
+        <v>98</v>
+      </c>
       <c r="C119" s="7" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="F119" s="4" t="s">
         <v>179</v>
@@ -4761,20 +4752,20 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
-        <v>119</v>
-      </c>
-      <c r="B120" s="10"/>
+        <v>117</v>
+      </c>
+      <c r="B120" s="12"/>
       <c r="C120" s="7" t="s">
-        <v>381</v>
+        <v>105</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="4" t="s">
@@ -4784,20 +4775,20 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
-        <v>120</v>
-      </c>
-      <c r="B121" s="10"/>
+        <v>118</v>
+      </c>
+      <c r="B121" s="12"/>
       <c r="C121" s="7" t="s">
-        <v>103</v>
+        <v>382</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="G121" s="4"/>
       <c r="H121" s="4" t="s">
@@ -4807,41 +4798,43 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
-        <v>121</v>
-      </c>
-      <c r="B122" s="10"/>
-      <c r="C122" s="13" t="s">
-        <v>107</v>
+        <v>119</v>
+      </c>
+      <c r="B122" s="12"/>
+      <c r="C122" s="7" t="s">
+        <v>381</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>219</v>
+        <v>183</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="G122" s="4"/>
       <c r="H122" s="4" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="I122" s="4"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
-        <v>122</v>
-      </c>
-      <c r="B123" s="10"/>
-      <c r="C123" s="13"/>
+        <v>120</v>
+      </c>
+      <c r="B123" s="12"/>
+      <c r="C123" s="7" t="s">
+        <v>103</v>
+      </c>
       <c r="D123" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>219</v>
+        <v>185</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G123" s="4"/>
       <c r="H123" s="4" t="s">
@@ -4851,12 +4844,14 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="4">
-        <v>123</v>
-      </c>
-      <c r="B124" s="10"/>
-      <c r="C124" s="13"/>
+        <v>121</v>
+      </c>
+      <c r="B124" s="12"/>
+      <c r="C124" s="17" t="s">
+        <v>107</v>
+      </c>
       <c r="D124" s="4" t="s">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="E124" s="4" t="s">
         <v>219</v>
@@ -4872,56 +4867,56 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
-        <v>124</v>
-      </c>
-      <c r="B125" s="10"/>
-      <c r="C125" s="13" t="s">
-        <v>116</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="B125" s="12"/>
+      <c r="C125" s="17"/>
       <c r="D125" s="4" t="s">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="G125" s="4"/>
       <c r="H125" s="4" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="I125" s="4"/>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="4">
-        <v>125</v>
-      </c>
-      <c r="B126" s="10"/>
-      <c r="C126" s="13"/>
+        <v>123</v>
+      </c>
+      <c r="B126" s="12"/>
+      <c r="C126" s="17"/>
       <c r="D126" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="G126" s="4"/>
       <c r="H126" s="4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="I126" s="4"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
-        <v>126</v>
-      </c>
-      <c r="B127" s="10"/>
-      <c r="C127" s="13"/>
+        <v>124</v>
+      </c>
+      <c r="B127" s="12"/>
+      <c r="C127" s="17" t="s">
+        <v>116</v>
+      </c>
       <c r="D127" s="4" t="s">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="E127" s="4" t="s">
         <v>182</v>
@@ -4937,146 +4932,146 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="4">
-        <v>127</v>
-      </c>
-      <c r="B128" s="10"/>
-      <c r="C128" s="13" t="s">
-        <v>117</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="B128" s="12"/>
+      <c r="C128" s="17"/>
       <c r="D128" s="4" t="s">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="G128" s="4"/>
       <c r="H128" s="4" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="I128" s="4"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
-        <v>128</v>
-      </c>
-      <c r="B129" s="10"/>
-      <c r="C129" s="13"/>
+        <v>126</v>
+      </c>
+      <c r="B129" s="12"/>
+      <c r="C129" s="17"/>
       <c r="D129" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="G129" s="4"/>
       <c r="H129" s="4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="I129" s="4"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
-        <v>129</v>
-      </c>
-      <c r="B130" s="11"/>
-      <c r="C130" s="13"/>
+        <v>127</v>
+      </c>
+      <c r="B130" s="12"/>
+      <c r="C130" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="D130" s="4" t="s">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="E130" s="4" t="s">
         <v>187</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G130" s="4"/>
       <c r="H130" s="4" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I130" s="4"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="4">
-        <v>130</v>
-      </c>
-      <c r="B131" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C131" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="D131" s="8" t="s">
-        <v>376</v>
+        <v>128</v>
+      </c>
+      <c r="B131" s="12"/>
+      <c r="C131" s="17"/>
+      <c r="D131" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G131" s="4"/>
       <c r="H131" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I131" s="4"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="4">
-        <v>131</v>
-      </c>
-      <c r="B132" s="10"/>
-      <c r="C132" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="D132" t="s">
-        <v>372</v>
+        <v>129</v>
+      </c>
+      <c r="B132" s="13"/>
+      <c r="C132" s="17"/>
+      <c r="D132" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G132" s="4"/>
       <c r="H132" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="I132" s="4"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
-        <v>132</v>
-      </c>
-      <c r="B133" s="10"/>
-      <c r="C133" s="10"/>
-      <c r="D133" t="s">
-        <v>373</v>
+        <v>130</v>
+      </c>
+      <c r="B133" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D133" s="8" t="s">
+        <v>376</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G133" s="4"/>
       <c r="H133" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I133" s="4"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
-        <v>133</v>
-      </c>
-      <c r="B134" s="11"/>
-      <c r="C134" s="11"/>
+        <v>131</v>
+      </c>
+      <c r="B134" s="12"/>
+      <c r="C134" s="11" t="s">
+        <v>375</v>
+      </c>
       <c r="D134" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E134" s="4" t="s">
         <v>220</v>
@@ -5086,28 +5081,24 @@
       </c>
       <c r="G134" s="4"/>
       <c r="H134" s="4" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I134" s="4"/>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
-        <v>134</v>
-      </c>
-      <c r="B135" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C135" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="D135" s="4" t="s">
-        <v>114</v>
+        <v>132</v>
+      </c>
+      <c r="B135" s="12"/>
+      <c r="C135" s="12"/>
+      <c r="D135" t="s">
+        <v>373</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G135" s="4"/>
       <c r="H135" s="4" t="s">
@@ -5117,45 +5108,43 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B136" s="13"/>
-      <c r="C136" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="D136" s="4" t="s">
-        <v>118</v>
+      <c r="C136" s="13"/>
+      <c r="D136" t="s">
+        <v>374</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G136" s="4"/>
       <c r="H136" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I136" s="4"/>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
-        <v>136</v>
-      </c>
-      <c r="B137" s="7" t="s">
-        <v>120</v>
+        <v>134</v>
+      </c>
+      <c r="B137" s="17" t="s">
+        <v>112</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E137" s="4" t="s">
         <v>221</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G137" s="4"/>
       <c r="H137" s="4" t="s">
@@ -5165,43 +5154,45 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="4">
-        <v>137</v>
-      </c>
-      <c r="B138" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="C138" s="13" t="s">
-        <v>123</v>
+        <v>135</v>
+      </c>
+      <c r="B138" s="17"/>
+      <c r="C138" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E138" s="4" t="s">
         <v>221</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G138" s="4"/>
       <c r="H138" s="4" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="I138" s="4"/>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
-        <v>138</v>
-      </c>
-      <c r="B139" s="13"/>
-      <c r="C139" s="13"/>
+        <v>136</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>119</v>
+      </c>
       <c r="D139" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E139" s="4" t="s">
         <v>221</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G139" s="4"/>
       <c r="H139" s="4" t="s">
@@ -5211,41 +5202,43 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="4">
-        <v>139</v>
-      </c>
-      <c r="B140" s="13"/>
-      <c r="C140" s="13"/>
+        <v>137</v>
+      </c>
+      <c r="B140" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="C140" s="17" t="s">
+        <v>123</v>
+      </c>
       <c r="D140" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E140" s="4" t="s">
         <v>221</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G140" s="4"/>
       <c r="H140" s="4" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I140" s="4"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="4">
-        <v>140</v>
-      </c>
-      <c r="B141" s="13"/>
-      <c r="C141" s="13" t="s">
-        <v>26</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="B141" s="17"/>
+      <c r="C141" s="17"/>
       <c r="D141" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G141" s="4"/>
       <c r="H141" s="4" t="s">
@@ -5255,60 +5248,114 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="4">
-        <v>141</v>
-      </c>
-      <c r="B142" s="13"/>
-      <c r="C142" s="13"/>
+        <v>139</v>
+      </c>
+      <c r="B142" s="17"/>
+      <c r="C142" s="17"/>
       <c r="D142" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G142" s="4"/>
       <c r="H142" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="I142" s="4"/>
     </row>
-    <row r="143" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
-        <v>142</v>
-      </c>
-      <c r="B143" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="C143" s="14" t="s">
-        <v>202</v>
+        <v>140</v>
+      </c>
+      <c r="B143" s="17"/>
+      <c r="C143" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>203</v>
+        <v>127</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="G143" s="4"/>
       <c r="H143" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="I143" s="4"/>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" s="4">
+        <v>141</v>
+      </c>
+      <c r="B144" s="17"/>
+      <c r="C144" s="17"/>
+      <c r="D144" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E144" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="G144" s="4"/>
+      <c r="H144" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="I143" s="4"/>
+      <c r="I144" s="4"/>
+    </row>
+    <row r="145" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A145" s="4">
+        <v>142</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C145" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E145" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G145" s="4"/>
+      <c r="H145" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I145" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="C132:C134"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="B95:B109"/>
-    <mergeCell ref="C45:C48"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="C52:C57"/>
-    <mergeCell ref="B37:B60"/>
+    <mergeCell ref="C143:C144"/>
+    <mergeCell ref="B140:B144"/>
+    <mergeCell ref="B68:B71"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="C140:C142"/>
+    <mergeCell ref="C127:C129"/>
+    <mergeCell ref="C130:C132"/>
+    <mergeCell ref="C116:C118"/>
+    <mergeCell ref="B116:B118"/>
+    <mergeCell ref="C101:C103"/>
+    <mergeCell ref="B133:B136"/>
+    <mergeCell ref="C96:C98"/>
+    <mergeCell ref="C85:C87"/>
+    <mergeCell ref="B72:B77"/>
+    <mergeCell ref="C75:C77"/>
+    <mergeCell ref="B119:B132"/>
+    <mergeCell ref="B78:B82"/>
+    <mergeCell ref="B85:B87"/>
     <mergeCell ref="B2:B12"/>
     <mergeCell ref="C83:C84"/>
     <mergeCell ref="B83:B84"/>
@@ -5325,32 +5372,22 @@
     <mergeCell ref="B29:B36"/>
     <mergeCell ref="C65:C66"/>
     <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C134:C136"/>
+    <mergeCell ref="B112:B115"/>
+    <mergeCell ref="B95:B111"/>
+    <mergeCell ref="C45:C48"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="C52:C57"/>
+    <mergeCell ref="B37:B60"/>
     <mergeCell ref="B62:B67"/>
-    <mergeCell ref="C122:C124"/>
+    <mergeCell ref="C124:C126"/>
     <mergeCell ref="C99:C100"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="C106:C108"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="C108:C110"/>
     <mergeCell ref="C89:C91"/>
     <mergeCell ref="C92:C94"/>
     <mergeCell ref="B89:B94"/>
-    <mergeCell ref="C96:C98"/>
-    <mergeCell ref="C85:C87"/>
-    <mergeCell ref="B72:B77"/>
-    <mergeCell ref="C75:C77"/>
-    <mergeCell ref="B117:B130"/>
-    <mergeCell ref="B78:B82"/>
-    <mergeCell ref="B85:B87"/>
-    <mergeCell ref="C141:C142"/>
-    <mergeCell ref="B138:B142"/>
-    <mergeCell ref="B68:B71"/>
-    <mergeCell ref="B135:B136"/>
-    <mergeCell ref="C138:C140"/>
-    <mergeCell ref="C125:C127"/>
-    <mergeCell ref="C128:C130"/>
-    <mergeCell ref="C114:C116"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="C101:C103"/>
-    <mergeCell ref="B131:B134"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C53825F-D49D-4FC4-BF9B-38BC0B83CDC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA20DF98-B518-4A5C-9306-5C2B584F6773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{F425FBA8-E65A-4F03-9270-551F3EA7C4F5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="397">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1579,11 +1579,27 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>玩家修改头像</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>玩家修改昵称</t>
+    <t>点赞记录-记录同步</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间玩家修改头像</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间玩家修改昵称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>记录点赞前玩家昵称，然后修改点赞玩家昵称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>记录点赞前玩家头像，然后修改点赞玩家头像</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>同步正确</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4409,27 +4425,41 @@
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="4"/>
       <c r="B104" s="12"/>
-      <c r="C104" s="9"/>
+      <c r="C104" s="11" t="s">
+        <v>391</v>
+      </c>
       <c r="D104" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="E104" s="4"/>
-      <c r="F104" s="4"/>
+        <v>392</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>396</v>
+      </c>
       <c r="G104" s="4"/>
-      <c r="H104" s="4"/>
+      <c r="H104" s="4" t="s">
+        <v>142</v>
+      </c>
       <c r="I104" s="4"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="4"/>
       <c r="B105" s="12"/>
-      <c r="C105" s="9"/>
+      <c r="C105" s="13"/>
       <c r="D105" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="E105" s="4"/>
-      <c r="F105" s="4"/>
+        <v>393</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>396</v>
+      </c>
       <c r="G105" s="4"/>
-      <c r="H105" s="4"/>
+      <c r="H105" s="4" t="s">
+        <v>142</v>
+      </c>
       <c r="I105" s="4"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
@@ -5337,7 +5367,7 @@
       <c r="I145" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="50">
+  <mergeCells count="51">
     <mergeCell ref="C143:C144"/>
     <mergeCell ref="B140:B144"/>
     <mergeCell ref="B68:B71"/>
@@ -5349,6 +5379,7 @@
     <mergeCell ref="B116:B118"/>
     <mergeCell ref="C101:C103"/>
     <mergeCell ref="B133:B136"/>
+    <mergeCell ref="C104:C105"/>
     <mergeCell ref="C96:C98"/>
     <mergeCell ref="C85:C87"/>
     <mergeCell ref="B72:B77"/>

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA20DF98-B518-4A5C-9306-5C2B584F6773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8BB0308-4726-4C50-B085-8C470D76868A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{F425FBA8-E65A-4F03-9270-551F3EA7C4F5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="400">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -234,10 +234,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>分辨率测试</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>取得首胜但没有加分次数</t>
   </si>
   <si>
@@ -1523,10 +1519,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>点赞次数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>不同渠道的点赞</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1600,6 +1592,26 @@
   </si>
   <si>
     <t>同步正确</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点赞任务-条件：点赞次数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点赞任务-点赞奖励重复获得</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改点赞次数为40/60</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动在活动中心未开启</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动在活动中心开启</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1667,7 +1679,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1727,44 +1739,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1789,12 +1770,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1805,15 +1780,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2136,7 +2102,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DF7E13A-4D63-4E82-9598-D598C8858D86}">
-  <dimension ref="A1:I145"/>
+  <dimension ref="A1:I146"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
@@ -2180,24 +2146,24 @@
       <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="12" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>131</v>
+        <v>398</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I2" s="4"/>
     </row>
@@ -2205,20 +2171,20 @@
       <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
       <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>132</v>
+        <v>399</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I3" s="4"/>
     </row>
@@ -2226,20 +2192,20 @@
       <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
       <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>132</v>
+        <v>399</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I4" s="4"/>
     </row>
@@ -2247,22 +2213,22 @@
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17" t="s">
+      <c r="B5" s="12"/>
+      <c r="C5" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I5" s="4"/>
     </row>
@@ -2270,20 +2236,20 @@
       <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
       <c r="D6" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -2291,20 +2257,20 @@
       <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
       <c r="D7" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I7" s="4"/>
     </row>
@@ -2312,7 +2278,7 @@
       <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="17"/>
+      <c r="B8" s="12"/>
       <c r="C8" s="7" t="s">
         <v>32</v>
       </c>
@@ -2320,14 +2286,14 @@
         <v>33</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I8" s="4"/>
     </row>
@@ -2335,45 +2301,45 @@
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17" t="s">
+      <c r="B9" s="12"/>
+      <c r="C9" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
       <c r="D10" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I10" s="4"/>
     </row>
@@ -2381,20 +2347,20 @@
       <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
       <c r="D11" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I11" s="4"/>
     </row>
@@ -2402,7 +2368,7 @@
       <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="17"/>
+      <c r="B12" s="12"/>
       <c r="C12" s="7" t="s">
         <v>44</v>
       </c>
@@ -2410,14 +2376,14 @@
         <v>45</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I12" s="4"/>
     </row>
@@ -2425,7 +2391,7 @@
       <c r="A13" s="4">
         <v>12</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C13" s="7" t="s">
@@ -2435,14 +2401,14 @@
         <v>23</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I13" s="4"/>
     </row>
@@ -2450,7 +2416,7 @@
       <c r="A14" s="4">
         <v>13</v>
       </c>
-      <c r="B14" s="17"/>
+      <c r="B14" s="12"/>
       <c r="C14" s="7" t="s">
         <v>24</v>
       </c>
@@ -2458,14 +2424,14 @@
         <v>25</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I14" s="4"/>
     </row>
@@ -2473,7 +2439,7 @@
       <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="17"/>
+      <c r="B15" s="12"/>
       <c r="C15" s="7" t="s">
         <v>27</v>
       </c>
@@ -2481,14 +2447,14 @@
         <v>28</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I15" s="4"/>
     </row>
@@ -2496,22 +2462,22 @@
       <c r="A16" s="4">
         <v>15</v>
       </c>
-      <c r="B16" s="17"/>
+      <c r="B16" s="12"/>
       <c r="C16" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I16" s="4"/>
     </row>
@@ -2519,24 +2485,24 @@
       <c r="A17" s="4">
         <v>16</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="12" t="s">
         <v>30</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I17" s="4"/>
     </row>
@@ -2544,20 +2510,20 @@
       <c r="A18" s="4">
         <v>17</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
       <c r="D18" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I18" s="4"/>
     </row>
@@ -2565,20 +2531,20 @@
       <c r="A19" s="4">
         <v>18</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
       <c r="D19" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I19" s="4"/>
     </row>
@@ -2586,22 +2552,22 @@
       <c r="A20" s="4">
         <v>19</v>
       </c>
-      <c r="B20" s="17"/>
+      <c r="B20" s="12"/>
       <c r="C20" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E20" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>234</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>235</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I20" s="4"/>
     </row>
@@ -2609,7 +2575,7 @@
       <c r="A21" s="4">
         <v>20</v>
       </c>
-      <c r="B21" s="17"/>
+      <c r="B21" s="12"/>
       <c r="C21" s="7" t="s">
         <v>37</v>
       </c>
@@ -2617,14 +2583,14 @@
         <v>38</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I21" s="4"/>
     </row>
@@ -2632,7 +2598,7 @@
       <c r="A22" s="4">
         <v>21</v>
       </c>
-      <c r="B22" s="17"/>
+      <c r="B22" s="12"/>
       <c r="C22" s="7" t="s">
         <v>36</v>
       </c>
@@ -2640,14 +2606,14 @@
         <v>36</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I22" s="4"/>
     </row>
@@ -2655,7 +2621,7 @@
       <c r="A23" s="4">
         <v>22</v>
       </c>
-      <c r="B23" s="17"/>
+      <c r="B23" s="12"/>
       <c r="C23" s="7" t="s">
         <v>34</v>
       </c>
@@ -2663,14 +2629,14 @@
         <v>35</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I23" s="4"/>
     </row>
@@ -2678,22 +2644,22 @@
       <c r="A24" s="4">
         <v>23</v>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17" t="s">
+      <c r="B24" s="12"/>
+      <c r="C24" s="12" t="s">
         <v>31</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I24" s="4"/>
     </row>
@@ -2701,20 +2667,20 @@
       <c r="A25" s="4">
         <v>24</v>
       </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
       <c r="D25" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I25" s="4"/>
     </row>
@@ -2722,20 +2688,20 @@
       <c r="A26" s="4">
         <v>25</v>
       </c>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
       <c r="D26" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I26" s="4"/>
     </row>
@@ -2743,22 +2709,22 @@
       <c r="A27" s="4">
         <v>26</v>
       </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17" t="s">
+      <c r="B27" s="12"/>
+      <c r="C27" s="12" t="s">
         <v>44</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E27" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F27" s="5" t="s">
         <v>228</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>229</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I27" s="4"/>
     </row>
@@ -2766,20 +2732,20 @@
       <c r="A28" s="4">
         <v>27</v>
       </c>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
       <c r="D28" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I28" s="4"/>
     </row>
@@ -2787,7 +2753,7 @@
       <c r="A29" s="4">
         <v>28</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="12" t="s">
         <v>39</v>
       </c>
       <c r="C29" s="7" t="s">
@@ -2797,14 +2763,14 @@
         <v>41</v>
       </c>
       <c r="E29" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F29" s="5" t="s">
         <v>239</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>240</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I29" s="4"/>
     </row>
@@ -2812,7 +2778,7 @@
       <c r="A30" s="4">
         <v>29</v>
       </c>
-      <c r="B30" s="17"/>
+      <c r="B30" s="12"/>
       <c r="C30" s="7" t="s">
         <v>42</v>
       </c>
@@ -2820,14 +2786,14 @@
         <v>41</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I30" s="4"/>
     </row>
@@ -2835,7 +2801,7 @@
       <c r="A31" s="4">
         <v>30</v>
       </c>
-      <c r="B31" s="17"/>
+      <c r="B31" s="12"/>
       <c r="C31" s="7" t="s">
         <v>43</v>
       </c>
@@ -2843,14 +2809,14 @@
         <v>41</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I31" s="4"/>
     </row>
@@ -2858,22 +2824,22 @@
       <c r="A32" s="4">
         <v>31</v>
       </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17" t="s">
-        <v>50</v>
+      <c r="B32" s="12"/>
+      <c r="C32" s="9" t="s">
+        <v>46</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>47</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I32" s="4"/>
     </row>
@@ -2881,20 +2847,20 @@
       <c r="A33" s="4">
         <v>32</v>
       </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="10"/>
       <c r="D33" s="4" t="s">
         <v>48</v>
       </c>
       <c r="E33" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F33" s="5" t="s">
         <v>148</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>149</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I33" s="4"/>
     </row>
@@ -2902,20 +2868,20 @@
       <c r="A34" s="4">
         <v>33</v>
       </c>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="10"/>
       <c r="D34" s="4" t="s">
         <v>49</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I34" s="4"/>
     </row>
@@ -2923,22 +2889,20 @@
       <c r="A35" s="4">
         <v>34</v>
       </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17" t="s">
-        <v>46</v>
-      </c>
+      <c r="B35" s="12"/>
+      <c r="C35" s="10"/>
       <c r="D35" s="4" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I35" s="4"/>
     </row>
@@ -2946,20 +2910,20 @@
       <c r="A36" s="4">
         <v>35</v>
       </c>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="11"/>
       <c r="D36" s="4" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I36" s="4"/>
     </row>
@@ -2967,20 +2931,20 @@
       <c r="A37" s="4">
         <v>36</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="E37" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="C37" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>247</v>
-      </c>
       <c r="F37" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
@@ -2990,18 +2954,18 @@
       <c r="A38" s="4">
         <v>37</v>
       </c>
-      <c r="B38" s="17"/>
+      <c r="B38" s="12"/>
       <c r="C38" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D38" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="E38" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="F38" s="5" t="s">
         <v>249</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>250</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -3011,18 +2975,18 @@
       <c r="A39" s="4">
         <v>38</v>
       </c>
-      <c r="B39" s="17"/>
+      <c r="B39" s="12"/>
       <c r="C39" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E39" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="F39" s="5" t="s">
         <v>251</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>252</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
@@ -3032,18 +2996,18 @@
       <c r="A40" s="4">
         <v>39</v>
       </c>
-      <c r="B40" s="17"/>
+      <c r="B40" s="12"/>
       <c r="C40" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E40" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="F40" s="5" t="s">
         <v>253</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>254</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
@@ -3053,18 +3017,18 @@
       <c r="A41" s="4">
         <v>40</v>
       </c>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17" t="s">
-        <v>260</v>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12" t="s">
+        <v>259</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
@@ -3074,16 +3038,16 @@
       <c r="A42" s="4">
         <v>41</v>
       </c>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
       <c r="D42" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -3093,16 +3057,16 @@
       <c r="A43" s="4">
         <v>42</v>
       </c>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
       <c r="D43" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
@@ -3112,18 +3076,18 @@
       <c r="A44" s="4">
         <v>43</v>
       </c>
-      <c r="B44" s="17"/>
+      <c r="B44" s="12"/>
       <c r="C44" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E44" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="D44" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="E44" s="5" t="s">
+      <c r="F44" s="5" t="s">
         <v>274</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>275</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
@@ -3133,18 +3097,18 @@
       <c r="A45" s="4">
         <v>44</v>
       </c>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17" t="s">
-        <v>261</v>
+      <c r="B45" s="12"/>
+      <c r="C45" s="12" t="s">
+        <v>260</v>
       </c>
       <c r="D45" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="F45" s="5" t="s">
         <v>277</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>278</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
@@ -3154,16 +3118,16 @@
       <c r="A46" s="4">
         <v>45</v>
       </c>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
       <c r="D46" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -3173,16 +3137,16 @@
       <c r="A47" s="4">
         <v>46</v>
       </c>
-      <c r="B47" s="17"/>
-      <c r="C47" s="17"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
       <c r="D47" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E47" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="F47" s="5" t="s">
         <v>280</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>281</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
@@ -3192,16 +3156,16 @@
       <c r="A48" s="4">
         <v>47</v>
       </c>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
       <c r="D48" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
@@ -3211,18 +3175,18 @@
       <c r="A49" s="4">
         <v>48</v>
       </c>
-      <c r="B49" s="17"/>
-      <c r="C49" s="17" t="s">
-        <v>262</v>
+      <c r="B49" s="12"/>
+      <c r="C49" s="12" t="s">
+        <v>261</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
@@ -3232,16 +3196,16 @@
       <c r="A50" s="4">
         <v>49</v>
       </c>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
       <c r="D50" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
@@ -3251,16 +3215,16 @@
       <c r="A51" s="4">
         <v>50</v>
       </c>
-      <c r="B51" s="17"/>
-      <c r="C51" s="17"/>
+      <c r="B51" s="12"/>
+      <c r="C51" s="12"/>
       <c r="D51" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -3270,18 +3234,18 @@
       <c r="A52" s="4">
         <v>51</v>
       </c>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17" t="s">
-        <v>263</v>
+      <c r="B52" s="12"/>
+      <c r="C52" s="12" t="s">
+        <v>262</v>
       </c>
       <c r="D52" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="F52" s="5" t="s">
         <v>286</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>287</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
@@ -3291,16 +3255,16 @@
       <c r="A53" s="4">
         <v>52</v>
       </c>
-      <c r="B53" s="17"/>
-      <c r="C53" s="17"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
       <c r="D53" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -3310,16 +3274,16 @@
       <c r="A54" s="4">
         <v>53</v>
       </c>
-      <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
       <c r="D54" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
@@ -3329,16 +3293,16 @@
       <c r="A55" s="4">
         <v>54</v>
       </c>
-      <c r="B55" s="17"/>
-      <c r="C55" s="17"/>
+      <c r="B55" s="12"/>
+      <c r="C55" s="12"/>
       <c r="D55" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
@@ -3348,16 +3312,16 @@
       <c r="A56" s="4">
         <v>55</v>
       </c>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
       <c r="D56" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
@@ -3367,16 +3331,16 @@
       <c r="A57" s="4">
         <v>56</v>
       </c>
-      <c r="B57" s="17"/>
-      <c r="C57" s="17"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
       <c r="D57" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
@@ -3386,18 +3350,18 @@
       <c r="A58" s="4">
         <v>57</v>
       </c>
-      <c r="B58" s="17"/>
+      <c r="B58" s="12"/>
       <c r="C58" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="E58" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="D58" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="E58" s="5" t="s">
+      <c r="F58" s="5" t="s">
         <v>300</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>301</v>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
@@ -3407,18 +3371,18 @@
       <c r="A59" s="4">
         <v>58</v>
       </c>
-      <c r="B59" s="17"/>
-      <c r="C59" s="17" t="s">
-        <v>264</v>
+      <c r="B59" s="12"/>
+      <c r="C59" s="12" t="s">
+        <v>263</v>
       </c>
       <c r="D59" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="E59" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="F59" s="5" t="s">
         <v>303</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>304</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
@@ -3428,16 +3392,16 @@
       <c r="A60" s="4">
         <v>59</v>
       </c>
-      <c r="B60" s="17"/>
-      <c r="C60" s="17"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="12"/>
       <c r="D60" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
@@ -3448,19 +3412,19 @@
         <v>60</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C61" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="D61" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="D61" s="5" t="s">
+      <c r="E61" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="F61" s="5" t="s">
         <v>257</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>258</v>
       </c>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
@@ -3470,24 +3434,24 @@
       <c r="A62" s="4">
         <v>61</v>
       </c>
-      <c r="B62" s="17" t="s">
+      <c r="B62" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="C62" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="C62" s="7" t="s">
-        <v>311</v>
-      </c>
       <c r="D62" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E62" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>313</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>314</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I62" s="4"/>
     </row>
@@ -3495,22 +3459,22 @@
       <c r="A63" s="4">
         <v>62</v>
       </c>
-      <c r="B63" s="17"/>
+      <c r="B63" s="12"/>
       <c r="C63" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="E63" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="D63" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="E63" s="4" t="s">
+      <c r="F63" s="4" t="s">
         <v>313</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>314</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I63" s="4"/>
     </row>
@@ -3518,22 +3482,22 @@
       <c r="A64" s="4">
         <v>63</v>
       </c>
-      <c r="B64" s="17"/>
+      <c r="B64" s="12"/>
       <c r="C64" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I64" s="4"/>
     </row>
@@ -3541,45 +3505,45 @@
       <c r="A65" s="4">
         <v>64</v>
       </c>
-      <c r="B65" s="17"/>
-      <c r="C65" s="17" t="s">
-        <v>316</v>
+      <c r="B65" s="12"/>
+      <c r="C65" s="12" t="s">
+        <v>315</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G65" s="4"/>
       <c r="H65" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>65</v>
       </c>
-      <c r="B66" s="17"/>
-      <c r="C66" s="17"/>
+      <c r="B66" s="12"/>
+      <c r="C66" s="12"/>
       <c r="D66" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E66" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="E66" s="4" t="s">
-        <v>322</v>
-      </c>
       <c r="F66" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I66" s="4"/>
     </row>
@@ -3587,22 +3551,22 @@
       <c r="A67" s="4">
         <v>66</v>
       </c>
-      <c r="B67" s="17"/>
+      <c r="B67" s="12"/>
       <c r="C67" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="E67" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="E67" s="4" t="s">
+      <c r="F67" s="4" t="s">
         <v>325</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>326</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I67" s="4"/>
     </row>
@@ -3610,24 +3574,24 @@
       <c r="A68" s="4">
         <v>67</v>
       </c>
-      <c r="B68" s="18" t="s">
+      <c r="B68" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="D68" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="C68" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>348</v>
-      </c>
       <c r="E68" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G68" s="4"/>
       <c r="H68" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I68" s="4"/>
     </row>
@@ -3635,22 +3599,22 @@
       <c r="A69" s="4">
         <v>68</v>
       </c>
-      <c r="B69" s="18"/>
+      <c r="B69" s="13"/>
       <c r="C69" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="E69" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="D69" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="E69" s="4" t="s">
+      <c r="F69" s="4" t="s">
         <v>307</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>308</v>
       </c>
       <c r="G69" s="4"/>
       <c r="H69" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I69" s="4"/>
     </row>
@@ -3658,22 +3622,22 @@
       <c r="A70" s="4">
         <v>69</v>
       </c>
-      <c r="B70" s="18"/>
+      <c r="B70" s="13"/>
       <c r="C70" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="D70" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="D70" s="8" t="s">
-        <v>352</v>
-      </c>
       <c r="E70" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="F70" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>154</v>
       </c>
       <c r="G70" s="4"/>
       <c r="H70" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I70" s="4"/>
     </row>
@@ -3681,22 +3645,22 @@
       <c r="A71" s="4">
         <v>70</v>
       </c>
-      <c r="B71" s="18"/>
+      <c r="B71" s="13"/>
       <c r="C71" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="D71" s="8" t="s">
-        <v>353</v>
+        <v>128</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>352</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G71" s="4"/>
       <c r="H71" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I71" s="4"/>
     </row>
@@ -3704,24 +3668,24 @@
       <c r="A72" s="4">
         <v>71</v>
       </c>
-      <c r="B72" s="11" t="s">
-        <v>327</v>
+      <c r="B72" s="12" t="s">
+        <v>326</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D72" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="F72" s="4" t="s">
         <v>332</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>333</v>
       </c>
       <c r="G72" s="4"/>
       <c r="H72" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I72" s="4"/>
     </row>
@@ -3731,20 +3695,20 @@
       </c>
       <c r="B73" s="12"/>
       <c r="C73" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="F73" s="4" t="s">
         <v>334</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>335</v>
       </c>
       <c r="G73" s="4"/>
       <c r="H73" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I73" s="4"/>
     </row>
@@ -3754,20 +3718,20 @@
       </c>
       <c r="B74" s="12"/>
       <c r="C74" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G74" s="4"/>
       <c r="H74" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I74" s="4"/>
     </row>
@@ -3776,21 +3740,21 @@
         <v>74</v>
       </c>
       <c r="B75" s="12"/>
-      <c r="C75" s="11" t="s">
-        <v>328</v>
+      <c r="C75" s="12" t="s">
+        <v>327</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E75" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="F75" s="4" t="s">
         <v>345</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>346</v>
       </c>
       <c r="G75" s="4"/>
       <c r="H75" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I75" s="4"/>
     </row>
@@ -3801,17 +3765,17 @@
       <c r="B76" s="12"/>
       <c r="C76" s="12"/>
       <c r="D76" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="F76" s="4" t="s">
         <v>354</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>355</v>
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I76" s="4"/>
     </row>
@@ -3819,20 +3783,20 @@
       <c r="A77" s="4">
         <v>76</v>
       </c>
-      <c r="B77" s="13"/>
-      <c r="C77" s="13"/>
+      <c r="B77" s="12"/>
+      <c r="C77" s="12"/>
       <c r="D77" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="E77" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="E77" s="4" t="s">
+      <c r="F77" s="4" t="s">
         <v>345</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>346</v>
       </c>
       <c r="G77" s="4"/>
       <c r="H77" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I77" s="4"/>
     </row>
@@ -3840,24 +3804,24 @@
       <c r="A78" s="4">
         <v>77</v>
       </c>
-      <c r="B78" s="11" t="s">
-        <v>342</v>
+      <c r="B78" s="12" t="s">
+        <v>341</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="E78" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="F78" s="5" t="s">
         <v>362</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>363</v>
       </c>
       <c r="G78" s="4"/>
       <c r="H78" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I78" s="4"/>
     </row>
@@ -3867,20 +3831,20 @@
       </c>
       <c r="B79" s="12"/>
       <c r="C79" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D79" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>369</v>
+        <v>50</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>368</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G79" s="4"/>
       <c r="H79" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I79" s="4"/>
     </row>
@@ -3890,20 +3854,20 @@
       </c>
       <c r="B80" s="12"/>
       <c r="C80" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D80" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="F80" s="5" t="s">
         <v>364</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>365</v>
       </c>
       <c r="G80" s="4"/>
       <c r="H80" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I80" s="4"/>
     </row>
@@ -3913,20 +3877,20 @@
       </c>
       <c r="B81" s="12"/>
       <c r="C81" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D81" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="F81" s="5" t="s">
         <v>366</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>367</v>
       </c>
       <c r="G81" s="4"/>
       <c r="H81" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I81" s="4"/>
     </row>
@@ -3934,22 +3898,22 @@
       <c r="A82" s="4">
         <v>81</v>
       </c>
-      <c r="B82" s="13"/>
+      <c r="B82" s="12"/>
       <c r="C82" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D82" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="E82" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="E82" s="8" t="s">
-        <v>369</v>
-      </c>
       <c r="F82" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G82" s="4"/>
       <c r="H82" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I82" s="4"/>
     </row>
@@ -3957,24 +3921,24 @@
       <c r="A83" s="4">
         <v>82</v>
       </c>
-      <c r="B83" s="17" t="s">
+      <c r="B83" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C83" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C83" s="17" t="s">
+      <c r="D83" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D83" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="E83" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F83" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>158</v>
       </c>
       <c r="G83" s="4"/>
       <c r="H83" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I83" s="4"/>
     </row>
@@ -3982,20 +3946,20 @@
       <c r="A84" s="4">
         <v>83</v>
       </c>
-      <c r="B84" s="17"/>
-      <c r="C84" s="17"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="12"/>
       <c r="D84" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G84" s="4"/>
       <c r="H84" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I84" s="4"/>
     </row>
@@ -4003,24 +3967,24 @@
       <c r="A85" s="4">
         <v>84</v>
       </c>
-      <c r="B85" s="11" t="s">
+      <c r="B85" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C85" s="17" t="s">
-        <v>358</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="E85" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G85" s="4"/>
       <c r="H85" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I85" s="4"/>
     </row>
@@ -4029,19 +3993,19 @@
         <v>85</v>
       </c>
       <c r="B86" s="12"/>
-      <c r="C86" s="17"/>
+      <c r="C86" s="12"/>
       <c r="D86" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I86" s="4"/>
     </row>
@@ -4049,20 +4013,20 @@
       <c r="A87" s="4">
         <v>86</v>
       </c>
-      <c r="B87" s="13"/>
-      <c r="C87" s="17"/>
+      <c r="B87" s="12"/>
+      <c r="C87" s="12"/>
       <c r="D87" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G87" s="4"/>
       <c r="H87" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I87" s="4"/>
     </row>
@@ -4071,23 +4035,23 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="C88" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="C88" s="7" t="s">
-        <v>357</v>
-      </c>
       <c r="D88" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F88" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>163</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I88" s="4"/>
     </row>
@@ -4095,24 +4059,24 @@
       <c r="A89" s="4">
         <v>88</v>
       </c>
-      <c r="B89" s="17" t="s">
-        <v>341</v>
-      </c>
-      <c r="C89" s="17" t="s">
-        <v>377</v>
+      <c r="B89" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>395</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E89" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F89" s="5" t="s">
         <v>164</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>165</v>
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I89" s="4"/>
     </row>
@@ -4120,20 +4084,20 @@
       <c r="A90" s="4">
         <v>89</v>
       </c>
-      <c r="B90" s="17"/>
-      <c r="C90" s="17"/>
+      <c r="B90" s="10"/>
+      <c r="C90" s="12"/>
       <c r="D90" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I90" s="4"/>
     </row>
@@ -4141,20 +4105,20 @@
       <c r="A91" s="4">
         <v>90</v>
       </c>
-      <c r="B91" s="17"/>
-      <c r="C91" s="17"/>
+      <c r="B91" s="10"/>
+      <c r="C91" s="12"/>
       <c r="D91" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I91" s="4"/>
     </row>
@@ -4162,22 +4126,22 @@
       <c r="A92" s="4">
         <v>91</v>
       </c>
-      <c r="B92" s="17"/>
-      <c r="C92" s="17" t="s">
-        <v>359</v>
+      <c r="B92" s="10"/>
+      <c r="C92" s="12" t="s">
+        <v>358</v>
       </c>
       <c r="D92" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E92" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E92" s="4" t="s">
+      <c r="F92" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>69</v>
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I92" s="4"/>
     </row>
@@ -4185,20 +4149,20 @@
       <c r="A93" s="4">
         <v>92</v>
       </c>
-      <c r="B93" s="17"/>
-      <c r="C93" s="17"/>
+      <c r="B93" s="10"/>
+      <c r="C93" s="12"/>
       <c r="D93" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E93" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E93" s="4" t="s">
+      <c r="F93" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="F93" s="4" t="s">
-        <v>72</v>
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I93" s="4"/>
     </row>
@@ -4206,950 +4170,940 @@
       <c r="A94" s="4">
         <v>93</v>
       </c>
-      <c r="B94" s="17"/>
-      <c r="C94" s="17"/>
+      <c r="B94" s="10"/>
+      <c r="C94" s="12"/>
       <c r="D94" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E94" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E94" s="4" t="s">
+      <c r="F94" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>75</v>
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I94" s="4"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="4">
-        <v>94</v>
-      </c>
-      <c r="B95" s="11" t="s">
-        <v>76</v>
-      </c>
+      <c r="A95" s="4"/>
+      <c r="B95" s="11"/>
       <c r="C95" s="7" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>387</v>
+        <v>151</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>388</v>
+        <v>178</v>
       </c>
       <c r="G95" s="4"/>
-      <c r="H95" s="4" t="s">
-        <v>137</v>
-      </c>
+      <c r="H95" s="4"/>
       <c r="I95" s="4"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
-        <v>95</v>
-      </c>
-      <c r="B96" s="12"/>
-      <c r="C96" s="17" t="s">
-        <v>378</v>
+        <v>94</v>
+      </c>
+      <c r="B96" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>383</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>77</v>
+        <v>384</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>167</v>
+        <v>385</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>170</v>
+        <v>386</v>
       </c>
       <c r="G96" s="4"/>
       <c r="H96" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I96" s="4"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B97" s="12"/>
-      <c r="C97" s="17"/>
+      <c r="C97" s="12" t="s">
+        <v>376</v>
+      </c>
       <c r="D97" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I97" s="4"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B98" s="12"/>
-      <c r="C98" s="17"/>
+      <c r="C98" s="12"/>
       <c r="D98" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E98" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F98" s="4" t="s">
         <v>169</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>170</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I98" s="4"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B99" s="12"/>
-      <c r="C99" s="17" t="s">
-        <v>81</v>
-      </c>
+      <c r="C99" s="12"/>
       <c r="D99" s="4" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="G99" s="4"/>
       <c r="H99" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="I99" s="4"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B100" s="12"/>
-      <c r="C100" s="17"/>
+      <c r="C100" s="12" t="s">
+        <v>80</v>
+      </c>
       <c r="D100" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G100" s="4"/>
       <c r="H100" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I100" s="4"/>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B101" s="12"/>
-      <c r="C101" s="17" t="s">
-        <v>379</v>
-      </c>
+      <c r="C101" s="12"/>
       <c r="D101" s="4" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="G101" s="4"/>
       <c r="H101" s="4" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="I101" s="4"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B102" s="12"/>
-      <c r="C102" s="17"/>
+      <c r="C102" s="12" t="s">
+        <v>377</v>
+      </c>
       <c r="D102" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I102" s="4"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B103" s="12"/>
-      <c r="C103" s="17"/>
+      <c r="C103" s="12"/>
       <c r="D103" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I103" s="4"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="4"/>
+      <c r="A104" s="4">
+        <v>102</v>
+      </c>
       <c r="B104" s="12"/>
-      <c r="C104" s="11" t="s">
-        <v>391</v>
-      </c>
+      <c r="C104" s="12"/>
       <c r="D104" s="4" t="s">
-        <v>392</v>
+        <v>96</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>395</v>
+        <v>170</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>396</v>
+        <v>143</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="I104" s="4"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="4"/>
+      <c r="A105" s="4">
+        <v>103</v>
+      </c>
       <c r="B105" s="12"/>
-      <c r="C105" s="13"/>
+      <c r="C105" s="12" t="s">
+        <v>389</v>
+      </c>
       <c r="D105" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="E105" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="E105" s="4" t="s">
+      <c r="F105" s="4" t="s">
         <v>394</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>396</v>
       </c>
       <c r="G105" s="4"/>
       <c r="H105" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I105" s="4"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B106" s="12"/>
-      <c r="C106" s="17" t="s">
-        <v>84</v>
-      </c>
+      <c r="C106" s="12"/>
       <c r="D106" s="4" t="s">
-        <v>87</v>
+        <v>391</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>171</v>
+        <v>392</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>85</v>
+        <v>394</v>
       </c>
       <c r="G106" s="4"/>
       <c r="H106" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I106" s="4"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B107" s="12"/>
-      <c r="C107" s="17"/>
+      <c r="C107" s="12" t="s">
+        <v>83</v>
+      </c>
       <c r="D107" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G107" s="4"/>
       <c r="H107" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I107" s="4"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B108" s="12"/>
-      <c r="C108" s="17" t="s">
-        <v>370</v>
-      </c>
+      <c r="C108" s="12"/>
       <c r="D108" s="4" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>172</v>
+        <v>85</v>
       </c>
       <c r="G108" s="4"/>
       <c r="H108" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I108" s="4"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B109" s="12"/>
-      <c r="C109" s="17"/>
+      <c r="C109" s="12" t="s">
+        <v>369</v>
+      </c>
       <c r="D109" s="4" t="s">
         <v>91</v>
       </c>
       <c r="E109" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F109" s="4" t="s">
         <v>171</v>
-      </c>
-      <c r="F109" s="4" t="s">
-        <v>172</v>
       </c>
       <c r="G109" s="4"/>
       <c r="H109" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I109" s="4"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B110" s="12"/>
-      <c r="C110" s="17"/>
+      <c r="C110" s="12"/>
       <c r="D110" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E110" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F110" s="4" t="s">
         <v>171</v>
-      </c>
-      <c r="F110" s="4" t="s">
-        <v>172</v>
       </c>
       <c r="G110" s="4"/>
       <c r="H110" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="I110" s="4"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
-        <v>108</v>
-      </c>
-      <c r="B111" s="13"/>
-      <c r="C111" s="7" t="s">
-        <v>380</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="B111" s="12"/>
+      <c r="C111" s="12"/>
       <c r="D111" s="4" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E111" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F111" s="4" t="s">
         <v>171</v>
-      </c>
-      <c r="F111" s="4" t="s">
-        <v>173</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I111" s="4"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
-        <v>109</v>
-      </c>
-      <c r="B112" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="C112" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="D112" s="8" t="s">
-        <v>383</v>
+        <v>110</v>
+      </c>
+      <c r="B112" s="12"/>
+      <c r="C112" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G112" s="4"/>
       <c r="H112" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I112" s="4"/>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
-        <v>110</v>
-      </c>
-      <c r="B113" s="15"/>
-      <c r="C113" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B113" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C113" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="D113" s="8" t="s">
-        <v>383</v>
+      <c r="D113" s="5" t="s">
+        <v>381</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G113" s="4"/>
       <c r="H113" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I113" s="4"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="4">
-        <v>111</v>
-      </c>
-      <c r="B114" s="15"/>
-      <c r="C114" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="D114" s="8" t="s">
-        <v>383</v>
+        <v>112</v>
+      </c>
+      <c r="B114" s="12"/>
+      <c r="C114" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>381</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G114" s="4"/>
       <c r="H114" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I114" s="4"/>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
-        <v>112</v>
-      </c>
-      <c r="B115" s="16"/>
-      <c r="C115" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="D115" s="8" t="s">
-        <v>384</v>
+        <v>113</v>
+      </c>
+      <c r="B115" s="12"/>
+      <c r="C115" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>381</v>
       </c>
       <c r="E115" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="F115" s="4" t="s">
         <v>175</v>
-      </c>
-      <c r="F115" s="4" t="s">
-        <v>231</v>
       </c>
       <c r="G115" s="4"/>
       <c r="H115" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I115" s="4"/>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
-        <v>113</v>
-      </c>
-      <c r="B116" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="C116" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D116" s="4" t="s">
-        <v>92</v>
+        <v>114</v>
+      </c>
+      <c r="B116" s="12"/>
+      <c r="C116" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>382</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>178</v>
+        <v>230</v>
       </c>
       <c r="G116" s="4"/>
       <c r="H116" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="I116" s="4"/>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
-        <v>114</v>
-      </c>
-      <c r="B117" s="17"/>
-      <c r="C117" s="17"/>
+        <v>115</v>
+      </c>
+      <c r="B117" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>93</v>
+      </c>
       <c r="D117" s="4" t="s">
         <v>91</v>
       </c>
       <c r="E117" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F117" s="4" t="s">
         <v>177</v>
-      </c>
-      <c r="F117" s="4" t="s">
-        <v>90</v>
       </c>
       <c r="G117" s="4"/>
       <c r="H117" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I117" s="4"/>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="4">
-        <v>115</v>
-      </c>
-      <c r="B118" s="17"/>
-      <c r="C118" s="17"/>
+        <v>116</v>
+      </c>
+      <c r="B118" s="12"/>
+      <c r="C118" s="12"/>
       <c r="D118" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G118" s="4"/>
       <c r="H118" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="I118" s="4"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
-        <v>116</v>
-      </c>
-      <c r="B119" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="C119" s="7" t="s">
-        <v>371</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="B119" s="12"/>
+      <c r="C119" s="12"/>
       <c r="D119" s="4" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="G119" s="4"/>
       <c r="H119" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I119" s="4"/>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
-        <v>117</v>
-      </c>
-      <c r="B120" s="12"/>
+        <v>118</v>
+      </c>
+      <c r="B120" s="12" t="s">
+        <v>97</v>
+      </c>
       <c r="C120" s="7" t="s">
-        <v>105</v>
+        <v>370</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I120" s="4"/>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B121" s="12"/>
       <c r="C121" s="7" t="s">
-        <v>382</v>
+        <v>104</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G121" s="4"/>
       <c r="H121" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I121" s="4"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B122" s="12"/>
       <c r="C122" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="G122" s="4"/>
       <c r="H122" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I122" s="4"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B123" s="12"/>
       <c r="C123" s="7" t="s">
-        <v>103</v>
+        <v>379</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G123" s="4"/>
       <c r="H123" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I123" s="4"/>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="4">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B124" s="12"/>
-      <c r="C124" s="17" t="s">
-        <v>107</v>
+      <c r="C124" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G124" s="4"/>
       <c r="H124" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="I124" s="4"/>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B125" s="12"/>
-      <c r="C125" s="17"/>
+      <c r="C125" s="12" t="s">
+        <v>115</v>
+      </c>
       <c r="D125" s="4" t="s">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="G125" s="4"/>
       <c r="H125" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I125" s="4"/>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="4">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B126" s="12"/>
-      <c r="C126" s="17"/>
+      <c r="C126" s="12"/>
       <c r="D126" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="G126" s="4"/>
       <c r="H126" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="I126" s="4"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B127" s="12"/>
-      <c r="C127" s="17" t="s">
-        <v>116</v>
-      </c>
+      <c r="C127" s="12"/>
       <c r="D127" s="4" t="s">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G127" s="4"/>
       <c r="H127" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I127" s="4"/>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="4">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B128" s="12"/>
-      <c r="C128" s="17"/>
+      <c r="C128" s="12" t="s">
+        <v>116</v>
+      </c>
       <c r="D128" s="4" t="s">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="G128" s="4"/>
       <c r="H128" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I128" s="4"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B129" s="12"/>
-      <c r="C129" s="17"/>
+      <c r="C129" s="12"/>
       <c r="D129" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="G129" s="4"/>
       <c r="H129" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="I129" s="4"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B130" s="12"/>
-      <c r="C130" s="17" t="s">
-        <v>117</v>
-      </c>
+      <c r="C130" s="12"/>
       <c r="D130" s="4" t="s">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F130" s="4" t="s">
         <v>190</v>
       </c>
       <c r="G130" s="4"/>
       <c r="H130" s="4" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="I130" s="4"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A131" s="4">
-        <v>128</v>
-      </c>
-      <c r="B131" s="12"/>
-      <c r="C131" s="17"/>
+      <c r="A131" s="4"/>
+      <c r="B131" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C131" s="12" t="s">
+        <v>106</v>
+      </c>
       <c r="D131" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="G131" s="4"/>
+      <c r="H131" s="4"/>
+      <c r="I131" s="4"/>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" s="4"/>
+      <c r="B132" s="10"/>
+      <c r="C132" s="12"/>
+      <c r="D132" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="G132" s="4"/>
+      <c r="H132" s="4"/>
+      <c r="I132" s="4"/>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" s="4"/>
+      <c r="B133" s="10"/>
+      <c r="C133" s="12"/>
+      <c r="D133" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E131" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="F131" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="G131" s="4"/>
-      <c r="H131" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="I131" s="4"/>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="4">
-        <v>129</v>
-      </c>
-      <c r="B132" s="13"/>
-      <c r="C132" s="17"/>
-      <c r="D132" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E132" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="F132" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="G132" s="4"/>
-      <c r="H132" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="I132" s="4"/>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A133" s="4">
-        <v>130</v>
-      </c>
-      <c r="B133" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="C133" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="D133" s="8" t="s">
-        <v>376</v>
-      </c>
       <c r="E133" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F133" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="F133" s="4" t="s">
-        <v>192</v>
-      </c>
       <c r="G133" s="4"/>
-      <c r="H133" s="4" t="s">
-        <v>136</v>
-      </c>
+      <c r="H133" s="4"/>
       <c r="I133" s="4"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
-        <v>131</v>
-      </c>
-      <c r="B134" s="12"/>
-      <c r="C134" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B134" s="10"/>
+      <c r="C134" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D134" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="D134" t="s">
-        <v>372</v>
-      </c>
       <c r="E134" s="4" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G134" s="4"/>
       <c r="H134" s="4" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="I134" s="4"/>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
-        <v>132</v>
-      </c>
-      <c r="B135" s="12"/>
-      <c r="C135" s="12"/>
-      <c r="D135" t="s">
-        <v>373</v>
+        <v>133</v>
+      </c>
+      <c r="B135" s="10"/>
+      <c r="C135" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>371</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G135" s="4"/>
       <c r="H135" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I135" s="4"/>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
-        <v>133</v>
-      </c>
-      <c r="B136" s="13"/>
-      <c r="C136" s="13"/>
-      <c r="D136" t="s">
-        <v>374</v>
+        <v>134</v>
+      </c>
+      <c r="B136" s="10"/>
+      <c r="C136" s="12"/>
+      <c r="D136" s="4" t="s">
+        <v>372</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G136" s="4"/>
       <c r="H136" s="4" t="s">
@@ -5159,137 +5113,137 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
-        <v>134</v>
-      </c>
-      <c r="B137" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="C137" s="7" t="s">
-        <v>113</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="B137" s="11"/>
+      <c r="C137" s="12"/>
       <c r="D137" s="4" t="s">
-        <v>114</v>
+        <v>373</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G137" s="4"/>
       <c r="H137" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I137" s="4"/>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="4">
-        <v>135</v>
-      </c>
-      <c r="B138" s="17"/>
+        <v>136</v>
+      </c>
+      <c r="B138" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="C138" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G138" s="4"/>
       <c r="H138" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I138" s="4"/>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
-        <v>136</v>
-      </c>
-      <c r="B139" s="7" t="s">
-        <v>120</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="B139" s="12"/>
       <c r="C139" s="7" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G139" s="4"/>
       <c r="H139" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I139" s="4"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="4">
-        <v>137</v>
-      </c>
-      <c r="B140" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="C140" s="17" t="s">
-        <v>123</v>
+        <v>138</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>118</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G140" s="4"/>
       <c r="H140" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="I140" s="4"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="4">
-        <v>138</v>
-      </c>
-      <c r="B141" s="17"/>
-      <c r="C141" s="17"/>
+        <v>139</v>
+      </c>
+      <c r="B141" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C141" s="12" t="s">
+        <v>122</v>
+      </c>
       <c r="D141" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G141" s="4"/>
       <c r="H141" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I141" s="4"/>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="4">
-        <v>139</v>
-      </c>
-      <c r="B142" s="17"/>
-      <c r="C142" s="17"/>
+        <v>140</v>
+      </c>
+      <c r="B142" s="12"/>
+      <c r="C142" s="12"/>
       <c r="D142" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G142" s="4"/>
       <c r="H142" s="4" t="s">
@@ -5299,92 +5253,115 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
-        <v>140</v>
-      </c>
-      <c r="B143" s="17"/>
-      <c r="C143" s="17" t="s">
-        <v>26</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="B143" s="12"/>
+      <c r="C143" s="12"/>
       <c r="D143" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="G143" s="4"/>
       <c r="H143" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I143" s="4"/>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="4">
-        <v>141</v>
-      </c>
-      <c r="B144" s="17"/>
-      <c r="C144" s="17"/>
+        <v>142</v>
+      </c>
+      <c r="B144" s="12"/>
+      <c r="C144" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="D144" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G144" s="4"/>
       <c r="H144" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="I144" s="4"/>
     </row>
-    <row r="145" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="4">
-        <v>142</v>
-      </c>
-      <c r="B145" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="C145" s="10" t="s">
-        <v>202</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="B145" s="12"/>
+      <c r="C145" s="12"/>
       <c r="D145" s="4" t="s">
-        <v>203</v>
+        <v>127</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="G145" s="4"/>
       <c r="H145" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I145" s="4"/>
     </row>
+    <row r="146" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A146" s="4">
+        <v>144</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="G146" s="4"/>
+      <c r="H146" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I146" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="51">
-    <mergeCell ref="C143:C144"/>
-    <mergeCell ref="B140:B144"/>
+  <mergeCells count="50">
+    <mergeCell ref="C32:C36"/>
+    <mergeCell ref="B131:B137"/>
+    <mergeCell ref="C144:C145"/>
+    <mergeCell ref="B141:B145"/>
     <mergeCell ref="B68:B71"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="C140:C142"/>
-    <mergeCell ref="C127:C129"/>
-    <mergeCell ref="C130:C132"/>
-    <mergeCell ref="C116:C118"/>
-    <mergeCell ref="B116:B118"/>
-    <mergeCell ref="C101:C103"/>
-    <mergeCell ref="B133:B136"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="C96:C98"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C141:C143"/>
+    <mergeCell ref="C125:C127"/>
+    <mergeCell ref="C128:C130"/>
+    <mergeCell ref="C117:C119"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="C102:C104"/>
+    <mergeCell ref="C105:C106"/>
+    <mergeCell ref="B89:B95"/>
+    <mergeCell ref="C97:C99"/>
     <mergeCell ref="C85:C87"/>
     <mergeCell ref="B72:B77"/>
     <mergeCell ref="C75:C77"/>
-    <mergeCell ref="B119:B132"/>
+    <mergeCell ref="B120:B130"/>
     <mergeCell ref="B78:B82"/>
     <mergeCell ref="B85:B87"/>
     <mergeCell ref="B2:B12"/>
@@ -5397,28 +5374,25 @@
     <mergeCell ref="C5:C7"/>
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="B13:B16"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="C32:C34"/>
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="B29:B36"/>
     <mergeCell ref="C65:C66"/>
     <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C134:C136"/>
-    <mergeCell ref="B112:B115"/>
-    <mergeCell ref="B95:B111"/>
+    <mergeCell ref="C135:C137"/>
+    <mergeCell ref="B113:B116"/>
+    <mergeCell ref="B96:B112"/>
     <mergeCell ref="C45:C48"/>
     <mergeCell ref="C49:C51"/>
     <mergeCell ref="C59:C60"/>
     <mergeCell ref="C52:C57"/>
     <mergeCell ref="B37:B60"/>
     <mergeCell ref="B62:B67"/>
-    <mergeCell ref="C124:C126"/>
-    <mergeCell ref="C99:C100"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="C108:C110"/>
+    <mergeCell ref="C131:C133"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="C107:C108"/>
+    <mergeCell ref="C109:C111"/>
     <mergeCell ref="C89:C91"/>
     <mergeCell ref="C92:C94"/>
-    <mergeCell ref="B89:B94"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8BB0308-4726-4C50-B085-8C470D76868A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9820FE-E70D-4C8E-BE06-9C7C9E13A05C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{F425FBA8-E65A-4F03-9270-551F3EA7C4F5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="398">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -547,10 +547,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>活动页面未开启</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>活动页面开启</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -576,14 +572,6 @@
     <t>P3</t>
   </si>
   <si>
-    <t>活动页面未关闭</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>活动页面关闭</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>能修改时间至周一凌晨五点</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1612,6 +1600,10 @@
   </si>
   <si>
     <t>活动在活动中心开启</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动在活动中心关闭</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2156,14 +2148,14 @@
         <v>11</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I2" s="4"/>
     </row>
@@ -2177,14 +2169,14 @@
         <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I3" s="4"/>
     </row>
@@ -2198,14 +2190,14 @@
         <v>13</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I4" s="4"/>
     </row>
@@ -2221,14 +2213,14 @@
         <v>15</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I5" s="4"/>
     </row>
@@ -2239,17 +2231,17 @@
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
       <c r="D6" s="4" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -2263,14 +2255,14 @@
         <v>16</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I7" s="4"/>
     </row>
@@ -2289,11 +2281,11 @@
         <v>129</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I8" s="4"/>
     </row>
@@ -2309,17 +2301,17 @@
         <v>18</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>138</v>
+        <v>396</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -2332,14 +2324,14 @@
         <v>19</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>139</v>
+        <v>397</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I10" s="4"/>
     </row>
@@ -2353,14 +2345,14 @@
         <v>20</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>139</v>
+        <v>397</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I11" s="4"/>
     </row>
@@ -2376,14 +2368,14 @@
         <v>45</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I12" s="4"/>
     </row>
@@ -2401,14 +2393,14 @@
         <v>23</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>130</v>
+        <v>395</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I13" s="4"/>
     </row>
@@ -2424,14 +2416,14 @@
         <v>25</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I14" s="4"/>
     </row>
@@ -2447,14 +2439,14 @@
         <v>28</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I15" s="4"/>
     </row>
@@ -2467,17 +2459,17 @@
         <v>26</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I16" s="4"/>
     </row>
@@ -2495,14 +2487,14 @@
         <v>11</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I17" s="4"/>
     </row>
@@ -2516,14 +2508,14 @@
         <v>12</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I18" s="4"/>
     </row>
@@ -2537,14 +2529,14 @@
         <v>13</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I19" s="4"/>
     </row>
@@ -2554,20 +2546,20 @@
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I20" s="4"/>
     </row>
@@ -2583,14 +2575,14 @@
         <v>38</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I21" s="4"/>
     </row>
@@ -2606,14 +2598,14 @@
         <v>36</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I22" s="4"/>
     </row>
@@ -2629,14 +2621,14 @@
         <v>35</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I23" s="4"/>
     </row>
@@ -2652,14 +2644,14 @@
         <v>18</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I24" s="4"/>
     </row>
@@ -2673,14 +2665,14 @@
         <v>19</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I25" s="4"/>
     </row>
@@ -2694,14 +2686,14 @@
         <v>20</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I26" s="4"/>
     </row>
@@ -2714,17 +2706,17 @@
         <v>44</v>
       </c>
       <c r="D27" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="F27" s="5" t="s">
         <v>225</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>228</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I27" s="4"/>
     </row>
@@ -2735,17 +2727,17 @@
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
       <c r="D28" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I28" s="4"/>
     </row>
@@ -2763,14 +2755,14 @@
         <v>41</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I29" s="4"/>
     </row>
@@ -2786,14 +2778,14 @@
         <v>41</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I30" s="4"/>
     </row>
@@ -2809,14 +2801,14 @@
         <v>41</v>
       </c>
       <c r="E31" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>238</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>241</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I31" s="4"/>
     </row>
@@ -2832,14 +2824,14 @@
         <v>47</v>
       </c>
       <c r="E32" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F32" s="5" t="s">
         <v>145</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>148</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I32" s="4"/>
     </row>
@@ -2853,14 +2845,14 @@
         <v>48</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I33" s="4"/>
     </row>
@@ -2874,14 +2866,14 @@
         <v>49</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I34" s="4"/>
     </row>
@@ -2892,17 +2884,17 @@
       <c r="B35" s="12"/>
       <c r="C35" s="10"/>
       <c r="D35" s="4" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I35" s="4"/>
     </row>
@@ -2913,17 +2905,17 @@
       <c r="B36" s="12"/>
       <c r="C36" s="11"/>
       <c r="D36" s="4" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I36" s="4"/>
     </row>
@@ -2932,19 +2924,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
@@ -2956,16 +2948,16 @@
       </c>
       <c r="B38" s="12"/>
       <c r="C38" s="7" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -2977,16 +2969,16 @@
       </c>
       <c r="B39" s="12"/>
       <c r="C39" s="7" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D39" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>250</v>
-      </c>
       <c r="F39" s="5" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
@@ -2998,16 +2990,16 @@
       </c>
       <c r="B40" s="12"/>
       <c r="C40" s="7" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
@@ -3019,16 +3011,16 @@
       </c>
       <c r="B41" s="12"/>
       <c r="C41" s="12" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
@@ -3041,13 +3033,13 @@
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
       <c r="D42" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -3060,13 +3052,13 @@
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
       <c r="D43" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
@@ -3078,16 +3070,16 @@
       </c>
       <c r="B44" s="12"/>
       <c r="C44" s="7" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D44" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="F44" s="5" t="s">
         <v>271</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>274</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
@@ -3099,16 +3091,16 @@
       </c>
       <c r="B45" s="12"/>
       <c r="C45" s="12" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
@@ -3121,13 +3113,13 @@
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
       <c r="D46" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="E46" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="E46" s="5" t="s">
-        <v>278</v>
-      </c>
       <c r="F46" s="5" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -3140,13 +3132,13 @@
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
       <c r="D47" s="5" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
@@ -3159,13 +3151,13 @@
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
       <c r="D48" s="5" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
@@ -3177,16 +3169,16 @@
       </c>
       <c r="B49" s="12"/>
       <c r="C49" s="12" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
@@ -3199,13 +3191,13 @@
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
       <c r="D50" s="5" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
@@ -3218,13 +3210,13 @@
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
       <c r="D51" s="5" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -3236,16 +3228,16 @@
       </c>
       <c r="B52" s="12"/>
       <c r="C52" s="12" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
@@ -3258,13 +3250,13 @@
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
       <c r="D53" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="E53" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="F53" s="5" t="s">
         <v>288</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>291</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -3277,13 +3269,13 @@
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
       <c r="D54" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E54" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="F54" s="5" t="s">
         <v>289</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>292</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
@@ -3296,13 +3288,13 @@
       <c r="B55" s="12"/>
       <c r="C55" s="12"/>
       <c r="D55" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
@@ -3315,13 +3307,13 @@
       <c r="B56" s="12"/>
       <c r="C56" s="12"/>
       <c r="D56" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
@@ -3334,13 +3326,13 @@
       <c r="B57" s="12"/>
       <c r="C57" s="12"/>
       <c r="D57" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
@@ -3352,16 +3344,16 @@
       </c>
       <c r="B58" s="12"/>
       <c r="C58" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
@@ -3373,16 +3365,16 @@
       </c>
       <c r="B59" s="12"/>
       <c r="C59" s="12" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
@@ -3395,13 +3387,13 @@
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
       <c r="D60" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="E60" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="E60" s="5" t="s">
-        <v>304</v>
-      </c>
       <c r="F60" s="5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
@@ -3412,19 +3404,19 @@
         <v>60</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C61" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="F61" s="5" t="s">
         <v>254</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>257</v>
       </c>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
@@ -3435,23 +3427,23 @@
         <v>61</v>
       </c>
       <c r="B62" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E62" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="F62" s="4" t="s">
         <v>310</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>313</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I62" s="4"/>
     </row>
@@ -3461,20 +3453,20 @@
       </c>
       <c r="B63" s="12"/>
       <c r="C63" s="7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I63" s="4"/>
     </row>
@@ -3484,20 +3476,20 @@
       </c>
       <c r="B64" s="12"/>
       <c r="C64" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="D64" s="4" t="s">
-        <v>317</v>
-      </c>
       <c r="E64" s="4" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I64" s="4"/>
     </row>
@@ -3507,23 +3499,23 @@
       </c>
       <c r="B65" s="12"/>
       <c r="C65" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="F65" s="4" t="s">
         <v>315</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>318</v>
       </c>
       <c r="G65" s="4"/>
       <c r="H65" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -3533,17 +3525,17 @@
       <c r="B66" s="12"/>
       <c r="C66" s="12"/>
       <c r="D66" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I66" s="4"/>
     </row>
@@ -3553,20 +3545,20 @@
       </c>
       <c r="B67" s="12"/>
       <c r="C67" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="F67" s="4" t="s">
         <v>322</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>325</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I67" s="4"/>
     </row>
@@ -3575,23 +3567,23 @@
         <v>67</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G68" s="4"/>
       <c r="H68" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I68" s="4"/>
     </row>
@@ -3601,20 +3593,20 @@
       </c>
       <c r="B69" s="13"/>
       <c r="C69" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G69" s="4"/>
       <c r="H69" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I69" s="4"/>
     </row>
@@ -3624,20 +3616,20 @@
       </c>
       <c r="B70" s="13"/>
       <c r="C70" s="7" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G70" s="4"/>
       <c r="H70" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I70" s="4"/>
     </row>
@@ -3650,17 +3642,17 @@
         <v>128</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G71" s="4"/>
       <c r="H71" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I71" s="4"/>
     </row>
@@ -3669,23 +3661,23 @@
         <v>71</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C72" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="D72" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="D72" s="4" t="s">
-        <v>331</v>
-      </c>
       <c r="E72" s="4" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="G72" s="4"/>
       <c r="H72" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I72" s="4"/>
     </row>
@@ -3695,20 +3687,20 @@
       </c>
       <c r="B73" s="12"/>
       <c r="C73" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="D73" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="D73" s="4" t="s">
-        <v>336</v>
-      </c>
       <c r="E73" s="4" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="G73" s="4"/>
       <c r="H73" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I73" s="4"/>
     </row>
@@ -3718,20 +3710,20 @@
       </c>
       <c r="B74" s="12"/>
       <c r="C74" s="7" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D74" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="F74" s="4" t="s">
         <v>335</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>338</v>
       </c>
       <c r="G74" s="4"/>
       <c r="H74" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I74" s="4"/>
     </row>
@@ -3741,20 +3733,20 @@
       </c>
       <c r="B75" s="12"/>
       <c r="C75" s="12" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D75" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="F75" s="4" t="s">
         <v>342</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>345</v>
       </c>
       <c r="G75" s="4"/>
       <c r="H75" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I75" s="4"/>
     </row>
@@ -3765,17 +3757,17 @@
       <c r="B76" s="12"/>
       <c r="C76" s="12"/>
       <c r="D76" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I76" s="4"/>
     </row>
@@ -3786,17 +3778,17 @@
       <c r="B77" s="12"/>
       <c r="C77" s="12"/>
       <c r="D77" s="4" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G77" s="4"/>
       <c r="H77" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I77" s="4"/>
     </row>
@@ -3805,23 +3797,23 @@
         <v>77</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C78" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D78" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="F78" s="5" t="s">
         <v>359</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>362</v>
       </c>
       <c r="G78" s="4"/>
       <c r="H78" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I78" s="4"/>
     </row>
@@ -3834,17 +3826,17 @@
         <v>50</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G79" s="4"/>
       <c r="H79" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I79" s="4"/>
     </row>
@@ -3857,17 +3849,17 @@
         <v>52</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G80" s="4"/>
       <c r="H80" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I80" s="4"/>
     </row>
@@ -3880,17 +3872,17 @@
         <v>53</v>
       </c>
       <c r="D81" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="E81" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="E81" s="5" t="s">
-        <v>368</v>
-      </c>
       <c r="F81" s="5" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="G81" s="4"/>
       <c r="H81" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I81" s="4"/>
     </row>
@@ -3903,17 +3895,17 @@
         <v>54</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G82" s="4"/>
       <c r="H82" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I82" s="4"/>
     </row>
@@ -3931,14 +3923,14 @@
         <v>61</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G83" s="4"/>
       <c r="H83" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I83" s="4"/>
     </row>
@@ -3952,14 +3944,14 @@
         <v>62</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G84" s="4"/>
       <c r="H84" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I84" s="4"/>
     </row>
@@ -3971,20 +3963,20 @@
         <v>55</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>56</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G85" s="4"/>
       <c r="H85" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I85" s="4"/>
     </row>
@@ -3998,14 +3990,14 @@
         <v>57</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I86" s="4"/>
     </row>
@@ -4019,14 +4011,14 @@
         <v>58</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G87" s="4"/>
       <c r="H87" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I87" s="4"/>
     </row>
@@ -4035,23 +4027,23 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I88" s="4"/>
     </row>
@@ -4060,23 +4052,23 @@
         <v>88</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>63</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I89" s="4"/>
     </row>
@@ -4090,14 +4082,14 @@
         <v>64</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I90" s="4"/>
     </row>
@@ -4111,14 +4103,14 @@
         <v>65</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I91" s="4"/>
     </row>
@@ -4128,7 +4120,7 @@
       </c>
       <c r="B92" s="10"/>
       <c r="C92" s="12" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>66</v>
@@ -4141,7 +4133,7 @@
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I92" s="4"/>
     </row>
@@ -4162,7 +4154,7 @@
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I93" s="4"/>
     </row>
@@ -4183,7 +4175,7 @@
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I94" s="4"/>
     </row>
@@ -4191,16 +4183,16 @@
       <c r="A95" s="4"/>
       <c r="B95" s="11"/>
       <c r="C95" s="7" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
@@ -4214,20 +4206,20 @@
         <v>75</v>
       </c>
       <c r="C96" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="F96" s="4" t="s">
         <v>383</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="E96" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>386</v>
       </c>
       <c r="G96" s="4"/>
       <c r="H96" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I96" s="4"/>
     </row>
@@ -4237,20 +4229,20 @@
       </c>
       <c r="B97" s="12"/>
       <c r="C97" s="12" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>76</v>
       </c>
       <c r="E97" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F97" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="F97" s="4" t="s">
-        <v>169</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I97" s="4"/>
     </row>
@@ -4264,14 +4256,14 @@
         <v>77</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I98" s="4"/>
     </row>
@@ -4285,14 +4277,14 @@
         <v>78</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G99" s="4"/>
       <c r="H99" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I99" s="4"/>
     </row>
@@ -4308,14 +4300,14 @@
         <v>86</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>81</v>
       </c>
       <c r="G100" s="4"/>
       <c r="H100" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I100" s="4"/>
     </row>
@@ -4329,14 +4321,14 @@
         <v>86</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>82</v>
       </c>
       <c r="G101" s="4"/>
       <c r="H101" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I101" s="4"/>
     </row>
@@ -4346,20 +4338,20 @@
       </c>
       <c r="B102" s="12"/>
       <c r="C102" s="12" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>94</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I102" s="4"/>
     </row>
@@ -4373,14 +4365,14 @@
         <v>95</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I103" s="4"/>
     </row>
@@ -4394,14 +4386,14 @@
         <v>96</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I104" s="4"/>
     </row>
@@ -4411,20 +4403,20 @@
       </c>
       <c r="B105" s="12"/>
       <c r="C105" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D105" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="E105" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="E105" s="4" t="s">
-        <v>393</v>
-      </c>
       <c r="F105" s="4" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="G105" s="4"/>
       <c r="H105" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I105" s="4"/>
     </row>
@@ -4435,17 +4427,17 @@
       <c r="B106" s="12"/>
       <c r="C106" s="12"/>
       <c r="D106" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="F106" s="4" t="s">
         <v>391</v>
-      </c>
-      <c r="E106" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="F106" s="4" t="s">
-        <v>394</v>
       </c>
       <c r="G106" s="4"/>
       <c r="H106" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I106" s="4"/>
     </row>
@@ -4461,14 +4453,14 @@
         <v>86</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>84</v>
       </c>
       <c r="G107" s="4"/>
       <c r="H107" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I107" s="4"/>
     </row>
@@ -4482,14 +4474,14 @@
         <v>86</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>85</v>
       </c>
       <c r="G108" s="4"/>
       <c r="H108" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I108" s="4"/>
     </row>
@@ -4499,20 +4491,20 @@
       </c>
       <c r="B109" s="12"/>
       <c r="C109" s="12" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>91</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G109" s="4"/>
       <c r="H109" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I109" s="4"/>
     </row>
@@ -4526,14 +4518,14 @@
         <v>90</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G110" s="4"/>
       <c r="H110" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I110" s="4"/>
     </row>
@@ -4547,14 +4539,14 @@
         <v>92</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I111" s="4"/>
     </row>
@@ -4564,20 +4556,20 @@
       </c>
       <c r="B112" s="12"/>
       <c r="C112" s="7" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>79</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G112" s="4"/>
       <c r="H112" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I112" s="4"/>
     </row>
@@ -4589,20 +4581,20 @@
         <v>87</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G113" s="4"/>
       <c r="H113" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I113" s="4"/>
     </row>
@@ -4612,20 +4604,20 @@
       </c>
       <c r="B114" s="12"/>
       <c r="C114" s="7" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G114" s="4"/>
       <c r="H114" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I114" s="4"/>
     </row>
@@ -4638,17 +4630,17 @@
         <v>88</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G115" s="4"/>
       <c r="H115" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I115" s="4"/>
     </row>
@@ -4661,17 +4653,17 @@
         <v>100</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G116" s="4"/>
       <c r="H116" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I116" s="4"/>
     </row>
@@ -4689,14 +4681,14 @@
         <v>91</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G117" s="4"/>
       <c r="H117" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I117" s="4"/>
     </row>
@@ -4710,14 +4702,14 @@
         <v>90</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F118" s="4" t="s">
         <v>89</v>
       </c>
       <c r="G118" s="4"/>
       <c r="H118" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I118" s="4"/>
     </row>
@@ -4731,14 +4723,14 @@
         <v>92</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F119" s="4" t="s">
         <v>89</v>
       </c>
       <c r="G119" s="4"/>
       <c r="H119" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I119" s="4"/>
     </row>
@@ -4750,20 +4742,20 @@
         <v>97</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>99</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I120" s="4"/>
     </row>
@@ -4779,14 +4771,14 @@
         <v>105</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G121" s="4"/>
       <c r="H121" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I121" s="4"/>
     </row>
@@ -4796,20 +4788,20 @@
       </c>
       <c r="B122" s="12"/>
       <c r="C122" s="7" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>98</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G122" s="4"/>
       <c r="H122" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I122" s="4"/>
     </row>
@@ -4819,20 +4811,20 @@
       </c>
       <c r="B123" s="12"/>
       <c r="C123" s="7" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>101</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G123" s="4"/>
       <c r="H123" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I123" s="4"/>
     </row>
@@ -4848,14 +4840,14 @@
         <v>103</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G124" s="4"/>
       <c r="H124" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I124" s="4"/>
     </row>
@@ -4871,14 +4863,14 @@
         <v>18</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G125" s="4"/>
       <c r="H125" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I125" s="4"/>
     </row>
@@ -4892,14 +4884,14 @@
         <v>107</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G126" s="4"/>
       <c r="H126" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I126" s="4"/>
     </row>
@@ -4913,14 +4905,14 @@
         <v>108</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G127" s="4"/>
       <c r="H127" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I127" s="4"/>
     </row>
@@ -4936,14 +4928,14 @@
         <v>18</v>
       </c>
       <c r="E128" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="F128" s="4" t="s">
         <v>186</v>
-      </c>
-      <c r="F128" s="4" t="s">
-        <v>189</v>
       </c>
       <c r="G128" s="4"/>
       <c r="H128" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I128" s="4"/>
     </row>
@@ -4957,14 +4949,14 @@
         <v>107</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G129" s="4"/>
       <c r="H129" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I129" s="4"/>
     </row>
@@ -4978,14 +4970,14 @@
         <v>108</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G130" s="4"/>
       <c r="H130" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I130" s="4"/>
     </row>
@@ -5001,10 +4993,10 @@
         <v>18</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G131" s="4"/>
       <c r="H131" s="4"/>
@@ -5018,10 +5010,10 @@
         <v>107</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G132" s="4"/>
       <c r="H132" s="4"/>
@@ -5035,10 +5027,10 @@
         <v>108</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G133" s="4"/>
       <c r="H133" s="4"/>
@@ -5053,17 +5045,17 @@
         <v>110</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G134" s="4"/>
       <c r="H134" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I134" s="4"/>
     </row>
@@ -5073,20 +5065,20 @@
       </c>
       <c r="B135" s="10"/>
       <c r="C135" s="12" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G135" s="4"/>
       <c r="H135" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I135" s="4"/>
     </row>
@@ -5097,17 +5089,17 @@
       <c r="B136" s="10"/>
       <c r="C136" s="12"/>
       <c r="D136" s="4" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G136" s="4"/>
       <c r="H136" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I136" s="4"/>
     </row>
@@ -5118,17 +5110,17 @@
       <c r="B137" s="11"/>
       <c r="C137" s="12"/>
       <c r="D137" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G137" s="4"/>
       <c r="H137" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I137" s="4"/>
     </row>
@@ -5146,14 +5138,14 @@
         <v>113</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G138" s="4"/>
       <c r="H138" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I138" s="4"/>
     </row>
@@ -5169,14 +5161,14 @@
         <v>117</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G139" s="4"/>
       <c r="H139" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I139" s="4"/>
     </row>
@@ -5194,14 +5186,14 @@
         <v>120</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G140" s="4"/>
       <c r="H140" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I140" s="4"/>
     </row>
@@ -5219,14 +5211,14 @@
         <v>123</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G141" s="4"/>
       <c r="H141" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I141" s="4"/>
     </row>
@@ -5240,14 +5232,14 @@
         <v>124</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G142" s="4"/>
       <c r="H142" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I142" s="4"/>
     </row>
@@ -5261,14 +5253,14 @@
         <v>125</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G143" s="4"/>
       <c r="H143" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I143" s="4"/>
     </row>
@@ -5284,14 +5276,14 @@
         <v>126</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G144" s="4"/>
       <c r="H144" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I144" s="4"/>
     </row>
@@ -5305,14 +5297,14 @@
         <v>127</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G145" s="4"/>
       <c r="H145" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I145" s="4"/>
     </row>
@@ -5321,23 +5313,23 @@
         <v>144</v>
       </c>
       <c r="B146" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="F146" s="4" t="s">
         <v>200</v>
-      </c>
-      <c r="C146" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="D146" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="E146" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="F146" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="G146" s="4"/>
       <c r="H146" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I146" s="4"/>
     </row>

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9820FE-E70D-4C8E-BE06-9C7C9E13A05C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7FEDEA1-01B7-4F21-ACCE-B5A3F5CD33BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{F425FBA8-E65A-4F03-9270-551F3EA7C4F5}"/>
   </bookViews>
@@ -353,9 +353,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>点赞记录的排序方式</t>
-  </si>
-  <si>
     <t>升序</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1507,14 +1504,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>不同渠道的点赞</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>点赞记录记录的信息</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>点赞记录界面没有点赞时的默认展示</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1535,10 +1524,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>点赞记录弹窗</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>活动期间在活动页面</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1604,6 +1589,22 @@
   </si>
   <si>
     <t>活动在活动中心关闭</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点赞记录-记录信息</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点赞记录-排序方式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点赞记录-不同渠道的点赞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点赞记录-点赞记录弹窗功能</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2148,14 +2149,14 @@
         <v>11</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I2" s="4"/>
     </row>
@@ -2169,14 +2170,14 @@
         <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I3" s="4"/>
     </row>
@@ -2190,14 +2191,14 @@
         <v>13</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I4" s="4"/>
     </row>
@@ -2213,14 +2214,14 @@
         <v>15</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I5" s="4"/>
     </row>
@@ -2231,17 +2232,17 @@
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
       <c r="D6" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -2255,14 +2256,14 @@
         <v>16</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I7" s="4"/>
     </row>
@@ -2278,14 +2279,14 @@
         <v>33</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I8" s="4"/>
     </row>
@@ -2301,17 +2302,17 @@
         <v>18</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -2324,14 +2325,14 @@
         <v>19</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I10" s="4"/>
     </row>
@@ -2345,14 +2346,14 @@
         <v>20</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I11" s="4"/>
     </row>
@@ -2368,14 +2369,14 @@
         <v>45</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I12" s="4"/>
     </row>
@@ -2393,14 +2394,14 @@
         <v>23</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I13" s="4"/>
     </row>
@@ -2416,14 +2417,14 @@
         <v>25</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I14" s="4"/>
     </row>
@@ -2439,14 +2440,14 @@
         <v>28</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I15" s="4"/>
     </row>
@@ -2459,17 +2460,17 @@
         <v>26</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I16" s="4"/>
     </row>
@@ -2487,14 +2488,14 @@
         <v>11</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I17" s="4"/>
     </row>
@@ -2508,14 +2509,14 @@
         <v>12</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I18" s="4"/>
     </row>
@@ -2529,14 +2530,14 @@
         <v>13</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I19" s="4"/>
     </row>
@@ -2546,20 +2547,20 @@
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E20" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>230</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>231</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I20" s="4"/>
     </row>
@@ -2575,14 +2576,14 @@
         <v>38</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I21" s="4"/>
     </row>
@@ -2598,14 +2599,14 @@
         <v>36</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I22" s="4"/>
     </row>
@@ -2621,14 +2622,14 @@
         <v>35</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I23" s="4"/>
     </row>
@@ -2644,14 +2645,14 @@
         <v>18</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I24" s="4"/>
     </row>
@@ -2665,14 +2666,14 @@
         <v>19</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I25" s="4"/>
     </row>
@@ -2686,14 +2687,14 @@
         <v>20</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I26" s="4"/>
     </row>
@@ -2706,17 +2707,17 @@
         <v>44</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E27" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="F27" s="5" t="s">
         <v>224</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>225</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I27" s="4"/>
     </row>
@@ -2727,17 +2728,17 @@
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
       <c r="D28" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I28" s="4"/>
     </row>
@@ -2755,14 +2756,14 @@
         <v>41</v>
       </c>
       <c r="E29" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="F29" s="5" t="s">
         <v>235</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>236</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I29" s="4"/>
     </row>
@@ -2778,14 +2779,14 @@
         <v>41</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I30" s="4"/>
     </row>
@@ -2801,14 +2802,14 @@
         <v>41</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I31" s="4"/>
     </row>
@@ -2824,14 +2825,14 @@
         <v>47</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I32" s="4"/>
     </row>
@@ -2845,14 +2846,14 @@
         <v>48</v>
       </c>
       <c r="E33" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F33" s="5" t="s">
         <v>144</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>145</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I33" s="4"/>
     </row>
@@ -2866,14 +2867,14 @@
         <v>49</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I34" s="4"/>
     </row>
@@ -2884,17 +2885,17 @@
       <c r="B35" s="12"/>
       <c r="C35" s="10"/>
       <c r="D35" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I35" s="4"/>
     </row>
@@ -2905,17 +2906,17 @@
       <c r="B36" s="12"/>
       <c r="C36" s="11"/>
       <c r="D36" s="4" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I36" s="4"/>
     </row>
@@ -2924,19 +2925,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E37" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="C37" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>243</v>
-      </c>
       <c r="F37" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
@@ -2948,16 +2949,16 @@
       </c>
       <c r="B38" s="12"/>
       <c r="C38" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D38" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="E38" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="F38" s="5" t="s">
         <v>245</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>246</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -2969,16 +2970,16 @@
       </c>
       <c r="B39" s="12"/>
       <c r="C39" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E39" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="F39" s="5" t="s">
         <v>247</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>248</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
@@ -2990,16 +2991,16 @@
       </c>
       <c r="B40" s="12"/>
       <c r="C40" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E40" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="F40" s="5" t="s">
         <v>249</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>250</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
@@ -3011,16 +3012,16 @@
       </c>
       <c r="B41" s="12"/>
       <c r="C41" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
@@ -3033,13 +3034,13 @@
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
       <c r="D42" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -3052,13 +3053,13 @@
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
       <c r="D43" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
@@ -3070,16 +3071,16 @@
       </c>
       <c r="B44" s="12"/>
       <c r="C44" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E44" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D44" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="E44" s="5" t="s">
+      <c r="F44" s="5" t="s">
         <v>270</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
@@ -3091,16 +3092,16 @@
       </c>
       <c r="B45" s="12"/>
       <c r="C45" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D45" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="F45" s="5" t="s">
         <v>273</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>274</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
@@ -3113,13 +3114,13 @@
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
       <c r="D46" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -3132,13 +3133,13 @@
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
       <c r="D47" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E47" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="F47" s="5" t="s">
         <v>276</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>277</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
@@ -3151,13 +3152,13 @@
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
       <c r="D48" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
@@ -3169,16 +3170,16 @@
       </c>
       <c r="B49" s="12"/>
       <c r="C49" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
@@ -3191,13 +3192,13 @@
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
       <c r="D50" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
@@ -3210,13 +3211,13 @@
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
       <c r="D51" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -3228,16 +3229,16 @@
       </c>
       <c r="B52" s="12"/>
       <c r="C52" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D52" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="F52" s="5" t="s">
         <v>282</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>283</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
@@ -3250,13 +3251,13 @@
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
       <c r="D53" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -3269,13 +3270,13 @@
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
       <c r="D54" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
@@ -3288,13 +3289,13 @@
       <c r="B55" s="12"/>
       <c r="C55" s="12"/>
       <c r="D55" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
@@ -3307,13 +3308,13 @@
       <c r="B56" s="12"/>
       <c r="C56" s="12"/>
       <c r="D56" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
@@ -3326,13 +3327,13 @@
       <c r="B57" s="12"/>
       <c r="C57" s="12"/>
       <c r="D57" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
@@ -3344,16 +3345,16 @@
       </c>
       <c r="B58" s="12"/>
       <c r="C58" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="E58" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="D58" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="E58" s="5" t="s">
+      <c r="F58" s="5" t="s">
         <v>296</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>297</v>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
@@ -3365,16 +3366,16 @@
       </c>
       <c r="B59" s="12"/>
       <c r="C59" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D59" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="E59" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="F59" s="5" t="s">
         <v>299</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>300</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
@@ -3387,13 +3388,13 @@
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
       <c r="D60" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
@@ -3404,19 +3405,19 @@
         <v>60</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C61" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D61" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="D61" s="5" t="s">
+      <c r="E61" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="F61" s="5" t="s">
         <v>253</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>254</v>
       </c>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
@@ -3427,23 +3428,23 @@
         <v>61</v>
       </c>
       <c r="B62" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="C62" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="C62" s="7" t="s">
-        <v>307</v>
-      </c>
       <c r="D62" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E62" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>309</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>310</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I62" s="4"/>
     </row>
@@ -3453,20 +3454,20 @@
       </c>
       <c r="B63" s="12"/>
       <c r="C63" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="E63" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="D63" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E63" s="4" t="s">
+      <c r="F63" s="4" t="s">
         <v>309</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>310</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I63" s="4"/>
     </row>
@@ -3476,20 +3477,20 @@
       </c>
       <c r="B64" s="12"/>
       <c r="C64" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I64" s="4"/>
     </row>
@@ -3499,23 +3500,23 @@
       </c>
       <c r="B65" s="12"/>
       <c r="C65" s="12" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G65" s="4"/>
       <c r="H65" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -3525,17 +3526,17 @@
       <c r="B66" s="12"/>
       <c r="C66" s="12"/>
       <c r="D66" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="E66" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="E66" s="4" t="s">
-        <v>318</v>
-      </c>
       <c r="F66" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I66" s="4"/>
     </row>
@@ -3545,20 +3546,20 @@
       </c>
       <c r="B67" s="12"/>
       <c r="C67" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="E67" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E67" s="4" t="s">
+      <c r="F67" s="4" t="s">
         <v>321</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>322</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I67" s="4"/>
     </row>
@@ -3567,23 +3568,23 @@
         <v>67</v>
       </c>
       <c r="B68" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="D68" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="C68" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>344</v>
-      </c>
       <c r="E68" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G68" s="4"/>
       <c r="H68" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I68" s="4"/>
     </row>
@@ -3593,20 +3594,20 @@
       </c>
       <c r="B69" s="13"/>
       <c r="C69" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="E69" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="D69" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="E69" s="4" t="s">
+      <c r="F69" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>304</v>
       </c>
       <c r="G69" s="4"/>
       <c r="H69" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I69" s="4"/>
     </row>
@@ -3616,20 +3617,20 @@
       </c>
       <c r="B70" s="13"/>
       <c r="C70" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="D70" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="D70" s="5" t="s">
-        <v>348</v>
-      </c>
       <c r="E70" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F70" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>150</v>
       </c>
       <c r="G70" s="4"/>
       <c r="H70" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I70" s="4"/>
     </row>
@@ -3639,20 +3640,20 @@
       </c>
       <c r="B71" s="13"/>
       <c r="C71" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G71" s="4"/>
       <c r="H71" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I71" s="4"/>
     </row>
@@ -3661,23 +3662,23 @@
         <v>71</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D72" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="F72" s="4" t="s">
         <v>328</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>329</v>
       </c>
       <c r="G72" s="4"/>
       <c r="H72" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I72" s="4"/>
     </row>
@@ -3687,20 +3688,20 @@
       </c>
       <c r="B73" s="12"/>
       <c r="C73" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="F73" s="4" t="s">
         <v>330</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>331</v>
       </c>
       <c r="G73" s="4"/>
       <c r="H73" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I73" s="4"/>
     </row>
@@ -3710,20 +3711,20 @@
       </c>
       <c r="B74" s="12"/>
       <c r="C74" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G74" s="4"/>
       <c r="H74" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I74" s="4"/>
     </row>
@@ -3733,20 +3734,20 @@
       </c>
       <c r="B75" s="12"/>
       <c r="C75" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E75" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="F75" s="4" t="s">
         <v>341</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>342</v>
       </c>
       <c r="G75" s="4"/>
       <c r="H75" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I75" s="4"/>
     </row>
@@ -3757,17 +3758,17 @@
       <c r="B76" s="12"/>
       <c r="C76" s="12"/>
       <c r="D76" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="F76" s="4" t="s">
         <v>350</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>351</v>
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I76" s="4"/>
     </row>
@@ -3778,17 +3779,17 @@
       <c r="B77" s="12"/>
       <c r="C77" s="12"/>
       <c r="D77" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="E77" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="E77" s="4" t="s">
+      <c r="F77" s="4" t="s">
         <v>341</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>342</v>
       </c>
       <c r="G77" s="4"/>
       <c r="H77" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I77" s="4"/>
     </row>
@@ -3797,23 +3798,23 @@
         <v>77</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C78" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E78" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F78" s="5" t="s">
         <v>358</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>359</v>
       </c>
       <c r="G78" s="4"/>
       <c r="H78" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I78" s="4"/>
     </row>
@@ -3826,17 +3827,17 @@
         <v>50</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G79" s="4"/>
       <c r="H79" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I79" s="4"/>
     </row>
@@ -3849,17 +3850,17 @@
         <v>52</v>
       </c>
       <c r="D80" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="F80" s="5" t="s">
         <v>360</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>361</v>
       </c>
       <c r="G80" s="4"/>
       <c r="H80" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I80" s="4"/>
     </row>
@@ -3872,17 +3873,17 @@
         <v>53</v>
       </c>
       <c r="D81" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="F81" s="5" t="s">
         <v>362</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>363</v>
       </c>
       <c r="G81" s="4"/>
       <c r="H81" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I81" s="4"/>
     </row>
@@ -3895,17 +3896,17 @@
         <v>54</v>
       </c>
       <c r="D82" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="E82" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="E82" s="5" t="s">
-        <v>365</v>
-      </c>
       <c r="F82" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G82" s="4"/>
       <c r="H82" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I82" s="4"/>
     </row>
@@ -3923,14 +3924,14 @@
         <v>61</v>
       </c>
       <c r="E83" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F83" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>154</v>
       </c>
       <c r="G83" s="4"/>
       <c r="H83" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I83" s="4"/>
     </row>
@@ -3944,14 +3945,14 @@
         <v>62</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G84" s="4"/>
       <c r="H84" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I84" s="4"/>
     </row>
@@ -3963,20 +3964,20 @@
         <v>55</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>56</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G85" s="4"/>
       <c r="H85" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I85" s="4"/>
     </row>
@@ -3990,14 +3991,14 @@
         <v>57</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I86" s="4"/>
     </row>
@@ -4011,14 +4012,14 @@
         <v>58</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G87" s="4"/>
       <c r="H87" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I87" s="4"/>
     </row>
@@ -4027,23 +4028,23 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="C88" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="C88" s="7" t="s">
-        <v>353</v>
-      </c>
       <c r="D88" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F88" s="5" t="s">
         <v>158</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>159</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I88" s="4"/>
     </row>
@@ -4052,23 +4053,23 @@
         <v>88</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>63</v>
       </c>
       <c r="E89" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F89" s="5" t="s">
         <v>160</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>161</v>
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I89" s="4"/>
     </row>
@@ -4082,14 +4083,14 @@
         <v>64</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I90" s="4"/>
     </row>
@@ -4103,14 +4104,14 @@
         <v>65</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I91" s="4"/>
     </row>
@@ -4120,7 +4121,7 @@
       </c>
       <c r="B92" s="10"/>
       <c r="C92" s="12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>66</v>
@@ -4133,7 +4134,7 @@
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I92" s="4"/>
     </row>
@@ -4154,7 +4155,7 @@
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I93" s="4"/>
     </row>
@@ -4175,7 +4176,7 @@
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I94" s="4"/>
     </row>
@@ -4183,16 +4184,16 @@
       <c r="A95" s="4"/>
       <c r="B95" s="11"/>
       <c r="C95" s="7" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
@@ -4206,20 +4207,20 @@
         <v>75</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="G96" s="4"/>
       <c r="H96" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I96" s="4"/>
     </row>
@@ -4229,20 +4230,20 @@
       </c>
       <c r="B97" s="12"/>
       <c r="C97" s="12" t="s">
-        <v>373</v>
+        <v>396</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>76</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I97" s="4"/>
     </row>
@@ -4256,14 +4257,14 @@
         <v>77</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I98" s="4"/>
     </row>
@@ -4277,14 +4278,14 @@
         <v>78</v>
       </c>
       <c r="E99" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F99" s="4" t="s">
         <v>165</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>166</v>
       </c>
       <c r="G99" s="4"/>
       <c r="H99" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I99" s="4"/>
     </row>
@@ -4294,20 +4295,20 @@
       </c>
       <c r="B100" s="12"/>
       <c r="C100" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F100" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E100" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>81</v>
       </c>
       <c r="G100" s="4"/>
       <c r="H100" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I100" s="4"/>
     </row>
@@ -4318,17 +4319,17 @@
       <c r="B101" s="12"/>
       <c r="C101" s="12"/>
       <c r="D101" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G101" s="4"/>
       <c r="H101" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I101" s="4"/>
     </row>
@@ -4338,20 +4339,20 @@
       </c>
       <c r="B102" s="12"/>
       <c r="C102" s="12" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I102" s="4"/>
     </row>
@@ -4362,17 +4363,17 @@
       <c r="B103" s="12"/>
       <c r="C103" s="12"/>
       <c r="D103" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I103" s="4"/>
     </row>
@@ -4383,17 +4384,17 @@
       <c r="B104" s="12"/>
       <c r="C104" s="12"/>
       <c r="D104" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I104" s="4"/>
     </row>
@@ -4403,20 +4404,20 @@
       </c>
       <c r="B105" s="12"/>
       <c r="C105" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="E105" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="D105" s="4" t="s">
+      <c r="F105" s="4" t="s">
         <v>387</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>391</v>
       </c>
       <c r="G105" s="4"/>
       <c r="H105" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I105" s="4"/>
     </row>
@@ -4427,17 +4428,17 @@
       <c r="B106" s="12"/>
       <c r="C106" s="12"/>
       <c r="D106" s="4" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="G106" s="4"/>
       <c r="H106" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I106" s="4"/>
     </row>
@@ -4447,20 +4448,20 @@
       </c>
       <c r="B107" s="12"/>
       <c r="C107" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F107" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="D107" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E107" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="F107" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="G107" s="4"/>
       <c r="H107" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I107" s="4"/>
     </row>
@@ -4471,17 +4472,17 @@
       <c r="B108" s="12"/>
       <c r="C108" s="12"/>
       <c r="D108" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G108" s="4"/>
       <c r="H108" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I108" s="4"/>
     </row>
@@ -4491,20 +4492,20 @@
       </c>
       <c r="B109" s="12"/>
       <c r="C109" s="12" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E109" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F109" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="F109" s="4" t="s">
-        <v>168</v>
       </c>
       <c r="G109" s="4"/>
       <c r="H109" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I109" s="4"/>
     </row>
@@ -4515,17 +4516,17 @@
       <c r="B110" s="12"/>
       <c r="C110" s="12"/>
       <c r="D110" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E110" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F110" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="F110" s="4" t="s">
-        <v>168</v>
       </c>
       <c r="G110" s="4"/>
       <c r="H110" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I110" s="4"/>
     </row>
@@ -4536,17 +4537,17 @@
       <c r="B111" s="12"/>
       <c r="C111" s="12"/>
       <c r="D111" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E111" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F111" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="F111" s="4" t="s">
-        <v>168</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I111" s="4"/>
     </row>
@@ -4556,20 +4557,20 @@
       </c>
       <c r="B112" s="12"/>
       <c r="C112" s="7" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>79</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G112" s="4"/>
       <c r="H112" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I112" s="4"/>
     </row>
@@ -4578,23 +4579,23 @@
         <v>111</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G113" s="4"/>
       <c r="H113" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I113" s="4"/>
     </row>
@@ -4604,20 +4605,20 @@
       </c>
       <c r="B114" s="12"/>
       <c r="C114" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G114" s="4"/>
       <c r="H114" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I114" s="4"/>
     </row>
@@ -4627,20 +4628,20 @@
       </c>
       <c r="B115" s="12"/>
       <c r="C115" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G115" s="4"/>
       <c r="H115" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I115" s="4"/>
     </row>
@@ -4650,20 +4651,20 @@
       </c>
       <c r="B116" s="12"/>
       <c r="C116" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G116" s="4"/>
       <c r="H116" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I116" s="4"/>
     </row>
@@ -4672,23 +4673,23 @@
         <v>115</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E117" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F117" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="F117" s="4" t="s">
-        <v>174</v>
       </c>
       <c r="G117" s="4"/>
       <c r="H117" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I117" s="4"/>
     </row>
@@ -4699,17 +4700,17 @@
       <c r="B118" s="12"/>
       <c r="C118" s="12"/>
       <c r="D118" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G118" s="4"/>
       <c r="H118" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I118" s="4"/>
     </row>
@@ -4720,17 +4721,17 @@
       <c r="B119" s="12"/>
       <c r="C119" s="12"/>
       <c r="D119" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G119" s="4"/>
       <c r="H119" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I119" s="4"/>
     </row>
@@ -4739,23 +4740,23 @@
         <v>118</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I120" s="4"/>
     </row>
@@ -4765,20 +4766,20 @@
       </c>
       <c r="B121" s="12"/>
       <c r="C121" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D121" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D121" s="4" t="s">
-        <v>105</v>
-      </c>
       <c r="E121" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="F121" s="4" t="s">
         <v>176</v>
-      </c>
-      <c r="F121" s="4" t="s">
-        <v>177</v>
       </c>
       <c r="G121" s="4"/>
       <c r="H121" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I121" s="4"/>
     </row>
@@ -4788,20 +4789,20 @@
       </c>
       <c r="B122" s="12"/>
       <c r="C122" s="7" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G122" s="4"/>
       <c r="H122" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I122" s="4"/>
     </row>
@@ -4811,20 +4812,20 @@
       </c>
       <c r="B123" s="12"/>
       <c r="C123" s="7" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E123" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F123" s="4" t="s">
         <v>179</v>
-      </c>
-      <c r="F123" s="4" t="s">
-        <v>180</v>
       </c>
       <c r="G123" s="4"/>
       <c r="H123" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I123" s="4"/>
     </row>
@@ -4834,20 +4835,20 @@
       </c>
       <c r="B124" s="12"/>
       <c r="C124" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D124" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D124" s="4" t="s">
-        <v>103</v>
-      </c>
       <c r="E124" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F124" s="4" t="s">
         <v>181</v>
-      </c>
-      <c r="F124" s="4" t="s">
-        <v>182</v>
       </c>
       <c r="G124" s="4"/>
       <c r="H124" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I124" s="4"/>
     </row>
@@ -4857,20 +4858,20 @@
       </c>
       <c r="B125" s="12"/>
       <c r="C125" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G125" s="4"/>
       <c r="H125" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I125" s="4"/>
     </row>
@@ -4881,17 +4882,17 @@
       <c r="B126" s="12"/>
       <c r="C126" s="12"/>
       <c r="D126" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G126" s="4"/>
       <c r="H126" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I126" s="4"/>
     </row>
@@ -4902,17 +4903,17 @@
       <c r="B127" s="12"/>
       <c r="C127" s="12"/>
       <c r="D127" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G127" s="4"/>
       <c r="H127" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I127" s="4"/>
     </row>
@@ -4922,20 +4923,20 @@
       </c>
       <c r="B128" s="12"/>
       <c r="C128" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D128" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G128" s="4"/>
       <c r="H128" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I128" s="4"/>
     </row>
@@ -4946,17 +4947,17 @@
       <c r="B129" s="12"/>
       <c r="C129" s="12"/>
       <c r="D129" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G129" s="4"/>
       <c r="H129" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I129" s="4"/>
     </row>
@@ -4967,36 +4968,36 @@
       <c r="B130" s="12"/>
       <c r="C130" s="12"/>
       <c r="D130" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G130" s="4"/>
       <c r="H130" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I130" s="4"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="4"/>
       <c r="B131" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D131" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G131" s="4"/>
       <c r="H131" s="4"/>
@@ -5007,13 +5008,13 @@
       <c r="B132" s="10"/>
       <c r="C132" s="12"/>
       <c r="D132" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G132" s="4"/>
       <c r="H132" s="4"/>
@@ -5024,13 +5025,13 @@
       <c r="B133" s="10"/>
       <c r="C133" s="12"/>
       <c r="D133" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G133" s="4"/>
       <c r="H133" s="4"/>
@@ -5042,20 +5043,20 @@
       </c>
       <c r="B134" s="10"/>
       <c r="C134" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G134" s="4"/>
       <c r="H134" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I134" s="4"/>
     </row>
@@ -5065,20 +5066,20 @@
       </c>
       <c r="B135" s="10"/>
       <c r="C135" s="12" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G135" s="4"/>
       <c r="H135" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I135" s="4"/>
     </row>
@@ -5089,17 +5090,17 @@
       <c r="B136" s="10"/>
       <c r="C136" s="12"/>
       <c r="D136" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G136" s="4"/>
       <c r="H136" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I136" s="4"/>
     </row>
@@ -5110,17 +5111,17 @@
       <c r="B137" s="11"/>
       <c r="C137" s="12"/>
       <c r="D137" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G137" s="4"/>
       <c r="H137" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I137" s="4"/>
     </row>
@@ -5129,23 +5130,23 @@
         <v>136</v>
       </c>
       <c r="B138" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C138" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="C138" s="7" t="s">
+      <c r="D138" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D138" s="4" t="s">
-        <v>113</v>
-      </c>
       <c r="E138" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G138" s="4"/>
       <c r="H138" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I138" s="4"/>
     </row>
@@ -5155,20 +5156,20 @@
       </c>
       <c r="B139" s="12"/>
       <c r="C139" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G139" s="4"/>
       <c r="H139" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I139" s="4"/>
     </row>
@@ -5177,23 +5178,23 @@
         <v>138</v>
       </c>
       <c r="B140" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D140" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C140" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="D140" s="4" t="s">
-        <v>120</v>
-      </c>
       <c r="E140" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G140" s="4"/>
       <c r="H140" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I140" s="4"/>
     </row>
@@ -5202,23 +5203,23 @@
         <v>139</v>
       </c>
       <c r="B141" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C141" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="C141" s="12" t="s">
+      <c r="D141" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D141" s="4" t="s">
-        <v>123</v>
-      </c>
       <c r="E141" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G141" s="4"/>
       <c r="H141" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I141" s="4"/>
     </row>
@@ -5229,17 +5230,17 @@
       <c r="B142" s="12"/>
       <c r="C142" s="12"/>
       <c r="D142" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G142" s="4"/>
       <c r="H142" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I142" s="4"/>
     </row>
@@ -5250,17 +5251,17 @@
       <c r="B143" s="12"/>
       <c r="C143" s="12"/>
       <c r="D143" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G143" s="4"/>
       <c r="H143" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I143" s="4"/>
     </row>
@@ -5273,17 +5274,17 @@
         <v>26</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E144" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="F144" s="4" t="s">
         <v>193</v>
-      </c>
-      <c r="F144" s="4" t="s">
-        <v>194</v>
       </c>
       <c r="G144" s="4"/>
       <c r="H144" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I144" s="4"/>
     </row>
@@ -5294,17 +5295,17 @@
       <c r="B145" s="12"/>
       <c r="C145" s="12"/>
       <c r="D145" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G145" s="4"/>
       <c r="H145" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I145" s="4"/>
     </row>
@@ -5313,23 +5314,23 @@
         <v>144</v>
       </c>
       <c r="B146" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C146" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="C146" s="8" t="s">
+      <c r="D146" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="D146" s="4" t="s">
+      <c r="E146" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F146" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="E146" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="F146" s="4" t="s">
-        <v>200</v>
       </c>
       <c r="G146" s="4"/>
       <c r="H146" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I146" s="4"/>
     </row>

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7FEDEA1-01B7-4F21-ACCE-B5A3F5CD33BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64927988-4893-4F8C-B2C9-EC2E717EE1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{F425FBA8-E65A-4F03-9270-551F3EA7C4F5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="394">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -159,18 +159,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>活动入口关闭时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>活动时间文本</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>活动时间配置表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>活动入口跳转</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -540,10 +528,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>与活动时间配置表比对查看</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>活动页面开启</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -556,10 +540,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>活动时间文本没问题</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>P2</t>
   </si>
   <si>
@@ -1605,6 +1585,10 @@
   </si>
   <si>
     <t>点赞记录-点赞记录弹窗功能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动入口异常跳转测试</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2095,10 +2079,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DF7E13A-4D63-4E82-9598-D598C8858D86}">
-  <dimension ref="A1:I146"/>
+  <dimension ref="A1:I145"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" customWidth="1"/>
     <col min="3" max="3" width="81.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="94" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="53.44140625" bestFit="1" customWidth="1"/>
@@ -2149,14 +2133,14 @@
         <v>11</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I2" s="4"/>
     </row>
@@ -2170,14 +2154,14 @@
         <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I3" s="4"/>
     </row>
@@ -2191,14 +2175,14 @@
         <v>13</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I4" s="4"/>
     </row>
@@ -2214,14 +2198,14 @@
         <v>15</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I5" s="4"/>
     </row>
@@ -2232,17 +2216,17 @@
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
       <c r="D6" s="4" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -2256,685 +2240,683 @@
         <v>16</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="12"/>
-      <c r="C8" s="7" t="s">
-        <v>32</v>
+      <c r="C8" s="12" t="s">
+        <v>17</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>128</v>
+        <v>199</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>132</v>
+        <v>387</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="I8" s="4"/>
+        <v>128</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="12"/>
-      <c r="C9" s="12" t="s">
-        <v>17</v>
-      </c>
+      <c r="C9" s="12"/>
       <c r="D9" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>225</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
       <c r="D10" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
+      <c r="C11" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="D11" s="4" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>393</v>
+        <v>131</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I11" s="4"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
-        <v>11</v>
-      </c>
-      <c r="B12" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="C12" s="7" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>205</v>
+        <v>133</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>136</v>
+        <v>386</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <v>12</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>21</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B13" s="12"/>
       <c r="C13" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>391</v>
+        <v>125</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" s="12"/>
       <c r="C14" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" s="12"/>
       <c r="C15" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>28</v>
+        <v>214</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>129</v>
+        <v>222</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <v>15</v>
-      </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="7" t="s">
-        <v>26</v>
+        <v>16</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>30</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>227</v>
+        <v>11</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>201</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>129</v>
+        <v>195</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <v>16</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>30</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
       <c r="D17" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
       <c r="D18" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
+      <c r="C19" s="7" t="s">
+        <v>223</v>
+      </c>
       <c r="D19" s="4" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="7" t="s">
-        <v>228</v>
+        <v>34</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" s="12"/>
       <c r="C21" s="7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I21" s="4"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" s="12"/>
       <c r="C22" s="7" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" s="12"/>
-      <c r="C23" s="7" t="s">
-        <v>34</v>
+      <c r="C23" s="9" t="s">
+        <v>393</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I23" s="4"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" s="12"/>
-      <c r="C24" s="12" t="s">
-        <v>31</v>
-      </c>
+      <c r="C24" s="10"/>
       <c r="D24" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
+      <c r="C25" s="11"/>
       <c r="D25" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
+      <c r="C26" s="12" t="s">
+        <v>41</v>
+      </c>
       <c r="D26" s="4" t="s">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I26" s="4"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" s="12"/>
-      <c r="C27" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>221</v>
+      <c r="C27" s="12"/>
+      <c r="D27" s="6" t="s">
+        <v>217</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>224</v>
+        <v>135</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I27" s="4"/>
     </row>
-    <row r="28" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
-        <v>27</v>
-      </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="6" t="s">
-        <v>222</v>
+        <v>28</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="4" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="I28" s="4"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
-        <v>28</v>
-      </c>
-      <c r="B29" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="12"/>
+      <c r="C29" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="7" t="s">
-        <v>40</v>
-      </c>
       <c r="D29" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I29" s="4"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" s="12"/>
       <c r="C30" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I30" s="4"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" s="12"/>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="9" t="s">
         <v>43</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>234</v>
+        <v>136</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>237</v>
+        <v>139</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="4" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="I31" s="4"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" s="12"/>
-      <c r="C32" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="C32" s="10"/>
       <c r="D32" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I32" s="4"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" s="12"/>
       <c r="C33" s="10"/>
       <c r="D33" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I33" s="4"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34" s="12"/>
       <c r="C34" s="10"/>
       <c r="D34" s="4" t="s">
-        <v>49</v>
+        <v>375</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" s="12"/>
-      <c r="C35" s="10"/>
+      <c r="C35" s="11"/>
       <c r="D35" s="4" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I35" s="4"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
-        <v>35</v>
-      </c>
-      <c r="B36" s="12"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="4" t="s">
-        <v>381</v>
+        <v>36</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>233</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>146</v>
+        <v>237</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>144</v>
+        <v>235</v>
       </c>
       <c r="G36" s="4"/>
-      <c r="H36" s="4" t="s">
-        <v>137</v>
-      </c>
+      <c r="H36" s="4"/>
       <c r="I36" s="4"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
-        <v>36</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>241</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B37" s="12"/>
       <c r="C37" s="7" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>238</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>240</v>
@@ -2945,20 +2927,20 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" s="12"/>
       <c r="C38" s="7" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -2966,20 +2948,20 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" s="12"/>
       <c r="C39" s="7" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D39" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>246</v>
-      </c>
       <c r="F39" s="5" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
@@ -2987,20 +2969,20 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" s="12"/>
-      <c r="C40" s="7" t="s">
-        <v>262</v>
+      <c r="C40" s="12" t="s">
+        <v>250</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
@@ -3008,20 +2990,18 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" s="12"/>
-      <c r="C41" s="12" t="s">
-        <v>255</v>
-      </c>
+      <c r="C41" s="12"/>
       <c r="D41" s="5" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
@@ -3029,18 +3009,18 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
       <c r="D42" s="5" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -3048,18 +3028,20 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
+      <c r="C43" s="7" t="s">
+        <v>263</v>
+      </c>
       <c r="D43" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E43" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="F43" s="5" t="s">
         <v>265</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>247</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
@@ -3067,20 +3049,20 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44" s="12"/>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="F44" s="5" t="s">
         <v>268</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>270</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
@@ -3088,20 +3070,18 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B45" s="12"/>
-      <c r="C45" s="12" t="s">
-        <v>256</v>
-      </c>
+      <c r="C45" s="12"/>
       <c r="D45" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
@@ -3109,18 +3089,18 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
       <c r="D46" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="F46" s="5" t="s">
         <v>271</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>273</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -3128,18 +3108,18 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
       <c r="D47" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="F47" s="5" t="s">
         <v>271</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>276</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
@@ -3147,18 +3127,20 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B48" s="12"/>
-      <c r="C48" s="12"/>
+      <c r="C48" s="12" t="s">
+        <v>252</v>
+      </c>
       <c r="D48" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
@@ -3166,20 +3148,18 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B49" s="12"/>
-      <c r="C49" s="12" t="s">
-        <v>257</v>
-      </c>
+      <c r="C49" s="12"/>
       <c r="D49" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="F49" s="5" t="s">
         <v>271</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>273</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
@@ -3187,18 +3167,18 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
       <c r="D50" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="F50" s="5" t="s">
         <v>271</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>276</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
@@ -3206,18 +3186,20 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B51" s="12"/>
-      <c r="C51" s="12"/>
+      <c r="C51" s="12" t="s">
+        <v>253</v>
+      </c>
       <c r="D51" s="5" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -3225,17 +3207,15 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B52" s="12"/>
-      <c r="C52" s="12" t="s">
-        <v>258</v>
-      </c>
+      <c r="C52" s="12"/>
       <c r="D52" s="5" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>282</v>
@@ -3246,18 +3226,18 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
       <c r="D53" s="5" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -3265,18 +3245,18 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
       <c r="D54" s="5" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
@@ -3284,18 +3264,18 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B55" s="12"/>
       <c r="C55" s="12"/>
       <c r="D55" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="E55" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="E55" s="5" t="s">
-        <v>292</v>
-      </c>
       <c r="F55" s="5" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
@@ -3303,18 +3283,18 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B56" s="12"/>
       <c r="C56" s="12"/>
       <c r="D56" s="5" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E56" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F56" s="5" t="s">
         <v>286</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>290</v>
       </c>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
@@ -3322,15 +3302,17 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B57" s="12"/>
-      <c r="C57" s="12"/>
+      <c r="C57" s="7" t="s">
+        <v>289</v>
+      </c>
       <c r="D57" s="5" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>291</v>
@@ -3341,20 +3323,20 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B58" s="12"/>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="F58" s="5" t="s">
         <v>294</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>296</v>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
@@ -3362,20 +3344,18 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B59" s="12"/>
-      <c r="C59" s="12" t="s">
-        <v>259</v>
-      </c>
+      <c r="C59" s="12"/>
       <c r="D59" s="5" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
@@ -3383,18 +3363,22 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
-        <v>59</v>
-      </c>
-      <c r="B60" s="12"/>
-      <c r="C60" s="12"/>
+        <v>60</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>245</v>
+      </c>
       <c r="D60" s="5" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>299</v>
+        <v>248</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
@@ -3402,268 +3386,268 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
-        <v>60</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>254</v>
+        <v>61</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>300</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>253</v>
+        <v>301</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>304</v>
       </c>
       <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
+      <c r="H61" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="I61" s="4"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
-        <v>61</v>
-      </c>
-      <c r="B62" s="12" t="s">
-        <v>305</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B62" s="12"/>
       <c r="C62" s="7" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I62" s="4"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B63" s="12"/>
       <c r="C63" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>307</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>309</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I63" s="4"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B64" s="12"/>
-      <c r="C64" s="7" t="s">
+      <c r="C64" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="D64" s="4" t="s">
-        <v>313</v>
-      </c>
       <c r="E64" s="4" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="I64" s="4"/>
+        <v>128</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B65" s="12"/>
-      <c r="C65" s="12" t="s">
+      <c r="C65" s="12"/>
+      <c r="D65" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="D65" s="4" t="s">
-        <v>315</v>
-      </c>
       <c r="E65" s="4" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="G65" s="4"/>
       <c r="H65" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="I65" s="4" t="s">
-        <v>210</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="I65" s="4"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B66" s="12"/>
-      <c r="C66" s="12"/>
+      <c r="C66" s="7" t="s">
+        <v>313</v>
+      </c>
       <c r="D66" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="F66" s="4" t="s">
         <v>316</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>314</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I66" s="4"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
-        <v>66</v>
-      </c>
-      <c r="B67" s="12"/>
+        <v>67</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>337</v>
+      </c>
       <c r="C67" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>319</v>
+        <v>339</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>338</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>320</v>
+        <v>145</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>321</v>
+        <v>144</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I67" s="4"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
-        <v>67</v>
-      </c>
-      <c r="B68" s="13" t="s">
-        <v>342</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="B68" s="13"/>
       <c r="C68" s="7" t="s">
-        <v>344</v>
+        <v>296</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>150</v>
+        <v>297</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>149</v>
+        <v>298</v>
       </c>
       <c r="G68" s="4"/>
       <c r="H68" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I68" s="4"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B69" s="13"/>
       <c r="C69" s="7" t="s">
-        <v>301</v>
+        <v>341</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>302</v>
+        <v>143</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>303</v>
+        <v>144</v>
       </c>
       <c r="G69" s="4"/>
       <c r="H69" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B70" s="13"/>
       <c r="C70" s="7" t="s">
-        <v>346</v>
+        <v>124</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="G70" s="4"/>
       <c r="H70" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I70" s="4"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
-        <v>70</v>
-      </c>
-      <c r="B71" s="13"/>
+        <v>71</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>317</v>
+      </c>
       <c r="C71" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>348</v>
+        <v>319</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>322</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>195</v>
+        <v>321</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>174</v>
+        <v>323</v>
       </c>
       <c r="G71" s="4"/>
       <c r="H71" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I71" s="4"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
-        <v>71</v>
-      </c>
-      <c r="B72" s="12" t="s">
-        <v>322</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="B72" s="12"/>
       <c r="C72" s="7" t="s">
         <v>324</v>
       </c>
@@ -3671,458 +3655,456 @@
         <v>327</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="G72" s="4"/>
       <c r="H72" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I72" s="4"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B73" s="12"/>
       <c r="C73" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="F73" s="4" t="s">
         <v>329</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>330</v>
       </c>
       <c r="G73" s="4"/>
       <c r="H73" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I73" s="4"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B74" s="12"/>
-      <c r="C74" s="7" t="s">
-        <v>325</v>
+      <c r="C74" s="12" t="s">
+        <v>318</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>335</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="G74" s="4"/>
       <c r="H74" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I74" s="4"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B75" s="12"/>
-      <c r="C75" s="12" t="s">
-        <v>323</v>
-      </c>
+      <c r="C75" s="12"/>
       <c r="D75" s="4" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="G75" s="4"/>
       <c r="H75" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I75" s="4"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B76" s="12"/>
       <c r="C76" s="12"/>
       <c r="D76" s="4" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I76" s="4"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
-        <v>76</v>
-      </c>
-      <c r="B77" s="12"/>
-      <c r="C77" s="12"/>
-      <c r="D77" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>341</v>
+        <v>77</v>
+      </c>
+      <c r="B77" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>353</v>
       </c>
       <c r="G77" s="4"/>
       <c r="H77" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I77" s="4"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
-        <v>77</v>
-      </c>
-      <c r="B78" s="12" t="s">
-        <v>337</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="B78" s="12"/>
       <c r="C78" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>358</v>
+        <v>146</v>
       </c>
       <c r="G78" s="4"/>
       <c r="H78" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I78" s="4"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B79" s="12"/>
       <c r="C79" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>151</v>
+        <v>355</v>
       </c>
       <c r="G79" s="4"/>
       <c r="H79" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I79" s="4"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B80" s="12"/>
       <c r="C80" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D80" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="E80" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="E80" s="5" t="s">
-        <v>364</v>
-      </c>
       <c r="F80" s="5" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="G80" s="4"/>
       <c r="H80" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I80" s="4"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B81" s="12"/>
       <c r="C81" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="G81" s="4"/>
       <c r="H81" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I81" s="4"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
-        <v>81</v>
-      </c>
-      <c r="B82" s="12"/>
-      <c r="C82" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>363</v>
+        <v>82</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="F82" s="5" t="s">
-        <v>360</v>
+        <v>147</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>148</v>
       </c>
       <c r="G82" s="4"/>
       <c r="H82" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I82" s="4"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
-        <v>82</v>
-      </c>
-      <c r="B83" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B83" s="12"/>
+      <c r="C83" s="12"/>
+      <c r="D83" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C83" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>61</v>
-      </c>
       <c r="E83" s="5" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="G83" s="4"/>
       <c r="H83" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I83" s="4"/>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
-        <v>83</v>
-      </c>
-      <c r="B84" s="12"/>
-      <c r="C84" s="12"/>
+        <v>84</v>
+      </c>
+      <c r="B84" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>348</v>
+      </c>
       <c r="D84" s="4" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>152</v>
+        <v>206</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="G84" s="4"/>
       <c r="H84" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I84" s="4"/>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
-        <v>84</v>
-      </c>
-      <c r="B85" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C85" s="12" t="s">
-        <v>353</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="B85" s="12"/>
+      <c r="C85" s="12"/>
       <c r="D85" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G85" s="4"/>
       <c r="H85" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I85" s="4"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B86" s="12"/>
       <c r="C86" s="12"/>
       <c r="D86" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I86" s="4"/>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
-        <v>86</v>
-      </c>
-      <c r="B87" s="12"/>
-      <c r="C87" s="12"/>
-      <c r="D87" s="4" t="s">
-        <v>58</v>
+        <v>87</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>152</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>156</v>
+        <v>133</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>153</v>
       </c>
       <c r="G87" s="4"/>
       <c r="H87" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I87" s="4"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
-        <v>87</v>
-      </c>
-      <c r="B88" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>157</v>
+        <v>88</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I88" s="4"/>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
-        <v>88</v>
-      </c>
-      <c r="B89" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="C89" s="12" t="s">
-        <v>388</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="B89" s="10"/>
+      <c r="C89" s="12"/>
       <c r="D89" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I89" s="4"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B90" s="10"/>
       <c r="C90" s="12"/>
       <c r="D90" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I90" s="4"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B91" s="10"/>
-      <c r="C91" s="12"/>
+      <c r="C91" s="12" t="s">
+        <v>349</v>
+      </c>
       <c r="D91" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F91" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>161</v>
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I91" s="4"/>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B92" s="10"/>
-      <c r="C92" s="12" t="s">
-        <v>354</v>
-      </c>
+      <c r="C92" s="12"/>
       <c r="D92" s="4" t="s">
         <v>66</v>
       </c>
@@ -4134,13 +4116,13 @@
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I92" s="4"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B93" s="10"/>
       <c r="C93" s="12"/>
@@ -4155,1237 +4137,1224 @@
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I93" s="4"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
-        <v>93</v>
-      </c>
-      <c r="B94" s="10"/>
-      <c r="C94" s="12"/>
+        <v>94</v>
+      </c>
+      <c r="B94" s="11"/>
+      <c r="C94" s="7" t="s">
+        <v>384</v>
+      </c>
       <c r="D94" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G94" s="4"/>
+      <c r="H94" s="4"/>
+      <c r="I94" s="4"/>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="4">
+        <v>95</v>
+      </c>
+      <c r="B95" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="E94" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G94" s="4"/>
-      <c r="H94" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="I94" s="4"/>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="4"/>
-      <c r="B95" s="11"/>
       <c r="C95" s="7" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>147</v>
+        <v>373</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>174</v>
+        <v>374</v>
       </c>
       <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
+      <c r="H95" s="4" t="s">
+        <v>129</v>
+      </c>
       <c r="I95" s="4"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
-        <v>94</v>
-      </c>
-      <c r="B96" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>397</v>
+        <v>96</v>
+      </c>
+      <c r="B96" s="12"/>
+      <c r="C96" s="12" t="s">
+        <v>391</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>377</v>
+        <v>73</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>378</v>
+        <v>157</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>379</v>
+        <v>160</v>
       </c>
       <c r="G96" s="4"/>
       <c r="H96" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I96" s="4"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B97" s="12"/>
-      <c r="C97" s="12" t="s">
-        <v>396</v>
-      </c>
+      <c r="C97" s="12"/>
       <c r="D97" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I97" s="4"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B98" s="12"/>
       <c r="C98" s="12"/>
       <c r="D98" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I98" s="4"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B99" s="12"/>
-      <c r="C99" s="12"/>
+      <c r="C99" s="12" t="s">
+        <v>390</v>
+      </c>
       <c r="D99" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="G99" s="4"/>
       <c r="H99" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I99" s="4"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B100" s="12"/>
-      <c r="C100" s="12" t="s">
-        <v>395</v>
-      </c>
+      <c r="C100" s="12"/>
       <c r="D100" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G100" s="4"/>
       <c r="H100" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I100" s="4"/>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B101" s="12"/>
-      <c r="C101" s="12"/>
+      <c r="C101" s="12" t="s">
+        <v>389</v>
+      </c>
       <c r="D101" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="G101" s="4"/>
       <c r="H101" s="4" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="I101" s="4"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B102" s="12"/>
-      <c r="C102" s="12" t="s">
-        <v>394</v>
-      </c>
+      <c r="C102" s="12"/>
       <c r="D102" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I102" s="4"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B103" s="12"/>
       <c r="C103" s="12"/>
       <c r="D103" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I103" s="4"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B104" s="12"/>
-      <c r="C104" s="12"/>
+      <c r="C104" s="12" t="s">
+        <v>377</v>
+      </c>
       <c r="D104" s="4" t="s">
-        <v>95</v>
+        <v>378</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>166</v>
+        <v>381</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I104" s="4"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B105" s="12"/>
-      <c r="C105" s="12" t="s">
+      <c r="C105" s="12"/>
+      <c r="D105" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="F105" s="4" t="s">
         <v>382</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>387</v>
       </c>
       <c r="G105" s="4"/>
       <c r="H105" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I105" s="4"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B106" s="12"/>
-      <c r="C106" s="12"/>
+      <c r="C106" s="12" t="s">
+        <v>79</v>
+      </c>
       <c r="D106" s="4" t="s">
-        <v>384</v>
+        <v>82</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>385</v>
+        <v>161</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>387</v>
+        <v>80</v>
       </c>
       <c r="G106" s="4"/>
       <c r="H106" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I106" s="4"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B107" s="12"/>
-      <c r="C107" s="12" t="s">
+      <c r="C107" s="12"/>
+      <c r="D107" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D107" s="4" t="s">
-        <v>85</v>
-      </c>
       <c r="E107" s="4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G107" s="4"/>
       <c r="H107" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I107" s="4"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B108" s="12"/>
-      <c r="C108" s="12"/>
+      <c r="C108" s="12" t="s">
+        <v>360</v>
+      </c>
       <c r="D108" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>84</v>
+        <v>162</v>
       </c>
       <c r="G108" s="4"/>
       <c r="H108" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I108" s="4"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B109" s="12"/>
-      <c r="C109" s="12" t="s">
-        <v>365</v>
-      </c>
+      <c r="C109" s="12"/>
       <c r="D109" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G109" s="4"/>
       <c r="H109" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I109" s="4"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B110" s="12"/>
       <c r="C110" s="12"/>
       <c r="D110" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G110" s="4"/>
       <c r="H110" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I110" s="4"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B111" s="12"/>
-      <c r="C111" s="12"/>
+      <c r="C111" s="7" t="s">
+        <v>367</v>
+      </c>
       <c r="D111" s="4" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I111" s="4"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
-        <v>110</v>
-      </c>
-      <c r="B112" s="12"/>
+        <v>112</v>
+      </c>
+      <c r="B112" s="12" t="s">
+        <v>83</v>
+      </c>
       <c r="C112" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>79</v>
+        <v>208</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>370</v>
       </c>
       <c r="E112" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F112" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="F112" s="4" t="s">
-        <v>168</v>
       </c>
       <c r="G112" s="4"/>
       <c r="H112" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I112" s="4"/>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
-        <v>111</v>
-      </c>
-      <c r="B113" s="12" t="s">
-        <v>86</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="B113" s="12"/>
       <c r="C113" s="7" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G113" s="4"/>
       <c r="H113" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I113" s="4"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="4">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B114" s="12"/>
       <c r="C114" s="7" t="s">
-        <v>212</v>
+        <v>84</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G114" s="4"/>
       <c r="H114" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I114" s="4"/>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B115" s="12"/>
       <c r="C115" s="7" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>171</v>
+        <v>221</v>
       </c>
       <c r="G115" s="4"/>
       <c r="H115" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I115" s="4"/>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
-        <v>114</v>
-      </c>
-      <c r="B116" s="12"/>
-      <c r="C116" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D116" s="5" t="s">
-        <v>376</v>
+        <v>116</v>
+      </c>
+      <c r="B116" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C116" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>226</v>
+        <v>168</v>
       </c>
       <c r="G116" s="4"/>
       <c r="H116" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I116" s="4"/>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
-        <v>115</v>
-      </c>
-      <c r="B117" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C117" s="12" t="s">
-        <v>92</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="B117" s="12"/>
+      <c r="C117" s="12"/>
       <c r="D117" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>173</v>
+        <v>85</v>
       </c>
       <c r="G117" s="4"/>
       <c r="H117" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I117" s="4"/>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="4">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B118" s="12"/>
       <c r="C118" s="12"/>
       <c r="D118" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G118" s="4"/>
       <c r="H118" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I118" s="4"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
-        <v>117</v>
-      </c>
-      <c r="B119" s="12"/>
-      <c r="C119" s="12"/>
+        <v>119</v>
+      </c>
+      <c r="B119" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>361</v>
+      </c>
       <c r="D119" s="4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="G119" s="4"/>
       <c r="H119" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I119" s="4"/>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
-        <v>118</v>
-      </c>
-      <c r="B120" s="12" t="s">
-        <v>96</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="B120" s="12"/>
       <c r="C120" s="7" t="s">
-        <v>366</v>
+        <v>100</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I120" s="4"/>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B121" s="12"/>
       <c r="C121" s="7" t="s">
-        <v>103</v>
+        <v>369</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="G121" s="4"/>
       <c r="H121" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I121" s="4"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B122" s="12"/>
       <c r="C122" s="7" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>97</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F122" s="4" t="s">
         <v>174</v>
       </c>
       <c r="G122" s="4"/>
       <c r="H122" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I122" s="4"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B123" s="12"/>
       <c r="C123" s="7" t="s">
-        <v>373</v>
+        <v>98</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G123" s="4"/>
       <c r="H123" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I123" s="4"/>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="4">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B124" s="12"/>
-      <c r="C124" s="7" t="s">
-        <v>101</v>
+      <c r="C124" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="G124" s="4"/>
       <c r="H124" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I124" s="4"/>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B125" s="12"/>
-      <c r="C125" s="12" t="s">
-        <v>114</v>
-      </c>
+      <c r="C125" s="12"/>
       <c r="D125" s="4" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G125" s="4"/>
       <c r="H125" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I125" s="4"/>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="4">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B126" s="12"/>
       <c r="C126" s="12"/>
       <c r="D126" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G126" s="4"/>
       <c r="H126" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I126" s="4"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B127" s="12"/>
-      <c r="C127" s="12"/>
+      <c r="C127" s="12" t="s">
+        <v>112</v>
+      </c>
       <c r="D127" s="4" t="s">
-        <v>107</v>
+        <v>18</v>
       </c>
       <c r="E127" s="4" t="s">
         <v>177</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="G127" s="4"/>
       <c r="H127" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I127" s="4"/>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="4">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B128" s="12"/>
-      <c r="C128" s="12" t="s">
-        <v>115</v>
-      </c>
+      <c r="C128" s="12"/>
       <c r="D128" s="4" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G128" s="4"/>
       <c r="H128" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I128" s="4"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B129" s="12"/>
       <c r="C129" s="12"/>
       <c r="D129" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="G129" s="4"/>
       <c r="H129" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I129" s="4"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
+        <v>130</v>
+      </c>
+      <c r="B130" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C130" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E130" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="G130" s="4"/>
+      <c r="H130" s="4"/>
+      <c r="I130" s="4"/>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" s="4">
         <v>131</v>
       </c>
-      <c r="B130" s="12"/>
-      <c r="C130" s="12"/>
-      <c r="D130" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E130" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="F130" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="G130" s="4"/>
-      <c r="H130" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="I130" s="4"/>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A131" s="4"/>
-      <c r="B131" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C131" s="12" t="s">
-        <v>105</v>
-      </c>
+      <c r="B131" s="10"/>
+      <c r="C131" s="12"/>
       <c r="D131" s="4" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="G131" s="4"/>
       <c r="H131" s="4"/>
       <c r="I131" s="4"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="4"/>
+      <c r="A132" s="4">
+        <v>132</v>
+      </c>
       <c r="B132" s="10"/>
       <c r="C132" s="12"/>
       <c r="D132" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="G132" s="4"/>
       <c r="H132" s="4"/>
       <c r="I132" s="4"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A133" s="4"/>
+      <c r="A133" s="4">
+        <v>133</v>
+      </c>
       <c r="B133" s="10"/>
-      <c r="C133" s="12"/>
-      <c r="D133" s="4" t="s">
-        <v>107</v>
+      <c r="C133" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D133" s="5" t="s">
+        <v>366</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>214</v>
+        <v>178</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G133" s="4"/>
-      <c r="H133" s="4"/>
+      <c r="H133" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="I133" s="4"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B134" s="10"/>
-      <c r="C134" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D134" s="5" t="s">
-        <v>371</v>
+      <c r="C134" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>362</v>
       </c>
       <c r="E134" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F134" s="4" t="s">
         <v>183</v>
-      </c>
-      <c r="F134" s="4" t="s">
-        <v>187</v>
       </c>
       <c r="G134" s="4"/>
       <c r="H134" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I134" s="4"/>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B135" s="10"/>
-      <c r="C135" s="12" t="s">
-        <v>370</v>
-      </c>
+      <c r="C135" s="12"/>
       <c r="D135" s="4" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="G135" s="4"/>
       <c r="H135" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I135" s="4"/>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
-        <v>134</v>
-      </c>
-      <c r="B136" s="10"/>
+        <v>136</v>
+      </c>
+      <c r="B136" s="11"/>
       <c r="C136" s="12"/>
       <c r="D136" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="G136" s="4"/>
       <c r="H136" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I136" s="4"/>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
-        <v>135</v>
-      </c>
-      <c r="B137" s="11"/>
-      <c r="C137" s="12"/>
+        <v>137</v>
+      </c>
+      <c r="B137" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>108</v>
+      </c>
       <c r="D137" s="4" t="s">
-        <v>369</v>
+        <v>109</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G137" s="4"/>
       <c r="H137" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I137" s="4"/>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="4">
-        <v>136</v>
-      </c>
-      <c r="B138" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="B138" s="12"/>
+      <c r="C138" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C138" s="7" t="s">
-        <v>111</v>
-      </c>
       <c r="D138" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="G138" s="4"/>
       <c r="H138" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I138" s="4"/>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
-        <v>137</v>
-      </c>
-      <c r="B139" s="12"/>
+        <v>139</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>115</v>
+      </c>
       <c r="C139" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D139" s="4" t="s">
         <v>116</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G139" s="4"/>
       <c r="H139" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I139" s="4"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="4">
-        <v>138</v>
-      </c>
-      <c r="B140" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B140" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C140" s="12" t="s">
         <v>118</v>
-      </c>
-      <c r="C140" s="7" t="s">
-        <v>117</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>119</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G140" s="4"/>
       <c r="H140" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I140" s="4"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="4">
-        <v>139</v>
-      </c>
-      <c r="B141" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="B141" s="12"/>
+      <c r="C141" s="12"/>
+      <c r="D141" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C141" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="D141" s="4" t="s">
-        <v>122</v>
-      </c>
       <c r="E141" s="4" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="G141" s="4"/>
       <c r="H141" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I141" s="4"/>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="4">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B142" s="12"/>
       <c r="C142" s="12"/>
       <c r="D142" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="G142" s="4"/>
       <c r="H142" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I142" s="4"/>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B143" s="12"/>
-      <c r="C143" s="12"/>
+      <c r="C143" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="D143" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>216</v>
+        <v>187</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G143" s="4"/>
       <c r="H143" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I143" s="4"/>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="4">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B144" s="12"/>
-      <c r="C144" s="12" t="s">
-        <v>26</v>
-      </c>
+      <c r="C144" s="12"/>
       <c r="D144" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="G144" s="4"/>
       <c r="H144" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I144" s="4"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A145" s="4">
-        <v>143</v>
-      </c>
-      <c r="B145" s="12"/>
-      <c r="C145" s="12"/>
+        <v>145</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>192</v>
+      </c>
       <c r="D145" s="4" t="s">
-        <v>126</v>
+        <v>193</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="F145" s="4" t="s">
         <v>194</v>
       </c>
       <c r="G145" s="4"/>
       <c r="H145" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I145" s="4"/>
-    </row>
-    <row r="146" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A146" s="4">
-        <v>144</v>
-      </c>
-      <c r="B146" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="C146" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="D146" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="E146" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="F146" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="G146" s="4"/>
-      <c r="H146" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="I146" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="C32:C36"/>
-    <mergeCell ref="B131:B137"/>
-    <mergeCell ref="C144:C145"/>
-    <mergeCell ref="B141:B145"/>
-    <mergeCell ref="B68:B71"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C141:C143"/>
-    <mergeCell ref="C125:C127"/>
-    <mergeCell ref="C128:C130"/>
-    <mergeCell ref="C117:C119"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="C102:C104"/>
-    <mergeCell ref="C105:C106"/>
-    <mergeCell ref="B89:B95"/>
-    <mergeCell ref="C97:C99"/>
-    <mergeCell ref="C85:C87"/>
-    <mergeCell ref="B72:B77"/>
-    <mergeCell ref="C75:C77"/>
-    <mergeCell ref="B120:B130"/>
-    <mergeCell ref="B78:B82"/>
-    <mergeCell ref="B85:B87"/>
-    <mergeCell ref="B2:B12"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="B17:B28"/>
+    <mergeCell ref="C31:C35"/>
+    <mergeCell ref="B130:B136"/>
+    <mergeCell ref="C143:C144"/>
+    <mergeCell ref="B140:B144"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="C140:C142"/>
+    <mergeCell ref="C124:C126"/>
+    <mergeCell ref="C127:C129"/>
+    <mergeCell ref="C116:C118"/>
+    <mergeCell ref="B116:B118"/>
+    <mergeCell ref="C101:C103"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="B88:B94"/>
+    <mergeCell ref="C96:C98"/>
+    <mergeCell ref="C84:C86"/>
+    <mergeCell ref="B71:B76"/>
+    <mergeCell ref="C74:C76"/>
+    <mergeCell ref="B119:B129"/>
+    <mergeCell ref="B77:B81"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="B16:B27"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="B29:B36"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C135:C137"/>
-    <mergeCell ref="B113:B116"/>
-    <mergeCell ref="B96:B112"/>
-    <mergeCell ref="C45:C48"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="C52:C57"/>
-    <mergeCell ref="B37:B60"/>
-    <mergeCell ref="B62:B67"/>
-    <mergeCell ref="C131:C133"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="C107:C108"/>
-    <mergeCell ref="C109:C111"/>
-    <mergeCell ref="C89:C91"/>
-    <mergeCell ref="C92:C94"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="B28:B35"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="C134:C136"/>
+    <mergeCell ref="B112:B115"/>
+    <mergeCell ref="B95:B111"/>
+    <mergeCell ref="C44:C47"/>
+    <mergeCell ref="C48:C50"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="C51:C56"/>
+    <mergeCell ref="B36:B59"/>
+    <mergeCell ref="B61:B66"/>
+    <mergeCell ref="C130:C132"/>
+    <mergeCell ref="C99:C100"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="C108:C110"/>
+    <mergeCell ref="C88:C90"/>
+    <mergeCell ref="C91:C93"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64927988-4893-4F8C-B2C9-EC2E717EE1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75BC4388-2A9B-4504-8471-2D8E90A7AC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{F425FBA8-E65A-4F03-9270-551F3EA7C4F5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="398">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -155,14 +155,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>活动入口开始时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>活动入口跳转</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>左侧活动中心大屏-热点页签已开启</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -424,10 +416,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>礼包内奖励概率</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>徽章礼包奖励配置表，有大量徽章礼包</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1463,10 +1451,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>礼包领取</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>修改服务器时间到2025年1月18 23：59：59</t>
   </si>
   <si>
@@ -1589,6 +1573,38 @@
   </si>
   <si>
     <t>活动入口异常跳转测试</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点赞任务-点赞数据持久化</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在有点赞次数情况下退出游戏重新登录</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>回到活动页面查看点赞次数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点赞次数为退出时点赞次数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>集换徽章-礼包领取</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>集换徽章礼包-礼包内奖励概率（需要写全，不是写一条）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动入口-可跳转时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动入口-正常跳转</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2079,7 +2095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DF7E13A-4D63-4E82-9598-D598C8858D86}">
-  <dimension ref="A1:I145"/>
+  <dimension ref="A1:I146"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.21875" customWidth="1"/>
@@ -2133,14 +2149,14 @@
         <v>11</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I2" s="4"/>
     </row>
@@ -2154,14 +2170,14 @@
         <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I3" s="4"/>
     </row>
@@ -2175,14 +2191,14 @@
         <v>13</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I4" s="4"/>
     </row>
@@ -2198,14 +2214,14 @@
         <v>15</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I5" s="4"/>
     </row>
@@ -2216,17 +2232,17 @@
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
       <c r="D6" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -2240,20 +2256,20 @@
         <v>16</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="12"/>
       <c r="C8" s="12" t="s">
@@ -2263,22 +2279,22 @@
         <v>18</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
@@ -2286,20 +2302,20 @@
         <v>19</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -2307,43 +2323,43 @@
         <v>20</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I11" s="4"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>21</v>
@@ -2355,20 +2371,20 @@
         <v>23</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="7" t="s">
@@ -2378,20 +2394,20 @@
         <v>25</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="12"/>
       <c r="C14" s="7" t="s">
@@ -2401,68 +2417,68 @@
         <v>28</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="12"/>
       <c r="C15" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>30</v>
+        <v>396</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -2470,20 +2486,20 @@
         <v>12</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
@@ -2491,135 +2507,135 @@
         <v>13</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="12"/>
       <c r="C19" s="7" t="s">
-        <v>223</v>
+        <v>397</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>225</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="7" t="s">
-        <v>34</v>
+        <v>220</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="12"/>
       <c r="C21" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>33</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I21" s="4"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="12"/>
       <c r="C22" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="12"/>
       <c r="C23" s="9" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I23" s="4"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="12"/>
       <c r="C24" s="10"/>
@@ -2627,20 +2643,20 @@
         <v>19</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="12"/>
       <c r="C25" s="11"/>
@@ -2648,257 +2664,257 @@
         <v>20</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" s="12"/>
       <c r="C26" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D26" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>219</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I26" s="4"/>
     </row>
     <row r="27" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
       <c r="D27" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I27" s="4"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>38</v>
-      </c>
       <c r="E28" s="5" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I28" s="4"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I29" s="4"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" s="12"/>
       <c r="C30" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E30" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F30" s="5" t="s">
         <v>229</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>232</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I30" s="4"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31" s="12"/>
       <c r="C31" s="9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E31" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>139</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I31" s="4"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32" s="12"/>
       <c r="C32" s="10"/>
       <c r="D32" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I32" s="4"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" s="12"/>
       <c r="C33" s="10"/>
       <c r="D33" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I33" s="4"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" s="12"/>
       <c r="C34" s="10"/>
       <c r="D34" s="4" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35" s="12"/>
       <c r="C35" s="11"/>
       <c r="D35" s="4" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I35" s="4"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
@@ -2906,20 +2922,20 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37" s="12"/>
       <c r="C37" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
@@ -2927,20 +2943,20 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" s="12"/>
       <c r="C38" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D38" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="E38" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="E38" s="5" t="s">
-        <v>241</v>
-      </c>
       <c r="F38" s="5" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -2948,20 +2964,20 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" s="12"/>
       <c r="C39" s="7" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
@@ -2969,20 +2985,20 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="12"/>
       <c r="C40" s="12" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
@@ -2990,18 +3006,18 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
       <c r="D41" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
@@ -3009,18 +3025,18 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
       <c r="D42" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -3028,20 +3044,20 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B43" s="12"/>
       <c r="C43" s="7" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D43" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="F43" s="5" t="s">
         <v>262</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>265</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
@@ -3049,20 +3065,20 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B44" s="12"/>
       <c r="C44" s="12" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
@@ -3070,18 +3086,18 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
       <c r="D45" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="E45" s="5" t="s">
-        <v>269</v>
-      </c>
       <c r="F45" s="5" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
@@ -3089,18 +3105,18 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
       <c r="D46" s="5" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -3108,18 +3124,18 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
       <c r="D47" s="5" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
@@ -3127,20 +3143,20 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B48" s="12"/>
       <c r="C48" s="12" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
@@ -3148,18 +3164,18 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
       <c r="D49" s="5" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
@@ -3167,18 +3183,18 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
       <c r="D50" s="5" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
@@ -3186,20 +3202,20 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B51" s="12"/>
       <c r="C51" s="12" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -3207,18 +3223,18 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
       <c r="D52" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="E52" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="E52" s="5" t="s">
+      <c r="F52" s="5" t="s">
         <v>279</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>282</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
@@ -3226,18 +3242,18 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
       <c r="D53" s="5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E53" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="F53" s="5" t="s">
         <v>280</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>283</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -3245,18 +3261,18 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
       <c r="D54" s="5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
@@ -3264,18 +3280,18 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B55" s="12"/>
       <c r="C55" s="12"/>
       <c r="D55" s="5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
@@ -3283,18 +3299,18 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B56" s="12"/>
       <c r="C56" s="12"/>
       <c r="D56" s="5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
@@ -3302,20 +3318,20 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B57" s="12"/>
       <c r="C57" s="7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
@@ -3323,20 +3339,20 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B58" s="12"/>
       <c r="C58" s="12" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
@@ -3344,18 +3360,18 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B59" s="12"/>
       <c r="C59" s="12"/>
       <c r="D59" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="E59" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="E59" s="5" t="s">
-        <v>295</v>
-      </c>
       <c r="F59" s="5" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
@@ -3363,22 +3379,22 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C60" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F60" s="5" t="s">
         <v>245</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>248</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
@@ -3386,1106 +3402,1108 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B61" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="E61" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="F61" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>304</v>
       </c>
       <c r="G61" s="4"/>
       <c r="H61" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I61" s="4"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B62" s="12"/>
       <c r="C62" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I62" s="4"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B63" s="12"/>
       <c r="C63" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="D63" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="D63" s="4" t="s">
-        <v>308</v>
-      </c>
       <c r="E63" s="4" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I63" s="4"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B64" s="12"/>
       <c r="C64" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="F64" s="4" t="s">
         <v>306</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>309</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B65" s="12"/>
       <c r="C65" s="12"/>
       <c r="D65" s="4" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G65" s="4"/>
       <c r="H65" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I65" s="4"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B66" s="12"/>
       <c r="C66" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="F66" s="4" t="s">
         <v>313</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>316</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I66" s="4"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I67" s="4"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B68" s="13"/>
       <c r="C68" s="7" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G68" s="4"/>
       <c r="H68" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I68" s="4"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B69" s="13"/>
       <c r="C69" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G69" s="4"/>
       <c r="H69" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B70" s="13"/>
       <c r="C70" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G70" s="4"/>
       <c r="H70" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I70" s="4"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C71" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="D71" s="4" t="s">
-        <v>322</v>
-      </c>
       <c r="E71" s="4" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="G71" s="4"/>
       <c r="H71" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I71" s="4"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B72" s="12"/>
       <c r="C72" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="D72" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="D72" s="4" t="s">
-        <v>327</v>
-      </c>
       <c r="E72" s="4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G72" s="4"/>
       <c r="H72" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I72" s="4"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B73" s="12"/>
       <c r="C73" s="7" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D73" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="F73" s="4" t="s">
         <v>326</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>329</v>
       </c>
       <c r="G73" s="4"/>
       <c r="H73" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I73" s="4"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B74" s="12"/>
       <c r="C74" s="12" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D74" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="F74" s="4" t="s">
         <v>333</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>336</v>
       </c>
       <c r="G74" s="4"/>
       <c r="H74" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I74" s="4"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B75" s="12"/>
       <c r="C75" s="12"/>
       <c r="D75" s="4" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G75" s="4"/>
       <c r="H75" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I75" s="4"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B76" s="12"/>
       <c r="C76" s="12"/>
       <c r="D76" s="4" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I76" s="4"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D77" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="F77" s="5" t="s">
         <v>350</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>353</v>
       </c>
       <c r="G77" s="4"/>
       <c r="H77" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I77" s="4"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B78" s="12"/>
       <c r="C78" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G78" s="4"/>
       <c r="H78" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I78" s="4"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B79" s="12"/>
       <c r="C79" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G79" s="4"/>
       <c r="H79" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I79" s="4"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B80" s="12"/>
       <c r="C80" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D80" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="E80" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="E80" s="5" t="s">
-        <v>359</v>
-      </c>
       <c r="F80" s="5" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G80" s="4"/>
       <c r="H80" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I80" s="4"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B81" s="12"/>
       <c r="C81" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G81" s="4"/>
       <c r="H81" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I81" s="4"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B82" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D82" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C82" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>58</v>
-      </c>
       <c r="E82" s="5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G82" s="4"/>
       <c r="H82" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I82" s="4"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B83" s="12"/>
       <c r="C83" s="12"/>
       <c r="D83" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G83" s="4"/>
       <c r="H83" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I83" s="4"/>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G84" s="4"/>
       <c r="H84" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I84" s="4"/>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B85" s="12"/>
       <c r="C85" s="12"/>
       <c r="D85" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G85" s="4"/>
       <c r="H85" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I85" s="4"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B86" s="12"/>
       <c r="C86" s="12"/>
       <c r="D86" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I86" s="4"/>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G87" s="4"/>
       <c r="H87" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I87" s="4"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I88" s="4"/>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B89" s="10"/>
       <c r="C89" s="12"/>
       <c r="D89" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I89" s="4"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B90" s="10"/>
       <c r="C90" s="12"/>
       <c r="D90" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I90" s="4"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B91" s="10"/>
       <c r="C91" s="12" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D91" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F91" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="E91" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>65</v>
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I91" s="4"/>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B92" s="10"/>
       <c r="C92" s="12"/>
       <c r="D92" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F92" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="E92" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>68</v>
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I92" s="4"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B93" s="10"/>
       <c r="C93" s="12"/>
       <c r="D93" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F93" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="E93" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F93" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I93" s="4"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
-        <v>94</v>
-      </c>
-      <c r="B94" s="11"/>
+        <v>93</v>
+      </c>
+      <c r="B94" s="10"/>
       <c r="C94" s="7" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>142</v>
+        <v>392</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>169</v>
+        <v>393</v>
       </c>
       <c r="G94" s="4"/>
-      <c r="H94" s="4"/>
+      <c r="H94" s="4" t="s">
+        <v>129</v>
+      </c>
       <c r="I94" s="4"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
-        <v>95</v>
-      </c>
-      <c r="B95" s="12" t="s">
-        <v>72</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="B95" s="11"/>
       <c r="C95" s="7" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>373</v>
+        <v>139</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>374</v>
+        <v>166</v>
       </c>
       <c r="G95" s="4"/>
-      <c r="H95" s="4" t="s">
-        <v>129</v>
-      </c>
+      <c r="H95" s="4"/>
       <c r="I95" s="4"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
-        <v>96</v>
-      </c>
-      <c r="B96" s="12"/>
-      <c r="C96" s="12" t="s">
-        <v>391</v>
+        <v>95</v>
+      </c>
+      <c r="B96" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>388</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>73</v>
+        <v>368</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>157</v>
+        <v>369</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>160</v>
+        <v>370</v>
       </c>
       <c r="G96" s="4"/>
       <c r="H96" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I96" s="4"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B97" s="12"/>
-      <c r="C97" s="12"/>
+      <c r="C97" s="12" t="s">
+        <v>387</v>
+      </c>
       <c r="D97" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I97" s="4"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B98" s="12"/>
       <c r="C98" s="12"/>
       <c r="D98" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I98" s="4"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B99" s="12"/>
-      <c r="C99" s="12" t="s">
-        <v>390</v>
-      </c>
+      <c r="C99" s="12"/>
       <c r="D99" s="4" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="G99" s="4"/>
       <c r="H99" s="4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="I99" s="4"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B100" s="12"/>
-      <c r="C100" s="12"/>
+      <c r="C100" s="12" t="s">
+        <v>386</v>
+      </c>
       <c r="D100" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G100" s="4"/>
       <c r="H100" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I100" s="4"/>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B101" s="12"/>
-      <c r="C101" s="12" t="s">
-        <v>389</v>
-      </c>
+      <c r="C101" s="12"/>
       <c r="D101" s="4" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="G101" s="4"/>
       <c r="H101" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I101" s="4"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B102" s="12"/>
-      <c r="C102" s="12"/>
+      <c r="C102" s="12" t="s">
+        <v>385</v>
+      </c>
       <c r="D102" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I102" s="4"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B103" s="12"/>
       <c r="C103" s="12"/>
       <c r="D103" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I103" s="4"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B104" s="12"/>
-      <c r="C104" s="12" t="s">
-        <v>377</v>
-      </c>
+      <c r="C104" s="12"/>
       <c r="D104" s="4" t="s">
-        <v>378</v>
+        <v>90</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>381</v>
+        <v>158</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>382</v>
+        <v>131</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="I104" s="4"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B105" s="12"/>
-      <c r="C105" s="12"/>
+      <c r="C105" s="12" t="s">
+        <v>373</v>
+      </c>
       <c r="D105" s="4" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="G105" s="4"/>
       <c r="H105" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I105" s="4"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B106" s="12"/>
-      <c r="C106" s="12" t="s">
-        <v>79</v>
-      </c>
+      <c r="C106" s="12"/>
       <c r="D106" s="4" t="s">
-        <v>82</v>
+        <v>375</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>161</v>
+        <v>376</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>80</v>
+        <v>378</v>
       </c>
       <c r="G106" s="4"/>
       <c r="H106" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I106" s="4"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B107" s="12"/>
-      <c r="C107" s="12"/>
+      <c r="C107" s="12" t="s">
+        <v>77</v>
+      </c>
       <c r="D107" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G107" s="4"/>
       <c r="H107" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I107" s="4"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B108" s="12"/>
-      <c r="C108" s="12" t="s">
-        <v>360</v>
-      </c>
+      <c r="C108" s="12"/>
       <c r="D108" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>162</v>
+        <v>79</v>
       </c>
       <c r="G108" s="4"/>
       <c r="H108" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I108" s="4"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B109" s="12"/>
-      <c r="C109" s="12"/>
+      <c r="C109" s="12" t="s">
+        <v>357</v>
+      </c>
       <c r="D109" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G109" s="4"/>
       <c r="H109" s="4" t="s">
@@ -4495,135 +4513,133 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B110" s="12"/>
       <c r="C110" s="12"/>
       <c r="D110" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G110" s="4"/>
       <c r="H110" s="4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="I110" s="4"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B111" s="12"/>
-      <c r="C111" s="7" t="s">
-        <v>367</v>
-      </c>
+      <c r="C111" s="12"/>
       <c r="D111" s="4" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I111" s="4"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
-        <v>112</v>
-      </c>
-      <c r="B112" s="12" t="s">
-        <v>83</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="B112" s="12"/>
       <c r="C112" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>370</v>
+        <v>363</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="G112" s="4"/>
       <c r="H112" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I112" s="4"/>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
-        <v>113</v>
-      </c>
-      <c r="B113" s="12"/>
+        <v>112</v>
+      </c>
+      <c r="B113" s="12" t="s">
+        <v>81</v>
+      </c>
       <c r="C113" s="7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G113" s="4"/>
       <c r="H113" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I113" s="4"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="4">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B114" s="12"/>
       <c r="C114" s="7" t="s">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G114" s="4"/>
       <c r="H114" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I114" s="4"/>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B115" s="12"/>
       <c r="C115" s="7" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>221</v>
+        <v>163</v>
       </c>
       <c r="G115" s="4"/>
       <c r="H115" s="4" t="s">
@@ -4633,43 +4649,45 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
-        <v>116</v>
-      </c>
-      <c r="B116" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="C116" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D116" s="4" t="s">
-        <v>87</v>
+        <v>115</v>
+      </c>
+      <c r="B116" s="12"/>
+      <c r="C116" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>367</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>168</v>
+        <v>218</v>
       </c>
       <c r="G116" s="4"/>
       <c r="H116" s="4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="I116" s="4"/>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
-        <v>117</v>
-      </c>
-      <c r="B117" s="12"/>
-      <c r="C117" s="12"/>
+        <v>116</v>
+      </c>
+      <c r="B117" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>87</v>
+      </c>
       <c r="D117" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>85</v>
+        <v>165</v>
       </c>
       <c r="G117" s="4"/>
       <c r="H117" s="4" t="s">
@@ -4679,43 +4697,39 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="4">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B118" s="12"/>
       <c r="C118" s="12"/>
       <c r="D118" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G118" s="4"/>
       <c r="H118" s="4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="I118" s="4"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
-        <v>119</v>
-      </c>
-      <c r="B119" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="C119" s="7" t="s">
-        <v>361</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="B119" s="12"/>
+      <c r="C119" s="12"/>
       <c r="D119" s="4" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>169</v>
+        <v>83</v>
       </c>
       <c r="G119" s="4"/>
       <c r="H119" s="4" t="s">
@@ -4725,133 +4739,137 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
-        <v>120</v>
-      </c>
-      <c r="B120" s="12"/>
+        <v>119</v>
+      </c>
+      <c r="B120" s="12" t="s">
+        <v>91</v>
+      </c>
       <c r="C120" s="7" t="s">
-        <v>100</v>
+        <v>394</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I120" s="4"/>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B121" s="12"/>
       <c r="C121" s="7" t="s">
-        <v>369</v>
+        <v>97</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G121" s="4"/>
       <c r="H121" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I121" s="4"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B122" s="12"/>
       <c r="C122" s="7" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G122" s="4"/>
       <c r="H122" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I122" s="4"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B123" s="12"/>
       <c r="C123" s="7" t="s">
-        <v>98</v>
+        <v>364</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G123" s="4"/>
       <c r="H123" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I123" s="4"/>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="4">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B124" s="12"/>
-      <c r="C124" s="12" t="s">
-        <v>111</v>
+      <c r="C124" s="7" t="s">
+        <v>395</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="E124" s="4" t="s">
         <v>172</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G124" s="4"/>
       <c r="H124" s="4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="I124" s="4"/>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B125" s="12"/>
-      <c r="C125" s="12"/>
+      <c r="C125" s="12" t="s">
+        <v>108</v>
+      </c>
       <c r="D125" s="4" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G125" s="4"/>
       <c r="H125" s="4" t="s">
@@ -4861,62 +4879,62 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="4">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B126" s="12"/>
       <c r="C126" s="12"/>
       <c r="D126" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G126" s="4"/>
       <c r="H126" s="4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="I126" s="4"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B127" s="12"/>
-      <c r="C127" s="12" t="s">
-        <v>112</v>
-      </c>
+      <c r="C127" s="12"/>
       <c r="D127" s="4" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="G127" s="4"/>
       <c r="H127" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I127" s="4"/>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="4">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B128" s="12"/>
-      <c r="C128" s="12"/>
+      <c r="C128" s="12" t="s">
+        <v>109</v>
+      </c>
       <c r="D128" s="4" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="E128" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F128" s="4" t="s">
         <v>177</v>
-      </c>
-      <c r="F128" s="4" t="s">
-        <v>181</v>
       </c>
       <c r="G128" s="4"/>
       <c r="H128" s="4" t="s">
@@ -4926,62 +4944,64 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B129" s="12"/>
       <c r="C129" s="12"/>
       <c r="D129" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G129" s="4"/>
       <c r="H129" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I129" s="4"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
-        <v>130</v>
-      </c>
-      <c r="B130" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="C130" s="12" t="s">
-        <v>102</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="B130" s="12"/>
+      <c r="C130" s="12"/>
       <c r="D130" s="4" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>209</v>
+        <v>174</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G130" s="4"/>
-      <c r="H130" s="4"/>
+      <c r="H130" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="I130" s="4"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="4">
-        <v>131</v>
-      </c>
-      <c r="B131" s="10"/>
-      <c r="C131" s="12"/>
+        <v>130</v>
+      </c>
+      <c r="B131" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C131" s="12" t="s">
+        <v>99</v>
+      </c>
       <c r="D131" s="4" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G131" s="4"/>
       <c r="H131" s="4"/>
@@ -4989,18 +5009,18 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="4">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B132" s="10"/>
       <c r="C132" s="12"/>
       <c r="D132" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G132" s="4"/>
       <c r="H132" s="4"/>
@@ -5008,64 +5028,62 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B133" s="10"/>
-      <c r="C133" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="D133" s="5" t="s">
-        <v>366</v>
+      <c r="C133" s="12"/>
+      <c r="D133" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="G133" s="4"/>
-      <c r="H133" s="4" t="s">
-        <v>128</v>
-      </c>
+      <c r="H133" s="4"/>
       <c r="I133" s="4"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B134" s="10"/>
-      <c r="C134" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="D134" s="4" t="s">
+      <c r="C134" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D134" s="5" t="s">
         <v>362</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="G134" s="4"/>
       <c r="H134" s="4" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="I134" s="4"/>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B135" s="10"/>
-      <c r="C135" s="12"/>
+      <c r="C135" s="12" t="s">
+        <v>361</v>
+      </c>
       <c r="D135" s="4" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G135" s="4"/>
       <c r="H135" s="4" t="s">
@@ -5075,137 +5093,137 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
-        <v>136</v>
-      </c>
-      <c r="B136" s="11"/>
+        <v>135</v>
+      </c>
+      <c r="B136" s="10"/>
       <c r="C136" s="12"/>
       <c r="D136" s="4" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G136" s="4"/>
       <c r="H136" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I136" s="4"/>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
-        <v>137</v>
-      </c>
-      <c r="B137" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="C137" s="7" t="s">
-        <v>108</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="B137" s="11"/>
+      <c r="C137" s="12"/>
       <c r="D137" s="4" t="s">
-        <v>109</v>
+        <v>360</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G137" s="4"/>
       <c r="H137" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I137" s="4"/>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="4">
-        <v>138</v>
-      </c>
-      <c r="B138" s="12"/>
+        <v>137</v>
+      </c>
+      <c r="B138" s="12" t="s">
+        <v>104</v>
+      </c>
       <c r="C138" s="7" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G138" s="4"/>
       <c r="H138" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I138" s="4"/>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
-        <v>139</v>
-      </c>
-      <c r="B139" s="7" t="s">
-        <v>115</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="B139" s="12"/>
       <c r="C139" s="7" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G139" s="4"/>
       <c r="H139" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I139" s="4"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="4">
-        <v>140</v>
-      </c>
-      <c r="B140" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="C140" s="12" t="s">
-        <v>118</v>
+        <v>139</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G140" s="4"/>
       <c r="H140" s="4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="I140" s="4"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="4">
-        <v>141</v>
-      </c>
-      <c r="B141" s="12"/>
-      <c r="C141" s="12"/>
+        <v>140</v>
+      </c>
+      <c r="B141" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C141" s="12" t="s">
+        <v>115</v>
+      </c>
       <c r="D141" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G141" s="4"/>
       <c r="H141" s="4" t="s">
@@ -5215,115 +5233,136 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="4">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B142" s="12"/>
       <c r="C142" s="12"/>
       <c r="D142" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G142" s="4"/>
       <c r="H142" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I142" s="4"/>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B143" s="12"/>
-      <c r="C143" s="12" t="s">
-        <v>26</v>
-      </c>
+      <c r="C143" s="12"/>
       <c r="D143" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="G143" s="4"/>
       <c r="H143" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I143" s="4"/>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="4">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B144" s="12"/>
-      <c r="C144" s="12"/>
+      <c r="C144" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="D144" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>212</v>
+        <v>184</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G144" s="4"/>
       <c r="H144" s="4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="I144" s="4"/>
     </row>
-    <row r="145" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="4">
-        <v>145</v>
-      </c>
-      <c r="B145" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="C145" s="8" t="s">
-        <v>192</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="B145" s="12"/>
+      <c r="C145" s="12"/>
       <c r="D145" s="4" t="s">
-        <v>193</v>
+        <v>120</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="G145" s="4"/>
       <c r="H145" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I145" s="4"/>
+    </row>
+    <row r="146" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A146" s="4">
+        <v>145</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="G146" s="4"/>
+      <c r="H146" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="I146" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="50">
     <mergeCell ref="C31:C35"/>
-    <mergeCell ref="B130:B136"/>
-    <mergeCell ref="C143:C144"/>
-    <mergeCell ref="B140:B144"/>
+    <mergeCell ref="B131:B137"/>
+    <mergeCell ref="C144:C145"/>
+    <mergeCell ref="B141:B145"/>
     <mergeCell ref="B67:B70"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="C140:C142"/>
-    <mergeCell ref="C124:C126"/>
-    <mergeCell ref="C127:C129"/>
-    <mergeCell ref="C116:C118"/>
-    <mergeCell ref="B116:B118"/>
-    <mergeCell ref="C101:C103"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="B88:B94"/>
-    <mergeCell ref="C96:C98"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C141:C143"/>
+    <mergeCell ref="C125:C127"/>
+    <mergeCell ref="C128:C130"/>
+    <mergeCell ref="C117:C119"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="C102:C104"/>
+    <mergeCell ref="C105:C106"/>
+    <mergeCell ref="B88:B95"/>
+    <mergeCell ref="C97:C99"/>
     <mergeCell ref="C84:C86"/>
     <mergeCell ref="B71:B76"/>
     <mergeCell ref="C74:C76"/>
-    <mergeCell ref="B119:B129"/>
+    <mergeCell ref="B120:B130"/>
     <mergeCell ref="B77:B81"/>
     <mergeCell ref="B84:B86"/>
     <mergeCell ref="B2:B11"/>
@@ -5340,19 +5379,19 @@
     <mergeCell ref="B28:B35"/>
     <mergeCell ref="C64:C65"/>
     <mergeCell ref="C40:C42"/>
-    <mergeCell ref="C134:C136"/>
-    <mergeCell ref="B112:B115"/>
-    <mergeCell ref="B95:B111"/>
+    <mergeCell ref="C135:C137"/>
+    <mergeCell ref="B113:B116"/>
+    <mergeCell ref="B96:B112"/>
     <mergeCell ref="C44:C47"/>
     <mergeCell ref="C48:C50"/>
     <mergeCell ref="C58:C59"/>
     <mergeCell ref="C51:C56"/>
     <mergeCell ref="B36:B59"/>
     <mergeCell ref="B61:B66"/>
-    <mergeCell ref="C130:C132"/>
-    <mergeCell ref="C99:C100"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="C108:C110"/>
+    <mergeCell ref="C131:C133"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="C107:C108"/>
+    <mergeCell ref="C109:C111"/>
     <mergeCell ref="C88:C90"/>
     <mergeCell ref="C91:C93"/>
   </mergeCells>

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例作业.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75BC4388-2A9B-4504-8471-2D8E90A7AC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE7261B6-8FC9-40F8-AAD4-D75C57874FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{F425FBA8-E65A-4F03-9270-551F3EA7C4F5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="396">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -420,10 +420,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>礼包叠加上限</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>有大量可使用徽章礼包</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -989,10 +985,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>测试任务刷新时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>修改服务器时间到xxxxxx</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1005,10 +997,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>活动登录任务刷新</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>累计对局任务-任务状态</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1261,10 +1249,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>奖励到账</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>完成任务并已领取</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1403,10 +1387,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>点赞任务对象</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>在第二天首胜刷新前进入对局，结束后每日首胜刷新</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1472,14 +1452,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>礼包使用后获得的奖励</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>礼包使用的位置</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>两个可相互点赞的账号</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1600,11 +1572,31 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>活动入口-可跳转时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>活动入口-正常跳转</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动任务-活动任务刷新时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务奖励-奖励到账</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点赞任务-点赞任务对象</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>集换徽章礼包-礼包使用的位置</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>集换徽章礼包-礼包叠加上限</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>集换徽章礼包-奖励到账</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2095,7 +2087,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DF7E13A-4D63-4E82-9598-D598C8858D86}">
-  <dimension ref="A1:I146"/>
+  <dimension ref="A1:I143"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.21875" customWidth="1"/>
@@ -2149,14 +2141,14 @@
         <v>11</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I2" s="4"/>
     </row>
@@ -2170,14 +2162,14 @@
         <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I3" s="4"/>
     </row>
@@ -2191,14 +2183,14 @@
         <v>13</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I4" s="4"/>
     </row>
@@ -2214,14 +2206,14 @@
         <v>15</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I5" s="4"/>
     </row>
@@ -2232,17 +2224,17 @@
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
       <c r="D6" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -2256,14 +2248,14 @@
         <v>16</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I7" s="4"/>
     </row>
@@ -2279,17 +2271,17 @@
         <v>18</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -2302,14 +2294,14 @@
         <v>19</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I9" s="4"/>
     </row>
@@ -2323,14 +2315,14 @@
         <v>20</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I10" s="4"/>
     </row>
@@ -2346,14 +2338,14 @@
         <v>40</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I11" s="4"/>
     </row>
@@ -2371,14 +2363,14 @@
         <v>23</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I12" s="4"/>
     </row>
@@ -2394,14 +2386,14 @@
         <v>25</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I13" s="4"/>
     </row>
@@ -2417,14 +2409,14 @@
         <v>28</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I14" s="4"/>
     </row>
@@ -2437,17 +2429,17 @@
         <v>26</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I15" s="4"/>
     </row>
@@ -2458,21 +2450,21 @@
       <c r="B16" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>396</v>
+      <c r="C16" s="7" t="s">
+        <v>389</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I16" s="4"/>
     </row>
@@ -2481,19 +2473,21 @@
         <v>16</v>
       </c>
       <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
+      <c r="C17" s="7" t="s">
+        <v>219</v>
+      </c>
       <c r="D17" s="4" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>193</v>
+        <v>221</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I17" s="4"/>
     </row>
@@ -2502,19 +2496,21 @@
         <v>17</v>
       </c>
       <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
+      <c r="C18" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="D18" s="4" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I18" s="4"/>
     </row>
@@ -2524,16 +2520,16 @@
       </c>
       <c r="B19" s="12"/>
       <c r="C19" s="7" t="s">
-        <v>397</v>
+        <v>31</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
@@ -2546,21 +2542,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="12"/>
-      <c r="C20" s="7" t="s">
-        <v>220</v>
+      <c r="C20" s="9" t="s">
+        <v>382</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>222</v>
+        <v>192</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I20" s="4"/>
     </row>
@@ -2569,21 +2565,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="12"/>
-      <c r="C21" s="7" t="s">
-        <v>32</v>
-      </c>
+      <c r="C21" s="10"/>
       <c r="D21" s="4" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I21" s="4"/>
     </row>
@@ -2592,21 +2586,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="12"/>
-      <c r="C22" s="7" t="s">
-        <v>31</v>
-      </c>
+      <c r="C22" s="11"/>
       <c r="D22" s="4" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>224</v>
+        <v>191</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I22" s="4"/>
     </row>
@@ -2615,42 +2607,42 @@
         <v>22</v>
       </c>
       <c r="B23" s="12"/>
-      <c r="C23" s="9" t="s">
-        <v>389</v>
+      <c r="C23" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>18</v>
+        <v>212</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>23</v>
       </c>
       <c r="B24" s="12"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="4" t="s">
-        <v>19</v>
+      <c r="C24" s="12"/>
+      <c r="D24" s="6" t="s">
+        <v>213</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>192</v>
+        <v>131</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I24" s="4"/>
     </row>
@@ -2658,20 +2650,24 @@
       <c r="A25" s="4">
         <v>24</v>
       </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="11"/>
+      <c r="B25" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>35</v>
+      </c>
       <c r="D25" s="4" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I25" s="4"/>
     </row>
@@ -2680,42 +2676,44 @@
         <v>25</v>
       </c>
       <c r="B26" s="12"/>
-      <c r="C26" s="12" t="s">
-        <v>39</v>
+      <c r="C26" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>213</v>
+        <v>36</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I26" s="4"/>
     </row>
-    <row r="27" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>26</v>
       </c>
       <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="6" t="s">
-        <v>214</v>
+      <c r="C27" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>132</v>
+        <v>228</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I27" s="4"/>
     </row>
@@ -2723,24 +2721,22 @@
       <c r="A28" s="4">
         <v>27</v>
       </c>
-      <c r="B28" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>35</v>
+      <c r="B28" s="12"/>
+      <c r="C28" s="9" t="s">
+        <v>41</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>226</v>
+        <v>132</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>227</v>
+        <v>135</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I28" s="4"/>
     </row>
@@ -2749,21 +2745,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="12"/>
-      <c r="C29" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="C29" s="10"/>
       <c r="D29" s="4" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>226</v>
+        <v>134</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>228</v>
+        <v>135</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I29" s="4"/>
     </row>
@@ -2772,21 +2766,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="12"/>
-      <c r="C30" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="C30" s="10"/>
       <c r="D30" s="4" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>226</v>
+        <v>133</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>229</v>
+        <v>135</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I30" s="4"/>
     </row>
@@ -2795,21 +2787,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="12"/>
-      <c r="C31" s="9" t="s">
-        <v>41</v>
-      </c>
+      <c r="C31" s="10"/>
       <c r="D31" s="4" t="s">
-        <v>42</v>
+        <v>364</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I31" s="4"/>
     </row>
@@ -2818,19 +2808,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="12"/>
-      <c r="C32" s="10"/>
+      <c r="C32" s="11"/>
       <c r="D32" s="4" t="s">
-        <v>43</v>
+        <v>365</v>
       </c>
       <c r="E32" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F32" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>136</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I32" s="4"/>
     </row>
@@ -2838,83 +2828,83 @@
       <c r="A33" s="4">
         <v>32</v>
       </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="4" t="s">
-        <v>44</v>
+      <c r="B33" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>229</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>134</v>
+        <v>233</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>136</v>
+        <v>231</v>
       </c>
       <c r="G33" s="4"/>
-      <c r="H33" s="4" t="s">
-        <v>125</v>
-      </c>
+      <c r="H33" s="4"/>
       <c r="I33" s="4"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>33</v>
       </c>
-      <c r="B34" s="12"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="4" t="s">
-        <v>371</v>
+      <c r="B34" s="10"/>
+      <c r="C34" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>234</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>137</v>
+        <v>235</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>136</v>
+        <v>236</v>
       </c>
       <c r="G34" s="4"/>
-      <c r="H34" s="4" t="s">
-        <v>129</v>
-      </c>
+      <c r="H34" s="4"/>
       <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>34</v>
       </c>
-      <c r="B35" s="12"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="4" t="s">
-        <v>372</v>
+      <c r="B35" s="10"/>
+      <c r="C35" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>234</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>136</v>
+        <v>238</v>
       </c>
       <c r="G35" s="4"/>
-      <c r="H35" s="4" t="s">
-        <v>129</v>
-      </c>
+      <c r="H35" s="4"/>
       <c r="I35" s="4"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>35</v>
       </c>
-      <c r="B36" s="12" t="s">
-        <v>233</v>
-      </c>
+      <c r="B36" s="10"/>
       <c r="C36" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
@@ -2924,18 +2914,18 @@
       <c r="A37" s="4">
         <v>36</v>
       </c>
-      <c r="B37" s="12"/>
-      <c r="C37" s="7" t="s">
+      <c r="B37" s="10"/>
+      <c r="C37" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F37" s="5" t="s">
         <v>253</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>237</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
@@ -2945,18 +2935,16 @@
       <c r="A38" s="4">
         <v>37</v>
       </c>
-      <c r="B38" s="12"/>
-      <c r="C38" s="7" t="s">
-        <v>253</v>
-      </c>
+      <c r="B38" s="10"/>
+      <c r="C38" s="12"/>
       <c r="D38" s="5" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -2966,18 +2954,16 @@
       <c r="A39" s="4">
         <v>38</v>
       </c>
-      <c r="B39" s="12"/>
-      <c r="C39" s="7" t="s">
+      <c r="B39" s="10"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>240</v>
-      </c>
       <c r="F39" s="5" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
@@ -2987,18 +2973,18 @@
       <c r="A40" s="4">
         <v>39</v>
       </c>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12" t="s">
-        <v>247</v>
+      <c r="B40" s="10"/>
+      <c r="C40" s="7" t="s">
+        <v>257</v>
       </c>
       <c r="D40" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="E40" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>231</v>
-      </c>
       <c r="F40" s="5" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
@@ -3008,16 +2994,18 @@
       <c r="A41" s="4">
         <v>40</v>
       </c>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="12" t="s">
+        <v>245</v>
+      </c>
       <c r="D41" s="5" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
@@ -3027,16 +3015,16 @@
       <c r="A42" s="4">
         <v>41</v>
       </c>
-      <c r="B42" s="12"/>
+      <c r="B42" s="10"/>
       <c r="C42" s="12"/>
       <c r="D42" s="5" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -3046,18 +3034,16 @@
       <c r="A43" s="4">
         <v>42</v>
       </c>
-      <c r="B43" s="12"/>
-      <c r="C43" s="7" t="s">
+      <c r="B43" s="10"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="D43" s="5" t="s">
-        <v>259</v>
-      </c>
       <c r="E43" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
@@ -3067,15 +3053,13 @@
       <c r="A44" s="4">
         <v>43</v>
       </c>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12" t="s">
-        <v>248</v>
-      </c>
+      <c r="B44" s="10"/>
+      <c r="C44" s="12"/>
       <c r="D44" s="5" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>265</v>
@@ -3088,16 +3072,18 @@
       <c r="A45" s="4">
         <v>44</v>
       </c>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="12" t="s">
+        <v>246</v>
+      </c>
       <c r="D45" s="5" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
@@ -3107,16 +3093,16 @@
       <c r="A46" s="4">
         <v>45</v>
       </c>
-      <c r="B46" s="12"/>
+      <c r="B46" s="10"/>
       <c r="C46" s="12"/>
       <c r="D46" s="5" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -3126,16 +3112,16 @@
       <c r="A47" s="4">
         <v>46</v>
       </c>
-      <c r="B47" s="12"/>
+      <c r="B47" s="10"/>
       <c r="C47" s="12"/>
       <c r="D47" s="5" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>269</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
@@ -3145,18 +3131,18 @@
       <c r="A48" s="4">
         <v>47</v>
       </c>
-      <c r="B48" s="12"/>
+      <c r="B48" s="10"/>
       <c r="C48" s="12" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
@@ -3166,16 +3152,16 @@
       <c r="A49" s="4">
         <v>48</v>
       </c>
-      <c r="B49" s="12"/>
+      <c r="B49" s="10"/>
       <c r="C49" s="12"/>
       <c r="D49" s="5" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
@@ -3185,16 +3171,16 @@
       <c r="A50" s="4">
         <v>49</v>
       </c>
-      <c r="B50" s="12"/>
+      <c r="B50" s="10"/>
       <c r="C50" s="12"/>
       <c r="D50" s="5" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
@@ -3204,18 +3190,16 @@
       <c r="A51" s="4">
         <v>50</v>
       </c>
-      <c r="B51" s="12"/>
-      <c r="C51" s="12" t="s">
-        <v>250</v>
-      </c>
+      <c r="B51" s="10"/>
+      <c r="C51" s="12"/>
       <c r="D51" s="5" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -3225,13 +3209,13 @@
       <c r="A52" s="4">
         <v>51</v>
       </c>
-      <c r="B52" s="12"/>
+      <c r="B52" s="10"/>
       <c r="C52" s="12"/>
       <c r="D52" s="5" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>279</v>
@@ -3244,13 +3228,13 @@
       <c r="A53" s="4">
         <v>52</v>
       </c>
-      <c r="B53" s="12"/>
+      <c r="B53" s="10"/>
       <c r="C53" s="12"/>
       <c r="D53" s="5" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>280</v>
@@ -3263,16 +3247,18 @@
       <c r="A54" s="4">
         <v>53</v>
       </c>
-      <c r="B54" s="12"/>
-      <c r="C54" s="12"/>
+      <c r="B54" s="10"/>
+      <c r="C54" s="7" t="s">
+        <v>283</v>
+      </c>
       <c r="D54" s="5" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E54" s="5" t="s">
         <v>284</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
@@ -3282,16 +3268,18 @@
       <c r="A55" s="4">
         <v>54</v>
       </c>
-      <c r="B55" s="12"/>
-      <c r="C55" s="12"/>
+      <c r="B55" s="10"/>
+      <c r="C55" s="12" t="s">
+        <v>248</v>
+      </c>
       <c r="D55" s="5" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
@@ -3301,16 +3289,16 @@
       <c r="A56" s="4">
         <v>55</v>
       </c>
-      <c r="B56" s="12"/>
+      <c r="B56" s="10"/>
       <c r="C56" s="12"/>
       <c r="D56" s="5" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
@@ -3320,18 +3308,18 @@
       <c r="A57" s="4">
         <v>56</v>
       </c>
-      <c r="B57" s="12"/>
+      <c r="B57" s="11"/>
       <c r="C57" s="7" t="s">
-        <v>286</v>
+        <v>390</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>273</v>
+        <v>241</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>287</v>
+        <v>242</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>288</v>
+        <v>243</v>
       </c>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
@@ -3341,21 +3329,25 @@
       <c r="A58" s="4">
         <v>57</v>
       </c>
-      <c r="B58" s="12"/>
-      <c r="C58" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>291</v>
+      <c r="B58" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>298</v>
       </c>
       <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
+      <c r="H58" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="I58" s="4"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -3363,88 +3355,90 @@
         <v>58</v>
       </c>
       <c r="B59" s="12"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>291</v>
+      <c r="C59" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>298</v>
       </c>
       <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
+      <c r="H59" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="I59" s="4"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>59</v>
       </c>
-      <c r="B60" s="7" t="s">
-        <v>246</v>
-      </c>
+      <c r="B60" s="12"/>
       <c r="C60" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>245</v>
+        <v>299</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>301</v>
       </c>
       <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
+      <c r="H60" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="I60" s="4"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>60</v>
       </c>
-      <c r="B61" s="12" t="s">
-        <v>297</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>298</v>
+      <c r="B61" s="12"/>
+      <c r="C61" s="12" t="s">
+        <v>300</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>235</v>
+        <v>304</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G61" s="4"/>
       <c r="H61" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="I61" s="4"/>
+        <v>124</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>61</v>
       </c>
       <c r="B62" s="12"/>
-      <c r="C62" s="7" t="s">
-        <v>299</v>
-      </c>
+      <c r="C62" s="12"/>
       <c r="D62" s="4" t="s">
-        <v>235</v>
+        <v>305</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I62" s="4"/>
     </row>
@@ -3454,20 +3448,20 @@
       </c>
       <c r="B63" s="12"/>
       <c r="C63" s="7" t="s">
-        <v>302</v>
+        <v>391</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E63" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>309</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>304</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I63" s="4"/>
     </row>
@@ -3475,45 +3469,47 @@
       <c r="A64" s="4">
         <v>63</v>
       </c>
-      <c r="B64" s="12"/>
-      <c r="C64" s="12" t="s">
-        <v>303</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>307</v>
+      <c r="B64" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>331</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>309</v>
+        <v>141</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>306</v>
+        <v>140</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="I64" s="4" t="s">
-        <v>202</v>
-      </c>
+      <c r="I64" s="4"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>64</v>
       </c>
-      <c r="B65" s="12"/>
-      <c r="C65" s="12"/>
-      <c r="D65" s="4" t="s">
-        <v>308</v>
+      <c r="B65" s="13"/>
+      <c r="C65" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>333</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="G65" s="4"/>
       <c r="H65" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="I65" s="4"/>
     </row>
@@ -3521,22 +3517,22 @@
       <c r="A66" s="4">
         <v>65</v>
       </c>
-      <c r="B66" s="12"/>
+      <c r="B66" s="13"/>
       <c r="C66" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>311</v>
+        <v>334</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>335</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>312</v>
+        <v>139</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>313</v>
+        <v>140</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I66" s="4"/>
     </row>
@@ -3544,24 +3540,22 @@
       <c r="A67" s="4">
         <v>66</v>
       </c>
-      <c r="B67" s="13" t="s">
-        <v>334</v>
-      </c>
+      <c r="B67" s="13"/>
       <c r="C67" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D67" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="D67" s="5" t="s">
-        <v>335</v>
-      </c>
       <c r="E67" s="4" t="s">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I67" s="4"/>
     </row>
@@ -3569,18 +3563,20 @@
       <c r="A68" s="4">
         <v>67</v>
       </c>
-      <c r="B68" s="13"/>
+      <c r="B68" s="12" t="s">
+        <v>310</v>
+      </c>
       <c r="C68" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>337</v>
+        <v>312</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>315</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="G68" s="4"/>
       <c r="H68" s="4" t="s">
@@ -3592,22 +3588,22 @@
       <c r="A69" s="4">
         <v>68</v>
       </c>
-      <c r="B69" s="13"/>
+      <c r="B69" s="12"/>
       <c r="C69" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>339</v>
+        <v>317</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>320</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>140</v>
+        <v>321</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>141</v>
+        <v>318</v>
       </c>
       <c r="G69" s="4"/>
       <c r="H69" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I69" s="4"/>
     </row>
@@ -3615,22 +3611,22 @@
       <c r="A70" s="4">
         <v>69</v>
       </c>
-      <c r="B70" s="13"/>
+      <c r="B70" s="12"/>
       <c r="C70" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>340</v>
+        <v>313</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>319</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>187</v>
+        <v>323</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>166</v>
+        <v>322</v>
       </c>
       <c r="G70" s="4"/>
       <c r="H70" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I70" s="4"/>
     </row>
@@ -3638,24 +3634,22 @@
       <c r="A71" s="4">
         <v>70</v>
       </c>
-      <c r="B71" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>316</v>
+      <c r="B71" s="12"/>
+      <c r="C71" s="12" t="s">
+        <v>311</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G71" s="4"/>
       <c r="H71" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I71" s="4"/>
     </row>
@@ -3664,21 +3658,19 @@
         <v>71</v>
       </c>
       <c r="B72" s="12"/>
-      <c r="C72" s="7" t="s">
-        <v>321</v>
-      </c>
+      <c r="C72" s="12"/>
       <c r="D72" s="4" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="G72" s="4"/>
       <c r="H72" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I72" s="4"/>
     </row>
@@ -3687,21 +3679,19 @@
         <v>72</v>
       </c>
       <c r="B73" s="12"/>
-      <c r="C73" s="7" t="s">
-        <v>317</v>
-      </c>
+      <c r="C73" s="12"/>
       <c r="D73" s="4" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="G73" s="4"/>
       <c r="H73" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I73" s="4"/>
     </row>
@@ -3709,22 +3699,24 @@
       <c r="A74" s="4">
         <v>73</v>
       </c>
-      <c r="B74" s="12"/>
-      <c r="C74" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>333</v>
+      <c r="B74" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>345</v>
       </c>
       <c r="G74" s="4"/>
       <c r="H74" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I74" s="4"/>
     </row>
@@ -3733,19 +3725,21 @@
         <v>74</v>
       </c>
       <c r="B75" s="12"/>
-      <c r="C75" s="12"/>
-      <c r="D75" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>342</v>
+      <c r="C75" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>142</v>
       </c>
       <c r="G75" s="4"/>
       <c r="H75" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I75" s="4"/>
     </row>
@@ -3754,19 +3748,21 @@
         <v>75</v>
       </c>
       <c r="B76" s="12"/>
-      <c r="C76" s="12"/>
-      <c r="D76" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>333</v>
+      <c r="C76" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>347</v>
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I76" s="4"/>
     </row>
@@ -3774,24 +3770,22 @@
       <c r="A77" s="4">
         <v>76</v>
       </c>
-      <c r="B77" s="12" t="s">
-        <v>329</v>
-      </c>
+      <c r="B77" s="12"/>
       <c r="C77" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E77" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="F77" s="5" t="s">
         <v>349</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>350</v>
       </c>
       <c r="G77" s="4"/>
       <c r="H77" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I77" s="4"/>
     </row>
@@ -3801,20 +3795,20 @@
       </c>
       <c r="B78" s="12"/>
       <c r="C78" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>143</v>
+        <v>347</v>
       </c>
       <c r="G78" s="4"/>
       <c r="H78" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I78" s="4"/>
     </row>
@@ -3822,22 +3816,24 @@
       <c r="A79" s="4">
         <v>78</v>
       </c>
-      <c r="B79" s="12"/>
-      <c r="C79" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>351</v>
+      <c r="B79" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>352</v>
+        <v>143</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>144</v>
       </c>
       <c r="G79" s="4"/>
       <c r="H79" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I79" s="4"/>
     </row>
@@ -3846,21 +3842,19 @@
         <v>79</v>
       </c>
       <c r="B80" s="12"/>
-      <c r="C80" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>353</v>
+      <c r="C80" s="12"/>
+      <c r="D80" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>354</v>
+        <v>143</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="G80" s="4"/>
       <c r="H80" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I80" s="4"/>
     </row>
@@ -3868,22 +3862,24 @@
       <c r="A81" s="4">
         <v>80</v>
       </c>
-      <c r="B81" s="12"/>
-      <c r="C81" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>355</v>
+      <c r="B81" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>352</v>
+        <v>202</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>146</v>
       </c>
       <c r="G81" s="4"/>
       <c r="H81" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I81" s="4"/>
     </row>
@@ -3891,24 +3887,20 @@
       <c r="A82" s="4">
         <v>81</v>
       </c>
-      <c r="B82" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C82" s="12" t="s">
-        <v>55</v>
-      </c>
+      <c r="B82" s="12"/>
+      <c r="C82" s="12"/>
       <c r="D82" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>144</v>
+        <v>202</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G82" s="4"/>
       <c r="H82" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I82" s="4"/>
     </row>
@@ -3919,17 +3911,17 @@
       <c r="B83" s="12"/>
       <c r="C83" s="12"/>
       <c r="D83" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>144</v>
+        <v>202</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G83" s="4"/>
       <c r="H83" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I83" s="4"/>
     </row>
@@ -3937,24 +3929,24 @@
       <c r="A84" s="4">
         <v>83</v>
       </c>
-      <c r="B84" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C84" s="12" t="s">
-        <v>345</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>51</v>
+      <c r="B84" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>148</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>147</v>
+        <v>129</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>149</v>
       </c>
       <c r="G84" s="4"/>
       <c r="H84" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I84" s="4"/>
     </row>
@@ -3962,20 +3954,24 @@
       <c r="A85" s="4">
         <v>84</v>
       </c>
-      <c r="B85" s="12"/>
-      <c r="C85" s="12"/>
+      <c r="B85" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>372</v>
+      </c>
       <c r="D85" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>151</v>
       </c>
       <c r="G85" s="4"/>
       <c r="H85" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I85" s="4"/>
     </row>
@@ -3983,20 +3979,20 @@
       <c r="A86" s="4">
         <v>85</v>
       </c>
-      <c r="B86" s="12"/>
+      <c r="B86" s="10"/>
       <c r="C86" s="12"/>
       <c r="D86" s="4" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>152</v>
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I86" s="4"/>
     </row>
@@ -4004,24 +4000,20 @@
       <c r="A87" s="4">
         <v>86</v>
       </c>
-      <c r="B87" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>149</v>
+      <c r="B87" s="10"/>
+      <c r="C87" s="12"/>
+      <c r="D87" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G87" s="4"/>
       <c r="H87" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I87" s="4"/>
     </row>
@@ -4029,24 +4021,22 @@
       <c r="A88" s="4">
         <v>87</v>
       </c>
-      <c r="B88" s="9" t="s">
-        <v>328</v>
-      </c>
+      <c r="B88" s="10"/>
       <c r="C88" s="12" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>152</v>
+        <v>61</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I88" s="4"/>
     </row>
@@ -4057,17 +4047,17 @@
       <c r="B89" s="10"/>
       <c r="C89" s="12"/>
       <c r="D89" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>153</v>
+        <v>64</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I89" s="4"/>
     </row>
@@ -4078,17 +4068,17 @@
       <c r="B90" s="10"/>
       <c r="C90" s="12"/>
       <c r="D90" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>153</v>
+        <v>67</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I90" s="4"/>
     </row>
@@ -4097,21 +4087,21 @@
         <v>90</v>
       </c>
       <c r="B91" s="10"/>
-      <c r="C91" s="12" t="s">
-        <v>346</v>
+      <c r="C91" s="7" t="s">
+        <v>383</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>61</v>
+        <v>384</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>62</v>
+        <v>385</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>63</v>
+        <v>386</v>
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I91" s="4"/>
     </row>
@@ -4119,41 +4109,45 @@
       <c r="A92" s="4">
         <v>91</v>
       </c>
-      <c r="B92" s="10"/>
-      <c r="C92" s="12"/>
+      <c r="B92" s="11"/>
+      <c r="C92" s="7" t="s">
+        <v>373</v>
+      </c>
       <c r="D92" s="4" t="s">
-        <v>64</v>
+        <v>374</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>66</v>
+        <v>165</v>
       </c>
       <c r="G92" s="4"/>
-      <c r="H92" s="4" t="s">
-        <v>126</v>
-      </c>
+      <c r="H92" s="4"/>
       <c r="I92" s="4"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
         <v>92</v>
       </c>
-      <c r="B93" s="10"/>
-      <c r="C93" s="12"/>
+      <c r="B93" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>381</v>
+      </c>
       <c r="D93" s="4" t="s">
-        <v>67</v>
+        <v>361</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>68</v>
+        <v>362</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>69</v>
+        <v>363</v>
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I93" s="4"/>
     </row>
@@ -4161,22 +4155,22 @@
       <c r="A94" s="4">
         <v>93</v>
       </c>
-      <c r="B94" s="10"/>
-      <c r="C94" s="7" t="s">
-        <v>390</v>
+      <c r="B94" s="12"/>
+      <c r="C94" s="12" t="s">
+        <v>380</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>391</v>
+        <v>71</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>392</v>
+        <v>153</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>393</v>
+        <v>156</v>
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I94" s="4"/>
     </row>
@@ -4184,45 +4178,41 @@
       <c r="A95" s="4">
         <v>94</v>
       </c>
-      <c r="B95" s="11"/>
-      <c r="C95" s="7" t="s">
-        <v>380</v>
-      </c>
+      <c r="B95" s="12"/>
+      <c r="C95" s="12"/>
       <c r="D95" s="4" t="s">
-        <v>381</v>
+        <v>72</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
+      <c r="H95" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="I95" s="4"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
         <v>95</v>
       </c>
-      <c r="B96" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>388</v>
-      </c>
+      <c r="B96" s="12"/>
+      <c r="C96" s="12"/>
       <c r="D96" s="4" t="s">
-        <v>368</v>
+        <v>73</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>369</v>
+        <v>155</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>370</v>
+        <v>156</v>
       </c>
       <c r="G96" s="4"/>
       <c r="H96" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I96" s="4"/>
     </row>
@@ -4232,20 +4222,20 @@
       </c>
       <c r="B97" s="12"/>
       <c r="C97" s="12" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>157</v>
+        <v>75</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I97" s="4"/>
     </row>
@@ -4256,17 +4246,17 @@
       <c r="B98" s="12"/>
       <c r="C98" s="12"/>
       <c r="D98" s="4" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>157</v>
+        <v>76</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I98" s="4"/>
     </row>
@@ -4275,19 +4265,21 @@
         <v>98</v>
       </c>
       <c r="B99" s="12"/>
-      <c r="C99" s="12"/>
+      <c r="C99" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="D99" s="4" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="G99" s="4"/>
       <c r="H99" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I99" s="4"/>
     </row>
@@ -4296,21 +4288,19 @@
         <v>99</v>
       </c>
       <c r="B100" s="12"/>
-      <c r="C100" s="12" t="s">
-        <v>386</v>
-      </c>
+      <c r="C100" s="12"/>
       <c r="D100" s="4" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="G100" s="4"/>
       <c r="H100" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="I100" s="4"/>
     </row>
@@ -4321,17 +4311,17 @@
       <c r="B101" s="12"/>
       <c r="C101" s="12"/>
       <c r="D101" s="4" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="G101" s="4"/>
       <c r="H101" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="I101" s="4"/>
     </row>
@@ -4341,20 +4331,20 @@
       </c>
       <c r="B102" s="12"/>
       <c r="C102" s="12" t="s">
-        <v>385</v>
+        <v>366</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>88</v>
+        <v>367</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>158</v>
+        <v>370</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>131</v>
+        <v>371</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I102" s="4"/>
     </row>
@@ -4365,17 +4355,17 @@
       <c r="B103" s="12"/>
       <c r="C103" s="12"/>
       <c r="D103" s="4" t="s">
-        <v>89</v>
+        <v>368</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>158</v>
+        <v>369</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>131</v>
+        <v>371</v>
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I103" s="4"/>
     </row>
@@ -4384,19 +4374,21 @@
         <v>103</v>
       </c>
       <c r="B104" s="12"/>
-      <c r="C104" s="12"/>
+      <c r="C104" s="12" t="s">
+        <v>77</v>
+      </c>
       <c r="D104" s="4" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I104" s="4"/>
     </row>
@@ -4405,21 +4397,19 @@
         <v>104</v>
       </c>
       <c r="B105" s="12"/>
-      <c r="C105" s="12" t="s">
-        <v>373</v>
-      </c>
+      <c r="C105" s="12"/>
       <c r="D105" s="4" t="s">
-        <v>374</v>
+        <v>80</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>377</v>
+        <v>157</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>378</v>
+        <v>79</v>
       </c>
       <c r="G105" s="4"/>
       <c r="H105" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I105" s="4"/>
     </row>
@@ -4428,19 +4418,21 @@
         <v>105</v>
       </c>
       <c r="B106" s="12"/>
-      <c r="C106" s="12"/>
+      <c r="C106" s="12" t="s">
+        <v>352</v>
+      </c>
       <c r="D106" s="4" t="s">
-        <v>375</v>
+        <v>85</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>376</v>
+        <v>157</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>378</v>
+        <v>158</v>
       </c>
       <c r="G106" s="4"/>
       <c r="H106" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I106" s="4"/>
     </row>
@@ -4449,21 +4441,19 @@
         <v>106</v>
       </c>
       <c r="B107" s="12"/>
-      <c r="C107" s="12" t="s">
-        <v>77</v>
-      </c>
+      <c r="C107" s="12"/>
       <c r="D107" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E107" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="F107" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="F107" s="4" t="s">
-        <v>78</v>
       </c>
       <c r="G107" s="4"/>
       <c r="H107" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I107" s="4"/>
     </row>
@@ -4474,17 +4464,17 @@
       <c r="B108" s="12"/>
       <c r="C108" s="12"/>
       <c r="D108" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E108" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="F108" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="F108" s="4" t="s">
-        <v>79</v>
       </c>
       <c r="G108" s="4"/>
       <c r="H108" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I108" s="4"/>
     </row>
@@ -4493,21 +4483,21 @@
         <v>108</v>
       </c>
       <c r="B109" s="12"/>
-      <c r="C109" s="12" t="s">
-        <v>357</v>
+      <c r="C109" s="7" t="s">
+        <v>358</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>159</v>
       </c>
       <c r="G109" s="4"/>
       <c r="H109" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I109" s="4"/>
     </row>
@@ -4515,20 +4505,24 @@
       <c r="A110" s="4">
         <v>109</v>
       </c>
-      <c r="B110" s="12"/>
-      <c r="C110" s="12"/>
-      <c r="D110" s="4" t="s">
-        <v>84</v>
+      <c r="B110" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>359</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G110" s="4"/>
       <c r="H110" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I110" s="4"/>
     </row>
@@ -4537,19 +4531,21 @@
         <v>110</v>
       </c>
       <c r="B111" s="12"/>
-      <c r="C111" s="12"/>
-      <c r="D111" s="4" t="s">
-        <v>86</v>
+      <c r="C111" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>359</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I111" s="4"/>
     </row>
@@ -4559,20 +4555,20 @@
       </c>
       <c r="B112" s="12"/>
       <c r="C112" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>74</v>
+        <v>82</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>359</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G112" s="4"/>
       <c r="H112" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I112" s="4"/>
     </row>
@@ -4580,24 +4576,22 @@
       <c r="A113" s="4">
         <v>112</v>
       </c>
-      <c r="B113" s="12" t="s">
-        <v>81</v>
-      </c>
+      <c r="B113" s="12"/>
       <c r="C113" s="7" t="s">
-        <v>205</v>
+        <v>94</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E113" s="4" t="s">
         <v>161</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>163</v>
+        <v>217</v>
       </c>
       <c r="G113" s="4"/>
       <c r="H113" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I113" s="4"/>
     </row>
@@ -4605,22 +4599,24 @@
       <c r="A114" s="4">
         <v>113</v>
       </c>
-      <c r="B114" s="12"/>
-      <c r="C114" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>366</v>
+      <c r="B114" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C114" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G114" s="4"/>
       <c r="H114" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I114" s="4"/>
     </row>
@@ -4629,21 +4625,19 @@
         <v>114</v>
       </c>
       <c r="B115" s="12"/>
-      <c r="C115" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D115" s="5" t="s">
-        <v>366</v>
+      <c r="C115" s="12"/>
+      <c r="D115" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>163</v>
+        <v>83</v>
       </c>
       <c r="G115" s="4"/>
       <c r="H115" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I115" s="4"/>
     </row>
@@ -4652,21 +4646,19 @@
         <v>115</v>
       </c>
       <c r="B116" s="12"/>
-      <c r="C116" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D116" s="5" t="s">
-        <v>367</v>
+      <c r="C116" s="12"/>
+      <c r="D116" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="G116" s="4"/>
       <c r="H116" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I116" s="4"/>
     </row>
@@ -4674,24 +4666,24 @@
       <c r="A117" s="4">
         <v>116</v>
       </c>
-      <c r="B117" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C117" s="12" t="s">
-        <v>87</v>
+      <c r="B117" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>387</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>165</v>
       </c>
       <c r="G117" s="4"/>
       <c r="H117" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I117" s="4"/>
     </row>
@@ -4699,20 +4691,22 @@
       <c r="A118" s="4">
         <v>117</v>
       </c>
-      <c r="B118" s="12"/>
-      <c r="C118" s="12"/>
+      <c r="B118" s="10"/>
+      <c r="C118" s="7" t="s">
+        <v>394</v>
+      </c>
       <c r="D118" s="4" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>83</v>
+        <v>167</v>
       </c>
       <c r="G118" s="4"/>
       <c r="H118" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I118" s="4"/>
     </row>
@@ -4720,20 +4714,22 @@
       <c r="A119" s="4">
         <v>118</v>
       </c>
-      <c r="B119" s="12"/>
-      <c r="C119" s="12"/>
+      <c r="B119" s="10"/>
+      <c r="C119" s="7" t="s">
+        <v>393</v>
+      </c>
       <c r="D119" s="4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="G119" s="4"/>
       <c r="H119" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I119" s="4"/>
     </row>
@@ -4741,24 +4737,22 @@
       <c r="A120" s="4">
         <v>119</v>
       </c>
-      <c r="B120" s="12" t="s">
-        <v>91</v>
-      </c>
+      <c r="B120" s="10"/>
       <c r="C120" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I120" s="4"/>
     </row>
@@ -4766,22 +4760,22 @@
       <c r="A121" s="4">
         <v>120</v>
       </c>
-      <c r="B121" s="12"/>
+      <c r="B121" s="11"/>
       <c r="C121" s="7" t="s">
-        <v>97</v>
+        <v>388</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="G121" s="4"/>
       <c r="H121" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I121" s="4"/>
     </row>
@@ -4789,22 +4783,24 @@
       <c r="A122" s="4">
         <v>121</v>
       </c>
-      <c r="B122" s="12"/>
-      <c r="C122" s="7" t="s">
-        <v>365</v>
+      <c r="B122" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C122" s="12" t="s">
+        <v>107</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G122" s="4"/>
       <c r="H122" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I122" s="4"/>
     </row>
@@ -4812,22 +4808,20 @@
       <c r="A123" s="4">
         <v>122</v>
       </c>
-      <c r="B123" s="12"/>
-      <c r="C123" s="7" t="s">
-        <v>364</v>
-      </c>
+      <c r="B123" s="10"/>
+      <c r="C123" s="12"/>
       <c r="D123" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G123" s="4"/>
       <c r="H123" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I123" s="4"/>
     </row>
@@ -4835,22 +4829,20 @@
       <c r="A124" s="4">
         <v>123</v>
       </c>
-      <c r="B124" s="12"/>
-      <c r="C124" s="7" t="s">
-        <v>395</v>
-      </c>
+      <c r="B124" s="10"/>
+      <c r="C124" s="12"/>
       <c r="D124" s="4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="G124" s="4"/>
       <c r="H124" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I124" s="4"/>
     </row>
@@ -4858,7 +4850,7 @@
       <c r="A125" s="4">
         <v>124</v>
       </c>
-      <c r="B125" s="12"/>
+      <c r="B125" s="10"/>
       <c r="C125" s="12" t="s">
         <v>108</v>
       </c>
@@ -4866,14 +4858,14 @@
         <v>18</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="G125" s="4"/>
       <c r="H125" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I125" s="4"/>
     </row>
@@ -4881,20 +4873,20 @@
       <c r="A126" s="4">
         <v>125</v>
       </c>
-      <c r="B126" s="12"/>
+      <c r="B126" s="10"/>
       <c r="C126" s="12"/>
       <c r="D126" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="G126" s="4"/>
       <c r="H126" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I126" s="4"/>
     </row>
@@ -4902,20 +4894,20 @@
       <c r="A127" s="4">
         <v>126</v>
       </c>
-      <c r="B127" s="12"/>
+      <c r="B127" s="10"/>
       <c r="C127" s="12"/>
       <c r="D127" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="G127" s="4"/>
       <c r="H127" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="I127" s="4"/>
     </row>
@@ -4923,88 +4915,82 @@
       <c r="A128" s="4">
         <v>127</v>
       </c>
-      <c r="B128" s="12"/>
+      <c r="B128" s="10"/>
       <c r="C128" s="12" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D128" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G128" s="4"/>
-      <c r="H128" s="4" t="s">
-        <v>129</v>
-      </c>
+      <c r="H128" s="4"/>
       <c r="I128" s="4"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
         <v>128</v>
       </c>
-      <c r="B129" s="12"/>
+      <c r="B129" s="10"/>
       <c r="C129" s="12"/>
       <c r="D129" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G129" s="4"/>
-      <c r="H129" s="4" t="s">
-        <v>126</v>
-      </c>
+      <c r="H129" s="4"/>
       <c r="I129" s="4"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
         <v>129</v>
       </c>
-      <c r="B130" s="12"/>
+      <c r="B130" s="10"/>
       <c r="C130" s="12"/>
       <c r="D130" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G130" s="4"/>
-      <c r="H130" s="4" t="s">
-        <v>125</v>
-      </c>
+      <c r="H130" s="4"/>
       <c r="I130" s="4"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="4">
         <v>130</v>
       </c>
-      <c r="B131" s="9" t="s">
+      <c r="B131" s="10"/>
+      <c r="C131" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C131" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="D131" s="4" t="s">
-        <v>18</v>
+      <c r="D131" s="5" t="s">
+        <v>357</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G131" s="4"/>
-      <c r="H131" s="4"/>
+      <c r="H131" s="4" t="s">
+        <v>124</v>
+      </c>
       <c r="I131" s="4"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
@@ -5012,18 +4998,22 @@
         <v>131</v>
       </c>
       <c r="B132" s="10"/>
-      <c r="C132" s="12"/>
+      <c r="C132" s="12" t="s">
+        <v>356</v>
+      </c>
       <c r="D132" s="4" t="s">
-        <v>100</v>
+        <v>353</v>
       </c>
       <c r="E132" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G132" s="4"/>
-      <c r="H132" s="4"/>
+      <c r="H132" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="I132" s="4"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
@@ -5033,38 +5023,38 @@
       <c r="B133" s="10"/>
       <c r="C133" s="12"/>
       <c r="D133" s="4" t="s">
-        <v>101</v>
+        <v>354</v>
       </c>
       <c r="E133" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G133" s="4"/>
-      <c r="H133" s="4"/>
+      <c r="H133" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="I133" s="4"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
         <v>133</v>
       </c>
-      <c r="B134" s="10"/>
-      <c r="C134" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D134" s="5" t="s">
-        <v>362</v>
+      <c r="B134" s="11"/>
+      <c r="C134" s="12"/>
+      <c r="D134" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="F134" s="4" t="s">
         <v>179</v>
       </c>
       <c r="G134" s="4"/>
       <c r="H134" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I134" s="4"/>
     </row>
@@ -5072,12 +5062,14 @@
       <c r="A135" s="4">
         <v>134</v>
       </c>
-      <c r="B135" s="10"/>
-      <c r="C135" s="12" t="s">
-        <v>361</v>
+      <c r="B135" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>358</v>
+        <v>105</v>
       </c>
       <c r="E135" s="4" t="s">
         <v>207</v>
@@ -5087,7 +5079,7 @@
       </c>
       <c r="G135" s="4"/>
       <c r="H135" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I135" s="4"/>
     </row>
@@ -5095,10 +5087,12 @@
       <c r="A136" s="4">
         <v>135</v>
       </c>
-      <c r="B136" s="10"/>
-      <c r="C136" s="12"/>
+      <c r="B136" s="12"/>
+      <c r="C136" s="7" t="s">
+        <v>106</v>
+      </c>
       <c r="D136" s="4" t="s">
-        <v>359</v>
+        <v>109</v>
       </c>
       <c r="E136" s="4" t="s">
         <v>207</v>
@@ -5108,7 +5102,7 @@
       </c>
       <c r="G136" s="4"/>
       <c r="H136" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I136" s="4"/>
     </row>
@@ -5116,16 +5110,20 @@
       <c r="A137" s="4">
         <v>136</v>
       </c>
-      <c r="B137" s="11"/>
-      <c r="C137" s="12"/>
+      <c r="B137" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>110</v>
+      </c>
       <c r="D137" s="4" t="s">
-        <v>360</v>
+        <v>112</v>
       </c>
       <c r="E137" s="4" t="s">
         <v>207</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G137" s="4"/>
       <c r="H137" s="4" t="s">
@@ -5138,23 +5136,23 @@
         <v>137</v>
       </c>
       <c r="B138" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="C138" s="7" t="s">
-        <v>105</v>
+        <v>113</v>
+      </c>
+      <c r="C138" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G138" s="4"/>
       <c r="H138" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I138" s="4"/>
     </row>
@@ -5163,21 +5161,19 @@
         <v>138</v>
       </c>
       <c r="B139" s="12"/>
-      <c r="C139" s="7" t="s">
-        <v>107</v>
-      </c>
+      <c r="C139" s="12"/>
       <c r="D139" s="4" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G139" s="4"/>
       <c r="H139" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I139" s="4"/>
     </row>
@@ -5185,24 +5181,20 @@
       <c r="A140" s="4">
         <v>139</v>
       </c>
-      <c r="B140" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="C140" s="7" t="s">
-        <v>111</v>
-      </c>
+      <c r="B140" s="12"/>
+      <c r="C140" s="12"/>
       <c r="D140" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G140" s="4"/>
       <c r="H140" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I140" s="4"/>
     </row>
@@ -5210,24 +5202,22 @@
       <c r="A141" s="4">
         <v>140</v>
       </c>
-      <c r="B141" s="12" t="s">
-        <v>114</v>
-      </c>
+      <c r="B141" s="12"/>
       <c r="C141" s="12" t="s">
-        <v>115</v>
+        <v>26</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G141" s="4"/>
       <c r="H141" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I141" s="4"/>
     </row>
@@ -5238,162 +5228,96 @@
       <c r="B142" s="12"/>
       <c r="C142" s="12"/>
       <c r="D142" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E142" s="4" t="s">
         <v>208</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G142" s="4"/>
       <c r="H142" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I142" s="4"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
         <v>142</v>
       </c>
-      <c r="B143" s="12"/>
-      <c r="C143" s="12"/>
+      <c r="B143" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>188</v>
+      </c>
       <c r="D143" s="4" t="s">
-        <v>118</v>
+        <v>189</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="G143" s="4"/>
       <c r="H143" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I143" s="4"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A144" s="4">
-        <v>143</v>
-      </c>
-      <c r="B144" s="12"/>
-      <c r="C144" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D144" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E144" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="F144" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="G144" s="4"/>
-      <c r="H144" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="I144" s="4"/>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A145" s="4">
-        <v>144</v>
-      </c>
-      <c r="B145" s="12"/>
-      <c r="C145" s="12"/>
-      <c r="D145" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="E145" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F145" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="G145" s="4"/>
-      <c r="H145" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="I145" s="4"/>
-    </row>
-    <row r="146" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A146" s="4">
-        <v>145</v>
-      </c>
-      <c r="B146" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C146" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="D146" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="E146" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="F146" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="G146" s="4"/>
-      <c r="H146" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="I146" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="C31:C35"/>
-    <mergeCell ref="B131:B137"/>
-    <mergeCell ref="C144:C145"/>
-    <mergeCell ref="B141:B145"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C141:C143"/>
+  <mergeCells count="49">
+    <mergeCell ref="C28:C32"/>
+    <mergeCell ref="B33:B57"/>
+    <mergeCell ref="B117:B121"/>
+    <mergeCell ref="B122:B134"/>
+    <mergeCell ref="C141:C142"/>
+    <mergeCell ref="B138:B142"/>
+    <mergeCell ref="B64:B67"/>
+    <mergeCell ref="B135:B136"/>
+    <mergeCell ref="C138:C140"/>
+    <mergeCell ref="C122:C124"/>
     <mergeCell ref="C125:C127"/>
-    <mergeCell ref="C128:C130"/>
-    <mergeCell ref="C117:C119"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="C102:C104"/>
-    <mergeCell ref="C105:C106"/>
-    <mergeCell ref="B88:B95"/>
-    <mergeCell ref="C97:C99"/>
-    <mergeCell ref="C84:C86"/>
-    <mergeCell ref="B71:B76"/>
-    <mergeCell ref="C74:C76"/>
-    <mergeCell ref="B120:B130"/>
-    <mergeCell ref="B77:B81"/>
-    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="C114:C116"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="C99:C101"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="B85:B92"/>
+    <mergeCell ref="C94:C96"/>
+    <mergeCell ref="C81:C83"/>
+    <mergeCell ref="B68:B73"/>
+    <mergeCell ref="C71:C73"/>
+    <mergeCell ref="B74:B78"/>
+    <mergeCell ref="B81:B83"/>
     <mergeCell ref="B2:B11"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="B16:B27"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="B16:B24"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="C5:C7"/>
     <mergeCell ref="C8:C10"/>
     <mergeCell ref="B12:B15"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="B28:B35"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="C135:C137"/>
-    <mergeCell ref="B113:B116"/>
-    <mergeCell ref="B96:B112"/>
-    <mergeCell ref="C44:C47"/>
-    <mergeCell ref="C48:C50"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="C51:C56"/>
-    <mergeCell ref="B36:B59"/>
-    <mergeCell ref="B61:B66"/>
-    <mergeCell ref="C131:C133"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="C107:C108"/>
-    <mergeCell ref="C109:C111"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="B25:B32"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="C132:C134"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="B93:B109"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="C48:C53"/>
+    <mergeCell ref="B58:B63"/>
+    <mergeCell ref="C128:C130"/>
+    <mergeCell ref="C97:C98"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="C106:C108"/>
+    <mergeCell ref="C85:C87"/>
     <mergeCell ref="C88:C90"/>
-    <mergeCell ref="C91:C93"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
